--- a/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
+++ b/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Platform1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Map1\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D183273-FAD9-41CF-A8D4-30319DC75EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC1D7D2C-2AAA-463B-AB38-CC7D84325B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="C1">
-        <v>-200</v>
+        <v>-190</v>
       </c>
       <c r="D1">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="I1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J1">
         <f>G1*20</f>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L1">
         <f t="shared" si="0"/>
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="M1">
         <v>-1</v>
@@ -4622,10 +4622,10 @@
         <v>0</v>
       </c>
       <c r="B66">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -4637,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="J66">
         <f t="shared" si="31"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="K66">
         <f t="shared" si="30"/>
@@ -4675,13 +4675,13 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="B67">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J67">
         <f t="shared" si="31"/>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="L67">
         <f t="shared" si="32"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="M67">
         <v>-1</v>
@@ -4731,13 +4731,13 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="B68">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -4755,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J68">
         <f t="shared" si="31"/>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="L68">
         <f t="shared" si="32"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="M68">
         <v>-1</v>
@@ -4790,10 +4790,10 @@
         <v>0</v>
       </c>
       <c r="B69">
-        <v>-1000</v>
+        <v>40</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4818,8 +4818,7 @@
         <v>20</v>
       </c>
       <c r="K69">
-        <f t="shared" si="30"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L69">
         <f t="shared" si="32"/>

--- a/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
+++ b/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Map1\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC1D7D2C-2AAA-463B-AB38-CC7D84325B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5F26D2C-F072-4513-9D5D-33FB67E92397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
@@ -977,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q92"/>
+  <dimension ref="A1:Q120"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="17" width="5.625" customWidth="1"/>
@@ -4375,7 +4375,7 @@
         <v>20</v>
       </c>
       <c r="K61">
-        <f t="shared" ref="K61:K88" si="30">H61*20</f>
+        <f t="shared" ref="K61:K90" si="30">H61*20</f>
         <v>100</v>
       </c>
       <c r="L61">
@@ -4534,7 +4534,7 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <f t="shared" ref="J64:J88" si="31">G64*20</f>
+        <f t="shared" ref="J64:J90" si="31">G64*20</f>
         <v>1040</v>
       </c>
       <c r="K64">
@@ -4542,7 +4542,7 @@
         <v>100</v>
       </c>
       <c r="L64">
-        <f t="shared" ref="L64:L88" si="32">I64*20</f>
+        <f t="shared" ref="L64:L90" si="32">I64*20</f>
         <v>20</v>
       </c>
       <c r="M64">
@@ -4637,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -4646,8 +4646,7 @@
         <v>1</v>
       </c>
       <c r="J66">
-        <f t="shared" si="31"/>
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="K66">
         <f t="shared" si="30"/>
@@ -4675,13 +4674,13 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B67">
         <v>20</v>
       </c>
       <c r="C67">
-        <v>-200</v>
+        <v>20</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -4699,11 +4698,10 @@
         <v>1</v>
       </c>
       <c r="I67">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J67">
-        <f t="shared" si="31"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K67">
         <f t="shared" si="30"/>
@@ -4711,7 +4709,7 @@
       </c>
       <c r="L67">
         <f t="shared" si="32"/>
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="M67">
         <v>-1</v>
@@ -4731,13 +4729,13 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>-90</v>
+        <v>-60</v>
       </c>
       <c r="B68">
         <v>20</v>
       </c>
       <c r="C68">
-        <v>-200</v>
+        <v>20</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -4755,11 +4753,10 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J68">
-        <f t="shared" si="31"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K68">
         <f t="shared" si="30"/>
@@ -4767,7 +4764,7 @@
       </c>
       <c r="L68">
         <f t="shared" si="32"/>
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="M68">
         <v>-1</v>
@@ -4787,13 +4784,13 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="B69">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C69">
-        <v>-60</v>
+        <v>-390</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4805,24 +4802,24 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69">
         <f t="shared" si="31"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K69">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L69">
         <f t="shared" si="32"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M69">
         <v>-1</v>
@@ -4842,13 +4839,13 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="B70">
-        <v>-1000</v>
+        <v>80</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>-390</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -4860,25 +4857,24 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70">
         <f t="shared" si="31"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K70">
-        <f t="shared" si="30"/>
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="L70">
         <f t="shared" si="32"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M70">
         <v>-1</v>
@@ -4898,13 +4894,13 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="B71">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -4925,15 +4921,15 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="J71:J80" si="33">G71*20</f>
         <v>20</v>
       </c>
       <c r="K71">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="K71:K80" si="34">H71*20</f>
         <v>20</v>
       </c>
       <c r="L71">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="L71:L80" si="35">I71*20</f>
         <v>20</v>
       </c>
       <c r="M71">
@@ -4954,13 +4950,13 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="B72">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -4981,15 +4977,15 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="K72">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>20</v>
       </c>
       <c r="L72">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="M72">
@@ -5010,13 +5006,13 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="B73">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -5037,15 +5033,15 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="K73">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>20</v>
       </c>
       <c r="L73">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="M73">
@@ -5066,13 +5062,13 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="B74">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>-240</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -5093,15 +5089,15 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="K74">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>20</v>
       </c>
       <c r="L74">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="M74">
@@ -5122,13 +5118,13 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A75">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="B75">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -5149,15 +5145,15 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="K75">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>20</v>
       </c>
       <c r="L75">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="M75">
@@ -5178,13 +5174,13 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A76">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="B76">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>-360</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -5205,15 +5201,15 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="K76">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>20</v>
       </c>
       <c r="L76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="M76">
@@ -5234,13 +5230,13 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A77">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B77">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -5261,15 +5257,15 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="K77">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>20</v>
       </c>
       <c r="L77">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="M77">
@@ -5290,13 +5286,13 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A78">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="B78">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>-160</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -5317,15 +5313,15 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="K78">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>20</v>
       </c>
       <c r="L78">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="M78">
@@ -5346,13 +5342,13 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A79">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B79">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>-240</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -5373,15 +5369,15 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="K79">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>20</v>
       </c>
       <c r="L79">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="M79">
@@ -5402,13 +5398,13 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A80">
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="B80">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>-340</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -5429,15 +5425,15 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="K80">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>20</v>
       </c>
       <c r="L80">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="M80">
@@ -5458,13 +5454,13 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A81">
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="B81">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>-460</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -5514,13 +5510,13 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A82">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="B82">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>-520</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -5570,13 +5566,13 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A83">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="B83">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -5626,13 +5622,13 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A84">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="B84">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>-660</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -5682,13 +5678,13 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A85">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="B85">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>-740</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -5738,13 +5734,13 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A86">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B86">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -5794,13 +5790,13 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A87">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="B87">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>-440</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -5850,13 +5846,13 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A88">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="B88">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>-560</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -5906,13 +5902,13 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A89">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="B89">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>-680</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -5933,15 +5929,15 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <f t="shared" ref="J89:J90" si="33">G89*20</f>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K89">
-        <f t="shared" ref="K89:K90" si="34">H89*20</f>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L89">
-        <f t="shared" ref="L89:L90" si="35">I89*20</f>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M89">
@@ -5962,13 +5958,13 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A90">
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="B90">
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>-780</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -5989,15 +5985,15 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>20</v>
       </c>
       <c r="K90">
-        <f t="shared" si="34"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L90">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="M90">
@@ -6018,13 +6014,13 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A91">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="B91">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>-560</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -6045,15 +6041,15 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <f t="shared" ref="J91" si="36">G91*20</f>
+        <f t="shared" ref="J91:J92" si="36">G91*20</f>
         <v>20</v>
       </c>
       <c r="K91">
-        <f t="shared" ref="K91" si="37">H91*20</f>
+        <f t="shared" ref="K91:K92" si="37">H91*20</f>
         <v>20</v>
       </c>
       <c r="L91">
-        <f t="shared" ref="L91" si="38">I91*20</f>
+        <f t="shared" ref="L91:L92" si="38">I91*20</f>
         <v>20</v>
       </c>
       <c r="M91">
@@ -6074,57 +6070,1621 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A92">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92">
+        <v>-720</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <f t="shared" si="36"/>
+        <v>20</v>
+      </c>
+      <c r="K92">
+        <f t="shared" si="37"/>
+        <v>20</v>
+      </c>
+      <c r="L92">
+        <f t="shared" si="38"/>
+        <v>20</v>
+      </c>
+      <c r="M92">
+        <v>-1</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A93">
+        <v>10</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
+        <v>-620</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <f t="shared" ref="J93" si="39">G93*20</f>
+        <v>20</v>
+      </c>
+      <c r="K93">
+        <f t="shared" ref="K93" si="40">H93*20</f>
+        <v>20</v>
+      </c>
+      <c r="L93">
+        <f t="shared" ref="L93" si="41">I93*20</f>
+        <v>20</v>
+      </c>
+      <c r="M93">
+        <v>-1</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A94">
+        <v>90</v>
+      </c>
+      <c r="B94">
+        <v>40</v>
+      </c>
+      <c r="C94">
+        <v>-600</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94">
+        <v>19</v>
+      </c>
+      <c r="J94">
+        <f>G94*20</f>
+        <v>20</v>
+      </c>
+      <c r="K94">
+        <f>H94*20</f>
+        <v>20</v>
+      </c>
+      <c r="L94">
+        <f>I94*20</f>
+        <v>380</v>
+      </c>
+      <c r="M94">
+        <v>-1</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A95">
+        <v>-90</v>
+      </c>
+      <c r="B95">
+        <v>40</v>
+      </c>
+      <c r="C95">
+        <v>-600</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95">
+        <v>19</v>
+      </c>
+      <c r="J95">
+        <f>G95*20</f>
+        <v>20</v>
+      </c>
+      <c r="K95">
+        <f>H95*20</f>
+        <v>20</v>
+      </c>
+      <c r="L95">
+        <f>I95*20</f>
+        <v>380</v>
+      </c>
+      <c r="M95">
+        <v>-1</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A96">
+        <v>80</v>
+      </c>
+      <c r="B96">
+        <v>100</v>
+      </c>
+      <c r="C96">
+        <v>-800</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>2</v>
+      </c>
+      <c r="H96">
+        <v>2</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+      <c r="J96">
+        <f>G96*20</f>
+        <v>40</v>
+      </c>
+      <c r="K96">
+        <v>80</v>
+      </c>
+      <c r="L96">
+        <f>I96*20</f>
+        <v>40</v>
+      </c>
+      <c r="M96">
+        <v>-1</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A97">
+        <v>-80</v>
+      </c>
+      <c r="B97">
+        <v>100</v>
+      </c>
+      <c r="C97">
+        <v>-800</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>2</v>
+      </c>
+      <c r="H97">
+        <v>2</v>
+      </c>
+      <c r="I97">
+        <v>2</v>
+      </c>
+      <c r="J97">
+        <f>G97*20</f>
+        <v>40</v>
+      </c>
+      <c r="K97">
+        <v>80</v>
+      </c>
+      <c r="L97">
+        <f>I97*20</f>
+        <v>40</v>
+      </c>
+      <c r="M97">
+        <v>-1</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A98">
+        <v>-70</v>
+      </c>
+      <c r="B98">
+        <v>40</v>
+      </c>
+      <c r="C98">
+        <v>-840</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <f t="shared" ref="J98" si="42">G98*20</f>
+        <v>20</v>
+      </c>
+      <c r="K98">
+        <f t="shared" ref="K98" si="43">H98*20</f>
+        <v>20</v>
+      </c>
+      <c r="L98">
+        <f t="shared" ref="L98" si="44">I98*20</f>
+        <v>20</v>
+      </c>
+      <c r="M98">
+        <v>-1</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A99">
+        <v>30</v>
+      </c>
+      <c r="B99">
+        <v>40</v>
+      </c>
+      <c r="C99">
+        <v>-880</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <f t="shared" ref="J99:J107" si="45">G99*20</f>
+        <v>20</v>
+      </c>
+      <c r="K99">
+        <f t="shared" ref="K99:K107" si="46">H99*20</f>
+        <v>20</v>
+      </c>
+      <c r="L99">
+        <f t="shared" ref="L99:L107" si="47">I99*20</f>
+        <v>20</v>
+      </c>
+      <c r="M99">
+        <v>-1</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A100">
+        <v>-10</v>
+      </c>
+      <c r="B100">
+        <v>40</v>
+      </c>
+      <c r="C100">
+        <v>-920</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <f t="shared" si="45"/>
+        <v>20</v>
+      </c>
+      <c r="K100">
+        <f t="shared" si="46"/>
+        <v>20</v>
+      </c>
+      <c r="L100">
+        <f t="shared" si="47"/>
+        <v>20</v>
+      </c>
+      <c r="M100">
+        <v>-1</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A101">
+        <v>70</v>
+      </c>
+      <c r="B101">
+        <v>40</v>
+      </c>
+      <c r="C101">
+        <v>-960</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <f t="shared" si="45"/>
+        <v>20</v>
+      </c>
+      <c r="K101">
+        <f t="shared" si="46"/>
+        <v>20</v>
+      </c>
+      <c r="L101">
+        <f t="shared" si="47"/>
+        <v>20</v>
+      </c>
+      <c r="M101">
+        <v>-1</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A102">
+        <v>-30</v>
+      </c>
+      <c r="B102">
+        <v>40</v>
+      </c>
+      <c r="C102">
+        <v>-1020</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <f t="shared" si="45"/>
+        <v>20</v>
+      </c>
+      <c r="K102">
+        <f t="shared" si="46"/>
+        <v>20</v>
+      </c>
+      <c r="L102">
+        <f t="shared" si="47"/>
+        <v>20</v>
+      </c>
+      <c r="M102">
+        <v>-1</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A103">
+        <v>50</v>
+      </c>
+      <c r="B103">
+        <v>60</v>
+      </c>
+      <c r="C103">
+        <v>-1060</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="J103">
+        <f t="shared" si="45"/>
+        <v>20</v>
+      </c>
+      <c r="K103">
+        <f t="shared" si="46"/>
+        <v>20</v>
+      </c>
+      <c r="L103">
+        <f t="shared" si="47"/>
+        <v>20</v>
+      </c>
+      <c r="M103">
+        <v>-1</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A104">
+        <v>-50</v>
+      </c>
+      <c r="B104">
+        <v>60</v>
+      </c>
+      <c r="C104">
+        <v>-1100</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104">
+        <f t="shared" si="45"/>
+        <v>20</v>
+      </c>
+      <c r="K104">
+        <f t="shared" si="46"/>
+        <v>20</v>
+      </c>
+      <c r="L104">
+        <f t="shared" si="47"/>
+        <v>20</v>
+      </c>
+      <c r="M104">
+        <v>-1</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A105">
+        <v>10</v>
+      </c>
+      <c r="B105">
+        <v>60</v>
+      </c>
+      <c r="C105">
+        <v>-1160</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105">
+        <f t="shared" si="45"/>
+        <v>20</v>
+      </c>
+      <c r="K105">
+        <f t="shared" si="46"/>
+        <v>20</v>
+      </c>
+      <c r="L105">
+        <f t="shared" si="47"/>
+        <v>20</v>
+      </c>
+      <c r="M105">
+        <v>-1</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A106">
+        <v>-70</v>
+      </c>
+      <c r="B106">
+        <v>60</v>
+      </c>
+      <c r="C106">
+        <v>-1200</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="J106">
+        <f t="shared" si="45"/>
+        <v>20</v>
+      </c>
+      <c r="K106">
+        <f t="shared" si="46"/>
+        <v>20</v>
+      </c>
+      <c r="L106">
+        <f t="shared" si="47"/>
+        <v>20</v>
+      </c>
+      <c r="M106">
+        <v>-1</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A107">
+        <v>10</v>
+      </c>
+      <c r="B107">
+        <v>40</v>
+      </c>
+      <c r="C107">
+        <v>-860</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107">
+        <f t="shared" si="45"/>
+        <v>20</v>
+      </c>
+      <c r="K107">
+        <f t="shared" si="46"/>
+        <v>20</v>
+      </c>
+      <c r="L107">
+        <f t="shared" si="47"/>
+        <v>20</v>
+      </c>
+      <c r="M107">
+        <v>-1</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A108">
+        <v>-50</v>
+      </c>
+      <c r="B108">
+        <v>40</v>
+      </c>
+      <c r="C108">
+        <v>-900</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <f t="shared" ref="J108:J116" si="48">G108*20</f>
+        <v>20</v>
+      </c>
+      <c r="K108">
+        <f t="shared" ref="K108:K116" si="49">H108*20</f>
+        <v>20</v>
+      </c>
+      <c r="L108">
+        <f t="shared" ref="L108:L116" si="50">I108*20</f>
+        <v>20</v>
+      </c>
+      <c r="M108">
+        <v>-1</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A109">
+        <v>50</v>
+      </c>
+      <c r="B109">
+        <v>40</v>
+      </c>
+      <c r="C109">
+        <v>-940</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>1</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="J109">
+        <f t="shared" si="48"/>
+        <v>20</v>
+      </c>
+      <c r="K109">
+        <f t="shared" si="49"/>
+        <v>20</v>
+      </c>
+      <c r="L109">
+        <f t="shared" si="50"/>
+        <v>20</v>
+      </c>
+      <c r="M109">
+        <v>-1</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A110">
+        <v>-10</v>
+      </c>
+      <c r="B110">
+        <v>40</v>
+      </c>
+      <c r="C110">
         <v>-1000</v>
       </c>
-      <c r="C92">
-        <v>0</v>
-      </c>
-      <c r="D92">
-        <v>0</v>
-      </c>
-      <c r="E92">
-        <v>0</v>
-      </c>
-      <c r="F92">
-        <v>0</v>
-      </c>
-      <c r="G92">
-        <v>1</v>
-      </c>
-      <c r="H92">
-        <v>1</v>
-      </c>
-      <c r="I92">
-        <v>1</v>
-      </c>
-      <c r="J92">
-        <f t="shared" ref="J92" si="39">G92*20</f>
-        <v>20</v>
-      </c>
-      <c r="K92">
-        <f t="shared" ref="K92" si="40">H92*20</f>
-        <v>20</v>
-      </c>
-      <c r="L92">
-        <f t="shared" ref="L92" si="41">I92*20</f>
-        <v>20</v>
-      </c>
-      <c r="M92">
-        <v>-1</v>
-      </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
-      <c r="O92">
-        <v>0</v>
-      </c>
-      <c r="P92">
-        <v>0</v>
-      </c>
-      <c r="Q92">
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <f t="shared" si="48"/>
+        <v>20</v>
+      </c>
+      <c r="K110">
+        <f t="shared" si="49"/>
+        <v>20</v>
+      </c>
+      <c r="L110">
+        <f t="shared" si="50"/>
+        <v>20</v>
+      </c>
+      <c r="M110">
+        <v>-1</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A111">
+        <v>-30</v>
+      </c>
+      <c r="B111">
+        <v>60</v>
+      </c>
+      <c r="C111">
+        <v>-1080</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111">
+        <f t="shared" si="48"/>
+        <v>20</v>
+      </c>
+      <c r="K111">
+        <f t="shared" si="49"/>
+        <v>20</v>
+      </c>
+      <c r="L111">
+        <f t="shared" si="50"/>
+        <v>20</v>
+      </c>
+      <c r="M111">
+        <v>-1</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A112">
+        <v>70</v>
+      </c>
+      <c r="B112">
+        <v>60</v>
+      </c>
+      <c r="C112">
+        <v>-1120</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112">
+        <f t="shared" si="48"/>
+        <v>20</v>
+      </c>
+      <c r="K112">
+        <f t="shared" si="49"/>
+        <v>20</v>
+      </c>
+      <c r="L112">
+        <f t="shared" si="50"/>
+        <v>20</v>
+      </c>
+      <c r="M112">
+        <v>-1</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A113">
+        <v>-10</v>
+      </c>
+      <c r="B113">
+        <v>60</v>
+      </c>
+      <c r="C113">
+        <v>-1180</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>1</v>
+      </c>
+      <c r="H113">
+        <v>1</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113">
+        <f t="shared" si="48"/>
+        <v>20</v>
+      </c>
+      <c r="K113">
+        <f t="shared" si="49"/>
+        <v>20</v>
+      </c>
+      <c r="L113">
+        <f t="shared" si="50"/>
+        <v>20</v>
+      </c>
+      <c r="M113">
+        <v>-1</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A114">
+        <v>30</v>
+      </c>
+      <c r="B114">
+        <v>60</v>
+      </c>
+      <c r="C114">
+        <v>-1240</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <f t="shared" si="48"/>
+        <v>20</v>
+      </c>
+      <c r="K114">
+        <f t="shared" si="49"/>
+        <v>20</v>
+      </c>
+      <c r="L114">
+        <f t="shared" si="50"/>
+        <v>20</v>
+      </c>
+      <c r="M114">
+        <v>-1</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A115">
+        <v>90</v>
+      </c>
+      <c r="B115">
+        <v>60</v>
+      </c>
+      <c r="C115">
+        <v>-920</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>1</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115">
+        <v>9</v>
+      </c>
+      <c r="J115">
+        <f t="shared" si="48"/>
+        <v>20</v>
+      </c>
+      <c r="K115">
+        <f t="shared" si="49"/>
+        <v>20</v>
+      </c>
+      <c r="L115">
+        <f t="shared" si="50"/>
+        <v>180</v>
+      </c>
+      <c r="M115">
+        <v>-1</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A116">
+        <v>-90</v>
+      </c>
+      <c r="B116">
+        <v>60</v>
+      </c>
+      <c r="C116">
+        <v>-920</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+      <c r="I116">
+        <v>9</v>
+      </c>
+      <c r="J116">
+        <f t="shared" ref="J116" si="51">G116*20</f>
+        <v>20</v>
+      </c>
+      <c r="K116">
+        <f t="shared" ref="K116" si="52">H116*20</f>
+        <v>20</v>
+      </c>
+      <c r="L116">
+        <f t="shared" ref="L116" si="53">I116*20</f>
+        <v>180</v>
+      </c>
+      <c r="M116">
+        <v>-1</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A117">
+        <v>90</v>
+      </c>
+      <c r="B117">
+        <v>80</v>
+      </c>
+      <c r="C117">
+        <v>-1150</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>1</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117">
+        <v>10</v>
+      </c>
+      <c r="J117">
+        <f>G117*20</f>
+        <v>20</v>
+      </c>
+      <c r="K117">
+        <f>H117*20</f>
+        <v>20</v>
+      </c>
+      <c r="L117">
+        <f>I117*20</f>
+        <v>200</v>
+      </c>
+      <c r="M117">
+        <v>-1</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A118">
+        <v>-90</v>
+      </c>
+      <c r="B118">
+        <v>80</v>
+      </c>
+      <c r="C118">
+        <v>-1150</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>1</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118">
+        <v>10</v>
+      </c>
+      <c r="J118">
+        <f>G118*20</f>
+        <v>20</v>
+      </c>
+      <c r="K118">
+        <f>H118*20</f>
+        <v>20</v>
+      </c>
+      <c r="L118">
+        <f>I118*20</f>
+        <v>200</v>
+      </c>
+      <c r="M118">
+        <v>-1</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A119">
+        <v>-80</v>
+      </c>
+      <c r="B119">
+        <v>120</v>
+      </c>
+      <c r="C119">
+        <v>-1020</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>2</v>
+      </c>
+      <c r="H119">
+        <v>2</v>
+      </c>
+      <c r="I119">
+        <v>2</v>
+      </c>
+      <c r="J119">
+        <f t="shared" ref="J119:J120" si="54">G119*20</f>
+        <v>40</v>
+      </c>
+      <c r="K119">
+        <v>80</v>
+      </c>
+      <c r="L119">
+        <f t="shared" ref="L119:L120" si="55">I119*20</f>
+        <v>40</v>
+      </c>
+      <c r="M119">
+        <v>-1</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A120">
+        <v>80</v>
+      </c>
+      <c r="B120">
+        <v>120</v>
+      </c>
+      <c r="C120">
+        <v>-1020</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>2</v>
+      </c>
+      <c r="H120">
+        <v>2</v>
+      </c>
+      <c r="I120">
+        <v>2</v>
+      </c>
+      <c r="J120">
+        <f t="shared" si="54"/>
+        <v>40</v>
+      </c>
+      <c r="K120">
+        <v>80</v>
+      </c>
+      <c r="L120">
+        <f t="shared" si="55"/>
+        <v>40</v>
+      </c>
+      <c r="M120">
+        <v>-1</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
+++ b/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Map1\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{384B2EB8-F3B6-4023-BC50-CDF895769B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B126777-D81B-42AA-BC01-80D0BBCC9FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -977,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q260"/>
+  <dimension ref="A1:Q261"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="17" width="5.625" customWidth="1"/>
@@ -14794,7 +14794,7 @@
         <v>120</v>
       </c>
       <c r="C249">
-        <v>-2160</v>
+        <v>-2180</v>
       </c>
       <c r="D249">
         <v>0</v>
@@ -14842,7 +14842,7 @@
     </row>
     <row r="250" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A250">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B250">
         <v>120</v>
@@ -14896,13 +14896,13 @@
     </row>
     <row r="251" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A251">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B251">
         <v>180</v>
       </c>
       <c r="C251">
-        <v>-2120</v>
+        <v>-2130</v>
       </c>
       <c r="D251">
         <v>0</v>
@@ -14914,23 +14914,24 @@
         <v>0</v>
       </c>
       <c r="G251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H251">
         <v>2</v>
       </c>
       <c r="I251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J251">
-        <f t="shared" ref="J251" si="120">G251*20</f>
-        <v>20</v>
+        <f t="shared" ref="J251:L251" si="120">G251*20</f>
+        <v>40</v>
       </c>
       <c r="K251">
         <v>80</v>
       </c>
       <c r="L251">
-        <v>20</v>
+        <f t="shared" si="120"/>
+        <v>40</v>
       </c>
       <c r="M251">
         <v>-1</v>
@@ -14956,7 +14957,7 @@
         <v>120</v>
       </c>
       <c r="C252">
-        <v>-2160</v>
+        <v>-2180</v>
       </c>
       <c r="D252">
         <v>0</v>
@@ -15004,7 +15005,7 @@
     </row>
     <row r="253" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A253">
-        <v>-200</v>
+        <v>-180</v>
       </c>
       <c r="B253">
         <v>120</v>
@@ -15058,13 +15059,13 @@
     </row>
     <row r="254" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A254">
-        <v>-240</v>
+        <v>-230</v>
       </c>
       <c r="B254">
         <v>180</v>
       </c>
       <c r="C254">
-        <v>-2120</v>
+        <v>-2130</v>
       </c>
       <c r="D254">
         <v>0</v>
@@ -15076,23 +15077,24 @@
         <v>0</v>
       </c>
       <c r="G254">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H254">
         <v>2</v>
       </c>
       <c r="I254">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J254">
         <f t="shared" ref="J254" si="122">G254*20</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K254">
         <v>80</v>
       </c>
       <c r="L254">
-        <v>20</v>
+        <f t="shared" ref="L254" si="123">I254*20</f>
+        <v>40</v>
       </c>
       <c r="M254">
         <v>-1</v>
@@ -15118,7 +15120,7 @@
         <v>120</v>
       </c>
       <c r="C255">
-        <v>-2560</v>
+        <v>-2540</v>
       </c>
       <c r="D255">
         <v>0</v>
@@ -15142,7 +15144,7 @@
         <v>20</v>
       </c>
       <c r="K255">
-        <f t="shared" ref="K255:K256" si="123">H255*20</f>
+        <f t="shared" ref="K255:K256" si="124">H255*20</f>
         <v>20</v>
       </c>
       <c r="L255">
@@ -15166,7 +15168,7 @@
     </row>
     <row r="256" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A256">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B256">
         <v>120</v>
@@ -15178,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="E256">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="F256">
         <v>0</v>
@@ -15196,7 +15198,7 @@
         <v>60</v>
       </c>
       <c r="K256">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>20</v>
       </c>
       <c r="L256">
@@ -15220,41 +15222,42 @@
     </row>
     <row r="257" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A257">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B257">
         <v>180</v>
       </c>
       <c r="C257">
-        <v>-2600</v>
+        <v>-2590</v>
       </c>
       <c r="D257">
         <v>0</v>
       </c>
       <c r="E257">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="F257">
         <v>0</v>
       </c>
       <c r="G257">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H257">
         <v>2</v>
       </c>
       <c r="I257">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J257">
-        <f t="shared" ref="J257" si="124">G257*20</f>
-        <v>20</v>
+        <f t="shared" ref="J257" si="125">G257*20</f>
+        <v>40</v>
       </c>
       <c r="K257">
         <v>80</v>
       </c>
       <c r="L257">
-        <v>20</v>
+        <f t="shared" ref="L257" si="126">I257*20</f>
+        <v>40</v>
       </c>
       <c r="M257">
         <v>-1</v>
@@ -15280,7 +15283,7 @@
         <v>120</v>
       </c>
       <c r="C258">
-        <v>-2560</v>
+        <v>-2540</v>
       </c>
       <c r="D258">
         <v>0</v>
@@ -15304,7 +15307,7 @@
         <v>20</v>
       </c>
       <c r="K258">
-        <f t="shared" ref="K258:K259" si="125">H258*20</f>
+        <f t="shared" ref="K258:K259" si="127">H258*20</f>
         <v>20</v>
       </c>
       <c r="L258">
@@ -15328,7 +15331,7 @@
     </row>
     <row r="259" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A259">
-        <v>-200</v>
+        <v>-180</v>
       </c>
       <c r="B259">
         <v>120</v>
@@ -15340,7 +15343,7 @@
         <v>0</v>
       </c>
       <c r="E259">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="F259">
         <v>0</v>
@@ -15358,7 +15361,7 @@
         <v>60</v>
       </c>
       <c r="K259">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>20</v>
       </c>
       <c r="L259">
@@ -15382,41 +15385,42 @@
     </row>
     <row r="260" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A260">
-        <v>-240</v>
+        <v>-230</v>
       </c>
       <c r="B260">
         <v>180</v>
       </c>
       <c r="C260">
-        <v>-2600</v>
+        <v>-2590</v>
       </c>
       <c r="D260">
         <v>0</v>
       </c>
       <c r="E260">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="F260">
         <v>0</v>
       </c>
       <c r="G260">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H260">
         <v>2</v>
       </c>
       <c r="I260">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J260">
-        <f t="shared" ref="J260" si="126">G260*20</f>
-        <v>20</v>
+        <f t="shared" ref="J260" si="128">G260*20</f>
+        <v>40</v>
       </c>
       <c r="K260">
         <v>80</v>
       </c>
       <c r="L260">
-        <v>20</v>
+        <f t="shared" ref="L260" si="129">I260*20</f>
+        <v>40</v>
       </c>
       <c r="M260">
         <v>-1</v>
@@ -15431,6 +15435,61 @@
         <v>0</v>
       </c>
       <c r="Q260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A261">
+        <v>0</v>
+      </c>
+      <c r="B261">
+        <v>30</v>
+      </c>
+      <c r="C261">
+        <v>-3030</v>
+      </c>
+      <c r="D261">
+        <v>0</v>
+      </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
+      <c r="F261">
+        <v>0</v>
+      </c>
+      <c r="G261">
+        <v>1</v>
+      </c>
+      <c r="H261">
+        <v>1</v>
+      </c>
+      <c r="I261">
+        <v>1</v>
+      </c>
+      <c r="J261">
+        <f t="shared" ref="J261:K261" si="130">G261*20</f>
+        <v>20</v>
+      </c>
+      <c r="K261">
+        <v>30</v>
+      </c>
+      <c r="L261">
+        <f t="shared" ref="L261" si="131">I261*20</f>
+        <v>20</v>
+      </c>
+      <c r="M261">
+        <v>-1</v>
+      </c>
+      <c r="N261">
+        <v>0</v>
+      </c>
+      <c r="O261">
+        <v>0</v>
+      </c>
+      <c r="P261">
+        <v>0</v>
+      </c>
+      <c r="Q261">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
+++ b/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Map1\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B126777-D81B-42AA-BC01-80D0BBCC9FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9AF08CD-C06D-41B2-9BAD-9878CF1C9AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
@@ -977,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q261"/>
+  <dimension ref="A1:Q303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="17" width="5.625" customWidth="1"/>
@@ -15443,10 +15443,10 @@
         <v>0</v>
       </c>
       <c r="B261">
-        <v>30</v>
+        <v>330</v>
       </c>
       <c r="C261">
-        <v>-3030</v>
+        <v>-3120</v>
       </c>
       <c r="D261">
         <v>0</v>
@@ -15467,7 +15467,7 @@
         <v>1</v>
       </c>
       <c r="J261">
-        <f t="shared" ref="J261:K261" si="130">G261*20</f>
+        <f t="shared" ref="J261" si="130">G261*20</f>
         <v>20</v>
       </c>
       <c r="K261">
@@ -15490,6 +15490,2350 @@
         <v>0</v>
       </c>
       <c r="Q261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A262">
+        <v>80</v>
+      </c>
+      <c r="B262">
+        <v>380</v>
+      </c>
+      <c r="C262">
+        <v>-2730</v>
+      </c>
+      <c r="D262">
+        <v>0</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>0</v>
+      </c>
+      <c r="G262">
+        <v>2</v>
+      </c>
+      <c r="H262">
+        <v>2</v>
+      </c>
+      <c r="I262">
+        <v>2</v>
+      </c>
+      <c r="J262">
+        <f t="shared" ref="J262" si="132">G262*20</f>
+        <v>40</v>
+      </c>
+      <c r="K262">
+        <v>80</v>
+      </c>
+      <c r="L262">
+        <f t="shared" ref="L262" si="133">I262*20</f>
+        <v>40</v>
+      </c>
+      <c r="M262">
+        <v>-1</v>
+      </c>
+      <c r="N262">
+        <v>0</v>
+      </c>
+      <c r="O262">
+        <v>0</v>
+      </c>
+      <c r="P262">
+        <v>0</v>
+      </c>
+      <c r="Q262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A263">
+        <v>-80</v>
+      </c>
+      <c r="B263">
+        <v>380</v>
+      </c>
+      <c r="C263">
+        <v>-2730</v>
+      </c>
+      <c r="D263">
+        <v>0</v>
+      </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
+      <c r="F263">
+        <v>0</v>
+      </c>
+      <c r="G263">
+        <v>2</v>
+      </c>
+      <c r="H263">
+        <v>2</v>
+      </c>
+      <c r="I263">
+        <v>2</v>
+      </c>
+      <c r="J263">
+        <f t="shared" ref="J263" si="134">G263*20</f>
+        <v>40</v>
+      </c>
+      <c r="K263">
+        <v>80</v>
+      </c>
+      <c r="L263">
+        <f t="shared" ref="L263" si="135">I263*20</f>
+        <v>40</v>
+      </c>
+      <c r="M263">
+        <v>-1</v>
+      </c>
+      <c r="N263">
+        <v>0</v>
+      </c>
+      <c r="O263">
+        <v>0</v>
+      </c>
+      <c r="P263">
+        <v>0</v>
+      </c>
+      <c r="Q263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A264">
+        <v>80</v>
+      </c>
+      <c r="B264">
+        <v>380</v>
+      </c>
+      <c r="C264">
+        <v>-2930</v>
+      </c>
+      <c r="D264">
+        <v>0</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264">
+        <v>0</v>
+      </c>
+      <c r="G264">
+        <v>2</v>
+      </c>
+      <c r="H264">
+        <v>2</v>
+      </c>
+      <c r="I264">
+        <v>2</v>
+      </c>
+      <c r="J264">
+        <f t="shared" ref="J264:J266" si="136">G264*20</f>
+        <v>40</v>
+      </c>
+      <c r="K264">
+        <v>81</v>
+      </c>
+      <c r="L264">
+        <f t="shared" ref="L264:L266" si="137">I264*20</f>
+        <v>40</v>
+      </c>
+      <c r="M264">
+        <v>-1</v>
+      </c>
+      <c r="N264">
+        <v>0</v>
+      </c>
+      <c r="O264">
+        <v>0</v>
+      </c>
+      <c r="P264">
+        <v>0</v>
+      </c>
+      <c r="Q264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A265">
+        <v>-80</v>
+      </c>
+      <c r="B265">
+        <v>380</v>
+      </c>
+      <c r="C265">
+        <v>-3110</v>
+      </c>
+      <c r="D265">
+        <v>0</v>
+      </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
+      <c r="F265">
+        <v>0</v>
+      </c>
+      <c r="G265">
+        <v>2</v>
+      </c>
+      <c r="H265">
+        <v>2</v>
+      </c>
+      <c r="I265">
+        <v>2</v>
+      </c>
+      <c r="J265">
+        <f t="shared" si="136"/>
+        <v>40</v>
+      </c>
+      <c r="K265">
+        <v>80</v>
+      </c>
+      <c r="L265">
+        <f t="shared" si="137"/>
+        <v>40</v>
+      </c>
+      <c r="M265">
+        <v>-1</v>
+      </c>
+      <c r="N265">
+        <v>0</v>
+      </c>
+      <c r="O265">
+        <v>0</v>
+      </c>
+      <c r="P265">
+        <v>0</v>
+      </c>
+      <c r="Q265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A266">
+        <v>-90</v>
+      </c>
+      <c r="B266">
+        <v>320</v>
+      </c>
+      <c r="C266">
+        <v>-3060</v>
+      </c>
+      <c r="D266">
+        <v>0</v>
+      </c>
+      <c r="E266">
+        <v>4.71</v>
+      </c>
+      <c r="F266">
+        <v>0</v>
+      </c>
+      <c r="G266">
+        <v>1</v>
+      </c>
+      <c r="H266">
+        <v>1</v>
+      </c>
+      <c r="I266">
+        <v>1</v>
+      </c>
+      <c r="J266">
+        <f t="shared" si="136"/>
+        <v>20</v>
+      </c>
+      <c r="K266">
+        <f t="shared" ref="K266" si="138">H266*20</f>
+        <v>20</v>
+      </c>
+      <c r="L266">
+        <v>60</v>
+      </c>
+      <c r="M266">
+        <v>-1</v>
+      </c>
+      <c r="N266">
+        <v>0</v>
+      </c>
+      <c r="O266">
+        <v>0</v>
+      </c>
+      <c r="P266">
+        <v>0</v>
+      </c>
+      <c r="Q266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A267">
+        <v>-90</v>
+      </c>
+      <c r="B267">
+        <v>320</v>
+      </c>
+      <c r="C267">
+        <v>-2780</v>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267">
+        <v>4.71</v>
+      </c>
+      <c r="F267">
+        <v>0</v>
+      </c>
+      <c r="G267">
+        <v>1</v>
+      </c>
+      <c r="H267">
+        <v>1</v>
+      </c>
+      <c r="I267">
+        <v>1</v>
+      </c>
+      <c r="J267">
+        <f t="shared" ref="J267" si="139">G267*20</f>
+        <v>20</v>
+      </c>
+      <c r="K267">
+        <f t="shared" ref="K267" si="140">H267*20</f>
+        <v>20</v>
+      </c>
+      <c r="L267">
+        <v>60</v>
+      </c>
+      <c r="M267">
+        <v>-1</v>
+      </c>
+      <c r="N267">
+        <v>0</v>
+      </c>
+      <c r="O267">
+        <v>0</v>
+      </c>
+      <c r="P267">
+        <v>0</v>
+      </c>
+      <c r="Q267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A268">
+        <v>90</v>
+      </c>
+      <c r="B268">
+        <v>320</v>
+      </c>
+      <c r="C268">
+        <v>-2780</v>
+      </c>
+      <c r="D268">
+        <v>0</v>
+      </c>
+      <c r="E268">
+        <v>1.57</v>
+      </c>
+      <c r="F268">
+        <v>0</v>
+      </c>
+      <c r="G268">
+        <v>1</v>
+      </c>
+      <c r="H268">
+        <v>1</v>
+      </c>
+      <c r="I268">
+        <v>1</v>
+      </c>
+      <c r="J268">
+        <f t="shared" ref="J268" si="141">G268*20</f>
+        <v>20</v>
+      </c>
+      <c r="K268">
+        <f t="shared" ref="K268" si="142">H268*20</f>
+        <v>20</v>
+      </c>
+      <c r="L268">
+        <v>60</v>
+      </c>
+      <c r="M268">
+        <v>-1</v>
+      </c>
+      <c r="N268">
+        <v>0</v>
+      </c>
+      <c r="O268">
+        <v>0</v>
+      </c>
+      <c r="P268">
+        <v>0</v>
+      </c>
+      <c r="Q268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A269">
+        <v>90</v>
+      </c>
+      <c r="B269">
+        <v>320</v>
+      </c>
+      <c r="C269">
+        <v>-2880</v>
+      </c>
+      <c r="D269">
+        <v>0</v>
+      </c>
+      <c r="E269">
+        <v>1.57</v>
+      </c>
+      <c r="F269">
+        <v>0</v>
+      </c>
+      <c r="G269">
+        <v>1</v>
+      </c>
+      <c r="H269">
+        <v>1</v>
+      </c>
+      <c r="I269">
+        <v>1</v>
+      </c>
+      <c r="J269">
+        <f t="shared" ref="J269:J270" si="143">G269*20</f>
+        <v>20</v>
+      </c>
+      <c r="K269">
+        <f t="shared" ref="K269:K270" si="144">H269*20</f>
+        <v>20</v>
+      </c>
+      <c r="L269">
+        <v>60</v>
+      </c>
+      <c r="M269">
+        <v>-1</v>
+      </c>
+      <c r="N269">
+        <v>0</v>
+      </c>
+      <c r="O269">
+        <v>0</v>
+      </c>
+      <c r="P269">
+        <v>0</v>
+      </c>
+      <c r="Q269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A270">
+        <v>-50</v>
+      </c>
+      <c r="B270">
+        <v>300</v>
+      </c>
+      <c r="C270">
+        <v>-2740</v>
+      </c>
+      <c r="D270">
+        <v>0</v>
+      </c>
+      <c r="E270">
+        <v>0</v>
+      </c>
+      <c r="F270">
+        <v>0</v>
+      </c>
+      <c r="G270">
+        <v>1</v>
+      </c>
+      <c r="H270">
+        <v>1</v>
+      </c>
+      <c r="I270">
+        <v>1</v>
+      </c>
+      <c r="J270">
+        <f t="shared" si="143"/>
+        <v>20</v>
+      </c>
+      <c r="K270">
+        <f t="shared" si="144"/>
+        <v>20</v>
+      </c>
+      <c r="L270">
+        <f t="shared" ref="L270" si="145">I270*20</f>
+        <v>20</v>
+      </c>
+      <c r="M270">
+        <v>-1</v>
+      </c>
+      <c r="N270">
+        <v>0</v>
+      </c>
+      <c r="O270">
+        <v>0</v>
+      </c>
+      <c r="P270">
+        <v>0</v>
+      </c>
+      <c r="Q270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A271">
+        <v>50</v>
+      </c>
+      <c r="B271">
+        <v>300</v>
+      </c>
+      <c r="C271">
+        <v>-2820</v>
+      </c>
+      <c r="D271">
+        <v>0</v>
+      </c>
+      <c r="E271">
+        <v>0</v>
+      </c>
+      <c r="F271">
+        <v>0</v>
+      </c>
+      <c r="G271">
+        <v>1</v>
+      </c>
+      <c r="H271">
+        <v>1</v>
+      </c>
+      <c r="I271">
+        <v>1</v>
+      </c>
+      <c r="J271">
+        <f t="shared" ref="J271:J273" si="146">G271*20</f>
+        <v>20</v>
+      </c>
+      <c r="K271">
+        <f t="shared" ref="K271:K273" si="147">H271*20</f>
+        <v>20</v>
+      </c>
+      <c r="L271">
+        <f t="shared" ref="L271:L273" si="148">I271*20</f>
+        <v>20</v>
+      </c>
+      <c r="M271">
+        <v>-1</v>
+      </c>
+      <c r="N271">
+        <v>0</v>
+      </c>
+      <c r="O271">
+        <v>0</v>
+      </c>
+      <c r="P271">
+        <v>0</v>
+      </c>
+      <c r="Q271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A272">
+        <v>-30</v>
+      </c>
+      <c r="B272">
+        <v>300</v>
+      </c>
+      <c r="C272">
+        <v>-2920</v>
+      </c>
+      <c r="D272">
+        <v>0</v>
+      </c>
+      <c r="E272">
+        <v>0</v>
+      </c>
+      <c r="F272">
+        <v>0</v>
+      </c>
+      <c r="G272">
+        <v>1</v>
+      </c>
+      <c r="H272">
+        <v>1</v>
+      </c>
+      <c r="I272">
+        <v>1</v>
+      </c>
+      <c r="J272">
+        <f t="shared" si="146"/>
+        <v>20</v>
+      </c>
+      <c r="K272">
+        <f t="shared" si="147"/>
+        <v>20</v>
+      </c>
+      <c r="L272">
+        <f t="shared" si="148"/>
+        <v>20</v>
+      </c>
+      <c r="M272">
+        <v>-1</v>
+      </c>
+      <c r="N272">
+        <v>0</v>
+      </c>
+      <c r="O272">
+        <v>0</v>
+      </c>
+      <c r="P272">
+        <v>0</v>
+      </c>
+      <c r="Q272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A273">
+        <v>50</v>
+      </c>
+      <c r="B273">
+        <v>300</v>
+      </c>
+      <c r="C273">
+        <v>-3040</v>
+      </c>
+      <c r="D273">
+        <v>0</v>
+      </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
+      <c r="F273">
+        <v>0</v>
+      </c>
+      <c r="G273">
+        <v>1</v>
+      </c>
+      <c r="H273">
+        <v>1</v>
+      </c>
+      <c r="I273">
+        <v>1</v>
+      </c>
+      <c r="J273">
+        <f t="shared" si="146"/>
+        <v>20</v>
+      </c>
+      <c r="K273">
+        <f t="shared" si="147"/>
+        <v>20</v>
+      </c>
+      <c r="L273">
+        <f t="shared" si="148"/>
+        <v>20</v>
+      </c>
+      <c r="M273">
+        <v>-1</v>
+      </c>
+      <c r="N273">
+        <v>0</v>
+      </c>
+      <c r="O273">
+        <v>0</v>
+      </c>
+      <c r="P273">
+        <v>0</v>
+      </c>
+      <c r="Q273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A274">
+        <v>-70</v>
+      </c>
+      <c r="B274">
+        <v>300</v>
+      </c>
+      <c r="C274">
+        <v>-2720</v>
+      </c>
+      <c r="D274">
+        <v>0</v>
+      </c>
+      <c r="E274">
+        <v>0</v>
+      </c>
+      <c r="F274">
+        <v>0</v>
+      </c>
+      <c r="G274">
+        <v>1</v>
+      </c>
+      <c r="H274">
+        <v>1</v>
+      </c>
+      <c r="I274">
+        <v>1</v>
+      </c>
+      <c r="J274">
+        <f t="shared" ref="J274:J289" si="149">G274*20</f>
+        <v>20</v>
+      </c>
+      <c r="K274">
+        <f t="shared" ref="K274:K289" si="150">H274*20</f>
+        <v>20</v>
+      </c>
+      <c r="L274">
+        <f t="shared" ref="L274:L289" si="151">I274*20</f>
+        <v>20</v>
+      </c>
+      <c r="M274">
+        <v>-1</v>
+      </c>
+      <c r="N274">
+        <v>0</v>
+      </c>
+      <c r="O274">
+        <v>0</v>
+      </c>
+      <c r="P274">
+        <v>0</v>
+      </c>
+      <c r="Q274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A275">
+        <v>30</v>
+      </c>
+      <c r="B275">
+        <v>300</v>
+      </c>
+      <c r="C275">
+        <v>-2760</v>
+      </c>
+      <c r="D275">
+        <v>0</v>
+      </c>
+      <c r="E275">
+        <v>0</v>
+      </c>
+      <c r="F275">
+        <v>0</v>
+      </c>
+      <c r="G275">
+        <v>1</v>
+      </c>
+      <c r="H275">
+        <v>1</v>
+      </c>
+      <c r="I275">
+        <v>1</v>
+      </c>
+      <c r="J275">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K275">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L275">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M275">
+        <v>-1</v>
+      </c>
+      <c r="N275">
+        <v>0</v>
+      </c>
+      <c r="O275">
+        <v>0</v>
+      </c>
+      <c r="P275">
+        <v>0</v>
+      </c>
+      <c r="Q275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A276">
+        <v>-50</v>
+      </c>
+      <c r="B276">
+        <v>300</v>
+      </c>
+      <c r="C276">
+        <v>-2800</v>
+      </c>
+      <c r="D276">
+        <v>0</v>
+      </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
+      <c r="F276">
+        <v>0</v>
+      </c>
+      <c r="G276">
+        <v>1</v>
+      </c>
+      <c r="H276">
+        <v>1</v>
+      </c>
+      <c r="I276">
+        <v>1</v>
+      </c>
+      <c r="J276">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K276">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L276">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M276">
+        <v>-1</v>
+      </c>
+      <c r="N276">
+        <v>0</v>
+      </c>
+      <c r="O276">
+        <v>0</v>
+      </c>
+      <c r="P276">
+        <v>0</v>
+      </c>
+      <c r="Q276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A277">
+        <v>70</v>
+      </c>
+      <c r="B277">
+        <v>300</v>
+      </c>
+      <c r="C277">
+        <v>-2840</v>
+      </c>
+      <c r="D277">
+        <v>0</v>
+      </c>
+      <c r="E277">
+        <v>0</v>
+      </c>
+      <c r="F277">
+        <v>0</v>
+      </c>
+      <c r="G277">
+        <v>1</v>
+      </c>
+      <c r="H277">
+        <v>1</v>
+      </c>
+      <c r="I277">
+        <v>1</v>
+      </c>
+      <c r="J277">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K277">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L277">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M277">
+        <v>-1</v>
+      </c>
+      <c r="N277">
+        <v>0</v>
+      </c>
+      <c r="O277">
+        <v>0</v>
+      </c>
+      <c r="P277">
+        <v>0</v>
+      </c>
+      <c r="Q277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A278">
+        <v>-30</v>
+      </c>
+      <c r="B278">
+        <v>300</v>
+      </c>
+      <c r="C278">
+        <v>-2880</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
+      <c r="F278">
+        <v>0</v>
+      </c>
+      <c r="G278">
+        <v>1</v>
+      </c>
+      <c r="H278">
+        <v>1</v>
+      </c>
+      <c r="I278">
+        <v>1</v>
+      </c>
+      <c r="J278">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K278">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L278">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M278">
+        <v>-1</v>
+      </c>
+      <c r="N278">
+        <v>0</v>
+      </c>
+      <c r="O278">
+        <v>0</v>
+      </c>
+      <c r="P278">
+        <v>0</v>
+      </c>
+      <c r="Q278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A279">
+        <v>50</v>
+      </c>
+      <c r="B279">
+        <v>300</v>
+      </c>
+      <c r="C279">
+        <v>-2920</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
+      <c r="F279">
+        <v>0</v>
+      </c>
+      <c r="G279">
+        <v>1</v>
+      </c>
+      <c r="H279">
+        <v>1</v>
+      </c>
+      <c r="I279">
+        <v>1</v>
+      </c>
+      <c r="J279">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K279">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L279">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M279">
+        <v>-1</v>
+      </c>
+      <c r="N279">
+        <v>0</v>
+      </c>
+      <c r="O279">
+        <v>0</v>
+      </c>
+      <c r="P279">
+        <v>0</v>
+      </c>
+      <c r="Q279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A280">
+        <v>-70</v>
+      </c>
+      <c r="B280">
+        <v>300</v>
+      </c>
+      <c r="C280">
+        <v>-2960</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>0</v>
+      </c>
+      <c r="G280">
+        <v>1</v>
+      </c>
+      <c r="H280">
+        <v>1</v>
+      </c>
+      <c r="I280">
+        <v>1</v>
+      </c>
+      <c r="J280">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K280">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L280">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M280">
+        <v>-1</v>
+      </c>
+      <c r="N280">
+        <v>0</v>
+      </c>
+      <c r="O280">
+        <v>0</v>
+      </c>
+      <c r="P280">
+        <v>0</v>
+      </c>
+      <c r="Q280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A281">
+        <v>30</v>
+      </c>
+      <c r="B281">
+        <v>300</v>
+      </c>
+      <c r="C281">
+        <v>-3000</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
+      <c r="F281">
+        <v>0</v>
+      </c>
+      <c r="G281">
+        <v>1</v>
+      </c>
+      <c r="H281">
+        <v>1</v>
+      </c>
+      <c r="I281">
+        <v>1</v>
+      </c>
+      <c r="J281">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K281">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L281">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M281">
+        <v>-1</v>
+      </c>
+      <c r="N281">
+        <v>0</v>
+      </c>
+      <c r="O281">
+        <v>0</v>
+      </c>
+      <c r="P281">
+        <v>0</v>
+      </c>
+      <c r="Q281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A282">
+        <v>-50</v>
+      </c>
+      <c r="B282">
+        <v>300</v>
+      </c>
+      <c r="C282">
+        <v>-3060</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>0</v>
+      </c>
+      <c r="G282">
+        <v>1</v>
+      </c>
+      <c r="H282">
+        <v>1</v>
+      </c>
+      <c r="I282">
+        <v>1</v>
+      </c>
+      <c r="J282">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K282">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L282">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M282">
+        <v>-1</v>
+      </c>
+      <c r="N282">
+        <v>0</v>
+      </c>
+      <c r="O282">
+        <v>0</v>
+      </c>
+      <c r="P282">
+        <v>0</v>
+      </c>
+      <c r="Q282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A283">
+        <v>70</v>
+      </c>
+      <c r="B283">
+        <v>300</v>
+      </c>
+      <c r="C283">
+        <v>-3100</v>
+      </c>
+      <c r="D283">
+        <v>0</v>
+      </c>
+      <c r="E283">
+        <v>0</v>
+      </c>
+      <c r="F283">
+        <v>0</v>
+      </c>
+      <c r="G283">
+        <v>1</v>
+      </c>
+      <c r="H283">
+        <v>1</v>
+      </c>
+      <c r="I283">
+        <v>1</v>
+      </c>
+      <c r="J283">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K283">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L283">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M283">
+        <v>-1</v>
+      </c>
+      <c r="N283">
+        <v>0</v>
+      </c>
+      <c r="O283">
+        <v>0</v>
+      </c>
+      <c r="P283">
+        <v>0</v>
+      </c>
+      <c r="Q283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A284">
+        <v>10</v>
+      </c>
+      <c r="B284">
+        <v>300</v>
+      </c>
+      <c r="C284">
+        <v>-2780</v>
+      </c>
+      <c r="D284">
+        <v>0</v>
+      </c>
+      <c r="E284">
+        <v>0</v>
+      </c>
+      <c r="F284">
+        <v>0</v>
+      </c>
+      <c r="G284">
+        <v>1</v>
+      </c>
+      <c r="H284">
+        <v>1</v>
+      </c>
+      <c r="I284">
+        <v>1</v>
+      </c>
+      <c r="J284">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K284">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L284">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M284">
+        <v>-1</v>
+      </c>
+      <c r="N284">
+        <v>0</v>
+      </c>
+      <c r="O284">
+        <v>0</v>
+      </c>
+      <c r="P284">
+        <v>0</v>
+      </c>
+      <c r="Q284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A285">
+        <v>30</v>
+      </c>
+      <c r="B285">
+        <v>300</v>
+      </c>
+      <c r="C285">
+        <v>-2800</v>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
+      <c r="F285">
+        <v>0</v>
+      </c>
+      <c r="G285">
+        <v>1</v>
+      </c>
+      <c r="H285">
+        <v>1</v>
+      </c>
+      <c r="I285">
+        <v>1</v>
+      </c>
+      <c r="J285">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K285">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L285">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M285">
+        <v>-1</v>
+      </c>
+      <c r="N285">
+        <v>0</v>
+      </c>
+      <c r="O285">
+        <v>0</v>
+      </c>
+      <c r="P285">
+        <v>0</v>
+      </c>
+      <c r="Q285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A286">
+        <v>-50</v>
+      </c>
+      <c r="B286">
+        <v>300</v>
+      </c>
+      <c r="C286">
+        <v>-2860</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>0</v>
+      </c>
+      <c r="F286">
+        <v>0</v>
+      </c>
+      <c r="G286">
+        <v>1</v>
+      </c>
+      <c r="H286">
+        <v>1</v>
+      </c>
+      <c r="I286">
+        <v>1</v>
+      </c>
+      <c r="J286">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K286">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L286">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M286">
+        <v>-1</v>
+      </c>
+      <c r="N286">
+        <v>0</v>
+      </c>
+      <c r="O286">
+        <v>0</v>
+      </c>
+      <c r="P286">
+        <v>0</v>
+      </c>
+      <c r="Q286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A287">
+        <v>-30</v>
+      </c>
+      <c r="B287">
+        <v>300</v>
+      </c>
+      <c r="C287">
+        <v>-2880</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287">
+        <v>0</v>
+      </c>
+      <c r="F287">
+        <v>0</v>
+      </c>
+      <c r="G287">
+        <v>1</v>
+      </c>
+      <c r="H287">
+        <v>1</v>
+      </c>
+      <c r="I287">
+        <v>1</v>
+      </c>
+      <c r="J287">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K287">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L287">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M287">
+        <v>-1</v>
+      </c>
+      <c r="N287">
+        <v>0</v>
+      </c>
+      <c r="O287">
+        <v>0</v>
+      </c>
+      <c r="P287">
+        <v>0</v>
+      </c>
+      <c r="Q287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A288">
+        <v>30</v>
+      </c>
+      <c r="B288">
+        <v>300</v>
+      </c>
+      <c r="C288">
+        <v>-3020</v>
+      </c>
+      <c r="D288">
+        <v>0</v>
+      </c>
+      <c r="E288">
+        <v>0</v>
+      </c>
+      <c r="F288">
+        <v>0</v>
+      </c>
+      <c r="G288">
+        <v>1</v>
+      </c>
+      <c r="H288">
+        <v>1</v>
+      </c>
+      <c r="I288">
+        <v>1</v>
+      </c>
+      <c r="J288">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K288">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L288">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M288">
+        <v>-1</v>
+      </c>
+      <c r="N288">
+        <v>0</v>
+      </c>
+      <c r="O288">
+        <v>0</v>
+      </c>
+      <c r="P288">
+        <v>0</v>
+      </c>
+      <c r="Q288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A289">
+        <v>50</v>
+      </c>
+      <c r="B289">
+        <v>300</v>
+      </c>
+      <c r="C289">
+        <v>-3040</v>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+      <c r="E289">
+        <v>0</v>
+      </c>
+      <c r="F289">
+        <v>0</v>
+      </c>
+      <c r="G289">
+        <v>1</v>
+      </c>
+      <c r="H289">
+        <v>1</v>
+      </c>
+      <c r="I289">
+        <v>1</v>
+      </c>
+      <c r="J289">
+        <f t="shared" si="149"/>
+        <v>20</v>
+      </c>
+      <c r="K289">
+        <f t="shared" si="150"/>
+        <v>20</v>
+      </c>
+      <c r="L289">
+        <f t="shared" si="151"/>
+        <v>20</v>
+      </c>
+      <c r="M289">
+        <v>-1</v>
+      </c>
+      <c r="N289">
+        <v>0</v>
+      </c>
+      <c r="O289">
+        <v>0</v>
+      </c>
+      <c r="P289">
+        <v>0</v>
+      </c>
+      <c r="Q289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A290">
+        <v>150</v>
+      </c>
+      <c r="B290">
+        <v>300</v>
+      </c>
+      <c r="C290">
+        <v>-2980</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290">
+        <v>0</v>
+      </c>
+      <c r="F290">
+        <v>0</v>
+      </c>
+      <c r="G290">
+        <v>1</v>
+      </c>
+      <c r="H290">
+        <v>1</v>
+      </c>
+      <c r="I290">
+        <v>1</v>
+      </c>
+      <c r="J290">
+        <f t="shared" ref="J290:J303" si="152">G290*20</f>
+        <v>20</v>
+      </c>
+      <c r="K290">
+        <f t="shared" ref="K290:K303" si="153">H290*20</f>
+        <v>20</v>
+      </c>
+      <c r="L290">
+        <f t="shared" ref="L290:L303" si="154">I290*20</f>
+        <v>20</v>
+      </c>
+      <c r="M290">
+        <v>-1</v>
+      </c>
+      <c r="N290">
+        <v>0</v>
+      </c>
+      <c r="O290">
+        <v>0</v>
+      </c>
+      <c r="P290">
+        <v>0</v>
+      </c>
+      <c r="Q290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A291">
+        <v>310</v>
+      </c>
+      <c r="B291">
+        <v>300</v>
+      </c>
+      <c r="C291">
+        <v>-3060</v>
+      </c>
+      <c r="D291">
+        <v>0</v>
+      </c>
+      <c r="E291">
+        <v>0</v>
+      </c>
+      <c r="F291">
+        <v>0</v>
+      </c>
+      <c r="G291">
+        <v>1</v>
+      </c>
+      <c r="H291">
+        <v>1</v>
+      </c>
+      <c r="I291">
+        <v>1</v>
+      </c>
+      <c r="J291">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K291">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L291">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M291">
+        <v>-1</v>
+      </c>
+      <c r="N291">
+        <v>0</v>
+      </c>
+      <c r="O291">
+        <v>0</v>
+      </c>
+      <c r="P291">
+        <v>0</v>
+      </c>
+      <c r="Q291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A292">
+        <v>450</v>
+      </c>
+      <c r="B292">
+        <v>300</v>
+      </c>
+      <c r="C292">
+        <v>-3000</v>
+      </c>
+      <c r="D292">
+        <v>0</v>
+      </c>
+      <c r="E292">
+        <v>0</v>
+      </c>
+      <c r="F292">
+        <v>0</v>
+      </c>
+      <c r="G292">
+        <v>1</v>
+      </c>
+      <c r="H292">
+        <v>1</v>
+      </c>
+      <c r="I292">
+        <v>1</v>
+      </c>
+      <c r="J292">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K292">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L292">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M292">
+        <v>-1</v>
+      </c>
+      <c r="N292">
+        <v>0</v>
+      </c>
+      <c r="O292">
+        <v>0</v>
+      </c>
+      <c r="P292">
+        <v>0</v>
+      </c>
+      <c r="Q292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A293">
+        <v>110</v>
+      </c>
+      <c r="B293">
+        <v>300</v>
+      </c>
+      <c r="C293">
+        <v>-3000</v>
+      </c>
+      <c r="D293">
+        <v>0</v>
+      </c>
+      <c r="E293">
+        <v>0</v>
+      </c>
+      <c r="F293">
+        <v>0</v>
+      </c>
+      <c r="G293">
+        <v>1</v>
+      </c>
+      <c r="H293">
+        <v>1</v>
+      </c>
+      <c r="I293">
+        <v>1</v>
+      </c>
+      <c r="J293">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K293">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L293">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M293">
+        <v>-1</v>
+      </c>
+      <c r="N293">
+        <v>0</v>
+      </c>
+      <c r="O293">
+        <v>0</v>
+      </c>
+      <c r="P293">
+        <v>0</v>
+      </c>
+      <c r="Q293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A294">
+        <v>190</v>
+      </c>
+      <c r="B294">
+        <v>300</v>
+      </c>
+      <c r="C294">
+        <v>-3080</v>
+      </c>
+      <c r="D294">
+        <v>0</v>
+      </c>
+      <c r="E294">
+        <v>0</v>
+      </c>
+      <c r="F294">
+        <v>0</v>
+      </c>
+      <c r="G294">
+        <v>1</v>
+      </c>
+      <c r="H294">
+        <v>1</v>
+      </c>
+      <c r="I294">
+        <v>1</v>
+      </c>
+      <c r="J294">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K294">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L294">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M294">
+        <v>-1</v>
+      </c>
+      <c r="N294">
+        <v>0</v>
+      </c>
+      <c r="O294">
+        <v>0</v>
+      </c>
+      <c r="P294">
+        <v>0</v>
+      </c>
+      <c r="Q294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A295">
+        <v>250</v>
+      </c>
+      <c r="B295">
+        <v>300</v>
+      </c>
+      <c r="C295">
+        <v>-2980</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
+      <c r="F295">
+        <v>0</v>
+      </c>
+      <c r="G295">
+        <v>1</v>
+      </c>
+      <c r="H295">
+        <v>1</v>
+      </c>
+      <c r="I295">
+        <v>1</v>
+      </c>
+      <c r="J295">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K295">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L295">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M295">
+        <v>-1</v>
+      </c>
+      <c r="N295">
+        <v>0</v>
+      </c>
+      <c r="O295">
+        <v>0</v>
+      </c>
+      <c r="P295">
+        <v>0</v>
+      </c>
+      <c r="Q295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A296">
+        <v>330</v>
+      </c>
+      <c r="B296">
+        <v>300</v>
+      </c>
+      <c r="C296">
+        <v>-3100</v>
+      </c>
+      <c r="D296">
+        <v>0</v>
+      </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
+      <c r="F296">
+        <v>0</v>
+      </c>
+      <c r="G296">
+        <v>1</v>
+      </c>
+      <c r="H296">
+        <v>1</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+      <c r="J296">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K296">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L296">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M296">
+        <v>-1</v>
+      </c>
+      <c r="N296">
+        <v>0</v>
+      </c>
+      <c r="O296">
+        <v>0</v>
+      </c>
+      <c r="P296">
+        <v>0</v>
+      </c>
+      <c r="Q296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A297">
+        <v>370</v>
+      </c>
+      <c r="B297">
+        <v>300</v>
+      </c>
+      <c r="C297">
+        <v>-3020</v>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+      <c r="E297">
+        <v>0</v>
+      </c>
+      <c r="F297">
+        <v>0</v>
+      </c>
+      <c r="G297">
+        <v>1</v>
+      </c>
+      <c r="H297">
+        <v>1</v>
+      </c>
+      <c r="I297">
+        <v>1</v>
+      </c>
+      <c r="J297">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K297">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L297">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M297">
+        <v>-1</v>
+      </c>
+      <c r="N297">
+        <v>0</v>
+      </c>
+      <c r="O297">
+        <v>0</v>
+      </c>
+      <c r="P297">
+        <v>0</v>
+      </c>
+      <c r="Q297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A298">
+        <v>430</v>
+      </c>
+      <c r="B298">
+        <v>300</v>
+      </c>
+      <c r="C298">
+        <v>-3080</v>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+      <c r="F298">
+        <v>0</v>
+      </c>
+      <c r="G298">
+        <v>1</v>
+      </c>
+      <c r="H298">
+        <v>1</v>
+      </c>
+      <c r="I298">
+        <v>1</v>
+      </c>
+      <c r="J298">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K298">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L298">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M298">
+        <v>-1</v>
+      </c>
+      <c r="N298">
+        <v>0</v>
+      </c>
+      <c r="O298">
+        <v>0</v>
+      </c>
+      <c r="P298">
+        <v>0</v>
+      </c>
+      <c r="Q298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A299">
+        <v>490</v>
+      </c>
+      <c r="B299">
+        <v>300</v>
+      </c>
+      <c r="C299">
+        <v>-2980</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+      <c r="E299">
+        <v>0</v>
+      </c>
+      <c r="F299">
+        <v>0</v>
+      </c>
+      <c r="G299">
+        <v>1</v>
+      </c>
+      <c r="H299">
+        <v>1</v>
+      </c>
+      <c r="I299">
+        <v>1</v>
+      </c>
+      <c r="J299">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K299">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L299">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M299">
+        <v>-1</v>
+      </c>
+      <c r="N299">
+        <v>0</v>
+      </c>
+      <c r="O299">
+        <v>0</v>
+      </c>
+      <c r="P299">
+        <v>0</v>
+      </c>
+      <c r="Q299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A300">
+        <v>210</v>
+      </c>
+      <c r="B300">
+        <v>300</v>
+      </c>
+      <c r="C300">
+        <v>-3020</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
+      </c>
+      <c r="E300">
+        <v>0</v>
+      </c>
+      <c r="F300">
+        <v>0</v>
+      </c>
+      <c r="G300">
+        <v>1</v>
+      </c>
+      <c r="H300">
+        <v>1</v>
+      </c>
+      <c r="I300">
+        <v>1</v>
+      </c>
+      <c r="J300">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K300">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L300">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M300">
+        <v>-1</v>
+      </c>
+      <c r="N300">
+        <v>0</v>
+      </c>
+      <c r="O300">
+        <v>0</v>
+      </c>
+      <c r="P300">
+        <v>0</v>
+      </c>
+      <c r="Q300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A301">
+        <v>230</v>
+      </c>
+      <c r="B301">
+        <v>300</v>
+      </c>
+      <c r="C301">
+        <v>-3040</v>
+      </c>
+      <c r="D301">
+        <v>0</v>
+      </c>
+      <c r="E301">
+        <v>0</v>
+      </c>
+      <c r="F301">
+        <v>0</v>
+      </c>
+      <c r="G301">
+        <v>1</v>
+      </c>
+      <c r="H301">
+        <v>1</v>
+      </c>
+      <c r="I301">
+        <v>1</v>
+      </c>
+      <c r="J301">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K301">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L301">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M301">
+        <v>-1</v>
+      </c>
+      <c r="N301">
+        <v>0</v>
+      </c>
+      <c r="O301">
+        <v>0</v>
+      </c>
+      <c r="P301">
+        <v>0</v>
+      </c>
+      <c r="Q301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A302">
+        <v>390</v>
+      </c>
+      <c r="B302">
+        <v>300</v>
+      </c>
+      <c r="C302">
+        <v>-3060</v>
+      </c>
+      <c r="D302">
+        <v>0</v>
+      </c>
+      <c r="E302">
+        <v>0</v>
+      </c>
+      <c r="F302">
+        <v>0</v>
+      </c>
+      <c r="G302">
+        <v>1</v>
+      </c>
+      <c r="H302">
+        <v>1</v>
+      </c>
+      <c r="I302">
+        <v>1</v>
+      </c>
+      <c r="J302">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K302">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L302">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M302">
+        <v>-1</v>
+      </c>
+      <c r="N302">
+        <v>0</v>
+      </c>
+      <c r="O302">
+        <v>0</v>
+      </c>
+      <c r="P302">
+        <v>0</v>
+      </c>
+      <c r="Q302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A303">
+        <v>410</v>
+      </c>
+      <c r="B303">
+        <v>300</v>
+      </c>
+      <c r="C303">
+        <v>-3080</v>
+      </c>
+      <c r="D303">
+        <v>0</v>
+      </c>
+      <c r="E303">
+        <v>0</v>
+      </c>
+      <c r="F303">
+        <v>0</v>
+      </c>
+      <c r="G303">
+        <v>1</v>
+      </c>
+      <c r="H303">
+        <v>1</v>
+      </c>
+      <c r="I303">
+        <v>1</v>
+      </c>
+      <c r="J303">
+        <f t="shared" si="152"/>
+        <v>20</v>
+      </c>
+      <c r="K303">
+        <f t="shared" si="153"/>
+        <v>20</v>
+      </c>
+      <c r="L303">
+        <f t="shared" si="154"/>
+        <v>20</v>
+      </c>
+      <c r="M303">
+        <v>-1</v>
+      </c>
+      <c r="N303">
+        <v>0</v>
+      </c>
+      <c r="O303">
+        <v>0</v>
+      </c>
+      <c r="P303">
+        <v>0</v>
+      </c>
+      <c r="Q303">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
+++ b/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Map1\Platform\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Map1\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9AF08CD-C06D-41B2-9BAD-9878CF1C9AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5223C8F-D4F6-48AD-B512-88A929BBFF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -977,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q303"/>
+  <dimension ref="A1:Q470"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="17" width="5.625" customWidth="1"/>
@@ -15639,7 +15639,7 @@
         <v>81</v>
       </c>
       <c r="L264">
-        <f t="shared" ref="L264:L266" si="137">I264*20</f>
+        <f t="shared" ref="L264:L265" si="137">I264*20</f>
         <v>40</v>
       </c>
       <c r="M264">
@@ -17834,6 +17834,9303 @@
         <v>0</v>
       </c>
       <c r="Q303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A304">
+        <v>130</v>
+      </c>
+      <c r="B304">
+        <v>320</v>
+      </c>
+      <c r="C304">
+        <v>-2940</v>
+      </c>
+      <c r="D304">
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>0</v>
+      </c>
+      <c r="F304">
+        <v>0</v>
+      </c>
+      <c r="G304">
+        <v>1</v>
+      </c>
+      <c r="H304">
+        <v>1</v>
+      </c>
+      <c r="I304">
+        <v>1</v>
+      </c>
+      <c r="J304">
+        <v>60</v>
+      </c>
+      <c r="K304">
+        <f t="shared" ref="K304" si="155">H304*20</f>
+        <v>20</v>
+      </c>
+      <c r="L304">
+        <f t="shared" ref="L304:L306" si="156">I304*20</f>
+        <v>20</v>
+      </c>
+      <c r="M304">
+        <v>-1</v>
+      </c>
+      <c r="N304">
+        <v>0</v>
+      </c>
+      <c r="O304">
+        <v>0</v>
+      </c>
+      <c r="P304">
+        <v>0</v>
+      </c>
+      <c r="Q304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A305">
+        <v>500</v>
+      </c>
+      <c r="B305">
+        <v>380</v>
+      </c>
+      <c r="C305">
+        <v>-2950</v>
+      </c>
+      <c r="D305">
+        <v>0</v>
+      </c>
+      <c r="E305">
+        <v>0</v>
+      </c>
+      <c r="F305">
+        <v>0</v>
+      </c>
+      <c r="G305">
+        <v>2</v>
+      </c>
+      <c r="H305">
+        <v>2</v>
+      </c>
+      <c r="I305">
+        <v>2</v>
+      </c>
+      <c r="J305">
+        <f t="shared" ref="J305:J306" si="157">G305*20</f>
+        <v>40</v>
+      </c>
+      <c r="K305">
+        <v>80</v>
+      </c>
+      <c r="L305">
+        <f t="shared" si="156"/>
+        <v>40</v>
+      </c>
+      <c r="M305">
+        <v>-1</v>
+      </c>
+      <c r="N305">
+        <v>0</v>
+      </c>
+      <c r="O305">
+        <v>0</v>
+      </c>
+      <c r="P305">
+        <v>0</v>
+      </c>
+      <c r="Q305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A306">
+        <v>500</v>
+      </c>
+      <c r="B306">
+        <v>380</v>
+      </c>
+      <c r="C306">
+        <v>-3110</v>
+      </c>
+      <c r="D306">
+        <v>0</v>
+      </c>
+      <c r="E306">
+        <v>0</v>
+      </c>
+      <c r="F306">
+        <v>0</v>
+      </c>
+      <c r="G306">
+        <v>2</v>
+      </c>
+      <c r="H306">
+        <v>2</v>
+      </c>
+      <c r="I306">
+        <v>2</v>
+      </c>
+      <c r="J306">
+        <f t="shared" si="157"/>
+        <v>40</v>
+      </c>
+      <c r="K306">
+        <v>80</v>
+      </c>
+      <c r="L306">
+        <f t="shared" si="156"/>
+        <v>40</v>
+      </c>
+      <c r="M306">
+        <v>-1</v>
+      </c>
+      <c r="N306">
+        <v>0</v>
+      </c>
+      <c r="O306">
+        <v>0</v>
+      </c>
+      <c r="P306">
+        <v>0</v>
+      </c>
+      <c r="Q306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A307">
+        <v>450</v>
+      </c>
+      <c r="B307">
+        <v>320</v>
+      </c>
+      <c r="C307">
+        <v>-2940</v>
+      </c>
+      <c r="D307">
+        <v>0</v>
+      </c>
+      <c r="E307">
+        <v>0</v>
+      </c>
+      <c r="F307">
+        <v>0</v>
+      </c>
+      <c r="G307">
+        <v>1</v>
+      </c>
+      <c r="H307">
+        <v>1</v>
+      </c>
+      <c r="I307">
+        <v>1</v>
+      </c>
+      <c r="J307">
+        <v>60</v>
+      </c>
+      <c r="K307">
+        <f t="shared" ref="K307:K311" si="158">H307*20</f>
+        <v>20</v>
+      </c>
+      <c r="L307">
+        <f t="shared" ref="L307:L311" si="159">I307*20</f>
+        <v>20</v>
+      </c>
+      <c r="M307">
+        <v>-1</v>
+      </c>
+      <c r="N307">
+        <v>0</v>
+      </c>
+      <c r="O307">
+        <v>0</v>
+      </c>
+      <c r="P307">
+        <v>0</v>
+      </c>
+      <c r="Q307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A308">
+        <v>450</v>
+      </c>
+      <c r="B308">
+        <v>320</v>
+      </c>
+      <c r="C308">
+        <v>-3120</v>
+      </c>
+      <c r="D308">
+        <v>0</v>
+      </c>
+      <c r="E308">
+        <v>3.14</v>
+      </c>
+      <c r="F308">
+        <v>0</v>
+      </c>
+      <c r="G308">
+        <v>1</v>
+      </c>
+      <c r="H308">
+        <v>1</v>
+      </c>
+      <c r="I308">
+        <v>1</v>
+      </c>
+      <c r="J308">
+        <v>60</v>
+      </c>
+      <c r="K308">
+        <f t="shared" si="158"/>
+        <v>20</v>
+      </c>
+      <c r="L308">
+        <f t="shared" si="159"/>
+        <v>20</v>
+      </c>
+      <c r="M308">
+        <v>-1</v>
+      </c>
+      <c r="N308">
+        <v>0</v>
+      </c>
+      <c r="O308">
+        <v>0</v>
+      </c>
+      <c r="P308">
+        <v>0</v>
+      </c>
+      <c r="Q308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A309">
+        <v>550</v>
+      </c>
+      <c r="B309">
+        <v>340</v>
+      </c>
+      <c r="C309">
+        <v>-2940</v>
+      </c>
+      <c r="D309">
+        <v>0</v>
+      </c>
+      <c r="E309">
+        <v>0</v>
+      </c>
+      <c r="F309">
+        <v>0</v>
+      </c>
+      <c r="G309">
+        <v>1</v>
+      </c>
+      <c r="H309">
+        <v>1</v>
+      </c>
+      <c r="I309">
+        <v>1</v>
+      </c>
+      <c r="J309">
+        <v>60</v>
+      </c>
+      <c r="K309">
+        <f t="shared" si="158"/>
+        <v>20</v>
+      </c>
+      <c r="L309">
+        <f t="shared" si="159"/>
+        <v>20</v>
+      </c>
+      <c r="M309">
+        <v>-1</v>
+      </c>
+      <c r="N309">
+        <v>0</v>
+      </c>
+      <c r="O309">
+        <v>0</v>
+      </c>
+      <c r="P309">
+        <v>0</v>
+      </c>
+      <c r="Q309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A310">
+        <v>550</v>
+      </c>
+      <c r="B310">
+        <v>340</v>
+      </c>
+      <c r="C310">
+        <v>-3120</v>
+      </c>
+      <c r="D310">
+        <v>0</v>
+      </c>
+      <c r="E310">
+        <v>3.14</v>
+      </c>
+      <c r="F310">
+        <v>0</v>
+      </c>
+      <c r="G310">
+        <v>1</v>
+      </c>
+      <c r="H310">
+        <v>1</v>
+      </c>
+      <c r="I310">
+        <v>1</v>
+      </c>
+      <c r="J310">
+        <v>60</v>
+      </c>
+      <c r="K310">
+        <f t="shared" si="158"/>
+        <v>20</v>
+      </c>
+      <c r="L310">
+        <f t="shared" si="159"/>
+        <v>20</v>
+      </c>
+      <c r="M310">
+        <v>-1</v>
+      </c>
+      <c r="N310">
+        <v>0</v>
+      </c>
+      <c r="O310">
+        <v>0</v>
+      </c>
+      <c r="P310">
+        <v>0</v>
+      </c>
+      <c r="Q310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A311">
+        <v>570</v>
+      </c>
+      <c r="B311">
+        <v>320</v>
+      </c>
+      <c r="C311">
+        <v>-2980</v>
+      </c>
+      <c r="D311">
+        <v>0</v>
+      </c>
+      <c r="E311">
+        <v>0</v>
+      </c>
+      <c r="F311">
+        <v>0</v>
+      </c>
+      <c r="G311">
+        <v>1</v>
+      </c>
+      <c r="H311">
+        <v>1</v>
+      </c>
+      <c r="I311">
+        <v>1</v>
+      </c>
+      <c r="J311">
+        <f t="shared" ref="J311" si="160">G311*20</f>
+        <v>20</v>
+      </c>
+      <c r="K311">
+        <f t="shared" si="158"/>
+        <v>20</v>
+      </c>
+      <c r="L311">
+        <f t="shared" si="159"/>
+        <v>20</v>
+      </c>
+      <c r="M311">
+        <v>-1</v>
+      </c>
+      <c r="N311">
+        <v>0</v>
+      </c>
+      <c r="O311">
+        <v>0</v>
+      </c>
+      <c r="P311">
+        <v>0</v>
+      </c>
+      <c r="Q311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A312">
+        <v>610</v>
+      </c>
+      <c r="B312">
+        <v>320</v>
+      </c>
+      <c r="C312">
+        <v>-3060</v>
+      </c>
+      <c r="D312">
+        <v>0</v>
+      </c>
+      <c r="E312">
+        <v>0</v>
+      </c>
+      <c r="F312">
+        <v>0</v>
+      </c>
+      <c r="G312">
+        <v>1</v>
+      </c>
+      <c r="H312">
+        <v>1</v>
+      </c>
+      <c r="I312">
+        <v>1</v>
+      </c>
+      <c r="J312">
+        <f t="shared" ref="J312:J317" si="161">G312*20</f>
+        <v>20</v>
+      </c>
+      <c r="K312">
+        <f t="shared" ref="K312:K317" si="162">H312*20</f>
+        <v>20</v>
+      </c>
+      <c r="L312">
+        <f t="shared" ref="L312:L317" si="163">I312*20</f>
+        <v>20</v>
+      </c>
+      <c r="M312">
+        <v>-1</v>
+      </c>
+      <c r="N312">
+        <v>0</v>
+      </c>
+      <c r="O312">
+        <v>0</v>
+      </c>
+      <c r="P312">
+        <v>0</v>
+      </c>
+      <c r="Q312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A313">
+        <v>690</v>
+      </c>
+      <c r="B313">
+        <v>320</v>
+      </c>
+      <c r="C313">
+        <v>-3000</v>
+      </c>
+      <c r="D313">
+        <v>0</v>
+      </c>
+      <c r="E313">
+        <v>0</v>
+      </c>
+      <c r="F313">
+        <v>0</v>
+      </c>
+      <c r="G313">
+        <v>1</v>
+      </c>
+      <c r="H313">
+        <v>1</v>
+      </c>
+      <c r="I313">
+        <v>1</v>
+      </c>
+      <c r="J313">
+        <f t="shared" si="161"/>
+        <v>20</v>
+      </c>
+      <c r="K313">
+        <f t="shared" si="162"/>
+        <v>20</v>
+      </c>
+      <c r="L313">
+        <f t="shared" si="163"/>
+        <v>20</v>
+      </c>
+      <c r="M313">
+        <v>-1</v>
+      </c>
+      <c r="N313">
+        <v>0</v>
+      </c>
+      <c r="O313">
+        <v>0</v>
+      </c>
+      <c r="P313">
+        <v>0</v>
+      </c>
+      <c r="Q313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A314">
+        <v>750</v>
+      </c>
+      <c r="B314">
+        <v>320</v>
+      </c>
+      <c r="C314">
+        <v>-3080</v>
+      </c>
+      <c r="D314">
+        <v>0</v>
+      </c>
+      <c r="E314">
+        <v>0</v>
+      </c>
+      <c r="F314">
+        <v>0</v>
+      </c>
+      <c r="G314">
+        <v>1</v>
+      </c>
+      <c r="H314">
+        <v>1</v>
+      </c>
+      <c r="I314">
+        <v>1</v>
+      </c>
+      <c r="J314">
+        <f t="shared" si="161"/>
+        <v>20</v>
+      </c>
+      <c r="K314">
+        <f t="shared" si="162"/>
+        <v>20</v>
+      </c>
+      <c r="L314">
+        <f t="shared" si="163"/>
+        <v>20</v>
+      </c>
+      <c r="M314">
+        <v>-1</v>
+      </c>
+      <c r="N314">
+        <v>0</v>
+      </c>
+      <c r="O314">
+        <v>0</v>
+      </c>
+      <c r="P314">
+        <v>0</v>
+      </c>
+      <c r="Q314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A315">
+        <v>810</v>
+      </c>
+      <c r="B315">
+        <v>320</v>
+      </c>
+      <c r="C315">
+        <v>-2960</v>
+      </c>
+      <c r="D315">
+        <v>0</v>
+      </c>
+      <c r="E315">
+        <v>0</v>
+      </c>
+      <c r="F315">
+        <v>0</v>
+      </c>
+      <c r="G315">
+        <v>1</v>
+      </c>
+      <c r="H315">
+        <v>1</v>
+      </c>
+      <c r="I315">
+        <v>1</v>
+      </c>
+      <c r="J315">
+        <f t="shared" si="161"/>
+        <v>20</v>
+      </c>
+      <c r="K315">
+        <f t="shared" si="162"/>
+        <v>20</v>
+      </c>
+      <c r="L315">
+        <f t="shared" si="163"/>
+        <v>20</v>
+      </c>
+      <c r="M315">
+        <v>-1</v>
+      </c>
+      <c r="N315">
+        <v>0</v>
+      </c>
+      <c r="O315">
+        <v>0</v>
+      </c>
+      <c r="P315">
+        <v>0</v>
+      </c>
+      <c r="Q315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A316">
+        <v>870</v>
+      </c>
+      <c r="B316">
+        <v>320</v>
+      </c>
+      <c r="C316">
+        <v>-3040</v>
+      </c>
+      <c r="D316">
+        <v>0</v>
+      </c>
+      <c r="E316">
+        <v>0</v>
+      </c>
+      <c r="F316">
+        <v>0</v>
+      </c>
+      <c r="G316">
+        <v>1</v>
+      </c>
+      <c r="H316">
+        <v>1</v>
+      </c>
+      <c r="I316">
+        <v>1</v>
+      </c>
+      <c r="J316">
+        <f t="shared" si="161"/>
+        <v>20</v>
+      </c>
+      <c r="K316">
+        <f t="shared" si="162"/>
+        <v>20</v>
+      </c>
+      <c r="L316">
+        <f t="shared" si="163"/>
+        <v>20</v>
+      </c>
+      <c r="M316">
+        <v>-1</v>
+      </c>
+      <c r="N316">
+        <v>0</v>
+      </c>
+      <c r="O316">
+        <v>0</v>
+      </c>
+      <c r="P316">
+        <v>0</v>
+      </c>
+      <c r="Q316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A317">
+        <v>930</v>
+      </c>
+      <c r="B317">
+        <v>320</v>
+      </c>
+      <c r="C317">
+        <v>-2980</v>
+      </c>
+      <c r="D317">
+        <v>0</v>
+      </c>
+      <c r="E317">
+        <v>0</v>
+      </c>
+      <c r="F317">
+        <v>0</v>
+      </c>
+      <c r="G317">
+        <v>1</v>
+      </c>
+      <c r="H317">
+        <v>1</v>
+      </c>
+      <c r="I317">
+        <v>1</v>
+      </c>
+      <c r="J317">
+        <f t="shared" si="161"/>
+        <v>20</v>
+      </c>
+      <c r="K317">
+        <f t="shared" si="162"/>
+        <v>20</v>
+      </c>
+      <c r="L317">
+        <f t="shared" si="163"/>
+        <v>20</v>
+      </c>
+      <c r="M317">
+        <v>-1</v>
+      </c>
+      <c r="N317">
+        <v>0</v>
+      </c>
+      <c r="O317">
+        <v>0</v>
+      </c>
+      <c r="P317">
+        <v>0</v>
+      </c>
+      <c r="Q317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A318">
+        <v>550</v>
+      </c>
+      <c r="B318">
+        <v>320</v>
+      </c>
+      <c r="C318">
+        <v>-2960</v>
+      </c>
+      <c r="D318">
+        <v>0</v>
+      </c>
+      <c r="E318">
+        <v>0</v>
+      </c>
+      <c r="F318">
+        <v>0</v>
+      </c>
+      <c r="G318">
+        <v>1</v>
+      </c>
+      <c r="H318">
+        <v>1</v>
+      </c>
+      <c r="I318">
+        <v>1</v>
+      </c>
+      <c r="J318">
+        <f t="shared" ref="J318:J328" si="164">G318*20</f>
+        <v>20</v>
+      </c>
+      <c r="K318">
+        <f t="shared" ref="K318:K328" si="165">H318*20</f>
+        <v>20</v>
+      </c>
+      <c r="L318">
+        <f t="shared" ref="L318:L328" si="166">I318*20</f>
+        <v>20</v>
+      </c>
+      <c r="M318">
+        <v>-1</v>
+      </c>
+      <c r="N318">
+        <v>0</v>
+      </c>
+      <c r="O318">
+        <v>0</v>
+      </c>
+      <c r="P318">
+        <v>0</v>
+      </c>
+      <c r="Q318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A319">
+        <v>590</v>
+      </c>
+      <c r="B319">
+        <v>320</v>
+      </c>
+      <c r="C319">
+        <v>-3020</v>
+      </c>
+      <c r="D319">
+        <v>0</v>
+      </c>
+      <c r="E319">
+        <v>0</v>
+      </c>
+      <c r="F319">
+        <v>0</v>
+      </c>
+      <c r="G319">
+        <v>1</v>
+      </c>
+      <c r="H319">
+        <v>1</v>
+      </c>
+      <c r="I319">
+        <v>1</v>
+      </c>
+      <c r="J319">
+        <f t="shared" si="164"/>
+        <v>20</v>
+      </c>
+      <c r="K319">
+        <f t="shared" si="165"/>
+        <v>20</v>
+      </c>
+      <c r="L319">
+        <f t="shared" si="166"/>
+        <v>20</v>
+      </c>
+      <c r="M319">
+        <v>-1</v>
+      </c>
+      <c r="N319">
+        <v>0</v>
+      </c>
+      <c r="O319">
+        <v>0</v>
+      </c>
+      <c r="P319">
+        <v>0</v>
+      </c>
+      <c r="Q319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A320">
+        <v>650</v>
+      </c>
+      <c r="B320">
+        <v>320</v>
+      </c>
+      <c r="C320">
+        <v>-3080</v>
+      </c>
+      <c r="D320">
+        <v>0</v>
+      </c>
+      <c r="E320">
+        <v>0</v>
+      </c>
+      <c r="F320">
+        <v>0</v>
+      </c>
+      <c r="G320">
+        <v>1</v>
+      </c>
+      <c r="H320">
+        <v>1</v>
+      </c>
+      <c r="I320">
+        <v>1</v>
+      </c>
+      <c r="J320">
+        <f t="shared" si="164"/>
+        <v>20</v>
+      </c>
+      <c r="K320">
+        <f t="shared" si="165"/>
+        <v>20</v>
+      </c>
+      <c r="L320">
+        <f t="shared" si="166"/>
+        <v>20</v>
+      </c>
+      <c r="M320">
+        <v>-1</v>
+      </c>
+      <c r="N320">
+        <v>0</v>
+      </c>
+      <c r="O320">
+        <v>0</v>
+      </c>
+      <c r="P320">
+        <v>0</v>
+      </c>
+      <c r="Q320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A321">
+        <v>670</v>
+      </c>
+      <c r="B321">
+        <v>320</v>
+      </c>
+      <c r="C321">
+        <v>-2980</v>
+      </c>
+      <c r="D321">
+        <v>0</v>
+      </c>
+      <c r="E321">
+        <v>0</v>
+      </c>
+      <c r="F321">
+        <v>0</v>
+      </c>
+      <c r="G321">
+        <v>1</v>
+      </c>
+      <c r="H321">
+        <v>1</v>
+      </c>
+      <c r="I321">
+        <v>1</v>
+      </c>
+      <c r="J321">
+        <f t="shared" si="164"/>
+        <v>20</v>
+      </c>
+      <c r="K321">
+        <f t="shared" si="165"/>
+        <v>20</v>
+      </c>
+      <c r="L321">
+        <f t="shared" si="166"/>
+        <v>20</v>
+      </c>
+      <c r="M321">
+        <v>-1</v>
+      </c>
+      <c r="N321">
+        <v>0</v>
+      </c>
+      <c r="O321">
+        <v>0</v>
+      </c>
+      <c r="P321">
+        <v>0</v>
+      </c>
+      <c r="Q321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A322">
+        <v>710</v>
+      </c>
+      <c r="B322">
+        <v>320</v>
+      </c>
+      <c r="C322">
+        <v>-3060</v>
+      </c>
+      <c r="D322">
+        <v>0</v>
+      </c>
+      <c r="E322">
+        <v>0</v>
+      </c>
+      <c r="F322">
+        <v>0</v>
+      </c>
+      <c r="G322">
+        <v>1</v>
+      </c>
+      <c r="H322">
+        <v>1</v>
+      </c>
+      <c r="I322">
+        <v>1</v>
+      </c>
+      <c r="J322">
+        <f t="shared" si="164"/>
+        <v>20</v>
+      </c>
+      <c r="K322">
+        <f t="shared" si="165"/>
+        <v>20</v>
+      </c>
+      <c r="L322">
+        <f t="shared" si="166"/>
+        <v>20</v>
+      </c>
+      <c r="M322">
+        <v>-1</v>
+      </c>
+      <c r="N322">
+        <v>0</v>
+      </c>
+      <c r="O322">
+        <v>0</v>
+      </c>
+      <c r="P322">
+        <v>0</v>
+      </c>
+      <c r="Q322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A323">
+        <v>770</v>
+      </c>
+      <c r="B323">
+        <v>320</v>
+      </c>
+      <c r="C323">
+        <v>-3000</v>
+      </c>
+      <c r="D323">
+        <v>0</v>
+      </c>
+      <c r="E323">
+        <v>0</v>
+      </c>
+      <c r="F323">
+        <v>0</v>
+      </c>
+      <c r="G323">
+        <v>1</v>
+      </c>
+      <c r="H323">
+        <v>1</v>
+      </c>
+      <c r="I323">
+        <v>1</v>
+      </c>
+      <c r="J323">
+        <f t="shared" si="164"/>
+        <v>20</v>
+      </c>
+      <c r="K323">
+        <f t="shared" si="165"/>
+        <v>20</v>
+      </c>
+      <c r="L323">
+        <f t="shared" si="166"/>
+        <v>20</v>
+      </c>
+      <c r="M323">
+        <v>-1</v>
+      </c>
+      <c r="N323">
+        <v>0</v>
+      </c>
+      <c r="O323">
+        <v>0</v>
+      </c>
+      <c r="P323">
+        <v>0</v>
+      </c>
+      <c r="Q323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A324">
+        <v>790</v>
+      </c>
+      <c r="B324">
+        <v>320</v>
+      </c>
+      <c r="C324">
+        <v>-3100</v>
+      </c>
+      <c r="D324">
+        <v>0</v>
+      </c>
+      <c r="E324">
+        <v>0</v>
+      </c>
+      <c r="F324">
+        <v>0</v>
+      </c>
+      <c r="G324">
+        <v>1</v>
+      </c>
+      <c r="H324">
+        <v>1</v>
+      </c>
+      <c r="I324">
+        <v>1</v>
+      </c>
+      <c r="J324">
+        <f t="shared" si="164"/>
+        <v>20</v>
+      </c>
+      <c r="K324">
+        <f t="shared" si="165"/>
+        <v>20</v>
+      </c>
+      <c r="L324">
+        <f t="shared" si="166"/>
+        <v>20</v>
+      </c>
+      <c r="M324">
+        <v>-1</v>
+      </c>
+      <c r="N324">
+        <v>0</v>
+      </c>
+      <c r="O324">
+        <v>0</v>
+      </c>
+      <c r="P324">
+        <v>0</v>
+      </c>
+      <c r="Q324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A325">
+        <v>830</v>
+      </c>
+      <c r="B325">
+        <v>320</v>
+      </c>
+      <c r="C325">
+        <v>-3020</v>
+      </c>
+      <c r="D325">
+        <v>0</v>
+      </c>
+      <c r="E325">
+        <v>0</v>
+      </c>
+      <c r="F325">
+        <v>0</v>
+      </c>
+      <c r="G325">
+        <v>1</v>
+      </c>
+      <c r="H325">
+        <v>1</v>
+      </c>
+      <c r="I325">
+        <v>1</v>
+      </c>
+      <c r="J325">
+        <f t="shared" si="164"/>
+        <v>20</v>
+      </c>
+      <c r="K325">
+        <f t="shared" si="165"/>
+        <v>20</v>
+      </c>
+      <c r="L325">
+        <f t="shared" si="166"/>
+        <v>20</v>
+      </c>
+      <c r="M325">
+        <v>-1</v>
+      </c>
+      <c r="N325">
+        <v>0</v>
+      </c>
+      <c r="O325">
+        <v>0</v>
+      </c>
+      <c r="P325">
+        <v>0</v>
+      </c>
+      <c r="Q325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A326">
+        <v>850</v>
+      </c>
+      <c r="B326">
+        <v>320</v>
+      </c>
+      <c r="C326">
+        <v>-3080</v>
+      </c>
+      <c r="D326">
+        <v>0</v>
+      </c>
+      <c r="E326">
+        <v>0</v>
+      </c>
+      <c r="F326">
+        <v>0</v>
+      </c>
+      <c r="G326">
+        <v>1</v>
+      </c>
+      <c r="H326">
+        <v>1</v>
+      </c>
+      <c r="I326">
+        <v>1</v>
+      </c>
+      <c r="J326">
+        <f t="shared" si="164"/>
+        <v>20</v>
+      </c>
+      <c r="K326">
+        <f t="shared" si="165"/>
+        <v>20</v>
+      </c>
+      <c r="L326">
+        <f t="shared" si="166"/>
+        <v>20</v>
+      </c>
+      <c r="M326">
+        <v>-1</v>
+      </c>
+      <c r="N326">
+        <v>0</v>
+      </c>
+      <c r="O326">
+        <v>0</v>
+      </c>
+      <c r="P326">
+        <v>0</v>
+      </c>
+      <c r="Q326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A327">
+        <v>910</v>
+      </c>
+      <c r="B327">
+        <v>320</v>
+      </c>
+      <c r="C327">
+        <v>-3000</v>
+      </c>
+      <c r="D327">
+        <v>0</v>
+      </c>
+      <c r="E327">
+        <v>0</v>
+      </c>
+      <c r="F327">
+        <v>0</v>
+      </c>
+      <c r="G327">
+        <v>1</v>
+      </c>
+      <c r="H327">
+        <v>1</v>
+      </c>
+      <c r="I327">
+        <v>1</v>
+      </c>
+      <c r="J327">
+        <f t="shared" si="164"/>
+        <v>20</v>
+      </c>
+      <c r="K327">
+        <f t="shared" si="165"/>
+        <v>20</v>
+      </c>
+      <c r="L327">
+        <f t="shared" si="166"/>
+        <v>20</v>
+      </c>
+      <c r="M327">
+        <v>-1</v>
+      </c>
+      <c r="N327">
+        <v>0</v>
+      </c>
+      <c r="O327">
+        <v>0</v>
+      </c>
+      <c r="P327">
+        <v>0</v>
+      </c>
+      <c r="Q327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A328">
+        <v>950</v>
+      </c>
+      <c r="B328">
+        <v>320</v>
+      </c>
+      <c r="C328">
+        <v>-3060</v>
+      </c>
+      <c r="D328">
+        <v>0</v>
+      </c>
+      <c r="E328">
+        <v>0</v>
+      </c>
+      <c r="F328">
+        <v>0</v>
+      </c>
+      <c r="G328">
+        <v>1</v>
+      </c>
+      <c r="H328">
+        <v>1</v>
+      </c>
+      <c r="I328">
+        <v>1</v>
+      </c>
+      <c r="J328">
+        <f t="shared" si="164"/>
+        <v>20</v>
+      </c>
+      <c r="K328">
+        <f t="shared" si="165"/>
+        <v>20</v>
+      </c>
+      <c r="L328">
+        <f t="shared" si="166"/>
+        <v>20</v>
+      </c>
+      <c r="M328">
+        <v>-1</v>
+      </c>
+      <c r="N328">
+        <v>0</v>
+      </c>
+      <c r="O328">
+        <v>0</v>
+      </c>
+      <c r="P328">
+        <v>0</v>
+      </c>
+      <c r="Q328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A329">
+        <v>550</v>
+      </c>
+      <c r="B329">
+        <v>320</v>
+      </c>
+      <c r="C329">
+        <v>-3000</v>
+      </c>
+      <c r="D329">
+        <v>0</v>
+      </c>
+      <c r="E329">
+        <v>0</v>
+      </c>
+      <c r="F329">
+        <v>0</v>
+      </c>
+      <c r="G329">
+        <v>1</v>
+      </c>
+      <c r="H329">
+        <v>1</v>
+      </c>
+      <c r="I329">
+        <v>1</v>
+      </c>
+      <c r="J329">
+        <f t="shared" ref="J329:J335" si="167">G329*20</f>
+        <v>20</v>
+      </c>
+      <c r="K329">
+        <f t="shared" ref="K329:K335" si="168">H329*20</f>
+        <v>20</v>
+      </c>
+      <c r="L329">
+        <f t="shared" ref="L329:L335" si="169">I329*20</f>
+        <v>20</v>
+      </c>
+      <c r="M329">
+        <v>-1</v>
+      </c>
+      <c r="N329">
+        <v>0</v>
+      </c>
+      <c r="O329">
+        <v>0</v>
+      </c>
+      <c r="P329">
+        <v>0</v>
+      </c>
+      <c r="Q329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A330">
+        <v>570</v>
+      </c>
+      <c r="B330">
+        <v>320</v>
+      </c>
+      <c r="C330">
+        <v>-3080</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+      <c r="E330">
+        <v>0</v>
+      </c>
+      <c r="F330">
+        <v>0</v>
+      </c>
+      <c r="G330">
+        <v>1</v>
+      </c>
+      <c r="H330">
+        <v>1</v>
+      </c>
+      <c r="I330">
+        <v>1</v>
+      </c>
+      <c r="J330">
+        <f t="shared" si="167"/>
+        <v>20</v>
+      </c>
+      <c r="K330">
+        <f t="shared" si="168"/>
+        <v>20</v>
+      </c>
+      <c r="L330">
+        <f t="shared" si="169"/>
+        <v>20</v>
+      </c>
+      <c r="M330">
+        <v>-1</v>
+      </c>
+      <c r="N330">
+        <v>0</v>
+      </c>
+      <c r="O330">
+        <v>0</v>
+      </c>
+      <c r="P330">
+        <v>0</v>
+      </c>
+      <c r="Q330">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A331">
+        <v>630</v>
+      </c>
+      <c r="B331">
+        <v>320</v>
+      </c>
+      <c r="C331">
+        <v>-2960</v>
+      </c>
+      <c r="D331">
+        <v>0</v>
+      </c>
+      <c r="E331">
+        <v>0</v>
+      </c>
+      <c r="F331">
+        <v>0</v>
+      </c>
+      <c r="G331">
+        <v>1</v>
+      </c>
+      <c r="H331">
+        <v>1</v>
+      </c>
+      <c r="I331">
+        <v>1</v>
+      </c>
+      <c r="J331">
+        <f t="shared" si="167"/>
+        <v>20</v>
+      </c>
+      <c r="K331">
+        <f t="shared" si="168"/>
+        <v>20</v>
+      </c>
+      <c r="L331">
+        <f t="shared" si="169"/>
+        <v>20</v>
+      </c>
+      <c r="M331">
+        <v>-1</v>
+      </c>
+      <c r="N331">
+        <v>0</v>
+      </c>
+      <c r="O331">
+        <v>0</v>
+      </c>
+      <c r="P331">
+        <v>0</v>
+      </c>
+      <c r="Q331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A332">
+        <v>690</v>
+      </c>
+      <c r="B332">
+        <v>320</v>
+      </c>
+      <c r="C332">
+        <v>-3040</v>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+      <c r="E332">
+        <v>0</v>
+      </c>
+      <c r="F332">
+        <v>0</v>
+      </c>
+      <c r="G332">
+        <v>1</v>
+      </c>
+      <c r="H332">
+        <v>1</v>
+      </c>
+      <c r="I332">
+        <v>1</v>
+      </c>
+      <c r="J332">
+        <f t="shared" si="167"/>
+        <v>20</v>
+      </c>
+      <c r="K332">
+        <f t="shared" si="168"/>
+        <v>20</v>
+      </c>
+      <c r="L332">
+        <f t="shared" si="169"/>
+        <v>20</v>
+      </c>
+      <c r="M332">
+        <v>-1</v>
+      </c>
+      <c r="N332">
+        <v>0</v>
+      </c>
+      <c r="O332">
+        <v>0</v>
+      </c>
+      <c r="P332">
+        <v>0</v>
+      </c>
+      <c r="Q332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A333">
+        <v>750</v>
+      </c>
+      <c r="B333">
+        <v>320</v>
+      </c>
+      <c r="C333">
+        <v>-3100</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+      <c r="E333">
+        <v>0</v>
+      </c>
+      <c r="F333">
+        <v>0</v>
+      </c>
+      <c r="G333">
+        <v>1</v>
+      </c>
+      <c r="H333">
+        <v>1</v>
+      </c>
+      <c r="I333">
+        <v>1</v>
+      </c>
+      <c r="J333">
+        <f t="shared" si="167"/>
+        <v>20</v>
+      </c>
+      <c r="K333">
+        <f t="shared" si="168"/>
+        <v>20</v>
+      </c>
+      <c r="L333">
+        <f t="shared" si="169"/>
+        <v>20</v>
+      </c>
+      <c r="M333">
+        <v>-1</v>
+      </c>
+      <c r="N333">
+        <v>0</v>
+      </c>
+      <c r="O333">
+        <v>0</v>
+      </c>
+      <c r="P333">
+        <v>0</v>
+      </c>
+      <c r="Q333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A334">
+        <v>850</v>
+      </c>
+      <c r="B334">
+        <v>320</v>
+      </c>
+      <c r="C334">
+        <v>-2980</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+      <c r="E334">
+        <v>0</v>
+      </c>
+      <c r="F334">
+        <v>0</v>
+      </c>
+      <c r="G334">
+        <v>1</v>
+      </c>
+      <c r="H334">
+        <v>1</v>
+      </c>
+      <c r="I334">
+        <v>1</v>
+      </c>
+      <c r="J334">
+        <f t="shared" si="167"/>
+        <v>20</v>
+      </c>
+      <c r="K334">
+        <f t="shared" si="168"/>
+        <v>20</v>
+      </c>
+      <c r="L334">
+        <f t="shared" si="169"/>
+        <v>20</v>
+      </c>
+      <c r="M334">
+        <v>-1</v>
+      </c>
+      <c r="N334">
+        <v>0</v>
+      </c>
+      <c r="O334">
+        <v>0</v>
+      </c>
+      <c r="P334">
+        <v>0</v>
+      </c>
+      <c r="Q334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A335">
+        <v>910</v>
+      </c>
+      <c r="B335">
+        <v>320</v>
+      </c>
+      <c r="C335">
+        <v>-3040</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>0</v>
+      </c>
+      <c r="F335">
+        <v>0</v>
+      </c>
+      <c r="G335">
+        <v>1</v>
+      </c>
+      <c r="H335">
+        <v>1</v>
+      </c>
+      <c r="I335">
+        <v>1</v>
+      </c>
+      <c r="J335">
+        <f t="shared" si="167"/>
+        <v>20</v>
+      </c>
+      <c r="K335">
+        <f t="shared" si="168"/>
+        <v>20</v>
+      </c>
+      <c r="L335">
+        <f t="shared" si="169"/>
+        <v>20</v>
+      </c>
+      <c r="M335">
+        <v>-1</v>
+      </c>
+      <c r="N335">
+        <v>0</v>
+      </c>
+      <c r="O335">
+        <v>0</v>
+      </c>
+      <c r="P335">
+        <v>0</v>
+      </c>
+      <c r="Q335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A336">
+        <v>990</v>
+      </c>
+      <c r="B336">
+        <v>320</v>
+      </c>
+      <c r="C336">
+        <v>-3040</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>0</v>
+      </c>
+      <c r="F336">
+        <v>0</v>
+      </c>
+      <c r="G336">
+        <v>1</v>
+      </c>
+      <c r="H336">
+        <v>1</v>
+      </c>
+      <c r="I336">
+        <v>1</v>
+      </c>
+      <c r="J336">
+        <f t="shared" ref="J336:J340" si="170">G336*20</f>
+        <v>20</v>
+      </c>
+      <c r="K336">
+        <f t="shared" ref="K336:K340" si="171">H336*20</f>
+        <v>20</v>
+      </c>
+      <c r="L336">
+        <f t="shared" ref="L336:L340" si="172">I336*20</f>
+        <v>20</v>
+      </c>
+      <c r="M336">
+        <v>-1</v>
+      </c>
+      <c r="N336">
+        <v>0</v>
+      </c>
+      <c r="O336">
+        <v>0</v>
+      </c>
+      <c r="P336">
+        <v>0</v>
+      </c>
+      <c r="Q336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A337">
+        <v>970</v>
+      </c>
+      <c r="B337">
+        <v>320</v>
+      </c>
+      <c r="C337">
+        <v>-3000</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>0</v>
+      </c>
+      <c r="F337">
+        <v>0</v>
+      </c>
+      <c r="G337">
+        <v>1</v>
+      </c>
+      <c r="H337">
+        <v>1</v>
+      </c>
+      <c r="I337">
+        <v>1</v>
+      </c>
+      <c r="J337">
+        <f t="shared" si="170"/>
+        <v>20</v>
+      </c>
+      <c r="K337">
+        <f t="shared" si="171"/>
+        <v>20</v>
+      </c>
+      <c r="L337">
+        <f t="shared" si="172"/>
+        <v>20</v>
+      </c>
+      <c r="M337">
+        <v>-1</v>
+      </c>
+      <c r="N337">
+        <v>0</v>
+      </c>
+      <c r="O337">
+        <v>0</v>
+      </c>
+      <c r="P337">
+        <v>0</v>
+      </c>
+      <c r="Q337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A338">
+        <v>990</v>
+      </c>
+      <c r="B338">
+        <v>320</v>
+      </c>
+      <c r="C338">
+        <v>-3060</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>0</v>
+      </c>
+      <c r="F338">
+        <v>0</v>
+      </c>
+      <c r="G338">
+        <v>1</v>
+      </c>
+      <c r="H338">
+        <v>1</v>
+      </c>
+      <c r="I338">
+        <v>1</v>
+      </c>
+      <c r="J338">
+        <f t="shared" si="170"/>
+        <v>20</v>
+      </c>
+      <c r="K338">
+        <f t="shared" si="171"/>
+        <v>20</v>
+      </c>
+      <c r="L338">
+        <f t="shared" si="172"/>
+        <v>20</v>
+      </c>
+      <c r="M338">
+        <v>-1</v>
+      </c>
+      <c r="N338">
+        <v>0</v>
+      </c>
+      <c r="O338">
+        <v>0</v>
+      </c>
+      <c r="P338">
+        <v>0</v>
+      </c>
+      <c r="Q338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A339">
+        <v>1010</v>
+      </c>
+      <c r="B339">
+        <v>320</v>
+      </c>
+      <c r="C339">
+        <v>-3020</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>0</v>
+      </c>
+      <c r="F339">
+        <v>0</v>
+      </c>
+      <c r="G339">
+        <v>1</v>
+      </c>
+      <c r="H339">
+        <v>1</v>
+      </c>
+      <c r="I339">
+        <v>1</v>
+      </c>
+      <c r="J339">
+        <f t="shared" si="170"/>
+        <v>20</v>
+      </c>
+      <c r="K339">
+        <f t="shared" si="171"/>
+        <v>20</v>
+      </c>
+      <c r="L339">
+        <f t="shared" si="172"/>
+        <v>20</v>
+      </c>
+      <c r="M339">
+        <v>-1</v>
+      </c>
+      <c r="N339">
+        <v>0</v>
+      </c>
+      <c r="O339">
+        <v>0</v>
+      </c>
+      <c r="P339">
+        <v>0</v>
+      </c>
+      <c r="Q339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A340">
+        <v>970</v>
+      </c>
+      <c r="B340">
+        <v>320</v>
+      </c>
+      <c r="C340">
+        <v>-3040</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>0</v>
+      </c>
+      <c r="F340">
+        <v>0</v>
+      </c>
+      <c r="G340">
+        <v>1</v>
+      </c>
+      <c r="H340">
+        <v>1</v>
+      </c>
+      <c r="I340">
+        <v>1</v>
+      </c>
+      <c r="J340">
+        <f t="shared" si="170"/>
+        <v>20</v>
+      </c>
+      <c r="K340">
+        <f t="shared" si="171"/>
+        <v>20</v>
+      </c>
+      <c r="L340">
+        <f t="shared" si="172"/>
+        <v>20</v>
+      </c>
+      <c r="M340">
+        <v>-1</v>
+      </c>
+      <c r="N340">
+        <v>0</v>
+      </c>
+      <c r="O340">
+        <v>0</v>
+      </c>
+      <c r="P340">
+        <v>0</v>
+      </c>
+      <c r="Q340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A341">
+        <v>1070</v>
+      </c>
+      <c r="B341">
+        <v>200</v>
+      </c>
+      <c r="C341">
+        <v>-2960</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>0</v>
+      </c>
+      <c r="F341">
+        <v>0</v>
+      </c>
+      <c r="G341">
+        <v>1</v>
+      </c>
+      <c r="H341">
+        <v>1</v>
+      </c>
+      <c r="I341">
+        <v>1</v>
+      </c>
+      <c r="J341">
+        <f t="shared" ref="J341:J344" si="173">G341*20</f>
+        <v>20</v>
+      </c>
+      <c r="K341">
+        <f t="shared" ref="K341:K344" si="174">H341*20</f>
+        <v>20</v>
+      </c>
+      <c r="L341">
+        <f t="shared" ref="L341:L344" si="175">I341*20</f>
+        <v>20</v>
+      </c>
+      <c r="M341">
+        <v>-1</v>
+      </c>
+      <c r="N341">
+        <v>0</v>
+      </c>
+      <c r="O341">
+        <v>0</v>
+      </c>
+      <c r="P341">
+        <v>0</v>
+      </c>
+      <c r="Q341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A342">
+        <v>1170</v>
+      </c>
+      <c r="B342">
+        <v>200</v>
+      </c>
+      <c r="C342">
+        <v>-3000</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>0</v>
+      </c>
+      <c r="F342">
+        <v>0</v>
+      </c>
+      <c r="G342">
+        <v>1</v>
+      </c>
+      <c r="H342">
+        <v>1</v>
+      </c>
+      <c r="I342">
+        <v>1</v>
+      </c>
+      <c r="J342">
+        <f t="shared" si="173"/>
+        <v>20</v>
+      </c>
+      <c r="K342">
+        <f t="shared" si="174"/>
+        <v>20</v>
+      </c>
+      <c r="L342">
+        <f t="shared" si="175"/>
+        <v>20</v>
+      </c>
+      <c r="M342">
+        <v>-1</v>
+      </c>
+      <c r="N342">
+        <v>0</v>
+      </c>
+      <c r="O342">
+        <v>0</v>
+      </c>
+      <c r="P342">
+        <v>0</v>
+      </c>
+      <c r="Q342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A343">
+        <v>1110</v>
+      </c>
+      <c r="B343">
+        <v>200</v>
+      </c>
+      <c r="C343">
+        <v>-3060</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>0</v>
+      </c>
+      <c r="F343">
+        <v>0</v>
+      </c>
+      <c r="G343">
+        <v>1</v>
+      </c>
+      <c r="H343">
+        <v>1</v>
+      </c>
+      <c r="I343">
+        <v>1</v>
+      </c>
+      <c r="J343">
+        <f t="shared" si="173"/>
+        <v>20</v>
+      </c>
+      <c r="K343">
+        <f t="shared" si="174"/>
+        <v>20</v>
+      </c>
+      <c r="L343">
+        <f t="shared" si="175"/>
+        <v>20</v>
+      </c>
+      <c r="M343">
+        <v>-1</v>
+      </c>
+      <c r="N343">
+        <v>0</v>
+      </c>
+      <c r="O343">
+        <v>0</v>
+      </c>
+      <c r="P343">
+        <v>0</v>
+      </c>
+      <c r="Q343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A344">
+        <v>1190</v>
+      </c>
+      <c r="B344">
+        <v>200</v>
+      </c>
+      <c r="C344">
+        <v>-3100</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>0</v>
+      </c>
+      <c r="F344">
+        <v>0</v>
+      </c>
+      <c r="G344">
+        <v>1</v>
+      </c>
+      <c r="H344">
+        <v>1</v>
+      </c>
+      <c r="I344">
+        <v>1</v>
+      </c>
+      <c r="J344">
+        <f t="shared" si="173"/>
+        <v>20</v>
+      </c>
+      <c r="K344">
+        <f t="shared" si="174"/>
+        <v>20</v>
+      </c>
+      <c r="L344">
+        <f t="shared" si="175"/>
+        <v>20</v>
+      </c>
+      <c r="M344">
+        <v>-1</v>
+      </c>
+      <c r="N344">
+        <v>0</v>
+      </c>
+      <c r="O344">
+        <v>0</v>
+      </c>
+      <c r="P344">
+        <v>0</v>
+      </c>
+      <c r="Q344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A345">
+        <v>1030</v>
+      </c>
+      <c r="B345">
+        <v>200</v>
+      </c>
+      <c r="C345">
+        <v>-2980</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>0</v>
+      </c>
+      <c r="F345">
+        <v>0</v>
+      </c>
+      <c r="G345">
+        <v>1</v>
+      </c>
+      <c r="H345">
+        <v>1</v>
+      </c>
+      <c r="I345">
+        <v>1</v>
+      </c>
+      <c r="J345">
+        <f t="shared" ref="J345:J351" si="176">G345*20</f>
+        <v>20</v>
+      </c>
+      <c r="K345">
+        <f t="shared" ref="K345:K351" si="177">H345*20</f>
+        <v>20</v>
+      </c>
+      <c r="L345">
+        <f t="shared" ref="L345:L351" si="178">I345*20</f>
+        <v>20</v>
+      </c>
+      <c r="M345">
+        <v>-1</v>
+      </c>
+      <c r="N345">
+        <v>0</v>
+      </c>
+      <c r="O345">
+        <v>0</v>
+      </c>
+      <c r="P345">
+        <v>0</v>
+      </c>
+      <c r="Q345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A346">
+        <v>1130</v>
+      </c>
+      <c r="B346">
+        <v>200</v>
+      </c>
+      <c r="C346">
+        <v>-2940</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>0</v>
+      </c>
+      <c r="F346">
+        <v>0</v>
+      </c>
+      <c r="G346">
+        <v>1</v>
+      </c>
+      <c r="H346">
+        <v>1</v>
+      </c>
+      <c r="I346">
+        <v>1</v>
+      </c>
+      <c r="J346">
+        <f t="shared" si="176"/>
+        <v>20</v>
+      </c>
+      <c r="K346">
+        <f t="shared" si="177"/>
+        <v>20</v>
+      </c>
+      <c r="L346">
+        <f t="shared" si="178"/>
+        <v>20</v>
+      </c>
+      <c r="M346">
+        <v>-1</v>
+      </c>
+      <c r="N346">
+        <v>0</v>
+      </c>
+      <c r="O346">
+        <v>0</v>
+      </c>
+      <c r="P346">
+        <v>0</v>
+      </c>
+      <c r="Q346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A347">
+        <v>1210</v>
+      </c>
+      <c r="B347">
+        <v>200</v>
+      </c>
+      <c r="C347">
+        <v>-2960</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>0</v>
+      </c>
+      <c r="F347">
+        <v>0</v>
+      </c>
+      <c r="G347">
+        <v>1</v>
+      </c>
+      <c r="H347">
+        <v>1</v>
+      </c>
+      <c r="I347">
+        <v>1</v>
+      </c>
+      <c r="J347">
+        <f t="shared" si="176"/>
+        <v>20</v>
+      </c>
+      <c r="K347">
+        <f t="shared" si="177"/>
+        <v>20</v>
+      </c>
+      <c r="L347">
+        <f t="shared" si="178"/>
+        <v>20</v>
+      </c>
+      <c r="M347">
+        <v>-1</v>
+      </c>
+      <c r="N347">
+        <v>0</v>
+      </c>
+      <c r="O347">
+        <v>0</v>
+      </c>
+      <c r="P347">
+        <v>0</v>
+      </c>
+      <c r="Q347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A348">
+        <v>1050</v>
+      </c>
+      <c r="B348">
+        <v>200</v>
+      </c>
+      <c r="C348">
+        <v>-3040</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>0</v>
+      </c>
+      <c r="F348">
+        <v>0</v>
+      </c>
+      <c r="G348">
+        <v>1</v>
+      </c>
+      <c r="H348">
+        <v>1</v>
+      </c>
+      <c r="I348">
+        <v>1</v>
+      </c>
+      <c r="J348">
+        <f t="shared" si="176"/>
+        <v>20</v>
+      </c>
+      <c r="K348">
+        <f t="shared" si="177"/>
+        <v>20</v>
+      </c>
+      <c r="L348">
+        <f t="shared" si="178"/>
+        <v>20</v>
+      </c>
+      <c r="M348">
+        <v>-1</v>
+      </c>
+      <c r="N348">
+        <v>0</v>
+      </c>
+      <c r="O348">
+        <v>0</v>
+      </c>
+      <c r="P348">
+        <v>0</v>
+      </c>
+      <c r="Q348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A349">
+        <v>1150</v>
+      </c>
+      <c r="B349">
+        <v>200</v>
+      </c>
+      <c r="C349">
+        <v>-3020</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>0</v>
+      </c>
+      <c r="F349">
+        <v>0</v>
+      </c>
+      <c r="G349">
+        <v>1</v>
+      </c>
+      <c r="H349">
+        <v>1</v>
+      </c>
+      <c r="I349">
+        <v>1</v>
+      </c>
+      <c r="J349">
+        <f t="shared" si="176"/>
+        <v>20</v>
+      </c>
+      <c r="K349">
+        <f t="shared" si="177"/>
+        <v>20</v>
+      </c>
+      <c r="L349">
+        <f t="shared" si="178"/>
+        <v>20</v>
+      </c>
+      <c r="M349">
+        <v>-1</v>
+      </c>
+      <c r="N349">
+        <v>0</v>
+      </c>
+      <c r="O349">
+        <v>0</v>
+      </c>
+      <c r="P349">
+        <v>0</v>
+      </c>
+      <c r="Q349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A350">
+        <v>1030</v>
+      </c>
+      <c r="B350">
+        <v>200</v>
+      </c>
+      <c r="C350">
+        <v>-3100</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>0</v>
+      </c>
+      <c r="F350">
+        <v>0</v>
+      </c>
+      <c r="G350">
+        <v>1</v>
+      </c>
+      <c r="H350">
+        <v>1</v>
+      </c>
+      <c r="I350">
+        <v>1</v>
+      </c>
+      <c r="J350">
+        <f t="shared" si="176"/>
+        <v>20</v>
+      </c>
+      <c r="K350">
+        <f t="shared" si="177"/>
+        <v>20</v>
+      </c>
+      <c r="L350">
+        <f t="shared" si="178"/>
+        <v>20</v>
+      </c>
+      <c r="M350">
+        <v>-1</v>
+      </c>
+      <c r="N350">
+        <v>0</v>
+      </c>
+      <c r="O350">
+        <v>0</v>
+      </c>
+      <c r="P350">
+        <v>0</v>
+      </c>
+      <c r="Q350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A351">
+        <v>1170</v>
+      </c>
+      <c r="B351">
+        <v>200</v>
+      </c>
+      <c r="C351">
+        <v>-3120</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>0</v>
+      </c>
+      <c r="F351">
+        <v>0</v>
+      </c>
+      <c r="G351">
+        <v>1</v>
+      </c>
+      <c r="H351">
+        <v>1</v>
+      </c>
+      <c r="I351">
+        <v>1</v>
+      </c>
+      <c r="J351">
+        <f t="shared" si="176"/>
+        <v>20</v>
+      </c>
+      <c r="K351">
+        <f t="shared" si="177"/>
+        <v>20</v>
+      </c>
+      <c r="L351">
+        <f t="shared" si="178"/>
+        <v>20</v>
+      </c>
+      <c r="M351">
+        <v>-1</v>
+      </c>
+      <c r="N351">
+        <v>0</v>
+      </c>
+      <c r="O351">
+        <v>0</v>
+      </c>
+      <c r="P351">
+        <v>0</v>
+      </c>
+      <c r="Q351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A352">
+        <v>1090</v>
+      </c>
+      <c r="B352">
+        <v>200</v>
+      </c>
+      <c r="C352">
+        <v>-2940</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>0</v>
+      </c>
+      <c r="F352">
+        <v>0</v>
+      </c>
+      <c r="G352">
+        <v>1</v>
+      </c>
+      <c r="H352">
+        <v>1</v>
+      </c>
+      <c r="I352">
+        <v>1</v>
+      </c>
+      <c r="J352">
+        <f t="shared" ref="J352:J356" si="179">G352*20</f>
+        <v>20</v>
+      </c>
+      <c r="K352">
+        <f t="shared" ref="K352:K356" si="180">H352*20</f>
+        <v>20</v>
+      </c>
+      <c r="L352">
+        <f t="shared" ref="L352:L356" si="181">I352*20</f>
+        <v>20</v>
+      </c>
+      <c r="M352">
+        <v>-1</v>
+      </c>
+      <c r="N352">
+        <v>0</v>
+      </c>
+      <c r="O352">
+        <v>0</v>
+      </c>
+      <c r="P352">
+        <v>0</v>
+      </c>
+      <c r="Q352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A353">
+        <v>1210</v>
+      </c>
+      <c r="B353">
+        <v>200</v>
+      </c>
+      <c r="C353">
+        <v>-3020</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>0</v>
+      </c>
+      <c r="F353">
+        <v>0</v>
+      </c>
+      <c r="G353">
+        <v>1</v>
+      </c>
+      <c r="H353">
+        <v>1</v>
+      </c>
+      <c r="I353">
+        <v>1</v>
+      </c>
+      <c r="J353">
+        <f t="shared" si="179"/>
+        <v>20</v>
+      </c>
+      <c r="K353">
+        <f t="shared" si="180"/>
+        <v>20</v>
+      </c>
+      <c r="L353">
+        <f t="shared" si="181"/>
+        <v>20</v>
+      </c>
+      <c r="M353">
+        <v>-1</v>
+      </c>
+      <c r="N353">
+        <v>0</v>
+      </c>
+      <c r="O353">
+        <v>0</v>
+      </c>
+      <c r="P353">
+        <v>0</v>
+      </c>
+      <c r="Q353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A354">
+        <v>1070</v>
+      </c>
+      <c r="B354">
+        <v>200</v>
+      </c>
+      <c r="C354">
+        <v>-3080</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>0</v>
+      </c>
+      <c r="F354">
+        <v>0</v>
+      </c>
+      <c r="G354">
+        <v>1</v>
+      </c>
+      <c r="H354">
+        <v>1</v>
+      </c>
+      <c r="I354">
+        <v>1</v>
+      </c>
+      <c r="J354">
+        <f t="shared" si="179"/>
+        <v>20</v>
+      </c>
+      <c r="K354">
+        <f t="shared" si="180"/>
+        <v>20</v>
+      </c>
+      <c r="L354">
+        <f t="shared" si="181"/>
+        <v>20</v>
+      </c>
+      <c r="M354">
+        <v>-1</v>
+      </c>
+      <c r="N354">
+        <v>0</v>
+      </c>
+      <c r="O354">
+        <v>0</v>
+      </c>
+      <c r="P354">
+        <v>0</v>
+      </c>
+      <c r="Q354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A355">
+        <v>1130</v>
+      </c>
+      <c r="B355">
+        <v>200</v>
+      </c>
+      <c r="C355">
+        <v>-3100</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>0</v>
+      </c>
+      <c r="F355">
+        <v>0</v>
+      </c>
+      <c r="G355">
+        <v>1</v>
+      </c>
+      <c r="H355">
+        <v>1</v>
+      </c>
+      <c r="I355">
+        <v>1</v>
+      </c>
+      <c r="J355">
+        <f t="shared" si="179"/>
+        <v>20</v>
+      </c>
+      <c r="K355">
+        <f t="shared" si="180"/>
+        <v>20</v>
+      </c>
+      <c r="L355">
+        <f t="shared" si="181"/>
+        <v>20</v>
+      </c>
+      <c r="M355">
+        <v>-1</v>
+      </c>
+      <c r="N355">
+        <v>0</v>
+      </c>
+      <c r="O355">
+        <v>0</v>
+      </c>
+      <c r="P355">
+        <v>0</v>
+      </c>
+      <c r="Q355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A356">
+        <v>1190</v>
+      </c>
+      <c r="B356">
+        <v>200</v>
+      </c>
+      <c r="C356">
+        <v>-3060</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>0</v>
+      </c>
+      <c r="F356">
+        <v>0</v>
+      </c>
+      <c r="G356">
+        <v>1</v>
+      </c>
+      <c r="H356">
+        <v>1</v>
+      </c>
+      <c r="I356">
+        <v>1</v>
+      </c>
+      <c r="J356">
+        <f t="shared" si="179"/>
+        <v>20</v>
+      </c>
+      <c r="K356">
+        <f t="shared" si="180"/>
+        <v>20</v>
+      </c>
+      <c r="L356">
+        <f t="shared" si="181"/>
+        <v>20</v>
+      </c>
+      <c r="M356">
+        <v>-1</v>
+      </c>
+      <c r="N356">
+        <v>0</v>
+      </c>
+      <c r="O356">
+        <v>0</v>
+      </c>
+      <c r="P356">
+        <v>0</v>
+      </c>
+      <c r="Q356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A357">
+        <v>1270</v>
+      </c>
+      <c r="B357">
+        <v>320</v>
+      </c>
+      <c r="C357">
+        <v>-2980</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>0</v>
+      </c>
+      <c r="F357">
+        <v>0</v>
+      </c>
+      <c r="G357">
+        <v>1</v>
+      </c>
+      <c r="H357">
+        <v>1</v>
+      </c>
+      <c r="I357">
+        <v>1</v>
+      </c>
+      <c r="J357">
+        <f t="shared" ref="J357:J377" si="182">G357*20</f>
+        <v>20</v>
+      </c>
+      <c r="K357">
+        <f t="shared" ref="K357:K376" si="183">H357*20</f>
+        <v>20</v>
+      </c>
+      <c r="L357">
+        <f t="shared" ref="L357:L377" si="184">I357*20</f>
+        <v>20</v>
+      </c>
+      <c r="M357">
+        <v>-1</v>
+      </c>
+      <c r="N357">
+        <v>0</v>
+      </c>
+      <c r="O357">
+        <v>0</v>
+      </c>
+      <c r="P357">
+        <v>0</v>
+      </c>
+      <c r="Q357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A358">
+        <v>1370</v>
+      </c>
+      <c r="B358">
+        <v>320</v>
+      </c>
+      <c r="C358">
+        <v>-3060</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>0</v>
+      </c>
+      <c r="F358">
+        <v>0</v>
+      </c>
+      <c r="G358">
+        <v>1</v>
+      </c>
+      <c r="H358">
+        <v>1</v>
+      </c>
+      <c r="I358">
+        <v>1</v>
+      </c>
+      <c r="J358">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K358">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L358">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M358">
+        <v>-1</v>
+      </c>
+      <c r="N358">
+        <v>0</v>
+      </c>
+      <c r="O358">
+        <v>0</v>
+      </c>
+      <c r="P358">
+        <v>0</v>
+      </c>
+      <c r="Q358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A359">
+        <v>1450</v>
+      </c>
+      <c r="B359">
+        <v>320</v>
+      </c>
+      <c r="C359">
+        <v>-3000</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>0</v>
+      </c>
+      <c r="F359">
+        <v>0</v>
+      </c>
+      <c r="G359">
+        <v>1</v>
+      </c>
+      <c r="H359">
+        <v>1</v>
+      </c>
+      <c r="I359">
+        <v>1</v>
+      </c>
+      <c r="J359">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K359">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L359">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M359">
+        <v>-1</v>
+      </c>
+      <c r="N359">
+        <v>0</v>
+      </c>
+      <c r="O359">
+        <v>0</v>
+      </c>
+      <c r="P359">
+        <v>0</v>
+      </c>
+      <c r="Q359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A360">
+        <v>1510</v>
+      </c>
+      <c r="B360">
+        <v>320</v>
+      </c>
+      <c r="C360">
+        <v>-3080</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>0</v>
+      </c>
+      <c r="F360">
+        <v>0</v>
+      </c>
+      <c r="G360">
+        <v>1</v>
+      </c>
+      <c r="H360">
+        <v>1</v>
+      </c>
+      <c r="I360">
+        <v>1</v>
+      </c>
+      <c r="J360">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K360">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L360">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M360">
+        <v>-1</v>
+      </c>
+      <c r="N360">
+        <v>0</v>
+      </c>
+      <c r="O360">
+        <v>0</v>
+      </c>
+      <c r="P360">
+        <v>0</v>
+      </c>
+      <c r="Q360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A361">
+        <v>1530</v>
+      </c>
+      <c r="B361">
+        <v>320</v>
+      </c>
+      <c r="C361">
+        <v>-2980</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>0</v>
+      </c>
+      <c r="F361">
+        <v>0</v>
+      </c>
+      <c r="G361">
+        <v>1</v>
+      </c>
+      <c r="H361">
+        <v>1</v>
+      </c>
+      <c r="I361">
+        <v>1</v>
+      </c>
+      <c r="J361">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K361">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L361">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M361">
+        <v>-1</v>
+      </c>
+      <c r="N361">
+        <v>0</v>
+      </c>
+      <c r="O361">
+        <v>0</v>
+      </c>
+      <c r="P361">
+        <v>0</v>
+      </c>
+      <c r="Q361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A362">
+        <v>1250</v>
+      </c>
+      <c r="B362">
+        <v>320</v>
+      </c>
+      <c r="C362">
+        <v>-2980</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>0</v>
+      </c>
+      <c r="F362">
+        <v>0</v>
+      </c>
+      <c r="G362">
+        <v>1</v>
+      </c>
+      <c r="H362">
+        <v>1</v>
+      </c>
+      <c r="I362">
+        <v>1</v>
+      </c>
+      <c r="J362">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K362">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L362">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M362">
+        <v>-1</v>
+      </c>
+      <c r="N362">
+        <v>0</v>
+      </c>
+      <c r="O362">
+        <v>0</v>
+      </c>
+      <c r="P362">
+        <v>0</v>
+      </c>
+      <c r="Q362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A363">
+        <v>1310</v>
+      </c>
+      <c r="B363">
+        <v>320</v>
+      </c>
+      <c r="C363">
+        <v>-3020</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>0</v>
+      </c>
+      <c r="F363">
+        <v>0</v>
+      </c>
+      <c r="G363">
+        <v>1</v>
+      </c>
+      <c r="H363">
+        <v>1</v>
+      </c>
+      <c r="I363">
+        <v>1</v>
+      </c>
+      <c r="J363">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K363">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L363">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M363">
+        <v>-1</v>
+      </c>
+      <c r="N363">
+        <v>0</v>
+      </c>
+      <c r="O363">
+        <v>0</v>
+      </c>
+      <c r="P363">
+        <v>0</v>
+      </c>
+      <c r="Q363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A364">
+        <v>1350</v>
+      </c>
+      <c r="B364">
+        <v>320</v>
+      </c>
+      <c r="C364">
+        <v>-3100</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>0</v>
+      </c>
+      <c r="F364">
+        <v>0</v>
+      </c>
+      <c r="G364">
+        <v>1</v>
+      </c>
+      <c r="H364">
+        <v>1</v>
+      </c>
+      <c r="I364">
+        <v>1</v>
+      </c>
+      <c r="J364">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K364">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L364">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M364">
+        <v>-1</v>
+      </c>
+      <c r="N364">
+        <v>0</v>
+      </c>
+      <c r="O364">
+        <v>0</v>
+      </c>
+      <c r="P364">
+        <v>0</v>
+      </c>
+      <c r="Q364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A365">
+        <v>1410</v>
+      </c>
+      <c r="B365">
+        <v>320</v>
+      </c>
+      <c r="C365">
+        <v>-2980</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>0</v>
+      </c>
+      <c r="F365">
+        <v>0</v>
+      </c>
+      <c r="G365">
+        <v>1</v>
+      </c>
+      <c r="H365">
+        <v>1</v>
+      </c>
+      <c r="I365">
+        <v>1</v>
+      </c>
+      <c r="J365">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K365">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L365">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M365">
+        <v>-1</v>
+      </c>
+      <c r="N365">
+        <v>0</v>
+      </c>
+      <c r="O365">
+        <v>0</v>
+      </c>
+      <c r="P365">
+        <v>0</v>
+      </c>
+      <c r="Q365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A366">
+        <v>1430</v>
+      </c>
+      <c r="B366">
+        <v>320</v>
+      </c>
+      <c r="C366">
+        <v>-3080</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>0</v>
+      </c>
+      <c r="F366">
+        <v>0</v>
+      </c>
+      <c r="G366">
+        <v>1</v>
+      </c>
+      <c r="H366">
+        <v>1</v>
+      </c>
+      <c r="I366">
+        <v>1</v>
+      </c>
+      <c r="J366">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K366">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L366">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M366">
+        <v>-1</v>
+      </c>
+      <c r="N366">
+        <v>0</v>
+      </c>
+      <c r="O366">
+        <v>0</v>
+      </c>
+      <c r="P366">
+        <v>0</v>
+      </c>
+      <c r="Q366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A367">
+        <v>1470</v>
+      </c>
+      <c r="B367">
+        <v>320</v>
+      </c>
+      <c r="C367">
+        <v>-3040</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>0</v>
+      </c>
+      <c r="F367">
+        <v>0</v>
+      </c>
+      <c r="G367">
+        <v>1</v>
+      </c>
+      <c r="H367">
+        <v>1</v>
+      </c>
+      <c r="I367">
+        <v>1</v>
+      </c>
+      <c r="J367">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K367">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L367">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M367">
+        <v>-1</v>
+      </c>
+      <c r="N367">
+        <v>0</v>
+      </c>
+      <c r="O367">
+        <v>0</v>
+      </c>
+      <c r="P367">
+        <v>0</v>
+      </c>
+      <c r="Q367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A368">
+        <v>1510</v>
+      </c>
+      <c r="B368">
+        <v>320</v>
+      </c>
+      <c r="C368">
+        <v>-2980</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>0</v>
+      </c>
+      <c r="F368">
+        <v>0</v>
+      </c>
+      <c r="G368">
+        <v>1</v>
+      </c>
+      <c r="H368">
+        <v>1</v>
+      </c>
+      <c r="I368">
+        <v>1</v>
+      </c>
+      <c r="J368">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K368">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L368">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M368">
+        <v>-1</v>
+      </c>
+      <c r="N368">
+        <v>0</v>
+      </c>
+      <c r="O368">
+        <v>0</v>
+      </c>
+      <c r="P368">
+        <v>0</v>
+      </c>
+      <c r="Q368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A369">
+        <v>1530</v>
+      </c>
+      <c r="B369">
+        <v>320</v>
+      </c>
+      <c r="C369">
+        <v>-3020</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>0</v>
+      </c>
+      <c r="F369">
+        <v>0</v>
+      </c>
+      <c r="G369">
+        <v>1</v>
+      </c>
+      <c r="H369">
+        <v>1</v>
+      </c>
+      <c r="I369">
+        <v>1</v>
+      </c>
+      <c r="J369">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K369">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L369">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M369">
+        <v>-1</v>
+      </c>
+      <c r="N369">
+        <v>0</v>
+      </c>
+      <c r="O369">
+        <v>0</v>
+      </c>
+      <c r="P369">
+        <v>0</v>
+      </c>
+      <c r="Q369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A370">
+        <v>1550</v>
+      </c>
+      <c r="B370">
+        <v>320</v>
+      </c>
+      <c r="C370">
+        <v>-3080</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>0</v>
+      </c>
+      <c r="F370">
+        <v>0</v>
+      </c>
+      <c r="G370">
+        <v>1</v>
+      </c>
+      <c r="H370">
+        <v>1</v>
+      </c>
+      <c r="I370">
+        <v>1</v>
+      </c>
+      <c r="J370">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K370">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L370">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M370">
+        <v>-1</v>
+      </c>
+      <c r="N370">
+        <v>0</v>
+      </c>
+      <c r="O370">
+        <v>0</v>
+      </c>
+      <c r="P370">
+        <v>0</v>
+      </c>
+      <c r="Q370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A371">
+        <v>1290</v>
+      </c>
+      <c r="B371">
+        <v>320</v>
+      </c>
+      <c r="C371">
+        <v>-3040</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>0</v>
+      </c>
+      <c r="F371">
+        <v>0</v>
+      </c>
+      <c r="G371">
+        <v>1</v>
+      </c>
+      <c r="H371">
+        <v>1</v>
+      </c>
+      <c r="I371">
+        <v>1</v>
+      </c>
+      <c r="J371">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K371">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L371">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M371">
+        <v>-1</v>
+      </c>
+      <c r="N371">
+        <v>0</v>
+      </c>
+      <c r="O371">
+        <v>0</v>
+      </c>
+      <c r="P371">
+        <v>0</v>
+      </c>
+      <c r="Q371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A372">
+        <v>1330</v>
+      </c>
+      <c r="B372">
+        <v>320</v>
+      </c>
+      <c r="C372">
+        <v>-2980</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>0</v>
+      </c>
+      <c r="F372">
+        <v>0</v>
+      </c>
+      <c r="G372">
+        <v>1</v>
+      </c>
+      <c r="H372">
+        <v>1</v>
+      </c>
+      <c r="I372">
+        <v>1</v>
+      </c>
+      <c r="J372">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K372">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L372">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M372">
+        <v>-1</v>
+      </c>
+      <c r="N372">
+        <v>0</v>
+      </c>
+      <c r="O372">
+        <v>0</v>
+      </c>
+      <c r="P372">
+        <v>0</v>
+      </c>
+      <c r="Q372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A373">
+        <v>1390</v>
+      </c>
+      <c r="B373">
+        <v>320</v>
+      </c>
+      <c r="C373">
+        <v>-3100</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>0</v>
+      </c>
+      <c r="F373">
+        <v>0</v>
+      </c>
+      <c r="G373">
+        <v>1</v>
+      </c>
+      <c r="H373">
+        <v>1</v>
+      </c>
+      <c r="I373">
+        <v>1</v>
+      </c>
+      <c r="J373">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K373">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L373">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M373">
+        <v>-1</v>
+      </c>
+      <c r="N373">
+        <v>0</v>
+      </c>
+      <c r="O373">
+        <v>0</v>
+      </c>
+      <c r="P373">
+        <v>0</v>
+      </c>
+      <c r="Q373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A374">
+        <v>1450</v>
+      </c>
+      <c r="B374">
+        <v>320</v>
+      </c>
+      <c r="C374">
+        <v>-3060</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>0</v>
+      </c>
+      <c r="F374">
+        <v>0</v>
+      </c>
+      <c r="G374">
+        <v>1</v>
+      </c>
+      <c r="H374">
+        <v>1</v>
+      </c>
+      <c r="I374">
+        <v>1</v>
+      </c>
+      <c r="J374">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K374">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L374">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M374">
+        <v>-1</v>
+      </c>
+      <c r="N374">
+        <v>0</v>
+      </c>
+      <c r="O374">
+        <v>0</v>
+      </c>
+      <c r="P374">
+        <v>0</v>
+      </c>
+      <c r="Q374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A375">
+        <v>1490</v>
+      </c>
+      <c r="B375">
+        <v>320</v>
+      </c>
+      <c r="C375">
+        <v>-3000</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>0</v>
+      </c>
+      <c r="F375">
+        <v>0</v>
+      </c>
+      <c r="G375">
+        <v>1</v>
+      </c>
+      <c r="H375">
+        <v>1</v>
+      </c>
+      <c r="I375">
+        <v>1</v>
+      </c>
+      <c r="J375">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K375">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L375">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M375">
+        <v>-1</v>
+      </c>
+      <c r="N375">
+        <v>0</v>
+      </c>
+      <c r="O375">
+        <v>0</v>
+      </c>
+      <c r="P375">
+        <v>0</v>
+      </c>
+      <c r="Q375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A376">
+        <v>1530</v>
+      </c>
+      <c r="B376">
+        <v>320</v>
+      </c>
+      <c r="C376">
+        <v>-3060</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>0</v>
+      </c>
+      <c r="F376">
+        <v>0</v>
+      </c>
+      <c r="G376">
+        <v>1</v>
+      </c>
+      <c r="H376">
+        <v>1</v>
+      </c>
+      <c r="I376">
+        <v>1</v>
+      </c>
+      <c r="J376">
+        <f t="shared" si="182"/>
+        <v>20</v>
+      </c>
+      <c r="K376">
+        <f t="shared" si="183"/>
+        <v>20</v>
+      </c>
+      <c r="L376">
+        <f t="shared" si="184"/>
+        <v>20</v>
+      </c>
+      <c r="M376">
+        <v>-1</v>
+      </c>
+      <c r="N376">
+        <v>0</v>
+      </c>
+      <c r="O376">
+        <v>0</v>
+      </c>
+      <c r="P376">
+        <v>0</v>
+      </c>
+      <c r="Q376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A377">
+        <v>1240</v>
+      </c>
+      <c r="B377">
+        <v>400</v>
+      </c>
+      <c r="C377">
+        <v>-2950</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>0</v>
+      </c>
+      <c r="F377">
+        <v>0</v>
+      </c>
+      <c r="G377">
+        <v>2</v>
+      </c>
+      <c r="H377">
+        <v>2</v>
+      </c>
+      <c r="I377">
+        <v>2</v>
+      </c>
+      <c r="J377">
+        <f t="shared" si="182"/>
+        <v>40</v>
+      </c>
+      <c r="K377">
+        <v>80</v>
+      </c>
+      <c r="L377">
+        <f t="shared" si="184"/>
+        <v>40</v>
+      </c>
+      <c r="M377">
+        <v>-1</v>
+      </c>
+      <c r="N377">
+        <v>0</v>
+      </c>
+      <c r="O377">
+        <v>0</v>
+      </c>
+      <c r="P377">
+        <v>0</v>
+      </c>
+      <c r="Q377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A378">
+        <v>1240</v>
+      </c>
+      <c r="B378">
+        <v>400</v>
+      </c>
+      <c r="C378">
+        <v>-3110</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>0</v>
+      </c>
+      <c r="F378">
+        <v>0</v>
+      </c>
+      <c r="G378">
+        <v>2</v>
+      </c>
+      <c r="H378">
+        <v>2</v>
+      </c>
+      <c r="I378">
+        <v>2</v>
+      </c>
+      <c r="J378">
+        <f t="shared" ref="J378:J380" si="185">G378*20</f>
+        <v>40</v>
+      </c>
+      <c r="K378">
+        <v>81</v>
+      </c>
+      <c r="L378">
+        <f t="shared" ref="L378:L381" si="186">I378*20</f>
+        <v>40</v>
+      </c>
+      <c r="M378">
+        <v>-1</v>
+      </c>
+      <c r="N378">
+        <v>0</v>
+      </c>
+      <c r="O378">
+        <v>0</v>
+      </c>
+      <c r="P378">
+        <v>0</v>
+      </c>
+      <c r="Q378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A379">
+        <v>1540</v>
+      </c>
+      <c r="B379">
+        <v>400</v>
+      </c>
+      <c r="C379">
+        <v>-2950</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>0</v>
+      </c>
+      <c r="F379">
+        <v>0</v>
+      </c>
+      <c r="G379">
+        <v>2</v>
+      </c>
+      <c r="H379">
+        <v>2</v>
+      </c>
+      <c r="I379">
+        <v>2</v>
+      </c>
+      <c r="J379">
+        <f t="shared" si="185"/>
+        <v>40</v>
+      </c>
+      <c r="K379">
+        <v>82</v>
+      </c>
+      <c r="L379">
+        <f t="shared" si="186"/>
+        <v>40</v>
+      </c>
+      <c r="M379">
+        <v>-1</v>
+      </c>
+      <c r="N379">
+        <v>0</v>
+      </c>
+      <c r="O379">
+        <v>0</v>
+      </c>
+      <c r="P379">
+        <v>0</v>
+      </c>
+      <c r="Q379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A380">
+        <v>1540</v>
+      </c>
+      <c r="B380">
+        <v>400</v>
+      </c>
+      <c r="C380">
+        <v>-3110</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>0</v>
+      </c>
+      <c r="F380">
+        <v>0</v>
+      </c>
+      <c r="G380">
+        <v>2</v>
+      </c>
+      <c r="H380">
+        <v>2</v>
+      </c>
+      <c r="I380">
+        <v>2</v>
+      </c>
+      <c r="J380">
+        <f t="shared" si="185"/>
+        <v>40</v>
+      </c>
+      <c r="K380">
+        <v>83</v>
+      </c>
+      <c r="L380">
+        <f t="shared" si="186"/>
+        <v>40</v>
+      </c>
+      <c r="M380">
+        <v>-1</v>
+      </c>
+      <c r="N380">
+        <v>0</v>
+      </c>
+      <c r="O380">
+        <v>0</v>
+      </c>
+      <c r="P380">
+        <v>0</v>
+      </c>
+      <c r="Q380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A381">
+        <v>1290</v>
+      </c>
+      <c r="B381">
+        <v>340</v>
+      </c>
+      <c r="C381">
+        <v>-2940</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>0</v>
+      </c>
+      <c r="F381">
+        <v>0</v>
+      </c>
+      <c r="G381">
+        <v>1</v>
+      </c>
+      <c r="H381">
+        <v>1</v>
+      </c>
+      <c r="I381">
+        <v>1</v>
+      </c>
+      <c r="J381">
+        <v>60</v>
+      </c>
+      <c r="K381">
+        <f t="shared" ref="K381" si="187">H381*20</f>
+        <v>20</v>
+      </c>
+      <c r="L381">
+        <f t="shared" si="186"/>
+        <v>20</v>
+      </c>
+      <c r="M381">
+        <v>-1</v>
+      </c>
+      <c r="N381">
+        <v>0</v>
+      </c>
+      <c r="O381">
+        <v>0</v>
+      </c>
+      <c r="P381">
+        <v>0</v>
+      </c>
+      <c r="Q381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A382">
+        <v>1290</v>
+      </c>
+      <c r="B382">
+        <v>340</v>
+      </c>
+      <c r="C382">
+        <v>-3120</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>3.14</v>
+      </c>
+      <c r="F382">
+        <v>0</v>
+      </c>
+      <c r="G382">
+        <v>1</v>
+      </c>
+      <c r="H382">
+        <v>1</v>
+      </c>
+      <c r="I382">
+        <v>1</v>
+      </c>
+      <c r="J382">
+        <v>60</v>
+      </c>
+      <c r="K382">
+        <f t="shared" ref="K382:K385" si="188">H382*20</f>
+        <v>20</v>
+      </c>
+      <c r="L382">
+        <f t="shared" ref="L382:L384" si="189">I382*20</f>
+        <v>20</v>
+      </c>
+      <c r="M382">
+        <v>-1</v>
+      </c>
+      <c r="N382">
+        <v>0</v>
+      </c>
+      <c r="O382">
+        <v>0</v>
+      </c>
+      <c r="P382">
+        <v>0</v>
+      </c>
+      <c r="Q382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A383">
+        <v>1490</v>
+      </c>
+      <c r="B383">
+        <v>340</v>
+      </c>
+      <c r="C383">
+        <v>-2940</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>0</v>
+      </c>
+      <c r="F383">
+        <v>0</v>
+      </c>
+      <c r="G383">
+        <v>1</v>
+      </c>
+      <c r="H383">
+        <v>1</v>
+      </c>
+      <c r="I383">
+        <v>1</v>
+      </c>
+      <c r="J383">
+        <v>60</v>
+      </c>
+      <c r="K383">
+        <f t="shared" si="188"/>
+        <v>20</v>
+      </c>
+      <c r="L383">
+        <f t="shared" si="189"/>
+        <v>20</v>
+      </c>
+      <c r="M383">
+        <v>-1</v>
+      </c>
+      <c r="N383">
+        <v>0</v>
+      </c>
+      <c r="O383">
+        <v>0</v>
+      </c>
+      <c r="P383">
+        <v>0</v>
+      </c>
+      <c r="Q383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A384">
+        <v>1490</v>
+      </c>
+      <c r="B384">
+        <v>340</v>
+      </c>
+      <c r="C384">
+        <v>-3120</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>3.14</v>
+      </c>
+      <c r="F384">
+        <v>0</v>
+      </c>
+      <c r="G384">
+        <v>1</v>
+      </c>
+      <c r="H384">
+        <v>1</v>
+      </c>
+      <c r="I384">
+        <v>1</v>
+      </c>
+      <c r="J384">
+        <v>60</v>
+      </c>
+      <c r="K384">
+        <f t="shared" si="188"/>
+        <v>20</v>
+      </c>
+      <c r="L384">
+        <f t="shared" si="189"/>
+        <v>20</v>
+      </c>
+      <c r="M384">
+        <v>-1</v>
+      </c>
+      <c r="N384">
+        <v>0</v>
+      </c>
+      <c r="O384">
+        <v>0</v>
+      </c>
+      <c r="P384">
+        <v>0</v>
+      </c>
+      <c r="Q384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A385">
+        <v>1650</v>
+      </c>
+      <c r="B385">
+        <v>340</v>
+      </c>
+      <c r="C385">
+        <v>-3030</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>1.57</v>
+      </c>
+      <c r="F385">
+        <v>0</v>
+      </c>
+      <c r="G385">
+        <v>1</v>
+      </c>
+      <c r="H385">
+        <v>1</v>
+      </c>
+      <c r="I385">
+        <v>1</v>
+      </c>
+      <c r="J385">
+        <v>20</v>
+      </c>
+      <c r="K385">
+        <f t="shared" si="188"/>
+        <v>20</v>
+      </c>
+      <c r="L385">
+        <v>60</v>
+      </c>
+      <c r="M385">
+        <v>-1</v>
+      </c>
+      <c r="N385">
+        <v>0</v>
+      </c>
+      <c r="O385">
+        <v>0</v>
+      </c>
+      <c r="P385">
+        <v>0</v>
+      </c>
+      <c r="Q385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A386">
+        <v>1650</v>
+      </c>
+      <c r="B386">
+        <v>340</v>
+      </c>
+      <c r="C386">
+        <v>-2960</v>
+      </c>
+      <c r="D386">
+        <v>0</v>
+      </c>
+      <c r="E386">
+        <v>1.57</v>
+      </c>
+      <c r="F386">
+        <v>0</v>
+      </c>
+      <c r="G386">
+        <v>1</v>
+      </c>
+      <c r="H386">
+        <v>1</v>
+      </c>
+      <c r="I386">
+        <v>1</v>
+      </c>
+      <c r="J386">
+        <v>20</v>
+      </c>
+      <c r="K386">
+        <f t="shared" ref="K386:K390" si="190">H386*20</f>
+        <v>20</v>
+      </c>
+      <c r="L386">
+        <v>60</v>
+      </c>
+      <c r="M386">
+        <v>-1</v>
+      </c>
+      <c r="N386">
+        <v>0</v>
+      </c>
+      <c r="O386">
+        <v>0</v>
+      </c>
+      <c r="P386">
+        <v>0</v>
+      </c>
+      <c r="Q386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A387">
+        <v>1650</v>
+      </c>
+      <c r="B387">
+        <v>340</v>
+      </c>
+      <c r="C387">
+        <v>-3100</v>
+      </c>
+      <c r="D387">
+        <v>0</v>
+      </c>
+      <c r="E387">
+        <v>1.57</v>
+      </c>
+      <c r="F387">
+        <v>0</v>
+      </c>
+      <c r="G387">
+        <v>1</v>
+      </c>
+      <c r="H387">
+        <v>1</v>
+      </c>
+      <c r="I387">
+        <v>1</v>
+      </c>
+      <c r="J387">
+        <v>20</v>
+      </c>
+      <c r="K387">
+        <f t="shared" si="190"/>
+        <v>20</v>
+      </c>
+      <c r="L387">
+        <v>60</v>
+      </c>
+      <c r="M387">
+        <v>-1</v>
+      </c>
+      <c r="N387">
+        <v>0</v>
+      </c>
+      <c r="O387">
+        <v>0</v>
+      </c>
+      <c r="P387">
+        <v>0</v>
+      </c>
+      <c r="Q387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A388">
+        <v>2570</v>
+      </c>
+      <c r="B388">
+        <v>340</v>
+      </c>
+      <c r="C388">
+        <v>-3030</v>
+      </c>
+      <c r="D388">
+        <v>0</v>
+      </c>
+      <c r="E388">
+        <v>4.71</v>
+      </c>
+      <c r="F388">
+        <v>0</v>
+      </c>
+      <c r="G388">
+        <v>1</v>
+      </c>
+      <c r="H388">
+        <v>1</v>
+      </c>
+      <c r="I388">
+        <v>1</v>
+      </c>
+      <c r="J388">
+        <v>20</v>
+      </c>
+      <c r="K388">
+        <f t="shared" si="190"/>
+        <v>20</v>
+      </c>
+      <c r="L388">
+        <v>60</v>
+      </c>
+      <c r="M388">
+        <v>-1</v>
+      </c>
+      <c r="N388">
+        <v>0</v>
+      </c>
+      <c r="O388">
+        <v>0</v>
+      </c>
+      <c r="P388">
+        <v>0</v>
+      </c>
+      <c r="Q388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A389">
+        <v>2570</v>
+      </c>
+      <c r="B389">
+        <v>340</v>
+      </c>
+      <c r="C389">
+        <v>-2960</v>
+      </c>
+      <c r="D389">
+        <v>0</v>
+      </c>
+      <c r="E389">
+        <v>4.71</v>
+      </c>
+      <c r="F389">
+        <v>0</v>
+      </c>
+      <c r="G389">
+        <v>1</v>
+      </c>
+      <c r="H389">
+        <v>1</v>
+      </c>
+      <c r="I389">
+        <v>1</v>
+      </c>
+      <c r="J389">
+        <v>20</v>
+      </c>
+      <c r="K389">
+        <f t="shared" si="190"/>
+        <v>20</v>
+      </c>
+      <c r="L389">
+        <v>60</v>
+      </c>
+      <c r="M389">
+        <v>-1</v>
+      </c>
+      <c r="N389">
+        <v>0</v>
+      </c>
+      <c r="O389">
+        <v>0</v>
+      </c>
+      <c r="P389">
+        <v>0</v>
+      </c>
+      <c r="Q389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A390">
+        <v>2570</v>
+      </c>
+      <c r="B390">
+        <v>340</v>
+      </c>
+      <c r="C390">
+        <v>-3100</v>
+      </c>
+      <c r="D390">
+        <v>0</v>
+      </c>
+      <c r="E390">
+        <v>4.71</v>
+      </c>
+      <c r="F390">
+        <v>0</v>
+      </c>
+      <c r="G390">
+        <v>1</v>
+      </c>
+      <c r="H390">
+        <v>1</v>
+      </c>
+      <c r="I390">
+        <v>1</v>
+      </c>
+      <c r="J390">
+        <v>20</v>
+      </c>
+      <c r="K390">
+        <f t="shared" si="190"/>
+        <v>20</v>
+      </c>
+      <c r="L390">
+        <v>60</v>
+      </c>
+      <c r="M390">
+        <v>-1</v>
+      </c>
+      <c r="N390">
+        <v>0</v>
+      </c>
+      <c r="O390">
+        <v>0</v>
+      </c>
+      <c r="P390">
+        <v>0</v>
+      </c>
+      <c r="Q390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A391">
+        <v>2960</v>
+      </c>
+      <c r="B391">
+        <v>400</v>
+      </c>
+      <c r="C391">
+        <v>-2950</v>
+      </c>
+      <c r="D391">
+        <v>0</v>
+      </c>
+      <c r="E391">
+        <v>0</v>
+      </c>
+      <c r="F391">
+        <v>0</v>
+      </c>
+      <c r="G391">
+        <v>2</v>
+      </c>
+      <c r="H391">
+        <v>2</v>
+      </c>
+      <c r="I391">
+        <v>2</v>
+      </c>
+      <c r="J391">
+        <f t="shared" ref="J391" si="191">G391*20</f>
+        <v>40</v>
+      </c>
+      <c r="K391">
+        <v>81</v>
+      </c>
+      <c r="L391">
+        <f t="shared" ref="L391" si="192">I391*20</f>
+        <v>40</v>
+      </c>
+      <c r="M391">
+        <v>-1</v>
+      </c>
+      <c r="N391">
+        <v>0</v>
+      </c>
+      <c r="O391">
+        <v>0</v>
+      </c>
+      <c r="P391">
+        <v>0</v>
+      </c>
+      <c r="Q391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A392">
+        <v>2960</v>
+      </c>
+      <c r="B392">
+        <v>400</v>
+      </c>
+      <c r="C392">
+        <v>-3110</v>
+      </c>
+      <c r="D392">
+        <v>0</v>
+      </c>
+      <c r="E392">
+        <v>0</v>
+      </c>
+      <c r="F392">
+        <v>0</v>
+      </c>
+      <c r="G392">
+        <v>2</v>
+      </c>
+      <c r="H392">
+        <v>2</v>
+      </c>
+      <c r="I392">
+        <v>2</v>
+      </c>
+      <c r="J392">
+        <f t="shared" ref="J392" si="193">G392*20</f>
+        <v>40</v>
+      </c>
+      <c r="K392">
+        <v>82</v>
+      </c>
+      <c r="L392">
+        <f t="shared" ref="L392" si="194">I392*20</f>
+        <v>40</v>
+      </c>
+      <c r="M392">
+        <v>-1</v>
+      </c>
+      <c r="N392">
+        <v>0</v>
+      </c>
+      <c r="O392">
+        <v>0</v>
+      </c>
+      <c r="P392">
+        <v>0</v>
+      </c>
+      <c r="Q392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A393">
+        <v>2880</v>
+      </c>
+      <c r="B393">
+        <v>400</v>
+      </c>
+      <c r="C393">
+        <v>-2950</v>
+      </c>
+      <c r="D393">
+        <v>0</v>
+      </c>
+      <c r="E393">
+        <v>0</v>
+      </c>
+      <c r="F393">
+        <v>0</v>
+      </c>
+      <c r="G393">
+        <v>2</v>
+      </c>
+      <c r="H393">
+        <v>2</v>
+      </c>
+      <c r="I393">
+        <v>2</v>
+      </c>
+      <c r="J393">
+        <f>G393*20</f>
+        <v>40</v>
+      </c>
+      <c r="K393">
+        <v>83</v>
+      </c>
+      <c r="L393">
+        <f>I393*20</f>
+        <v>40</v>
+      </c>
+      <c r="M393">
+        <v>-1</v>
+      </c>
+      <c r="N393">
+        <v>0</v>
+      </c>
+      <c r="O393">
+        <v>0</v>
+      </c>
+      <c r="P393">
+        <v>0</v>
+      </c>
+      <c r="Q393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A394">
+        <v>2880</v>
+      </c>
+      <c r="B394">
+        <v>400</v>
+      </c>
+      <c r="C394">
+        <v>-3110</v>
+      </c>
+      <c r="D394">
+        <v>0</v>
+      </c>
+      <c r="E394">
+        <v>0</v>
+      </c>
+      <c r="F394">
+        <v>0</v>
+      </c>
+      <c r="G394">
+        <v>2</v>
+      </c>
+      <c r="H394">
+        <v>2</v>
+      </c>
+      <c r="I394">
+        <v>2</v>
+      </c>
+      <c r="J394">
+        <f>G394*20</f>
+        <v>40</v>
+      </c>
+      <c r="K394">
+        <v>84</v>
+      </c>
+      <c r="L394">
+        <f>I394*20</f>
+        <v>40</v>
+      </c>
+      <c r="M394">
+        <v>-1</v>
+      </c>
+      <c r="N394">
+        <v>0</v>
+      </c>
+      <c r="O394">
+        <v>0</v>
+      </c>
+      <c r="P394">
+        <v>0</v>
+      </c>
+      <c r="Q394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A395">
+        <v>2800</v>
+      </c>
+      <c r="B395">
+        <v>400</v>
+      </c>
+      <c r="C395">
+        <v>-2950</v>
+      </c>
+      <c r="D395">
+        <v>0</v>
+      </c>
+      <c r="E395">
+        <v>0</v>
+      </c>
+      <c r="F395">
+        <v>0</v>
+      </c>
+      <c r="G395">
+        <v>2</v>
+      </c>
+      <c r="H395">
+        <v>2</v>
+      </c>
+      <c r="I395">
+        <v>2</v>
+      </c>
+      <c r="J395">
+        <f>G395*20</f>
+        <v>40</v>
+      </c>
+      <c r="K395">
+        <v>85</v>
+      </c>
+      <c r="L395">
+        <f>I395*20</f>
+        <v>40</v>
+      </c>
+      <c r="M395">
+        <v>-1</v>
+      </c>
+      <c r="N395">
+        <v>0</v>
+      </c>
+      <c r="O395">
+        <v>0</v>
+      </c>
+      <c r="P395">
+        <v>0</v>
+      </c>
+      <c r="Q395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A396">
+        <v>2800</v>
+      </c>
+      <c r="B396">
+        <v>400</v>
+      </c>
+      <c r="C396">
+        <v>-3110</v>
+      </c>
+      <c r="D396">
+        <v>0</v>
+      </c>
+      <c r="E396">
+        <v>0</v>
+      </c>
+      <c r="F396">
+        <v>0</v>
+      </c>
+      <c r="G396">
+        <v>2</v>
+      </c>
+      <c r="H396">
+        <v>2</v>
+      </c>
+      <c r="I396">
+        <v>2</v>
+      </c>
+      <c r="J396">
+        <f>G396*20</f>
+        <v>40</v>
+      </c>
+      <c r="K396">
+        <v>86</v>
+      </c>
+      <c r="L396">
+        <f>I396*20</f>
+        <v>40</v>
+      </c>
+      <c r="M396">
+        <v>-1</v>
+      </c>
+      <c r="N396">
+        <v>0</v>
+      </c>
+      <c r="O396">
+        <v>0</v>
+      </c>
+      <c r="P396">
+        <v>0</v>
+      </c>
+      <c r="Q396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A397">
+        <v>2720</v>
+      </c>
+      <c r="B397">
+        <v>400</v>
+      </c>
+      <c r="C397">
+        <v>-2950</v>
+      </c>
+      <c r="D397">
+        <v>0</v>
+      </c>
+      <c r="E397">
+        <v>0</v>
+      </c>
+      <c r="F397">
+        <v>0</v>
+      </c>
+      <c r="G397">
+        <v>2</v>
+      </c>
+      <c r="H397">
+        <v>2</v>
+      </c>
+      <c r="I397">
+        <v>2</v>
+      </c>
+      <c r="J397">
+        <f>G397*20</f>
+        <v>40</v>
+      </c>
+      <c r="K397">
+        <v>88</v>
+      </c>
+      <c r="L397">
+        <f>I397*20</f>
+        <v>40</v>
+      </c>
+      <c r="M397">
+        <v>-1</v>
+      </c>
+      <c r="N397">
+        <v>0</v>
+      </c>
+      <c r="O397">
+        <v>0</v>
+      </c>
+      <c r="P397">
+        <v>0</v>
+      </c>
+      <c r="Q397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A398">
+        <v>2720</v>
+      </c>
+      <c r="B398">
+        <v>400</v>
+      </c>
+      <c r="C398">
+        <v>-3110</v>
+      </c>
+      <c r="D398">
+        <v>0</v>
+      </c>
+      <c r="E398">
+        <v>0</v>
+      </c>
+      <c r="F398">
+        <v>0</v>
+      </c>
+      <c r="G398">
+        <v>2</v>
+      </c>
+      <c r="H398">
+        <v>2</v>
+      </c>
+      <c r="I398">
+        <v>2</v>
+      </c>
+      <c r="J398">
+        <f>G398*20</f>
+        <v>40</v>
+      </c>
+      <c r="K398">
+        <v>88</v>
+      </c>
+      <c r="L398">
+        <f>I398*20</f>
+        <v>40</v>
+      </c>
+      <c r="M398">
+        <v>-1</v>
+      </c>
+      <c r="N398">
+        <v>0</v>
+      </c>
+      <c r="O398">
+        <v>0</v>
+      </c>
+      <c r="P398">
+        <v>0</v>
+      </c>
+      <c r="Q398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A399">
+        <v>2610</v>
+      </c>
+      <c r="B399">
+        <v>320</v>
+      </c>
+      <c r="C399">
+        <v>-2980</v>
+      </c>
+      <c r="D399">
+        <v>0</v>
+      </c>
+      <c r="E399">
+        <v>0</v>
+      </c>
+      <c r="F399">
+        <v>0</v>
+      </c>
+      <c r="G399">
+        <v>1</v>
+      </c>
+      <c r="H399">
+        <v>1</v>
+      </c>
+      <c r="I399">
+        <v>1</v>
+      </c>
+      <c r="J399">
+        <f t="shared" ref="J399" si="195">G399*20</f>
+        <v>20</v>
+      </c>
+      <c r="K399">
+        <f t="shared" ref="K399" si="196">H399*20</f>
+        <v>20</v>
+      </c>
+      <c r="L399">
+        <f t="shared" ref="L399" si="197">I399*20</f>
+        <v>20</v>
+      </c>
+      <c r="M399">
+        <v>-1</v>
+      </c>
+      <c r="N399">
+        <v>0</v>
+      </c>
+      <c r="O399">
+        <v>0</v>
+      </c>
+      <c r="P399">
+        <v>0</v>
+      </c>
+      <c r="Q399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A400">
+        <v>2670</v>
+      </c>
+      <c r="B400">
+        <v>320</v>
+      </c>
+      <c r="C400">
+        <v>-3060</v>
+      </c>
+      <c r="D400">
+        <v>0</v>
+      </c>
+      <c r="E400">
+        <v>0</v>
+      </c>
+      <c r="F400">
+        <v>0</v>
+      </c>
+      <c r="G400">
+        <v>1</v>
+      </c>
+      <c r="H400">
+        <v>1</v>
+      </c>
+      <c r="I400">
+        <v>1</v>
+      </c>
+      <c r="J400">
+        <f t="shared" ref="J400:J419" si="198">G400*20</f>
+        <v>20</v>
+      </c>
+      <c r="K400">
+        <f t="shared" ref="K400:K418" si="199">H400*20</f>
+        <v>20</v>
+      </c>
+      <c r="L400">
+        <f t="shared" ref="L400:L419" si="200">I400*20</f>
+        <v>20</v>
+      </c>
+      <c r="M400">
+        <v>-1</v>
+      </c>
+      <c r="N400">
+        <v>0</v>
+      </c>
+      <c r="O400">
+        <v>0</v>
+      </c>
+      <c r="P400">
+        <v>0</v>
+      </c>
+      <c r="Q400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A401">
+        <v>2770</v>
+      </c>
+      <c r="B401">
+        <v>320</v>
+      </c>
+      <c r="C401">
+        <v>-3000</v>
+      </c>
+      <c r="D401">
+        <v>0</v>
+      </c>
+      <c r="E401">
+        <v>0</v>
+      </c>
+      <c r="F401">
+        <v>0</v>
+      </c>
+      <c r="G401">
+        <v>1</v>
+      </c>
+      <c r="H401">
+        <v>1</v>
+      </c>
+      <c r="I401">
+        <v>1</v>
+      </c>
+      <c r="J401">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K401">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L401">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M401">
+        <v>-1</v>
+      </c>
+      <c r="N401">
+        <v>0</v>
+      </c>
+      <c r="O401">
+        <v>0</v>
+      </c>
+      <c r="P401">
+        <v>0</v>
+      </c>
+      <c r="Q401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A402">
+        <v>2850</v>
+      </c>
+      <c r="B402">
+        <v>320</v>
+      </c>
+      <c r="C402">
+        <v>-3060</v>
+      </c>
+      <c r="D402">
+        <v>0</v>
+      </c>
+      <c r="E402">
+        <v>0</v>
+      </c>
+      <c r="F402">
+        <v>0</v>
+      </c>
+      <c r="G402">
+        <v>1</v>
+      </c>
+      <c r="H402">
+        <v>1</v>
+      </c>
+      <c r="I402">
+        <v>1</v>
+      </c>
+      <c r="J402">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K402">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L402">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M402">
+        <v>-1</v>
+      </c>
+      <c r="N402">
+        <v>0</v>
+      </c>
+      <c r="O402">
+        <v>0</v>
+      </c>
+      <c r="P402">
+        <v>0</v>
+      </c>
+      <c r="Q402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A403">
+        <v>2930</v>
+      </c>
+      <c r="B403">
+        <v>320</v>
+      </c>
+      <c r="C403">
+        <v>-3000</v>
+      </c>
+      <c r="D403">
+        <v>0</v>
+      </c>
+      <c r="E403">
+        <v>0</v>
+      </c>
+      <c r="F403">
+        <v>0</v>
+      </c>
+      <c r="G403">
+        <v>1</v>
+      </c>
+      <c r="H403">
+        <v>1</v>
+      </c>
+      <c r="I403">
+        <v>1</v>
+      </c>
+      <c r="J403">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K403">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L403">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M403">
+        <v>-1</v>
+      </c>
+      <c r="N403">
+        <v>0</v>
+      </c>
+      <c r="O403">
+        <v>0</v>
+      </c>
+      <c r="P403">
+        <v>0</v>
+      </c>
+      <c r="Q403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A404">
+        <v>2970</v>
+      </c>
+      <c r="B404">
+        <v>320</v>
+      </c>
+      <c r="C404">
+        <v>-3060</v>
+      </c>
+      <c r="D404">
+        <v>0</v>
+      </c>
+      <c r="E404">
+        <v>0</v>
+      </c>
+      <c r="F404">
+        <v>0</v>
+      </c>
+      <c r="G404">
+        <v>1</v>
+      </c>
+      <c r="H404">
+        <v>1</v>
+      </c>
+      <c r="I404">
+        <v>1</v>
+      </c>
+      <c r="J404">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K404">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L404">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M404">
+        <v>-1</v>
+      </c>
+      <c r="N404">
+        <v>0</v>
+      </c>
+      <c r="O404">
+        <v>0</v>
+      </c>
+      <c r="P404">
+        <v>0</v>
+      </c>
+      <c r="Q404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A405">
+        <v>2590</v>
+      </c>
+      <c r="B405">
+        <v>320</v>
+      </c>
+      <c r="C405">
+        <v>-2960</v>
+      </c>
+      <c r="D405">
+        <v>0</v>
+      </c>
+      <c r="E405">
+        <v>0</v>
+      </c>
+      <c r="F405">
+        <v>0</v>
+      </c>
+      <c r="G405">
+        <v>1</v>
+      </c>
+      <c r="H405">
+        <v>1</v>
+      </c>
+      <c r="I405">
+        <v>1</v>
+      </c>
+      <c r="J405">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K405">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L405">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M405">
+        <v>-1</v>
+      </c>
+      <c r="N405">
+        <v>0</v>
+      </c>
+      <c r="O405">
+        <v>0</v>
+      </c>
+      <c r="P405">
+        <v>0</v>
+      </c>
+      <c r="Q405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A406">
+        <v>2630</v>
+      </c>
+      <c r="B406">
+        <v>320</v>
+      </c>
+      <c r="C406">
+        <v>-3040</v>
+      </c>
+      <c r="D406">
+        <v>0</v>
+      </c>
+      <c r="E406">
+        <v>0</v>
+      </c>
+      <c r="F406">
+        <v>0</v>
+      </c>
+      <c r="G406">
+        <v>1</v>
+      </c>
+      <c r="H406">
+        <v>1</v>
+      </c>
+      <c r="I406">
+        <v>1</v>
+      </c>
+      <c r="J406">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K406">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L406">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M406">
+        <v>-1</v>
+      </c>
+      <c r="N406">
+        <v>0</v>
+      </c>
+      <c r="O406">
+        <v>0</v>
+      </c>
+      <c r="P406">
+        <v>0</v>
+      </c>
+      <c r="Q406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A407">
+        <v>2610</v>
+      </c>
+      <c r="B407">
+        <v>320</v>
+      </c>
+      <c r="C407">
+        <v>-3100</v>
+      </c>
+      <c r="D407">
+        <v>0</v>
+      </c>
+      <c r="E407">
+        <v>0</v>
+      </c>
+      <c r="F407">
+        <v>0</v>
+      </c>
+      <c r="G407">
+        <v>1</v>
+      </c>
+      <c r="H407">
+        <v>1</v>
+      </c>
+      <c r="I407">
+        <v>1</v>
+      </c>
+      <c r="J407">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K407">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L407">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M407">
+        <v>-1</v>
+      </c>
+      <c r="N407">
+        <v>0</v>
+      </c>
+      <c r="O407">
+        <v>0</v>
+      </c>
+      <c r="P407">
+        <v>0</v>
+      </c>
+      <c r="Q407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A408">
+        <v>2730</v>
+      </c>
+      <c r="B408">
+        <v>320</v>
+      </c>
+      <c r="C408">
+        <v>-2980</v>
+      </c>
+      <c r="D408">
+        <v>0</v>
+      </c>
+      <c r="E408">
+        <v>0</v>
+      </c>
+      <c r="F408">
+        <v>0</v>
+      </c>
+      <c r="G408">
+        <v>1</v>
+      </c>
+      <c r="H408">
+        <v>1</v>
+      </c>
+      <c r="I408">
+        <v>1</v>
+      </c>
+      <c r="J408">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K408">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L408">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M408">
+        <v>-1</v>
+      </c>
+      <c r="N408">
+        <v>0</v>
+      </c>
+      <c r="O408">
+        <v>0</v>
+      </c>
+      <c r="P408">
+        <v>0</v>
+      </c>
+      <c r="Q408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A409">
+        <v>2790</v>
+      </c>
+      <c r="B409">
+        <v>320</v>
+      </c>
+      <c r="C409">
+        <v>-3080</v>
+      </c>
+      <c r="D409">
+        <v>0</v>
+      </c>
+      <c r="E409">
+        <v>0</v>
+      </c>
+      <c r="F409">
+        <v>0</v>
+      </c>
+      <c r="G409">
+        <v>1</v>
+      </c>
+      <c r="H409">
+        <v>1</v>
+      </c>
+      <c r="I409">
+        <v>1</v>
+      </c>
+      <c r="J409">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K409">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L409">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M409">
+        <v>-1</v>
+      </c>
+      <c r="N409">
+        <v>0</v>
+      </c>
+      <c r="O409">
+        <v>0</v>
+      </c>
+      <c r="P409">
+        <v>0</v>
+      </c>
+      <c r="Q409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A410">
+        <v>2850</v>
+      </c>
+      <c r="B410">
+        <v>320</v>
+      </c>
+      <c r="C410">
+        <v>-3000</v>
+      </c>
+      <c r="D410">
+        <v>0</v>
+      </c>
+      <c r="E410">
+        <v>0</v>
+      </c>
+      <c r="F410">
+        <v>0</v>
+      </c>
+      <c r="G410">
+        <v>1</v>
+      </c>
+      <c r="H410">
+        <v>1</v>
+      </c>
+      <c r="I410">
+        <v>1</v>
+      </c>
+      <c r="J410">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K410">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L410">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M410">
+        <v>-1</v>
+      </c>
+      <c r="N410">
+        <v>0</v>
+      </c>
+      <c r="O410">
+        <v>0</v>
+      </c>
+      <c r="P410">
+        <v>0</v>
+      </c>
+      <c r="Q410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A411">
+        <v>2910</v>
+      </c>
+      <c r="B411">
+        <v>320</v>
+      </c>
+      <c r="C411">
+        <v>-3080</v>
+      </c>
+      <c r="D411">
+        <v>0</v>
+      </c>
+      <c r="E411">
+        <v>0</v>
+      </c>
+      <c r="F411">
+        <v>0</v>
+      </c>
+      <c r="G411">
+        <v>1</v>
+      </c>
+      <c r="H411">
+        <v>1</v>
+      </c>
+      <c r="I411">
+        <v>1</v>
+      </c>
+      <c r="J411">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K411">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L411">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M411">
+        <v>-1</v>
+      </c>
+      <c r="N411">
+        <v>0</v>
+      </c>
+      <c r="O411">
+        <v>0</v>
+      </c>
+      <c r="P411">
+        <v>0</v>
+      </c>
+      <c r="Q411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A412">
+        <v>2950</v>
+      </c>
+      <c r="B412">
+        <v>320</v>
+      </c>
+      <c r="C412">
+        <v>-3020</v>
+      </c>
+      <c r="D412">
+        <v>0</v>
+      </c>
+      <c r="E412">
+        <v>0</v>
+      </c>
+      <c r="F412">
+        <v>0</v>
+      </c>
+      <c r="G412">
+        <v>1</v>
+      </c>
+      <c r="H412">
+        <v>1</v>
+      </c>
+      <c r="I412">
+        <v>1</v>
+      </c>
+      <c r="J412">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K412">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L412">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M412">
+        <v>-1</v>
+      </c>
+      <c r="N412">
+        <v>0</v>
+      </c>
+      <c r="O412">
+        <v>0</v>
+      </c>
+      <c r="P412">
+        <v>0</v>
+      </c>
+      <c r="Q412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A413">
+        <v>2650</v>
+      </c>
+      <c r="B413">
+        <v>320</v>
+      </c>
+      <c r="C413">
+        <v>-2980</v>
+      </c>
+      <c r="D413">
+        <v>0</v>
+      </c>
+      <c r="E413">
+        <v>0</v>
+      </c>
+      <c r="F413">
+        <v>0</v>
+      </c>
+      <c r="G413">
+        <v>1</v>
+      </c>
+      <c r="H413">
+        <v>1</v>
+      </c>
+      <c r="I413">
+        <v>1</v>
+      </c>
+      <c r="J413">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K413">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L413">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M413">
+        <v>-1</v>
+      </c>
+      <c r="N413">
+        <v>0</v>
+      </c>
+      <c r="O413">
+        <v>0</v>
+      </c>
+      <c r="P413">
+        <v>0</v>
+      </c>
+      <c r="Q413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A414">
+        <v>2670</v>
+      </c>
+      <c r="B414">
+        <v>320</v>
+      </c>
+      <c r="C414">
+        <v>-3100</v>
+      </c>
+      <c r="D414">
+        <v>0</v>
+      </c>
+      <c r="E414">
+        <v>0</v>
+      </c>
+      <c r="F414">
+        <v>0</v>
+      </c>
+      <c r="G414">
+        <v>1</v>
+      </c>
+      <c r="H414">
+        <v>1</v>
+      </c>
+      <c r="I414">
+        <v>1</v>
+      </c>
+      <c r="J414">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K414">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L414">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M414">
+        <v>-1</v>
+      </c>
+      <c r="N414">
+        <v>0</v>
+      </c>
+      <c r="O414">
+        <v>0</v>
+      </c>
+      <c r="P414">
+        <v>0</v>
+      </c>
+      <c r="Q414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A415">
+        <v>2750</v>
+      </c>
+      <c r="B415">
+        <v>320</v>
+      </c>
+      <c r="C415">
+        <v>-3040</v>
+      </c>
+      <c r="D415">
+        <v>0</v>
+      </c>
+      <c r="E415">
+        <v>0</v>
+      </c>
+      <c r="F415">
+        <v>0</v>
+      </c>
+      <c r="G415">
+        <v>1</v>
+      </c>
+      <c r="H415">
+        <v>1</v>
+      </c>
+      <c r="I415">
+        <v>1</v>
+      </c>
+      <c r="J415">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K415">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L415">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M415">
+        <v>-1</v>
+      </c>
+      <c r="N415">
+        <v>0</v>
+      </c>
+      <c r="O415">
+        <v>0</v>
+      </c>
+      <c r="P415">
+        <v>0</v>
+      </c>
+      <c r="Q415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A416">
+        <v>2810</v>
+      </c>
+      <c r="B416">
+        <v>320</v>
+      </c>
+      <c r="C416">
+        <v>-2980</v>
+      </c>
+      <c r="D416">
+        <v>0</v>
+      </c>
+      <c r="E416">
+        <v>0</v>
+      </c>
+      <c r="F416">
+        <v>0</v>
+      </c>
+      <c r="G416">
+        <v>1</v>
+      </c>
+      <c r="H416">
+        <v>1</v>
+      </c>
+      <c r="I416">
+        <v>1</v>
+      </c>
+      <c r="J416">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K416">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L416">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M416">
+        <v>-1</v>
+      </c>
+      <c r="N416">
+        <v>0</v>
+      </c>
+      <c r="O416">
+        <v>0</v>
+      </c>
+      <c r="P416">
+        <v>0</v>
+      </c>
+      <c r="Q416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A417">
+        <v>2890</v>
+      </c>
+      <c r="B417">
+        <v>320</v>
+      </c>
+      <c r="C417">
+        <v>-3080</v>
+      </c>
+      <c r="D417">
+        <v>0</v>
+      </c>
+      <c r="E417">
+        <v>0</v>
+      </c>
+      <c r="F417">
+        <v>0</v>
+      </c>
+      <c r="G417">
+        <v>1</v>
+      </c>
+      <c r="H417">
+        <v>1</v>
+      </c>
+      <c r="I417">
+        <v>1</v>
+      </c>
+      <c r="J417">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K417">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L417">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M417">
+        <v>-1</v>
+      </c>
+      <c r="N417">
+        <v>0</v>
+      </c>
+      <c r="O417">
+        <v>0</v>
+      </c>
+      <c r="P417">
+        <v>0</v>
+      </c>
+      <c r="Q417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A418">
+        <v>2950</v>
+      </c>
+      <c r="B418">
+        <v>320</v>
+      </c>
+      <c r="C418">
+        <v>-3060</v>
+      </c>
+      <c r="D418">
+        <v>0</v>
+      </c>
+      <c r="E418">
+        <v>0</v>
+      </c>
+      <c r="F418">
+        <v>0</v>
+      </c>
+      <c r="G418">
+        <v>1</v>
+      </c>
+      <c r="H418">
+        <v>1</v>
+      </c>
+      <c r="I418">
+        <v>1</v>
+      </c>
+      <c r="J418">
+        <f t="shared" si="198"/>
+        <v>20</v>
+      </c>
+      <c r="K418">
+        <f t="shared" si="199"/>
+        <v>20</v>
+      </c>
+      <c r="L418">
+        <f t="shared" si="200"/>
+        <v>20</v>
+      </c>
+      <c r="M418">
+        <v>-1</v>
+      </c>
+      <c r="N418">
+        <v>0</v>
+      </c>
+      <c r="O418">
+        <v>0</v>
+      </c>
+      <c r="P418">
+        <v>0</v>
+      </c>
+      <c r="Q418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A419">
+        <v>3000</v>
+      </c>
+      <c r="B419">
+        <v>420</v>
+      </c>
+      <c r="C419">
+        <v>-2550</v>
+      </c>
+      <c r="D419">
+        <v>0</v>
+      </c>
+      <c r="E419">
+        <v>0</v>
+      </c>
+      <c r="F419">
+        <v>0</v>
+      </c>
+      <c r="G419">
+        <v>2</v>
+      </c>
+      <c r="H419">
+        <v>2</v>
+      </c>
+      <c r="I419">
+        <v>2</v>
+      </c>
+      <c r="J419">
+        <f t="shared" si="198"/>
+        <v>40</v>
+      </c>
+      <c r="K419">
+        <v>80</v>
+      </c>
+      <c r="L419">
+        <f t="shared" si="200"/>
+        <v>40</v>
+      </c>
+      <c r="M419">
+        <v>-1</v>
+      </c>
+      <c r="N419">
+        <v>0</v>
+      </c>
+      <c r="O419">
+        <v>0</v>
+      </c>
+      <c r="P419">
+        <v>0</v>
+      </c>
+      <c r="Q419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A420">
+        <v>3960</v>
+      </c>
+      <c r="B420">
+        <v>420</v>
+      </c>
+      <c r="C420">
+        <v>-2550</v>
+      </c>
+      <c r="D420">
+        <v>0</v>
+      </c>
+      <c r="E420">
+        <v>0</v>
+      </c>
+      <c r="F420">
+        <v>0</v>
+      </c>
+      <c r="G420">
+        <v>2</v>
+      </c>
+      <c r="H420">
+        <v>2</v>
+      </c>
+      <c r="I420">
+        <v>2</v>
+      </c>
+      <c r="J420">
+        <f t="shared" ref="J420:J422" si="201">G420*20</f>
+        <v>40</v>
+      </c>
+      <c r="K420">
+        <v>81</v>
+      </c>
+      <c r="L420">
+        <f t="shared" ref="L420:L422" si="202">I420*20</f>
+        <v>40</v>
+      </c>
+      <c r="M420">
+        <v>-1</v>
+      </c>
+      <c r="N420">
+        <v>0</v>
+      </c>
+      <c r="O420">
+        <v>0</v>
+      </c>
+      <c r="P420">
+        <v>0</v>
+      </c>
+      <c r="Q420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A421">
+        <v>3960</v>
+      </c>
+      <c r="B421">
+        <v>420</v>
+      </c>
+      <c r="C421">
+        <v>-3510</v>
+      </c>
+      <c r="D421">
+        <v>0</v>
+      </c>
+      <c r="E421">
+        <v>0</v>
+      </c>
+      <c r="F421">
+        <v>0</v>
+      </c>
+      <c r="G421">
+        <v>2</v>
+      </c>
+      <c r="H421">
+        <v>2</v>
+      </c>
+      <c r="I421">
+        <v>2</v>
+      </c>
+      <c r="J421">
+        <f t="shared" si="201"/>
+        <v>40</v>
+      </c>
+      <c r="K421">
+        <v>82</v>
+      </c>
+      <c r="L421">
+        <f t="shared" si="202"/>
+        <v>40</v>
+      </c>
+      <c r="M421">
+        <v>-1</v>
+      </c>
+      <c r="N421">
+        <v>0</v>
+      </c>
+      <c r="O421">
+        <v>0</v>
+      </c>
+      <c r="P421">
+        <v>0</v>
+      </c>
+      <c r="Q421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A422">
+        <v>3000</v>
+      </c>
+      <c r="B422">
+        <v>420</v>
+      </c>
+      <c r="C422">
+        <v>-3510</v>
+      </c>
+      <c r="D422">
+        <v>0</v>
+      </c>
+      <c r="E422">
+        <v>0</v>
+      </c>
+      <c r="F422">
+        <v>0</v>
+      </c>
+      <c r="G422">
+        <v>2</v>
+      </c>
+      <c r="H422">
+        <v>2</v>
+      </c>
+      <c r="I422">
+        <v>2</v>
+      </c>
+      <c r="J422">
+        <f t="shared" si="201"/>
+        <v>40</v>
+      </c>
+      <c r="K422">
+        <v>83</v>
+      </c>
+      <c r="L422">
+        <f t="shared" si="202"/>
+        <v>40</v>
+      </c>
+      <c r="M422">
+        <v>-1</v>
+      </c>
+      <c r="N422">
+        <v>0</v>
+      </c>
+      <c r="O422">
+        <v>0</v>
+      </c>
+      <c r="P422">
+        <v>0</v>
+      </c>
+      <c r="Q422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A423">
+        <v>3050</v>
+      </c>
+      <c r="B423">
+        <v>360</v>
+      </c>
+      <c r="C423">
+        <v>-2540</v>
+      </c>
+      <c r="D423">
+        <v>0</v>
+      </c>
+      <c r="E423">
+        <v>0</v>
+      </c>
+      <c r="F423">
+        <v>0</v>
+      </c>
+      <c r="G423">
+        <v>1</v>
+      </c>
+      <c r="H423">
+        <v>1</v>
+      </c>
+      <c r="I423">
+        <v>1</v>
+      </c>
+      <c r="J423">
+        <v>60</v>
+      </c>
+      <c r="K423">
+        <f t="shared" ref="K423" si="203">H423*20</f>
+        <v>20</v>
+      </c>
+      <c r="L423">
+        <v>20</v>
+      </c>
+      <c r="M423">
+        <v>-1</v>
+      </c>
+      <c r="N423">
+        <v>0</v>
+      </c>
+      <c r="O423">
+        <v>0</v>
+      </c>
+      <c r="P423">
+        <v>0</v>
+      </c>
+      <c r="Q423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A424">
+        <v>2990</v>
+      </c>
+      <c r="B424">
+        <v>360</v>
+      </c>
+      <c r="C424">
+        <v>-2600</v>
+      </c>
+      <c r="D424">
+        <v>0</v>
+      </c>
+      <c r="E424">
+        <v>4.71</v>
+      </c>
+      <c r="F424">
+        <v>0</v>
+      </c>
+      <c r="G424">
+        <v>1</v>
+      </c>
+      <c r="H424">
+        <v>1</v>
+      </c>
+      <c r="I424">
+        <v>1</v>
+      </c>
+      <c r="J424">
+        <v>20</v>
+      </c>
+      <c r="K424">
+        <f t="shared" ref="K424" si="204">H424*20</f>
+        <v>20</v>
+      </c>
+      <c r="L424">
+        <v>60</v>
+      </c>
+      <c r="M424">
+        <v>-1</v>
+      </c>
+      <c r="N424">
+        <v>0</v>
+      </c>
+      <c r="O424">
+        <v>0</v>
+      </c>
+      <c r="P424">
+        <v>0</v>
+      </c>
+      <c r="Q424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A425">
+        <v>3910</v>
+      </c>
+      <c r="B425">
+        <v>360</v>
+      </c>
+      <c r="C425">
+        <v>-3520</v>
+      </c>
+      <c r="D425">
+        <v>0</v>
+      </c>
+      <c r="E425">
+        <v>3.14</v>
+      </c>
+      <c r="F425">
+        <v>0</v>
+      </c>
+      <c r="G425">
+        <v>1</v>
+      </c>
+      <c r="H425">
+        <v>1</v>
+      </c>
+      <c r="I425">
+        <v>1</v>
+      </c>
+      <c r="J425">
+        <v>60</v>
+      </c>
+      <c r="K425">
+        <f t="shared" ref="K425" si="205">H425*20</f>
+        <v>20</v>
+      </c>
+      <c r="L425">
+        <v>20</v>
+      </c>
+      <c r="M425">
+        <v>-1</v>
+      </c>
+      <c r="N425">
+        <v>0</v>
+      </c>
+      <c r="O425">
+        <v>0</v>
+      </c>
+      <c r="P425">
+        <v>0</v>
+      </c>
+      <c r="Q425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A426">
+        <v>3970</v>
+      </c>
+      <c r="B426">
+        <v>360</v>
+      </c>
+      <c r="C426">
+        <v>-3460</v>
+      </c>
+      <c r="D426">
+        <v>0</v>
+      </c>
+      <c r="E426">
+        <v>1.57</v>
+      </c>
+      <c r="F426">
+        <v>0</v>
+      </c>
+      <c r="G426">
+        <v>1</v>
+      </c>
+      <c r="H426">
+        <v>1</v>
+      </c>
+      <c r="I426">
+        <v>1</v>
+      </c>
+      <c r="J426">
+        <v>20</v>
+      </c>
+      <c r="K426">
+        <f t="shared" ref="K426:K427" si="206">H426*20</f>
+        <v>20</v>
+      </c>
+      <c r="L426">
+        <v>60</v>
+      </c>
+      <c r="M426">
+        <v>-1</v>
+      </c>
+      <c r="N426">
+        <v>0</v>
+      </c>
+      <c r="O426">
+        <v>0</v>
+      </c>
+      <c r="P426">
+        <v>0</v>
+      </c>
+      <c r="Q426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A427">
+        <v>3910</v>
+      </c>
+      <c r="B427">
+        <v>360</v>
+      </c>
+      <c r="C427">
+        <v>-2540</v>
+      </c>
+      <c r="D427">
+        <v>0</v>
+      </c>
+      <c r="E427">
+        <v>0</v>
+      </c>
+      <c r="F427">
+        <v>0</v>
+      </c>
+      <c r="G427">
+        <v>1</v>
+      </c>
+      <c r="H427">
+        <v>1</v>
+      </c>
+      <c r="I427">
+        <v>1</v>
+      </c>
+      <c r="J427">
+        <v>60</v>
+      </c>
+      <c r="K427">
+        <f t="shared" si="206"/>
+        <v>20</v>
+      </c>
+      <c r="L427">
+        <v>20</v>
+      </c>
+      <c r="M427">
+        <v>-1</v>
+      </c>
+      <c r="N427">
+        <v>0</v>
+      </c>
+      <c r="O427">
+        <v>0</v>
+      </c>
+      <c r="P427">
+        <v>0</v>
+      </c>
+      <c r="Q427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A428">
+        <v>3970</v>
+      </c>
+      <c r="B428">
+        <v>360</v>
+      </c>
+      <c r="C428">
+        <v>-2600</v>
+      </c>
+      <c r="D428">
+        <v>0</v>
+      </c>
+      <c r="E428">
+        <v>1.57</v>
+      </c>
+      <c r="F428">
+        <v>0</v>
+      </c>
+      <c r="G428">
+        <v>1</v>
+      </c>
+      <c r="H428">
+        <v>1</v>
+      </c>
+      <c r="I428">
+        <v>1</v>
+      </c>
+      <c r="J428">
+        <v>20</v>
+      </c>
+      <c r="K428">
+        <f t="shared" ref="K428:K431" si="207">H428*20</f>
+        <v>20</v>
+      </c>
+      <c r="L428">
+        <v>60</v>
+      </c>
+      <c r="M428">
+        <v>-1</v>
+      </c>
+      <c r="N428">
+        <v>0</v>
+      </c>
+      <c r="O428">
+        <v>0</v>
+      </c>
+      <c r="P428">
+        <v>0</v>
+      </c>
+      <c r="Q428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A429">
+        <v>3050</v>
+      </c>
+      <c r="B429">
+        <v>360</v>
+      </c>
+      <c r="C429">
+        <v>-3520</v>
+      </c>
+      <c r="D429">
+        <v>0</v>
+      </c>
+      <c r="E429">
+        <v>3.14</v>
+      </c>
+      <c r="F429">
+        <v>0</v>
+      </c>
+      <c r="G429">
+        <v>1</v>
+      </c>
+      <c r="H429">
+        <v>1</v>
+      </c>
+      <c r="I429">
+        <v>1</v>
+      </c>
+      <c r="J429">
+        <v>60</v>
+      </c>
+      <c r="K429">
+        <f t="shared" si="207"/>
+        <v>20</v>
+      </c>
+      <c r="L429">
+        <v>20</v>
+      </c>
+      <c r="M429">
+        <v>-1</v>
+      </c>
+      <c r="N429">
+        <v>0</v>
+      </c>
+      <c r="O429">
+        <v>0</v>
+      </c>
+      <c r="P429">
+        <v>0</v>
+      </c>
+      <c r="Q429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A430">
+        <v>2990</v>
+      </c>
+      <c r="B430">
+        <v>360</v>
+      </c>
+      <c r="C430">
+        <v>-3460</v>
+      </c>
+      <c r="D430">
+        <v>0</v>
+      </c>
+      <c r="E430">
+        <v>4.71</v>
+      </c>
+      <c r="F430">
+        <v>0</v>
+      </c>
+      <c r="G430">
+        <v>1</v>
+      </c>
+      <c r="H430">
+        <v>1</v>
+      </c>
+      <c r="I430">
+        <v>1</v>
+      </c>
+      <c r="J430">
+        <v>20</v>
+      </c>
+      <c r="K430">
+        <f t="shared" si="207"/>
+        <v>20</v>
+      </c>
+      <c r="L430">
+        <v>60</v>
+      </c>
+      <c r="M430">
+        <v>-1</v>
+      </c>
+      <c r="N430">
+        <v>0</v>
+      </c>
+      <c r="O430">
+        <v>0</v>
+      </c>
+      <c r="P430">
+        <v>0</v>
+      </c>
+      <c r="Q430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A431">
+        <v>3470</v>
+      </c>
+      <c r="B431">
+        <v>340</v>
+      </c>
+      <c r="C431">
+        <v>-2760</v>
+      </c>
+      <c r="D431">
+        <v>0</v>
+      </c>
+      <c r="E431">
+        <v>0</v>
+      </c>
+      <c r="F431">
+        <v>0</v>
+      </c>
+      <c r="G431">
+        <v>1</v>
+      </c>
+      <c r="H431">
+        <v>1</v>
+      </c>
+      <c r="I431">
+        <v>1</v>
+      </c>
+      <c r="J431">
+        <f t="shared" ref="J431" si="208">G431*20</f>
+        <v>20</v>
+      </c>
+      <c r="K431">
+        <f t="shared" si="207"/>
+        <v>20</v>
+      </c>
+      <c r="L431">
+        <f t="shared" ref="L431" si="209">I431*20</f>
+        <v>20</v>
+      </c>
+      <c r="M431">
+        <v>-1</v>
+      </c>
+      <c r="N431">
+        <v>0</v>
+      </c>
+      <c r="O431">
+        <v>0</v>
+      </c>
+      <c r="P431">
+        <v>0</v>
+      </c>
+      <c r="Q431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A432">
+        <v>3630</v>
+      </c>
+      <c r="B432">
+        <v>340</v>
+      </c>
+      <c r="C432">
+        <v>-2840</v>
+      </c>
+      <c r="D432">
+        <v>0</v>
+      </c>
+      <c r="E432">
+        <v>0</v>
+      </c>
+      <c r="F432">
+        <v>0</v>
+      </c>
+      <c r="G432">
+        <v>1</v>
+      </c>
+      <c r="H432">
+        <v>1</v>
+      </c>
+      <c r="I432">
+        <v>1</v>
+      </c>
+      <c r="J432">
+        <f t="shared" ref="J432:J470" si="210">G432*20</f>
+        <v>20</v>
+      </c>
+      <c r="K432">
+        <f t="shared" ref="K432:K470" si="211">H432*20</f>
+        <v>20</v>
+      </c>
+      <c r="L432">
+        <f t="shared" ref="L432:L470" si="212">I432*20</f>
+        <v>20</v>
+      </c>
+      <c r="M432">
+        <v>-1</v>
+      </c>
+      <c r="N432">
+        <v>0</v>
+      </c>
+      <c r="O432">
+        <v>0</v>
+      </c>
+      <c r="P432">
+        <v>0</v>
+      </c>
+      <c r="Q432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A433">
+        <v>3710</v>
+      </c>
+      <c r="B433">
+        <v>340</v>
+      </c>
+      <c r="C433">
+        <v>-3000</v>
+      </c>
+      <c r="D433">
+        <v>0</v>
+      </c>
+      <c r="E433">
+        <v>0</v>
+      </c>
+      <c r="F433">
+        <v>0</v>
+      </c>
+      <c r="G433">
+        <v>1</v>
+      </c>
+      <c r="H433">
+        <v>1</v>
+      </c>
+      <c r="I433">
+        <v>1</v>
+      </c>
+      <c r="J433">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K433">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L433">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M433">
+        <v>-1</v>
+      </c>
+      <c r="N433">
+        <v>0</v>
+      </c>
+      <c r="O433">
+        <v>0</v>
+      </c>
+      <c r="P433">
+        <v>0</v>
+      </c>
+      <c r="Q433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A434">
+        <v>3670</v>
+      </c>
+      <c r="B434">
+        <v>340</v>
+      </c>
+      <c r="C434">
+        <v>-3180</v>
+      </c>
+      <c r="D434">
+        <v>0</v>
+      </c>
+      <c r="E434">
+        <v>0</v>
+      </c>
+      <c r="F434">
+        <v>0</v>
+      </c>
+      <c r="G434">
+        <v>1</v>
+      </c>
+      <c r="H434">
+        <v>1</v>
+      </c>
+      <c r="I434">
+        <v>1</v>
+      </c>
+      <c r="J434">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K434">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L434">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M434">
+        <v>-1</v>
+      </c>
+      <c r="N434">
+        <v>0</v>
+      </c>
+      <c r="O434">
+        <v>0</v>
+      </c>
+      <c r="P434">
+        <v>0</v>
+      </c>
+      <c r="Q434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A435">
+        <v>3530</v>
+      </c>
+      <c r="B435">
+        <v>340</v>
+      </c>
+      <c r="C435">
+        <v>-3320</v>
+      </c>
+      <c r="D435">
+        <v>0</v>
+      </c>
+      <c r="E435">
+        <v>0</v>
+      </c>
+      <c r="F435">
+        <v>0</v>
+      </c>
+      <c r="G435">
+        <v>1</v>
+      </c>
+      <c r="H435">
+        <v>1</v>
+      </c>
+      <c r="I435">
+        <v>1</v>
+      </c>
+      <c r="J435">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K435">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L435">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M435">
+        <v>-1</v>
+      </c>
+      <c r="N435">
+        <v>0</v>
+      </c>
+      <c r="O435">
+        <v>0</v>
+      </c>
+      <c r="P435">
+        <v>0</v>
+      </c>
+      <c r="Q435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A436">
+        <v>3350</v>
+      </c>
+      <c r="B436">
+        <v>340</v>
+      </c>
+      <c r="C436">
+        <v>-3300</v>
+      </c>
+      <c r="D436">
+        <v>0</v>
+      </c>
+      <c r="E436">
+        <v>0</v>
+      </c>
+      <c r="F436">
+        <v>0</v>
+      </c>
+      <c r="G436">
+        <v>1</v>
+      </c>
+      <c r="H436">
+        <v>1</v>
+      </c>
+      <c r="I436">
+        <v>1</v>
+      </c>
+      <c r="J436">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K436">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L436">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M436">
+        <v>-1</v>
+      </c>
+      <c r="N436">
+        <v>0</v>
+      </c>
+      <c r="O436">
+        <v>0</v>
+      </c>
+      <c r="P436">
+        <v>0</v>
+      </c>
+      <c r="Q436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A437">
+        <v>3190</v>
+      </c>
+      <c r="B437">
+        <v>340</v>
+      </c>
+      <c r="C437">
+        <v>-3160</v>
+      </c>
+      <c r="D437">
+        <v>0</v>
+      </c>
+      <c r="E437">
+        <v>0</v>
+      </c>
+      <c r="F437">
+        <v>0</v>
+      </c>
+      <c r="G437">
+        <v>1</v>
+      </c>
+      <c r="H437">
+        <v>1</v>
+      </c>
+      <c r="I437">
+        <v>1</v>
+      </c>
+      <c r="J437">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K437">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L437">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M437">
+        <v>-1</v>
+      </c>
+      <c r="N437">
+        <v>0</v>
+      </c>
+      <c r="O437">
+        <v>0</v>
+      </c>
+      <c r="P437">
+        <v>0</v>
+      </c>
+      <c r="Q437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A438">
+        <v>3130</v>
+      </c>
+      <c r="B438">
+        <v>340</v>
+      </c>
+      <c r="C438">
+        <v>-2960</v>
+      </c>
+      <c r="D438">
+        <v>0</v>
+      </c>
+      <c r="E438">
+        <v>0</v>
+      </c>
+      <c r="F438">
+        <v>0</v>
+      </c>
+      <c r="G438">
+        <v>1</v>
+      </c>
+      <c r="H438">
+        <v>1</v>
+      </c>
+      <c r="I438">
+        <v>1</v>
+      </c>
+      <c r="J438">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K438">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L438">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M438">
+        <v>-1</v>
+      </c>
+      <c r="N438">
+        <v>0</v>
+      </c>
+      <c r="O438">
+        <v>0</v>
+      </c>
+      <c r="P438">
+        <v>0</v>
+      </c>
+      <c r="Q438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A439">
+        <v>3230</v>
+      </c>
+      <c r="B439">
+        <v>340</v>
+      </c>
+      <c r="C439">
+        <v>-2800</v>
+      </c>
+      <c r="D439">
+        <v>0</v>
+      </c>
+      <c r="E439">
+        <v>0</v>
+      </c>
+      <c r="F439">
+        <v>0</v>
+      </c>
+      <c r="G439">
+        <v>1</v>
+      </c>
+      <c r="H439">
+        <v>1</v>
+      </c>
+      <c r="I439">
+        <v>1</v>
+      </c>
+      <c r="J439">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K439">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L439">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M439">
+        <v>-1</v>
+      </c>
+      <c r="N439">
+        <v>0</v>
+      </c>
+      <c r="O439">
+        <v>0</v>
+      </c>
+      <c r="P439">
+        <v>0</v>
+      </c>
+      <c r="Q439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A440">
+        <v>3370</v>
+      </c>
+      <c r="B440">
+        <v>340</v>
+      </c>
+      <c r="C440">
+        <v>-2720</v>
+      </c>
+      <c r="D440">
+        <v>0</v>
+      </c>
+      <c r="E440">
+        <v>0</v>
+      </c>
+      <c r="F440">
+        <v>0</v>
+      </c>
+      <c r="G440">
+        <v>1</v>
+      </c>
+      <c r="H440">
+        <v>1</v>
+      </c>
+      <c r="I440">
+        <v>1</v>
+      </c>
+      <c r="J440">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K440">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L440">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M440">
+        <v>-1</v>
+      </c>
+      <c r="N440">
+        <v>0</v>
+      </c>
+      <c r="O440">
+        <v>0</v>
+      </c>
+      <c r="P440">
+        <v>0</v>
+      </c>
+      <c r="Q440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A441">
+        <v>3390</v>
+      </c>
+      <c r="B441">
+        <v>340</v>
+      </c>
+      <c r="C441">
+        <v>-2600</v>
+      </c>
+      <c r="D441">
+        <v>0</v>
+      </c>
+      <c r="E441">
+        <v>0</v>
+      </c>
+      <c r="F441">
+        <v>0</v>
+      </c>
+      <c r="G441">
+        <v>1</v>
+      </c>
+      <c r="H441">
+        <v>1</v>
+      </c>
+      <c r="I441">
+        <v>1</v>
+      </c>
+      <c r="J441">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K441">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L441">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M441">
+        <v>-1</v>
+      </c>
+      <c r="N441">
+        <v>0</v>
+      </c>
+      <c r="O441">
+        <v>0</v>
+      </c>
+      <c r="P441">
+        <v>0</v>
+      </c>
+      <c r="Q441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A442">
+        <v>3570</v>
+      </c>
+      <c r="B442">
+        <v>340</v>
+      </c>
+      <c r="C442">
+        <v>-2640</v>
+      </c>
+      <c r="D442">
+        <v>0</v>
+      </c>
+      <c r="E442">
+        <v>0</v>
+      </c>
+      <c r="F442">
+        <v>0</v>
+      </c>
+      <c r="G442">
+        <v>1</v>
+      </c>
+      <c r="H442">
+        <v>1</v>
+      </c>
+      <c r="I442">
+        <v>1</v>
+      </c>
+      <c r="J442">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K442">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L442">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M442">
+        <v>-1</v>
+      </c>
+      <c r="N442">
+        <v>0</v>
+      </c>
+      <c r="O442">
+        <v>0</v>
+      </c>
+      <c r="P442">
+        <v>0</v>
+      </c>
+      <c r="Q442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A443">
+        <v>3790</v>
+      </c>
+      <c r="B443">
+        <v>340</v>
+      </c>
+      <c r="C443">
+        <v>-2760</v>
+      </c>
+      <c r="D443">
+        <v>0</v>
+      </c>
+      <c r="E443">
+        <v>0</v>
+      </c>
+      <c r="F443">
+        <v>0</v>
+      </c>
+      <c r="G443">
+        <v>1</v>
+      </c>
+      <c r="H443">
+        <v>1</v>
+      </c>
+      <c r="I443">
+        <v>1</v>
+      </c>
+      <c r="J443">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K443">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L443">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M443">
+        <v>-1</v>
+      </c>
+      <c r="N443">
+        <v>0</v>
+      </c>
+      <c r="O443">
+        <v>0</v>
+      </c>
+      <c r="P443">
+        <v>0</v>
+      </c>
+      <c r="Q443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A444">
+        <v>3870</v>
+      </c>
+      <c r="B444">
+        <v>340</v>
+      </c>
+      <c r="C444">
+        <v>-2920</v>
+      </c>
+      <c r="D444">
+        <v>0</v>
+      </c>
+      <c r="E444">
+        <v>0</v>
+      </c>
+      <c r="F444">
+        <v>0</v>
+      </c>
+      <c r="G444">
+        <v>1</v>
+      </c>
+      <c r="H444">
+        <v>1</v>
+      </c>
+      <c r="I444">
+        <v>1</v>
+      </c>
+      <c r="J444">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K444">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L444">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M444">
+        <v>-1</v>
+      </c>
+      <c r="N444">
+        <v>0</v>
+      </c>
+      <c r="O444">
+        <v>0</v>
+      </c>
+      <c r="P444">
+        <v>0</v>
+      </c>
+      <c r="Q444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A445">
+        <v>3830</v>
+      </c>
+      <c r="B445">
+        <v>340</v>
+      </c>
+      <c r="C445">
+        <v>-3120</v>
+      </c>
+      <c r="D445">
+        <v>0</v>
+      </c>
+      <c r="E445">
+        <v>0</v>
+      </c>
+      <c r="F445">
+        <v>0</v>
+      </c>
+      <c r="G445">
+        <v>1</v>
+      </c>
+      <c r="H445">
+        <v>1</v>
+      </c>
+      <c r="I445">
+        <v>1</v>
+      </c>
+      <c r="J445">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K445">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L445">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M445">
+        <v>-1</v>
+      </c>
+      <c r="N445">
+        <v>0</v>
+      </c>
+      <c r="O445">
+        <v>0</v>
+      </c>
+      <c r="P445">
+        <v>0</v>
+      </c>
+      <c r="Q445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A446">
+        <v>3750</v>
+      </c>
+      <c r="B446">
+        <v>340</v>
+      </c>
+      <c r="C446">
+        <v>-3280</v>
+      </c>
+      <c r="D446">
+        <v>0</v>
+      </c>
+      <c r="E446">
+        <v>0</v>
+      </c>
+      <c r="F446">
+        <v>0</v>
+      </c>
+      <c r="G446">
+        <v>1</v>
+      </c>
+      <c r="H446">
+        <v>1</v>
+      </c>
+      <c r="I446">
+        <v>1</v>
+      </c>
+      <c r="J446">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K446">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L446">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M446">
+        <v>-1</v>
+      </c>
+      <c r="N446">
+        <v>0</v>
+      </c>
+      <c r="O446">
+        <v>0</v>
+      </c>
+      <c r="P446">
+        <v>0</v>
+      </c>
+      <c r="Q446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A447">
+        <v>3590</v>
+      </c>
+      <c r="B447">
+        <v>340</v>
+      </c>
+      <c r="C447">
+        <v>-3420</v>
+      </c>
+      <c r="D447">
+        <v>0</v>
+      </c>
+      <c r="E447">
+        <v>0</v>
+      </c>
+      <c r="F447">
+        <v>0</v>
+      </c>
+      <c r="G447">
+        <v>1</v>
+      </c>
+      <c r="H447">
+        <v>1</v>
+      </c>
+      <c r="I447">
+        <v>1</v>
+      </c>
+      <c r="J447">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K447">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L447">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M447">
+        <v>-1</v>
+      </c>
+      <c r="N447">
+        <v>0</v>
+      </c>
+      <c r="O447">
+        <v>0</v>
+      </c>
+      <c r="P447">
+        <v>0</v>
+      </c>
+      <c r="Q447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A448">
+        <v>3410</v>
+      </c>
+      <c r="B448">
+        <v>340</v>
+      </c>
+      <c r="C448">
+        <v>-3440</v>
+      </c>
+      <c r="D448">
+        <v>0</v>
+      </c>
+      <c r="E448">
+        <v>0</v>
+      </c>
+      <c r="F448">
+        <v>0</v>
+      </c>
+      <c r="G448">
+        <v>1</v>
+      </c>
+      <c r="H448">
+        <v>1</v>
+      </c>
+      <c r="I448">
+        <v>1</v>
+      </c>
+      <c r="J448">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K448">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L448">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M448">
+        <v>-1</v>
+      </c>
+      <c r="N448">
+        <v>0</v>
+      </c>
+      <c r="O448">
+        <v>0</v>
+      </c>
+      <c r="P448">
+        <v>0</v>
+      </c>
+      <c r="Q448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A449">
+        <v>3210</v>
+      </c>
+      <c r="B449">
+        <v>340</v>
+      </c>
+      <c r="C449">
+        <v>-3340</v>
+      </c>
+      <c r="D449">
+        <v>0</v>
+      </c>
+      <c r="E449">
+        <v>0</v>
+      </c>
+      <c r="F449">
+        <v>0</v>
+      </c>
+      <c r="G449">
+        <v>1</v>
+      </c>
+      <c r="H449">
+        <v>1</v>
+      </c>
+      <c r="I449">
+        <v>1</v>
+      </c>
+      <c r="J449">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K449">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L449">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M449">
+        <v>-1</v>
+      </c>
+      <c r="N449">
+        <v>0</v>
+      </c>
+      <c r="O449">
+        <v>0</v>
+      </c>
+      <c r="P449">
+        <v>0</v>
+      </c>
+      <c r="Q449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A450">
+        <v>3070</v>
+      </c>
+      <c r="B450">
+        <v>340</v>
+      </c>
+      <c r="C450">
+        <v>-3200</v>
+      </c>
+      <c r="D450">
+        <v>0</v>
+      </c>
+      <c r="E450">
+        <v>0</v>
+      </c>
+      <c r="F450">
+        <v>0</v>
+      </c>
+      <c r="G450">
+        <v>1</v>
+      </c>
+      <c r="H450">
+        <v>1</v>
+      </c>
+      <c r="I450">
+        <v>1</v>
+      </c>
+      <c r="J450">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K450">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L450">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M450">
+        <v>-1</v>
+      </c>
+      <c r="N450">
+        <v>0</v>
+      </c>
+      <c r="O450">
+        <v>0</v>
+      </c>
+      <c r="P450">
+        <v>0</v>
+      </c>
+      <c r="Q450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A451">
+        <v>3050</v>
+      </c>
+      <c r="B451">
+        <v>340</v>
+      </c>
+      <c r="C451">
+        <v>-3000</v>
+      </c>
+      <c r="D451">
+        <v>0</v>
+      </c>
+      <c r="E451">
+        <v>0</v>
+      </c>
+      <c r="F451">
+        <v>0</v>
+      </c>
+      <c r="G451">
+        <v>1</v>
+      </c>
+      <c r="H451">
+        <v>1</v>
+      </c>
+      <c r="I451">
+        <v>1</v>
+      </c>
+      <c r="J451">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K451">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L451">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M451">
+        <v>-1</v>
+      </c>
+      <c r="N451">
+        <v>0</v>
+      </c>
+      <c r="O451">
+        <v>0</v>
+      </c>
+      <c r="P451">
+        <v>0</v>
+      </c>
+      <c r="Q451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A452">
+        <v>3110</v>
+      </c>
+      <c r="B452">
+        <v>340</v>
+      </c>
+      <c r="C452">
+        <v>-2800</v>
+      </c>
+      <c r="D452">
+        <v>0</v>
+      </c>
+      <c r="E452">
+        <v>0</v>
+      </c>
+      <c r="F452">
+        <v>0</v>
+      </c>
+      <c r="G452">
+        <v>1</v>
+      </c>
+      <c r="H452">
+        <v>1</v>
+      </c>
+      <c r="I452">
+        <v>1</v>
+      </c>
+      <c r="J452">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K452">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L452">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M452">
+        <v>-1</v>
+      </c>
+      <c r="N452">
+        <v>0</v>
+      </c>
+      <c r="O452">
+        <v>0</v>
+      </c>
+      <c r="P452">
+        <v>0</v>
+      </c>
+      <c r="Q452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A453">
+        <v>3270</v>
+      </c>
+      <c r="B453">
+        <v>340</v>
+      </c>
+      <c r="C453">
+        <v>-2640</v>
+      </c>
+      <c r="D453">
+        <v>0</v>
+      </c>
+      <c r="E453">
+        <v>0</v>
+      </c>
+      <c r="F453">
+        <v>0</v>
+      </c>
+      <c r="G453">
+        <v>1</v>
+      </c>
+      <c r="H453">
+        <v>1</v>
+      </c>
+      <c r="I453">
+        <v>1</v>
+      </c>
+      <c r="J453">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K453">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L453">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M453">
+        <v>-1</v>
+      </c>
+      <c r="N453">
+        <v>0</v>
+      </c>
+      <c r="O453">
+        <v>0</v>
+      </c>
+      <c r="P453">
+        <v>0</v>
+      </c>
+      <c r="Q453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A454">
+        <v>3670</v>
+      </c>
+      <c r="B454">
+        <v>340</v>
+      </c>
+      <c r="C454">
+        <v>-2740</v>
+      </c>
+      <c r="D454">
+        <v>0</v>
+      </c>
+      <c r="E454">
+        <v>0</v>
+      </c>
+      <c r="F454">
+        <v>0</v>
+      </c>
+      <c r="G454">
+        <v>1</v>
+      </c>
+      <c r="H454">
+        <v>1</v>
+      </c>
+      <c r="I454">
+        <v>1</v>
+      </c>
+      <c r="J454">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K454">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L454">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M454">
+        <v>-1</v>
+      </c>
+      <c r="N454">
+        <v>0</v>
+      </c>
+      <c r="O454">
+        <v>0</v>
+      </c>
+      <c r="P454">
+        <v>0</v>
+      </c>
+      <c r="Q454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A455">
+        <v>3850</v>
+      </c>
+      <c r="B455">
+        <v>340</v>
+      </c>
+      <c r="C455">
+        <v>-3020</v>
+      </c>
+      <c r="D455">
+        <v>0</v>
+      </c>
+      <c r="E455">
+        <v>0</v>
+      </c>
+      <c r="F455">
+        <v>0</v>
+      </c>
+      <c r="G455">
+        <v>1</v>
+      </c>
+      <c r="H455">
+        <v>1</v>
+      </c>
+      <c r="I455">
+        <v>1</v>
+      </c>
+      <c r="J455">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K455">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L455">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M455">
+        <v>-1</v>
+      </c>
+      <c r="N455">
+        <v>0</v>
+      </c>
+      <c r="O455">
+        <v>0</v>
+      </c>
+      <c r="P455">
+        <v>0</v>
+      </c>
+      <c r="Q455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A456">
+        <v>3630</v>
+      </c>
+      <c r="B456">
+        <v>340</v>
+      </c>
+      <c r="C456">
+        <v>-3260</v>
+      </c>
+      <c r="D456">
+        <v>0</v>
+      </c>
+      <c r="E456">
+        <v>0</v>
+      </c>
+      <c r="F456">
+        <v>0</v>
+      </c>
+      <c r="G456">
+        <v>1</v>
+      </c>
+      <c r="H456">
+        <v>1</v>
+      </c>
+      <c r="I456">
+        <v>1</v>
+      </c>
+      <c r="J456">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K456">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L456">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M456">
+        <v>-1</v>
+      </c>
+      <c r="N456">
+        <v>0</v>
+      </c>
+      <c r="O456">
+        <v>0</v>
+      </c>
+      <c r="P456">
+        <v>0</v>
+      </c>
+      <c r="Q456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A457">
+        <v>3510</v>
+      </c>
+      <c r="B457">
+        <v>340</v>
+      </c>
+      <c r="C457">
+        <v>-2560</v>
+      </c>
+      <c r="D457">
+        <v>0</v>
+      </c>
+      <c r="E457">
+        <v>0</v>
+      </c>
+      <c r="F457">
+        <v>0</v>
+      </c>
+      <c r="G457">
+        <v>1</v>
+      </c>
+      <c r="H457">
+        <v>1</v>
+      </c>
+      <c r="I457">
+        <v>1</v>
+      </c>
+      <c r="J457">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K457">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L457">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M457">
+        <v>-1</v>
+      </c>
+      <c r="N457">
+        <v>0</v>
+      </c>
+      <c r="O457">
+        <v>0</v>
+      </c>
+      <c r="P457">
+        <v>0</v>
+      </c>
+      <c r="Q457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A458">
+        <v>3710</v>
+      </c>
+      <c r="B458">
+        <v>340</v>
+      </c>
+      <c r="C458">
+        <v>-2680</v>
+      </c>
+      <c r="D458">
+        <v>0</v>
+      </c>
+      <c r="E458">
+        <v>0</v>
+      </c>
+      <c r="F458">
+        <v>0</v>
+      </c>
+      <c r="G458">
+        <v>1</v>
+      </c>
+      <c r="H458">
+        <v>1</v>
+      </c>
+      <c r="I458">
+        <v>1</v>
+      </c>
+      <c r="J458">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K458">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L458">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M458">
+        <v>-1</v>
+      </c>
+      <c r="N458">
+        <v>0</v>
+      </c>
+      <c r="O458">
+        <v>0</v>
+      </c>
+      <c r="P458">
+        <v>0</v>
+      </c>
+      <c r="Q458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A459">
+        <v>3910</v>
+      </c>
+      <c r="B459">
+        <v>340</v>
+      </c>
+      <c r="C459">
+        <v>-2820</v>
+      </c>
+      <c r="D459">
+        <v>0</v>
+      </c>
+      <c r="E459">
+        <v>0</v>
+      </c>
+      <c r="F459">
+        <v>0</v>
+      </c>
+      <c r="G459">
+        <v>1</v>
+      </c>
+      <c r="H459">
+        <v>1</v>
+      </c>
+      <c r="I459">
+        <v>1</v>
+      </c>
+      <c r="J459">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K459">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L459">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M459">
+        <v>-1</v>
+      </c>
+      <c r="N459">
+        <v>0</v>
+      </c>
+      <c r="O459">
+        <v>0</v>
+      </c>
+      <c r="P459">
+        <v>0</v>
+      </c>
+      <c r="Q459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A460">
+        <v>3930</v>
+      </c>
+      <c r="B460">
+        <v>340</v>
+      </c>
+      <c r="C460">
+        <v>-3060</v>
+      </c>
+      <c r="D460">
+        <v>0</v>
+      </c>
+      <c r="E460">
+        <v>0</v>
+      </c>
+      <c r="F460">
+        <v>0</v>
+      </c>
+      <c r="G460">
+        <v>1</v>
+      </c>
+      <c r="H460">
+        <v>1</v>
+      </c>
+      <c r="I460">
+        <v>1</v>
+      </c>
+      <c r="J460">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K460">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L460">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M460">
+        <v>-1</v>
+      </c>
+      <c r="N460">
+        <v>0</v>
+      </c>
+      <c r="O460">
+        <v>0</v>
+      </c>
+      <c r="P460">
+        <v>0</v>
+      </c>
+      <c r="Q460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A461">
+        <v>3890</v>
+      </c>
+      <c r="B461">
+        <v>340</v>
+      </c>
+      <c r="C461">
+        <v>-3220</v>
+      </c>
+      <c r="D461">
+        <v>0</v>
+      </c>
+      <c r="E461">
+        <v>0</v>
+      </c>
+      <c r="F461">
+        <v>0</v>
+      </c>
+      <c r="G461">
+        <v>1</v>
+      </c>
+      <c r="H461">
+        <v>1</v>
+      </c>
+      <c r="I461">
+        <v>1</v>
+      </c>
+      <c r="J461">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K461">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L461">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M461">
+        <v>-1</v>
+      </c>
+      <c r="N461">
+        <v>0</v>
+      </c>
+      <c r="O461">
+        <v>0</v>
+      </c>
+      <c r="P461">
+        <v>0</v>
+      </c>
+      <c r="Q461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A462">
+        <v>3730</v>
+      </c>
+      <c r="B462">
+        <v>340</v>
+      </c>
+      <c r="C462">
+        <v>-3380</v>
+      </c>
+      <c r="D462">
+        <v>0</v>
+      </c>
+      <c r="E462">
+        <v>0</v>
+      </c>
+      <c r="F462">
+        <v>0</v>
+      </c>
+      <c r="G462">
+        <v>1</v>
+      </c>
+      <c r="H462">
+        <v>1</v>
+      </c>
+      <c r="I462">
+        <v>1</v>
+      </c>
+      <c r="J462">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K462">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L462">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M462">
+        <v>-1</v>
+      </c>
+      <c r="N462">
+        <v>0</v>
+      </c>
+      <c r="O462">
+        <v>0</v>
+      </c>
+      <c r="P462">
+        <v>0</v>
+      </c>
+      <c r="Q462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A463">
+        <v>3550</v>
+      </c>
+      <c r="B463">
+        <v>340</v>
+      </c>
+      <c r="C463">
+        <v>-3480</v>
+      </c>
+      <c r="D463">
+        <v>0</v>
+      </c>
+      <c r="E463">
+        <v>0</v>
+      </c>
+      <c r="F463">
+        <v>0</v>
+      </c>
+      <c r="G463">
+        <v>1</v>
+      </c>
+      <c r="H463">
+        <v>1</v>
+      </c>
+      <c r="I463">
+        <v>1</v>
+      </c>
+      <c r="J463">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K463">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L463">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M463">
+        <v>-1</v>
+      </c>
+      <c r="N463">
+        <v>0</v>
+      </c>
+      <c r="O463">
+        <v>0</v>
+      </c>
+      <c r="P463">
+        <v>0</v>
+      </c>
+      <c r="Q463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A464">
+        <v>3290</v>
+      </c>
+      <c r="B464">
+        <v>340</v>
+      </c>
+      <c r="C464">
+        <v>-3400</v>
+      </c>
+      <c r="D464">
+        <v>0</v>
+      </c>
+      <c r="E464">
+        <v>0</v>
+      </c>
+      <c r="F464">
+        <v>0</v>
+      </c>
+      <c r="G464">
+        <v>1</v>
+      </c>
+      <c r="H464">
+        <v>1</v>
+      </c>
+      <c r="I464">
+        <v>1</v>
+      </c>
+      <c r="J464">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K464">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L464">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M464">
+        <v>-1</v>
+      </c>
+      <c r="N464">
+        <v>0</v>
+      </c>
+      <c r="O464">
+        <v>0</v>
+      </c>
+      <c r="P464">
+        <v>0</v>
+      </c>
+      <c r="Q464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A465">
+        <v>3130</v>
+      </c>
+      <c r="B465">
+        <v>340</v>
+      </c>
+      <c r="C465">
+        <v>-3260</v>
+      </c>
+      <c r="D465">
+        <v>0</v>
+      </c>
+      <c r="E465">
+        <v>0</v>
+      </c>
+      <c r="F465">
+        <v>0</v>
+      </c>
+      <c r="G465">
+        <v>1</v>
+      </c>
+      <c r="H465">
+        <v>1</v>
+      </c>
+      <c r="I465">
+        <v>1</v>
+      </c>
+      <c r="J465">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K465">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L465">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M465">
+        <v>-1</v>
+      </c>
+      <c r="N465">
+        <v>0</v>
+      </c>
+      <c r="O465">
+        <v>0</v>
+      </c>
+      <c r="P465">
+        <v>0</v>
+      </c>
+      <c r="Q465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A466">
+        <v>3010</v>
+      </c>
+      <c r="B466">
+        <v>340</v>
+      </c>
+      <c r="C466">
+        <v>-3100</v>
+      </c>
+      <c r="D466">
+        <v>0</v>
+      </c>
+      <c r="E466">
+        <v>0</v>
+      </c>
+      <c r="F466">
+        <v>0</v>
+      </c>
+      <c r="G466">
+        <v>1</v>
+      </c>
+      <c r="H466">
+        <v>1</v>
+      </c>
+      <c r="I466">
+        <v>1</v>
+      </c>
+      <c r="J466">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K466">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L466">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M466">
+        <v>-1</v>
+      </c>
+      <c r="N466">
+        <v>0</v>
+      </c>
+      <c r="O466">
+        <v>0</v>
+      </c>
+      <c r="P466">
+        <v>0</v>
+      </c>
+      <c r="Q466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A467">
+        <v>3030</v>
+      </c>
+      <c r="B467">
+        <v>340</v>
+      </c>
+      <c r="C467">
+        <v>-2880</v>
+      </c>
+      <c r="D467">
+        <v>0</v>
+      </c>
+      <c r="E467">
+        <v>0</v>
+      </c>
+      <c r="F467">
+        <v>0</v>
+      </c>
+      <c r="G467">
+        <v>1</v>
+      </c>
+      <c r="H467">
+        <v>1</v>
+      </c>
+      <c r="I467">
+        <v>1</v>
+      </c>
+      <c r="J467">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K467">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L467">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M467">
+        <v>-1</v>
+      </c>
+      <c r="N467">
+        <v>0</v>
+      </c>
+      <c r="O467">
+        <v>0</v>
+      </c>
+      <c r="P467">
+        <v>0</v>
+      </c>
+      <c r="Q467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A468">
+        <v>3150</v>
+      </c>
+      <c r="B468">
+        <v>340</v>
+      </c>
+      <c r="C468">
+        <v>-2700</v>
+      </c>
+      <c r="D468">
+        <v>0</v>
+      </c>
+      <c r="E468">
+        <v>0</v>
+      </c>
+      <c r="F468">
+        <v>0</v>
+      </c>
+      <c r="G468">
+        <v>1</v>
+      </c>
+      <c r="H468">
+        <v>1</v>
+      </c>
+      <c r="I468">
+        <v>1</v>
+      </c>
+      <c r="J468">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K468">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L468">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M468">
+        <v>-1</v>
+      </c>
+      <c r="N468">
+        <v>0</v>
+      </c>
+      <c r="O468">
+        <v>0</v>
+      </c>
+      <c r="P468">
+        <v>0</v>
+      </c>
+      <c r="Q468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A469">
+        <v>3310</v>
+      </c>
+      <c r="B469">
+        <v>340</v>
+      </c>
+      <c r="C469">
+        <v>-2580</v>
+      </c>
+      <c r="D469">
+        <v>0</v>
+      </c>
+      <c r="E469">
+        <v>0</v>
+      </c>
+      <c r="F469">
+        <v>0</v>
+      </c>
+      <c r="G469">
+        <v>1</v>
+      </c>
+      <c r="H469">
+        <v>1</v>
+      </c>
+      <c r="I469">
+        <v>1</v>
+      </c>
+      <c r="J469">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K469">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L469">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M469">
+        <v>-1</v>
+      </c>
+      <c r="N469">
+        <v>0</v>
+      </c>
+      <c r="O469">
+        <v>0</v>
+      </c>
+      <c r="P469">
+        <v>0</v>
+      </c>
+      <c r="Q469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A470">
+        <v>3430</v>
+      </c>
+      <c r="B470">
+        <v>340</v>
+      </c>
+      <c r="C470">
+        <v>-2680</v>
+      </c>
+      <c r="D470">
+        <v>0</v>
+      </c>
+      <c r="E470">
+        <v>0</v>
+      </c>
+      <c r="F470">
+        <v>0</v>
+      </c>
+      <c r="G470">
+        <v>1</v>
+      </c>
+      <c r="H470">
+        <v>1</v>
+      </c>
+      <c r="I470">
+        <v>1</v>
+      </c>
+      <c r="J470">
+        <f t="shared" si="210"/>
+        <v>20</v>
+      </c>
+      <c r="K470">
+        <f t="shared" si="211"/>
+        <v>20</v>
+      </c>
+      <c r="L470">
+        <f t="shared" si="212"/>
+        <v>20</v>
+      </c>
+      <c r="M470">
+        <v>-1</v>
+      </c>
+      <c r="N470">
+        <v>0</v>
+      </c>
+      <c r="O470">
+        <v>0</v>
+      </c>
+      <c r="P470">
+        <v>0</v>
+      </c>
+      <c r="Q470">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
+++ b/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Map1\Platform\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Map1\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5223C8F-D4F6-48AD-B512-88A929BBFF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFB21CD7-D195-4C77-9C73-8C5739E31F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -977,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q470"/>
+  <dimension ref="A1:Q480"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="17" width="5.625" customWidth="1"/>
@@ -22821,14 +22821,14 @@
         <v>2</v>
       </c>
       <c r="J393">
-        <f>G393*20</f>
+        <f t="shared" ref="J393:J398" si="195">G393*20</f>
         <v>40</v>
       </c>
       <c r="K393">
         <v>83</v>
       </c>
       <c r="L393">
-        <f>I393*20</f>
+        <f t="shared" ref="L393:L398" si="196">I393*20</f>
         <v>40</v>
       </c>
       <c r="M393">
@@ -22876,14 +22876,14 @@
         <v>2</v>
       </c>
       <c r="J394">
-        <f>G394*20</f>
+        <f t="shared" si="195"/>
         <v>40</v>
       </c>
       <c r="K394">
         <v>84</v>
       </c>
       <c r="L394">
-        <f>I394*20</f>
+        <f t="shared" si="196"/>
         <v>40</v>
       </c>
       <c r="M394">
@@ -22931,14 +22931,14 @@
         <v>2</v>
       </c>
       <c r="J395">
-        <f>G395*20</f>
+        <f t="shared" si="195"/>
         <v>40</v>
       </c>
       <c r="K395">
         <v>85</v>
       </c>
       <c r="L395">
-        <f>I395*20</f>
+        <f t="shared" si="196"/>
         <v>40</v>
       </c>
       <c r="M395">
@@ -22986,14 +22986,14 @@
         <v>2</v>
       </c>
       <c r="J396">
-        <f>G396*20</f>
+        <f t="shared" si="195"/>
         <v>40</v>
       </c>
       <c r="K396">
         <v>86</v>
       </c>
       <c r="L396">
-        <f>I396*20</f>
+        <f t="shared" si="196"/>
         <v>40</v>
       </c>
       <c r="M396">
@@ -23041,14 +23041,14 @@
         <v>2</v>
       </c>
       <c r="J397">
-        <f>G397*20</f>
+        <f t="shared" si="195"/>
         <v>40</v>
       </c>
       <c r="K397">
         <v>88</v>
       </c>
       <c r="L397">
-        <f>I397*20</f>
+        <f t="shared" si="196"/>
         <v>40</v>
       </c>
       <c r="M397">
@@ -23096,14 +23096,14 @@
         <v>2</v>
       </c>
       <c r="J398">
-        <f>G398*20</f>
+        <f t="shared" si="195"/>
         <v>40</v>
       </c>
       <c r="K398">
         <v>88</v>
       </c>
       <c r="L398">
-        <f>I398*20</f>
+        <f t="shared" si="196"/>
         <v>40</v>
       </c>
       <c r="M398">
@@ -23151,15 +23151,15 @@
         <v>1</v>
       </c>
       <c r="J399">
-        <f t="shared" ref="J399" si="195">G399*20</f>
+        <f t="shared" ref="J399" si="197">G399*20</f>
         <v>20</v>
       </c>
       <c r="K399">
-        <f t="shared" ref="K399" si="196">H399*20</f>
+        <f t="shared" ref="K399" si="198">H399*20</f>
         <v>20</v>
       </c>
       <c r="L399">
-        <f t="shared" ref="L399" si="197">I399*20</f>
+        <f t="shared" ref="L399" si="199">I399*20</f>
         <v>20</v>
       </c>
       <c r="M399">
@@ -23207,15 +23207,15 @@
         <v>1</v>
       </c>
       <c r="J400">
-        <f t="shared" ref="J400:J419" si="198">G400*20</f>
+        <f t="shared" ref="J400:J419" si="200">G400*20</f>
         <v>20</v>
       </c>
       <c r="K400">
-        <f t="shared" ref="K400:K418" si="199">H400*20</f>
+        <f t="shared" ref="K400:K418" si="201">H400*20</f>
         <v>20</v>
       </c>
       <c r="L400">
-        <f t="shared" ref="L400:L419" si="200">I400*20</f>
+        <f t="shared" ref="L400:L419" si="202">I400*20</f>
         <v>20</v>
       </c>
       <c r="M400">
@@ -23263,15 +23263,15 @@
         <v>1</v>
       </c>
       <c r="J401">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K401">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L401">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M401">
@@ -23319,15 +23319,15 @@
         <v>1</v>
       </c>
       <c r="J402">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K402">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L402">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M402">
@@ -23375,15 +23375,15 @@
         <v>1</v>
       </c>
       <c r="J403">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K403">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L403">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M403">
@@ -23431,15 +23431,15 @@
         <v>1</v>
       </c>
       <c r="J404">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K404">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L404">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M404">
@@ -23487,15 +23487,15 @@
         <v>1</v>
       </c>
       <c r="J405">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K405">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L405">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M405">
@@ -23543,15 +23543,15 @@
         <v>1</v>
       </c>
       <c r="J406">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K406">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L406">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M406">
@@ -23599,15 +23599,15 @@
         <v>1</v>
       </c>
       <c r="J407">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K407">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L407">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M407">
@@ -23655,15 +23655,15 @@
         <v>1</v>
       </c>
       <c r="J408">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K408">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L408">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M408">
@@ -23711,15 +23711,15 @@
         <v>1</v>
       </c>
       <c r="J409">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K409">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L409">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M409">
@@ -23767,15 +23767,15 @@
         <v>1</v>
       </c>
       <c r="J410">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K410">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L410">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M410">
@@ -23823,15 +23823,15 @@
         <v>1</v>
       </c>
       <c r="J411">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K411">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L411">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M411">
@@ -23879,15 +23879,15 @@
         <v>1</v>
       </c>
       <c r="J412">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K412">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L412">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M412">
@@ -23935,15 +23935,15 @@
         <v>1</v>
       </c>
       <c r="J413">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K413">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L413">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M413">
@@ -23991,15 +23991,15 @@
         <v>1</v>
       </c>
       <c r="J414">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K414">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L414">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M414">
@@ -24047,15 +24047,15 @@
         <v>1</v>
       </c>
       <c r="J415">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K415">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L415">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M415">
@@ -24103,15 +24103,15 @@
         <v>1</v>
       </c>
       <c r="J416">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K416">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L416">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M416">
@@ -24159,15 +24159,15 @@
         <v>1</v>
       </c>
       <c r="J417">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K417">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L417">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M417">
@@ -24215,15 +24215,15 @@
         <v>1</v>
       </c>
       <c r="J418">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>20</v>
       </c>
       <c r="K418">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>20</v>
       </c>
       <c r="L418">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>20</v>
       </c>
       <c r="M418">
@@ -24271,14 +24271,14 @@
         <v>2</v>
       </c>
       <c r="J419">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>40</v>
       </c>
       <c r="K419">
         <v>80</v>
       </c>
       <c r="L419">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>40</v>
       </c>
       <c r="M419">
@@ -24326,14 +24326,14 @@
         <v>2</v>
       </c>
       <c r="J420">
-        <f t="shared" ref="J420:J422" si="201">G420*20</f>
+        <f t="shared" ref="J420:J422" si="203">G420*20</f>
         <v>40</v>
       </c>
       <c r="K420">
         <v>81</v>
       </c>
       <c r="L420">
-        <f t="shared" ref="L420:L422" si="202">I420*20</f>
+        <f t="shared" ref="L420:L422" si="204">I420*20</f>
         <v>40</v>
       </c>
       <c r="M420">
@@ -24381,14 +24381,14 @@
         <v>2</v>
       </c>
       <c r="J421">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>40</v>
       </c>
       <c r="K421">
         <v>82</v>
       </c>
       <c r="L421">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>40</v>
       </c>
       <c r="M421">
@@ -24436,14 +24436,14 @@
         <v>2</v>
       </c>
       <c r="J422">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>40</v>
       </c>
       <c r="K422">
         <v>83</v>
       </c>
       <c r="L422">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>40</v>
       </c>
       <c r="M422">
@@ -24494,7 +24494,7 @@
         <v>60</v>
       </c>
       <c r="K423">
-        <f t="shared" ref="K423" si="203">H423*20</f>
+        <f t="shared" ref="K423" si="205">H423*20</f>
         <v>20</v>
       </c>
       <c r="L423">
@@ -24548,7 +24548,7 @@
         <v>20</v>
       </c>
       <c r="K424">
-        <f t="shared" ref="K424" si="204">H424*20</f>
+        <f t="shared" ref="K424" si="206">H424*20</f>
         <v>20</v>
       </c>
       <c r="L424">
@@ -24602,7 +24602,7 @@
         <v>60</v>
       </c>
       <c r="K425">
-        <f t="shared" ref="K425" si="205">H425*20</f>
+        <f t="shared" ref="K425" si="207">H425*20</f>
         <v>20</v>
       </c>
       <c r="L425">
@@ -24656,7 +24656,7 @@
         <v>20</v>
       </c>
       <c r="K426">
-        <f t="shared" ref="K426:K427" si="206">H426*20</f>
+        <f t="shared" ref="K426:K427" si="208">H426*20</f>
         <v>20</v>
       </c>
       <c r="L426">
@@ -24710,7 +24710,7 @@
         <v>60</v>
       </c>
       <c r="K427">
-        <f t="shared" si="206"/>
+        <f t="shared" si="208"/>
         <v>20</v>
       </c>
       <c r="L427">
@@ -24764,7 +24764,7 @@
         <v>20</v>
       </c>
       <c r="K428">
-        <f t="shared" ref="K428:K431" si="207">H428*20</f>
+        <f t="shared" ref="K428:K431" si="209">H428*20</f>
         <v>20</v>
       </c>
       <c r="L428">
@@ -24818,7 +24818,7 @@
         <v>60</v>
       </c>
       <c r="K429">
-        <f t="shared" si="207"/>
+        <f t="shared" si="209"/>
         <v>20</v>
       </c>
       <c r="L429">
@@ -24872,7 +24872,7 @@
         <v>20</v>
       </c>
       <c r="K430">
-        <f t="shared" si="207"/>
+        <f t="shared" si="209"/>
         <v>20</v>
       </c>
       <c r="L430">
@@ -24923,15 +24923,15 @@
         <v>1</v>
       </c>
       <c r="J431">
-        <f t="shared" ref="J431" si="208">G431*20</f>
+        <f t="shared" ref="J431" si="210">G431*20</f>
         <v>20</v>
       </c>
       <c r="K431">
-        <f t="shared" si="207"/>
+        <f t="shared" si="209"/>
         <v>20</v>
       </c>
       <c r="L431">
-        <f t="shared" ref="L431" si="209">I431*20</f>
+        <f t="shared" ref="L431" si="211">I431*20</f>
         <v>20</v>
       </c>
       <c r="M431">
@@ -24979,15 +24979,15 @@
         <v>1</v>
       </c>
       <c r="J432">
-        <f t="shared" ref="J432:J470" si="210">G432*20</f>
+        <f t="shared" ref="J432:J470" si="212">G432*20</f>
         <v>20</v>
       </c>
       <c r="K432">
-        <f t="shared" ref="K432:K470" si="211">H432*20</f>
+        <f t="shared" ref="K432:K470" si="213">H432*20</f>
         <v>20</v>
       </c>
       <c r="L432">
-        <f t="shared" ref="L432:L470" si="212">I432*20</f>
+        <f t="shared" ref="L432:L470" si="214">I432*20</f>
         <v>20</v>
       </c>
       <c r="M432">
@@ -25035,15 +25035,15 @@
         <v>1</v>
       </c>
       <c r="J433">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K433">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L433">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M433">
@@ -25091,15 +25091,15 @@
         <v>1</v>
       </c>
       <c r="J434">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K434">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L434">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M434">
@@ -25147,15 +25147,15 @@
         <v>1</v>
       </c>
       <c r="J435">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K435">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L435">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M435">
@@ -25203,15 +25203,15 @@
         <v>1</v>
       </c>
       <c r="J436">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K436">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L436">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M436">
@@ -25259,15 +25259,15 @@
         <v>1</v>
       </c>
       <c r="J437">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K437">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L437">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M437">
@@ -25315,15 +25315,15 @@
         <v>1</v>
       </c>
       <c r="J438">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K438">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L438">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M438">
@@ -25371,15 +25371,15 @@
         <v>1</v>
       </c>
       <c r="J439">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K439">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L439">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M439">
@@ -25427,15 +25427,15 @@
         <v>1</v>
       </c>
       <c r="J440">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K440">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L440">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M440">
@@ -25483,15 +25483,15 @@
         <v>1</v>
       </c>
       <c r="J441">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K441">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L441">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M441">
@@ -25539,15 +25539,15 @@
         <v>1</v>
       </c>
       <c r="J442">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K442">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L442">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M442">
@@ -25595,15 +25595,15 @@
         <v>1</v>
       </c>
       <c r="J443">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K443">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L443">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M443">
@@ -25651,15 +25651,15 @@
         <v>1</v>
       </c>
       <c r="J444">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K444">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L444">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M444">
@@ -25707,15 +25707,15 @@
         <v>1</v>
       </c>
       <c r="J445">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K445">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L445">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M445">
@@ -25763,15 +25763,15 @@
         <v>1</v>
       </c>
       <c r="J446">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K446">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L446">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M446">
@@ -25819,15 +25819,15 @@
         <v>1</v>
       </c>
       <c r="J447">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K447">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L447">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M447">
@@ -25875,15 +25875,15 @@
         <v>1</v>
       </c>
       <c r="J448">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K448">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L448">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M448">
@@ -25931,15 +25931,15 @@
         <v>1</v>
       </c>
       <c r="J449">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K449">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L449">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M449">
@@ -25987,15 +25987,15 @@
         <v>1</v>
       </c>
       <c r="J450">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K450">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L450">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M450">
@@ -26043,15 +26043,15 @@
         <v>1</v>
       </c>
       <c r="J451">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K451">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L451">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M451">
@@ -26099,15 +26099,15 @@
         <v>1</v>
       </c>
       <c r="J452">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K452">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L452">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M452">
@@ -26155,15 +26155,15 @@
         <v>1</v>
       </c>
       <c r="J453">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K453">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L453">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M453">
@@ -26211,15 +26211,15 @@
         <v>1</v>
       </c>
       <c r="J454">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K454">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L454">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M454">
@@ -26267,15 +26267,15 @@
         <v>1</v>
       </c>
       <c r="J455">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K455">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L455">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M455">
@@ -26323,15 +26323,15 @@
         <v>1</v>
       </c>
       <c r="J456">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K456">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L456">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M456">
@@ -26379,15 +26379,15 @@
         <v>1</v>
       </c>
       <c r="J457">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K457">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L457">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M457">
@@ -26435,15 +26435,15 @@
         <v>1</v>
       </c>
       <c r="J458">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K458">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L458">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M458">
@@ -26491,15 +26491,15 @@
         <v>1</v>
       </c>
       <c r="J459">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K459">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L459">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M459">
@@ -26547,15 +26547,15 @@
         <v>1</v>
       </c>
       <c r="J460">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K460">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L460">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M460">
@@ -26603,15 +26603,15 @@
         <v>1</v>
       </c>
       <c r="J461">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K461">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L461">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M461">
@@ -26659,15 +26659,15 @@
         <v>1</v>
       </c>
       <c r="J462">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K462">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L462">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M462">
@@ -26715,15 +26715,15 @@
         <v>1</v>
       </c>
       <c r="J463">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K463">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L463">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M463">
@@ -26771,15 +26771,15 @@
         <v>1</v>
       </c>
       <c r="J464">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K464">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L464">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M464">
@@ -26827,15 +26827,15 @@
         <v>1</v>
       </c>
       <c r="J465">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K465">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L465">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M465">
@@ -26883,15 +26883,15 @@
         <v>1</v>
       </c>
       <c r="J466">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K466">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L466">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M466">
@@ -26939,15 +26939,15 @@
         <v>1</v>
       </c>
       <c r="J467">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K467">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L467">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M467">
@@ -26995,15 +26995,15 @@
         <v>1</v>
       </c>
       <c r="J468">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K468">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L468">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M468">
@@ -27051,15 +27051,15 @@
         <v>1</v>
       </c>
       <c r="J469">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K469">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L469">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M469">
@@ -27107,15 +27107,15 @@
         <v>1</v>
       </c>
       <c r="J470">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>20</v>
       </c>
       <c r="K470">
-        <f t="shared" si="211"/>
+        <f t="shared" si="213"/>
         <v>20</v>
       </c>
       <c r="L470">
-        <f t="shared" si="212"/>
+        <f t="shared" si="214"/>
         <v>20</v>
       </c>
       <c r="M470">
@@ -27131,6 +27131,545 @@
         <v>0</v>
       </c>
       <c r="Q470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A471">
+        <v>0</v>
+      </c>
+      <c r="B471">
+        <v>20</v>
+      </c>
+      <c r="C471">
+        <v>-100</v>
+      </c>
+      <c r="D471">
+        <v>0</v>
+      </c>
+      <c r="E471">
+        <v>0</v>
+      </c>
+      <c r="F471">
+        <v>0</v>
+      </c>
+      <c r="G471">
+        <v>1</v>
+      </c>
+      <c r="H471">
+        <v>1</v>
+      </c>
+      <c r="I471">
+        <v>1</v>
+      </c>
+      <c r="J471">
+        <v>10</v>
+      </c>
+      <c r="K471">
+        <v>10</v>
+      </c>
+      <c r="L471">
+        <v>10</v>
+      </c>
+      <c r="M471">
+        <v>-1</v>
+      </c>
+      <c r="N471">
+        <v>0</v>
+      </c>
+      <c r="O471">
+        <v>0</v>
+      </c>
+      <c r="P471">
+        <v>0</v>
+      </c>
+      <c r="Q471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A472">
+        <v>0</v>
+      </c>
+      <c r="B472">
+        <v>20</v>
+      </c>
+      <c r="C472">
+        <f>C471-20</f>
+        <v>-120</v>
+      </c>
+      <c r="D472">
+        <v>0</v>
+      </c>
+      <c r="E472">
+        <v>0</v>
+      </c>
+      <c r="F472">
+        <v>0</v>
+      </c>
+      <c r="G472">
+        <v>1</v>
+      </c>
+      <c r="H472">
+        <v>1</v>
+      </c>
+      <c r="I472">
+        <v>1</v>
+      </c>
+      <c r="J472">
+        <v>10</v>
+      </c>
+      <c r="K472">
+        <v>10</v>
+      </c>
+      <c r="L472">
+        <v>10</v>
+      </c>
+      <c r="M472">
+        <v>-1</v>
+      </c>
+      <c r="N472">
+        <v>0</v>
+      </c>
+      <c r="O472">
+        <v>0</v>
+      </c>
+      <c r="P472">
+        <v>0</v>
+      </c>
+      <c r="Q472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A473">
+        <v>0</v>
+      </c>
+      <c r="B473">
+        <v>20</v>
+      </c>
+      <c r="C473">
+        <f t="shared" ref="C473:C480" si="215">C472-20</f>
+        <v>-140</v>
+      </c>
+      <c r="D473">
+        <v>0</v>
+      </c>
+      <c r="E473">
+        <v>0</v>
+      </c>
+      <c r="F473">
+        <v>0</v>
+      </c>
+      <c r="G473">
+        <v>1</v>
+      </c>
+      <c r="H473">
+        <v>1</v>
+      </c>
+      <c r="I473">
+        <v>1</v>
+      </c>
+      <c r="J473">
+        <v>10</v>
+      </c>
+      <c r="K473">
+        <v>10</v>
+      </c>
+      <c r="L473">
+        <v>10</v>
+      </c>
+      <c r="M473">
+        <v>-1</v>
+      </c>
+      <c r="N473">
+        <v>0</v>
+      </c>
+      <c r="O473">
+        <v>0</v>
+      </c>
+      <c r="P473">
+        <v>0</v>
+      </c>
+      <c r="Q473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A474">
+        <v>0</v>
+      </c>
+      <c r="B474">
+        <v>20</v>
+      </c>
+      <c r="C474">
+        <f t="shared" si="215"/>
+        <v>-160</v>
+      </c>
+      <c r="D474">
+        <v>0</v>
+      </c>
+      <c r="E474">
+        <v>0</v>
+      </c>
+      <c r="F474">
+        <v>0</v>
+      </c>
+      <c r="G474">
+        <v>1</v>
+      </c>
+      <c r="H474">
+        <v>1</v>
+      </c>
+      <c r="I474">
+        <v>1</v>
+      </c>
+      <c r="J474">
+        <v>10</v>
+      </c>
+      <c r="K474">
+        <v>10</v>
+      </c>
+      <c r="L474">
+        <v>10</v>
+      </c>
+      <c r="M474">
+        <v>-1</v>
+      </c>
+      <c r="N474">
+        <v>0</v>
+      </c>
+      <c r="O474">
+        <v>0</v>
+      </c>
+      <c r="P474">
+        <v>0</v>
+      </c>
+      <c r="Q474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A475">
+        <v>0</v>
+      </c>
+      <c r="B475">
+        <v>20</v>
+      </c>
+      <c r="C475">
+        <f t="shared" si="215"/>
+        <v>-180</v>
+      </c>
+      <c r="D475">
+        <v>0</v>
+      </c>
+      <c r="E475">
+        <v>0</v>
+      </c>
+      <c r="F475">
+        <v>0</v>
+      </c>
+      <c r="G475">
+        <v>1</v>
+      </c>
+      <c r="H475">
+        <v>1</v>
+      </c>
+      <c r="I475">
+        <v>1</v>
+      </c>
+      <c r="J475">
+        <v>10</v>
+      </c>
+      <c r="K475">
+        <v>10</v>
+      </c>
+      <c r="L475">
+        <v>10</v>
+      </c>
+      <c r="M475">
+        <v>-1</v>
+      </c>
+      <c r="N475">
+        <v>0</v>
+      </c>
+      <c r="O475">
+        <v>0</v>
+      </c>
+      <c r="P475">
+        <v>0</v>
+      </c>
+      <c r="Q475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A476">
+        <v>0</v>
+      </c>
+      <c r="B476">
+        <v>20</v>
+      </c>
+      <c r="C476">
+        <f t="shared" si="215"/>
+        <v>-200</v>
+      </c>
+      <c r="D476">
+        <v>0</v>
+      </c>
+      <c r="E476">
+        <v>0</v>
+      </c>
+      <c r="F476">
+        <v>0</v>
+      </c>
+      <c r="G476">
+        <v>1</v>
+      </c>
+      <c r="H476">
+        <v>1</v>
+      </c>
+      <c r="I476">
+        <v>1</v>
+      </c>
+      <c r="J476">
+        <v>10</v>
+      </c>
+      <c r="K476">
+        <v>10</v>
+      </c>
+      <c r="L476">
+        <v>10</v>
+      </c>
+      <c r="M476">
+        <v>-1</v>
+      </c>
+      <c r="N476">
+        <v>0</v>
+      </c>
+      <c r="O476">
+        <v>0</v>
+      </c>
+      <c r="P476">
+        <v>0</v>
+      </c>
+      <c r="Q476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A477">
+        <v>0</v>
+      </c>
+      <c r="B477">
+        <v>20</v>
+      </c>
+      <c r="C477">
+        <f t="shared" si="215"/>
+        <v>-220</v>
+      </c>
+      <c r="D477">
+        <v>0</v>
+      </c>
+      <c r="E477">
+        <v>0</v>
+      </c>
+      <c r="F477">
+        <v>0</v>
+      </c>
+      <c r="G477">
+        <v>1</v>
+      </c>
+      <c r="H477">
+        <v>1</v>
+      </c>
+      <c r="I477">
+        <v>1</v>
+      </c>
+      <c r="J477">
+        <v>10</v>
+      </c>
+      <c r="K477">
+        <v>10</v>
+      </c>
+      <c r="L477">
+        <v>10</v>
+      </c>
+      <c r="M477">
+        <v>-1</v>
+      </c>
+      <c r="N477">
+        <v>0</v>
+      </c>
+      <c r="O477">
+        <v>0</v>
+      </c>
+      <c r="P477">
+        <v>0</v>
+      </c>
+      <c r="Q477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A478">
+        <v>0</v>
+      </c>
+      <c r="B478">
+        <v>20</v>
+      </c>
+      <c r="C478">
+        <f t="shared" si="215"/>
+        <v>-240</v>
+      </c>
+      <c r="D478">
+        <v>0</v>
+      </c>
+      <c r="E478">
+        <v>0</v>
+      </c>
+      <c r="F478">
+        <v>0</v>
+      </c>
+      <c r="G478">
+        <v>1</v>
+      </c>
+      <c r="H478">
+        <v>1</v>
+      </c>
+      <c r="I478">
+        <v>1</v>
+      </c>
+      <c r="J478">
+        <v>10</v>
+      </c>
+      <c r="K478">
+        <v>10</v>
+      </c>
+      <c r="L478">
+        <v>10</v>
+      </c>
+      <c r="M478">
+        <v>-1</v>
+      </c>
+      <c r="N478">
+        <v>0</v>
+      </c>
+      <c r="O478">
+        <v>0</v>
+      </c>
+      <c r="P478">
+        <v>0</v>
+      </c>
+      <c r="Q478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A479">
+        <v>0</v>
+      </c>
+      <c r="B479">
+        <v>20</v>
+      </c>
+      <c r="C479">
+        <f t="shared" si="215"/>
+        <v>-260</v>
+      </c>
+      <c r="D479">
+        <v>0</v>
+      </c>
+      <c r="E479">
+        <v>0</v>
+      </c>
+      <c r="F479">
+        <v>0</v>
+      </c>
+      <c r="G479">
+        <v>1</v>
+      </c>
+      <c r="H479">
+        <v>1</v>
+      </c>
+      <c r="I479">
+        <v>1</v>
+      </c>
+      <c r="J479">
+        <v>10</v>
+      </c>
+      <c r="K479">
+        <v>10</v>
+      </c>
+      <c r="L479">
+        <v>10</v>
+      </c>
+      <c r="M479">
+        <v>-1</v>
+      </c>
+      <c r="N479">
+        <v>0</v>
+      </c>
+      <c r="O479">
+        <v>0</v>
+      </c>
+      <c r="P479">
+        <v>0</v>
+      </c>
+      <c r="Q479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A480">
+        <v>0</v>
+      </c>
+      <c r="B480">
+        <v>20</v>
+      </c>
+      <c r="C480">
+        <f t="shared" si="215"/>
+        <v>-280</v>
+      </c>
+      <c r="D480">
+        <v>0</v>
+      </c>
+      <c r="E480">
+        <v>0</v>
+      </c>
+      <c r="F480">
+        <v>0</v>
+      </c>
+      <c r="G480">
+        <v>1</v>
+      </c>
+      <c r="H480">
+        <v>1</v>
+      </c>
+      <c r="I480">
+        <v>1</v>
+      </c>
+      <c r="J480">
+        <v>10</v>
+      </c>
+      <c r="K480">
+        <v>10</v>
+      </c>
+      <c r="L480">
+        <v>10</v>
+      </c>
+      <c r="M480">
+        <v>-1</v>
+      </c>
+      <c r="N480">
+        <v>0</v>
+      </c>
+      <c r="O480">
+        <v>0</v>
+      </c>
+      <c r="P480">
+        <v>0</v>
+      </c>
+      <c r="Q480">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
+++ b/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Map1\Platform\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Map1\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFB21CD7-D195-4C77-9C73-8C5739E31F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76A4AA1C-A57C-4EFA-94CF-19DE7A5CE4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -977,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q480"/>
+  <dimension ref="A1:Q549"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="17" width="5.625" customWidth="1"/>
@@ -27303,8 +27303,7 @@
         <v>20</v>
       </c>
       <c r="C474">
-        <f t="shared" si="215"/>
-        <v>-160</v>
+        <v>-350</v>
       </c>
       <c r="D474">
         <v>0</v>
@@ -27354,11 +27353,10 @@
         <v>0</v>
       </c>
       <c r="B475">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C475">
-        <f t="shared" si="215"/>
-        <v>-180</v>
+        <v>-360</v>
       </c>
       <c r="D475">
         <v>0</v>
@@ -27408,11 +27406,10 @@
         <v>0</v>
       </c>
       <c r="B476">
-        <v>20</v>
+        <v>54.3</v>
       </c>
       <c r="C476">
-        <f t="shared" si="215"/>
-        <v>-200</v>
+        <v>-370</v>
       </c>
       <c r="D476">
         <v>0</v>
@@ -27462,11 +27459,10 @@
         <v>0</v>
       </c>
       <c r="B477">
-        <v>20</v>
+        <v>62.9</v>
       </c>
       <c r="C477">
-        <f t="shared" si="215"/>
-        <v>-220</v>
+        <v>-380</v>
       </c>
       <c r="D477">
         <v>0</v>
@@ -27516,11 +27512,10 @@
         <v>0</v>
       </c>
       <c r="B478">
-        <v>20</v>
+        <v>65.7</v>
       </c>
       <c r="C478">
-        <f t="shared" si="215"/>
-        <v>-240</v>
+        <v>-390</v>
       </c>
       <c r="D478">
         <v>0</v>
@@ -27570,11 +27565,10 @@
         <v>0</v>
       </c>
       <c r="B479">
-        <v>20</v>
+        <v>62.9</v>
       </c>
       <c r="C479">
-        <f t="shared" si="215"/>
-        <v>-260</v>
+        <v>-400</v>
       </c>
       <c r="D479">
         <v>0</v>
@@ -27624,11 +27618,10 @@
         <v>0</v>
       </c>
       <c r="B480">
-        <v>20</v>
+        <v>54.3</v>
       </c>
       <c r="C480">
-        <f t="shared" si="215"/>
-        <v>-280</v>
+        <v>-410</v>
       </c>
       <c r="D480">
         <v>0</v>
@@ -27670,6 +27663,3663 @@
         <v>0</v>
       </c>
       <c r="Q480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A481">
+        <v>0</v>
+      </c>
+      <c r="B481">
+        <v>40</v>
+      </c>
+      <c r="C481">
+        <v>-420</v>
+      </c>
+      <c r="D481">
+        <v>0</v>
+      </c>
+      <c r="E481">
+        <v>0</v>
+      </c>
+      <c r="F481">
+        <v>0</v>
+      </c>
+      <c r="G481">
+        <v>1</v>
+      </c>
+      <c r="H481">
+        <v>1</v>
+      </c>
+      <c r="I481">
+        <v>1</v>
+      </c>
+      <c r="J481">
+        <v>10</v>
+      </c>
+      <c r="K481">
+        <v>10</v>
+      </c>
+      <c r="L481">
+        <v>10</v>
+      </c>
+      <c r="M481">
+        <v>-1</v>
+      </c>
+      <c r="N481">
+        <v>0</v>
+      </c>
+      <c r="O481">
+        <v>0</v>
+      </c>
+      <c r="P481">
+        <v>0</v>
+      </c>
+      <c r="Q481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A482">
+        <v>5</v>
+      </c>
+      <c r="B482">
+        <v>40</v>
+      </c>
+      <c r="C482">
+        <v>-500</v>
+      </c>
+      <c r="D482">
+        <v>0</v>
+      </c>
+      <c r="E482">
+        <v>0</v>
+      </c>
+      <c r="F482">
+        <v>0</v>
+      </c>
+      <c r="G482">
+        <v>1</v>
+      </c>
+      <c r="H482">
+        <v>1</v>
+      </c>
+      <c r="I482">
+        <v>1</v>
+      </c>
+      <c r="J482">
+        <v>10</v>
+      </c>
+      <c r="K482">
+        <v>10</v>
+      </c>
+      <c r="L482">
+        <v>10</v>
+      </c>
+      <c r="M482">
+        <v>-1</v>
+      </c>
+      <c r="N482">
+        <v>0</v>
+      </c>
+      <c r="O482">
+        <v>0</v>
+      </c>
+      <c r="P482">
+        <v>0</v>
+      </c>
+      <c r="Q482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A483">
+        <v>5</v>
+      </c>
+      <c r="B483">
+        <v>40</v>
+      </c>
+      <c r="C483">
+        <v>-510</v>
+      </c>
+      <c r="D483">
+        <v>0</v>
+      </c>
+      <c r="E483">
+        <v>0</v>
+      </c>
+      <c r="F483">
+        <v>0</v>
+      </c>
+      <c r="G483">
+        <v>1</v>
+      </c>
+      <c r="H483">
+        <v>1</v>
+      </c>
+      <c r="I483">
+        <v>1</v>
+      </c>
+      <c r="J483">
+        <v>10</v>
+      </c>
+      <c r="K483">
+        <v>10</v>
+      </c>
+      <c r="L483">
+        <v>10</v>
+      </c>
+      <c r="M483">
+        <v>-1</v>
+      </c>
+      <c r="N483">
+        <v>0</v>
+      </c>
+      <c r="O483">
+        <v>0</v>
+      </c>
+      <c r="P483">
+        <v>0</v>
+      </c>
+      <c r="Q483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A484">
+        <v>5</v>
+      </c>
+      <c r="B484">
+        <v>40</v>
+      </c>
+      <c r="C484">
+        <v>-520</v>
+      </c>
+      <c r="D484">
+        <v>0</v>
+      </c>
+      <c r="E484">
+        <v>0</v>
+      </c>
+      <c r="F484">
+        <v>0</v>
+      </c>
+      <c r="G484">
+        <v>1</v>
+      </c>
+      <c r="H484">
+        <v>1</v>
+      </c>
+      <c r="I484">
+        <v>1</v>
+      </c>
+      <c r="J484">
+        <v>10</v>
+      </c>
+      <c r="K484">
+        <v>10</v>
+      </c>
+      <c r="L484">
+        <v>10</v>
+      </c>
+      <c r="M484">
+        <v>-1</v>
+      </c>
+      <c r="N484">
+        <v>0</v>
+      </c>
+      <c r="O484">
+        <v>0</v>
+      </c>
+      <c r="P484">
+        <v>0</v>
+      </c>
+      <c r="Q484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A485">
+        <v>5</v>
+      </c>
+      <c r="B485">
+        <v>40</v>
+      </c>
+      <c r="C485">
+        <v>-530</v>
+      </c>
+      <c r="D485">
+        <v>0</v>
+      </c>
+      <c r="E485">
+        <v>0</v>
+      </c>
+      <c r="F485">
+        <v>0</v>
+      </c>
+      <c r="G485">
+        <v>1</v>
+      </c>
+      <c r="H485">
+        <v>1</v>
+      </c>
+      <c r="I485">
+        <v>1</v>
+      </c>
+      <c r="J485">
+        <v>10</v>
+      </c>
+      <c r="K485">
+        <v>10</v>
+      </c>
+      <c r="L485">
+        <v>10</v>
+      </c>
+      <c r="M485">
+        <v>-1</v>
+      </c>
+      <c r="N485">
+        <v>0</v>
+      </c>
+      <c r="O485">
+        <v>0</v>
+      </c>
+      <c r="P485">
+        <v>0</v>
+      </c>
+      <c r="Q485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A486">
+        <v>5</v>
+      </c>
+      <c r="B486">
+        <v>40</v>
+      </c>
+      <c r="C486">
+        <v>-540</v>
+      </c>
+      <c r="D486">
+        <v>0</v>
+      </c>
+      <c r="E486">
+        <v>0</v>
+      </c>
+      <c r="F486">
+        <v>0</v>
+      </c>
+      <c r="G486">
+        <v>1</v>
+      </c>
+      <c r="H486">
+        <v>1</v>
+      </c>
+      <c r="I486">
+        <v>1</v>
+      </c>
+      <c r="J486">
+        <v>10</v>
+      </c>
+      <c r="K486">
+        <v>10</v>
+      </c>
+      <c r="L486">
+        <v>10</v>
+      </c>
+      <c r="M486">
+        <v>-1</v>
+      </c>
+      <c r="N486">
+        <v>0</v>
+      </c>
+      <c r="O486">
+        <v>0</v>
+      </c>
+      <c r="P486">
+        <v>0</v>
+      </c>
+      <c r="Q486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A487">
+        <v>-5</v>
+      </c>
+      <c r="B487">
+        <v>40</v>
+      </c>
+      <c r="C487">
+        <v>-500</v>
+      </c>
+      <c r="D487">
+        <v>0</v>
+      </c>
+      <c r="E487">
+        <v>0</v>
+      </c>
+      <c r="F487">
+        <v>0</v>
+      </c>
+      <c r="G487">
+        <v>1</v>
+      </c>
+      <c r="H487">
+        <v>1</v>
+      </c>
+      <c r="I487">
+        <v>1</v>
+      </c>
+      <c r="J487">
+        <v>10</v>
+      </c>
+      <c r="K487">
+        <v>10</v>
+      </c>
+      <c r="L487">
+        <v>10</v>
+      </c>
+      <c r="M487">
+        <v>-1</v>
+      </c>
+      <c r="N487">
+        <v>0</v>
+      </c>
+      <c r="O487">
+        <v>0</v>
+      </c>
+      <c r="P487">
+        <v>0</v>
+      </c>
+      <c r="Q487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A488">
+        <v>-5</v>
+      </c>
+      <c r="B488">
+        <v>40</v>
+      </c>
+      <c r="C488">
+        <v>-510</v>
+      </c>
+      <c r="D488">
+        <v>0</v>
+      </c>
+      <c r="E488">
+        <v>0</v>
+      </c>
+      <c r="F488">
+        <v>0</v>
+      </c>
+      <c r="G488">
+        <v>1</v>
+      </c>
+      <c r="H488">
+        <v>1</v>
+      </c>
+      <c r="I488">
+        <v>1</v>
+      </c>
+      <c r="J488">
+        <v>10</v>
+      </c>
+      <c r="K488">
+        <v>10</v>
+      </c>
+      <c r="L488">
+        <v>10</v>
+      </c>
+      <c r="M488">
+        <v>-1</v>
+      </c>
+      <c r="N488">
+        <v>0</v>
+      </c>
+      <c r="O488">
+        <v>0</v>
+      </c>
+      <c r="P488">
+        <v>0</v>
+      </c>
+      <c r="Q488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A489">
+        <v>-5</v>
+      </c>
+      <c r="B489">
+        <v>40</v>
+      </c>
+      <c r="C489">
+        <v>-520</v>
+      </c>
+      <c r="D489">
+        <v>0</v>
+      </c>
+      <c r="E489">
+        <v>0</v>
+      </c>
+      <c r="F489">
+        <v>0</v>
+      </c>
+      <c r="G489">
+        <v>1</v>
+      </c>
+      <c r="H489">
+        <v>1</v>
+      </c>
+      <c r="I489">
+        <v>1</v>
+      </c>
+      <c r="J489">
+        <v>10</v>
+      </c>
+      <c r="K489">
+        <v>10</v>
+      </c>
+      <c r="L489">
+        <v>10</v>
+      </c>
+      <c r="M489">
+        <v>-1</v>
+      </c>
+      <c r="N489">
+        <v>0</v>
+      </c>
+      <c r="O489">
+        <v>0</v>
+      </c>
+      <c r="P489">
+        <v>0</v>
+      </c>
+      <c r="Q489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A490">
+        <v>-5</v>
+      </c>
+      <c r="B490">
+        <v>40</v>
+      </c>
+      <c r="C490">
+        <v>-530</v>
+      </c>
+      <c r="D490">
+        <v>0</v>
+      </c>
+      <c r="E490">
+        <v>0</v>
+      </c>
+      <c r="F490">
+        <v>0</v>
+      </c>
+      <c r="G490">
+        <v>1</v>
+      </c>
+      <c r="H490">
+        <v>1</v>
+      </c>
+      <c r="I490">
+        <v>1</v>
+      </c>
+      <c r="J490">
+        <v>10</v>
+      </c>
+      <c r="K490">
+        <v>10</v>
+      </c>
+      <c r="L490">
+        <v>10</v>
+      </c>
+      <c r="M490">
+        <v>-1</v>
+      </c>
+      <c r="N490">
+        <v>0</v>
+      </c>
+      <c r="O490">
+        <v>0</v>
+      </c>
+      <c r="P490">
+        <v>0</v>
+      </c>
+      <c r="Q490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A491">
+        <v>-5</v>
+      </c>
+      <c r="B491">
+        <v>40</v>
+      </c>
+      <c r="C491">
+        <v>-540</v>
+      </c>
+      <c r="D491">
+        <v>0</v>
+      </c>
+      <c r="E491">
+        <v>0</v>
+      </c>
+      <c r="F491">
+        <v>0</v>
+      </c>
+      <c r="G491">
+        <v>1</v>
+      </c>
+      <c r="H491">
+        <v>1</v>
+      </c>
+      <c r="I491">
+        <v>1</v>
+      </c>
+      <c r="J491">
+        <v>10</v>
+      </c>
+      <c r="K491">
+        <v>10</v>
+      </c>
+      <c r="L491">
+        <v>10</v>
+      </c>
+      <c r="M491">
+        <v>-1</v>
+      </c>
+      <c r="N491">
+        <v>0</v>
+      </c>
+      <c r="O491">
+        <v>0</v>
+      </c>
+      <c r="P491">
+        <v>0</v>
+      </c>
+      <c r="Q491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A492">
+        <v>0</v>
+      </c>
+      <c r="B492">
+        <v>40</v>
+      </c>
+      <c r="C492">
+        <v>-770</v>
+      </c>
+      <c r="D492">
+        <v>0</v>
+      </c>
+      <c r="E492">
+        <v>0</v>
+      </c>
+      <c r="F492">
+        <v>0</v>
+      </c>
+      <c r="G492">
+        <v>1</v>
+      </c>
+      <c r="H492">
+        <v>1</v>
+      </c>
+      <c r="I492">
+        <v>1</v>
+      </c>
+      <c r="J492">
+        <v>10</v>
+      </c>
+      <c r="K492">
+        <v>10</v>
+      </c>
+      <c r="L492">
+        <v>10</v>
+      </c>
+      <c r="M492">
+        <v>-1</v>
+      </c>
+      <c r="N492">
+        <v>0</v>
+      </c>
+      <c r="O492">
+        <v>0</v>
+      </c>
+      <c r="P492">
+        <v>0</v>
+      </c>
+      <c r="Q492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A493">
+        <v>0</v>
+      </c>
+      <c r="B493">
+        <v>54.3</v>
+      </c>
+      <c r="C493">
+        <v>-777</v>
+      </c>
+      <c r="D493">
+        <v>0</v>
+      </c>
+      <c r="E493">
+        <v>0</v>
+      </c>
+      <c r="F493">
+        <v>0</v>
+      </c>
+      <c r="G493">
+        <v>1</v>
+      </c>
+      <c r="H493">
+        <v>1</v>
+      </c>
+      <c r="I493">
+        <v>1</v>
+      </c>
+      <c r="J493">
+        <v>10</v>
+      </c>
+      <c r="K493">
+        <v>10</v>
+      </c>
+      <c r="L493">
+        <v>10</v>
+      </c>
+      <c r="M493">
+        <v>-1</v>
+      </c>
+      <c r="N493">
+        <v>0</v>
+      </c>
+      <c r="O493">
+        <v>0</v>
+      </c>
+      <c r="P493">
+        <v>0</v>
+      </c>
+      <c r="Q493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A494">
+        <v>0</v>
+      </c>
+      <c r="B494">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="C494">
+        <v>-784</v>
+      </c>
+      <c r="D494">
+        <v>0</v>
+      </c>
+      <c r="E494">
+        <v>0</v>
+      </c>
+      <c r="F494">
+        <v>0</v>
+      </c>
+      <c r="G494">
+        <v>1</v>
+      </c>
+      <c r="H494">
+        <v>1</v>
+      </c>
+      <c r="I494">
+        <v>1</v>
+      </c>
+      <c r="J494">
+        <v>10</v>
+      </c>
+      <c r="K494">
+        <v>10</v>
+      </c>
+      <c r="L494">
+        <v>10</v>
+      </c>
+      <c r="M494">
+        <v>-1</v>
+      </c>
+      <c r="N494">
+        <v>0</v>
+      </c>
+      <c r="O494">
+        <v>0</v>
+      </c>
+      <c r="P494">
+        <v>0</v>
+      </c>
+      <c r="Q494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A495">
+        <v>0</v>
+      </c>
+      <c r="B495">
+        <v>74.8</v>
+      </c>
+      <c r="C495">
+        <v>-791</v>
+      </c>
+      <c r="D495">
+        <v>0</v>
+      </c>
+      <c r="E495">
+        <v>0</v>
+      </c>
+      <c r="F495">
+        <v>0</v>
+      </c>
+      <c r="G495">
+        <v>1</v>
+      </c>
+      <c r="H495">
+        <v>1</v>
+      </c>
+      <c r="I495">
+        <v>1</v>
+      </c>
+      <c r="J495">
+        <v>10</v>
+      </c>
+      <c r="K495">
+        <v>10</v>
+      </c>
+      <c r="L495">
+        <v>10</v>
+      </c>
+      <c r="M495">
+        <v>-1</v>
+      </c>
+      <c r="N495">
+        <v>0</v>
+      </c>
+      <c r="O495">
+        <v>0</v>
+      </c>
+      <c r="P495">
+        <v>0</v>
+      </c>
+      <c r="Q495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A496">
+        <v>0</v>
+      </c>
+      <c r="B496">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="C496">
+        <v>-798</v>
+      </c>
+      <c r="D496">
+        <v>0</v>
+      </c>
+      <c r="E496">
+        <v>0</v>
+      </c>
+      <c r="F496">
+        <v>0</v>
+      </c>
+      <c r="G496">
+        <v>1</v>
+      </c>
+      <c r="H496">
+        <v>1</v>
+      </c>
+      <c r="I496">
+        <v>1</v>
+      </c>
+      <c r="J496">
+        <v>10</v>
+      </c>
+      <c r="K496">
+        <v>10</v>
+      </c>
+      <c r="L496">
+        <v>10</v>
+      </c>
+      <c r="M496">
+        <v>-1</v>
+      </c>
+      <c r="N496">
+        <v>0</v>
+      </c>
+      <c r="O496">
+        <v>0</v>
+      </c>
+      <c r="P496">
+        <v>0</v>
+      </c>
+      <c r="Q496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A497">
+        <v>0</v>
+      </c>
+      <c r="B497">
+        <v>84.3</v>
+      </c>
+      <c r="C497">
+        <v>-805</v>
+      </c>
+      <c r="D497">
+        <v>0</v>
+      </c>
+      <c r="E497">
+        <v>0</v>
+      </c>
+      <c r="F497">
+        <v>0</v>
+      </c>
+      <c r="G497">
+        <v>1</v>
+      </c>
+      <c r="H497">
+        <v>1</v>
+      </c>
+      <c r="I497">
+        <v>1</v>
+      </c>
+      <c r="J497">
+        <v>10</v>
+      </c>
+      <c r="K497">
+        <v>10</v>
+      </c>
+      <c r="L497">
+        <v>10</v>
+      </c>
+      <c r="M497">
+        <v>-1</v>
+      </c>
+      <c r="N497">
+        <v>0</v>
+      </c>
+      <c r="O497">
+        <v>0</v>
+      </c>
+      <c r="P497">
+        <v>0</v>
+      </c>
+      <c r="Q497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A498">
+        <v>0</v>
+      </c>
+      <c r="B498">
+        <v>84.9</v>
+      </c>
+      <c r="C498">
+        <v>-812</v>
+      </c>
+      <c r="D498">
+        <v>0</v>
+      </c>
+      <c r="E498">
+        <v>0</v>
+      </c>
+      <c r="F498">
+        <v>0</v>
+      </c>
+      <c r="G498">
+        <v>1</v>
+      </c>
+      <c r="H498">
+        <v>1</v>
+      </c>
+      <c r="I498">
+        <v>1</v>
+      </c>
+      <c r="J498">
+        <v>10</v>
+      </c>
+      <c r="K498">
+        <v>10</v>
+      </c>
+      <c r="L498">
+        <v>10</v>
+      </c>
+      <c r="M498">
+        <v>-1</v>
+      </c>
+      <c r="N498">
+        <v>0</v>
+      </c>
+      <c r="O498">
+        <v>0</v>
+      </c>
+      <c r="P498">
+        <v>0</v>
+      </c>
+      <c r="Q498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A499">
+        <v>0</v>
+      </c>
+      <c r="B499">
+        <v>82.8</v>
+      </c>
+      <c r="C499">
+        <v>-819</v>
+      </c>
+      <c r="D499">
+        <v>0</v>
+      </c>
+      <c r="E499">
+        <v>0</v>
+      </c>
+      <c r="F499">
+        <v>0</v>
+      </c>
+      <c r="G499">
+        <v>1</v>
+      </c>
+      <c r="H499">
+        <v>1</v>
+      </c>
+      <c r="I499">
+        <v>1</v>
+      </c>
+      <c r="J499">
+        <v>10</v>
+      </c>
+      <c r="K499">
+        <v>10</v>
+      </c>
+      <c r="L499">
+        <v>10</v>
+      </c>
+      <c r="M499">
+        <v>-1</v>
+      </c>
+      <c r="N499">
+        <v>0</v>
+      </c>
+      <c r="O499">
+        <v>0</v>
+      </c>
+      <c r="P499">
+        <v>0</v>
+      </c>
+      <c r="Q499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A500">
+        <v>0</v>
+      </c>
+      <c r="B500">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="C500">
+        <v>-826</v>
+      </c>
+      <c r="D500">
+        <v>0</v>
+      </c>
+      <c r="E500">
+        <v>0</v>
+      </c>
+      <c r="F500">
+        <v>0</v>
+      </c>
+      <c r="G500">
+        <v>1</v>
+      </c>
+      <c r="H500">
+        <v>1</v>
+      </c>
+      <c r="I500">
+        <v>1</v>
+      </c>
+      <c r="J500">
+        <v>10</v>
+      </c>
+      <c r="K500">
+        <v>10</v>
+      </c>
+      <c r="L500">
+        <v>10</v>
+      </c>
+      <c r="M500">
+        <v>-1</v>
+      </c>
+      <c r="N500">
+        <v>0</v>
+      </c>
+      <c r="O500">
+        <v>0</v>
+      </c>
+      <c r="P500">
+        <v>0</v>
+      </c>
+      <c r="Q500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A501">
+        <v>0</v>
+      </c>
+      <c r="B501">
+        <v>70.3</v>
+      </c>
+      <c r="C501">
+        <v>-833</v>
+      </c>
+      <c r="D501">
+        <v>0</v>
+      </c>
+      <c r="E501">
+        <v>0</v>
+      </c>
+      <c r="F501">
+        <v>0</v>
+      </c>
+      <c r="G501">
+        <v>1</v>
+      </c>
+      <c r="H501">
+        <v>1</v>
+      </c>
+      <c r="I501">
+        <v>1</v>
+      </c>
+      <c r="J501">
+        <v>10</v>
+      </c>
+      <c r="K501">
+        <v>10</v>
+      </c>
+      <c r="L501">
+        <v>10</v>
+      </c>
+      <c r="M501">
+        <v>-1</v>
+      </c>
+      <c r="N501">
+        <v>0</v>
+      </c>
+      <c r="O501">
+        <v>0</v>
+      </c>
+      <c r="P501">
+        <v>0</v>
+      </c>
+      <c r="Q501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A502">
+        <v>0</v>
+      </c>
+      <c r="B502">
+        <v>60</v>
+      </c>
+      <c r="C502">
+        <v>-840</v>
+      </c>
+      <c r="D502">
+        <v>0</v>
+      </c>
+      <c r="E502">
+        <v>0</v>
+      </c>
+      <c r="F502">
+        <v>0</v>
+      </c>
+      <c r="G502">
+        <v>1</v>
+      </c>
+      <c r="H502">
+        <v>1</v>
+      </c>
+      <c r="I502">
+        <v>1</v>
+      </c>
+      <c r="J502">
+        <v>10</v>
+      </c>
+      <c r="K502">
+        <v>10</v>
+      </c>
+      <c r="L502">
+        <v>10</v>
+      </c>
+      <c r="M502">
+        <v>-1</v>
+      </c>
+      <c r="N502">
+        <v>0</v>
+      </c>
+      <c r="O502">
+        <v>0</v>
+      </c>
+      <c r="P502">
+        <v>0</v>
+      </c>
+      <c r="Q502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A503">
+        <v>5</v>
+      </c>
+      <c r="B503">
+        <v>60</v>
+      </c>
+      <c r="C503">
+        <v>-900</v>
+      </c>
+      <c r="D503">
+        <v>0</v>
+      </c>
+      <c r="E503">
+        <v>0</v>
+      </c>
+      <c r="F503">
+        <v>0</v>
+      </c>
+      <c r="G503">
+        <v>1</v>
+      </c>
+      <c r="H503">
+        <v>1</v>
+      </c>
+      <c r="I503">
+        <v>1</v>
+      </c>
+      <c r="J503">
+        <v>10</v>
+      </c>
+      <c r="K503">
+        <v>10</v>
+      </c>
+      <c r="L503">
+        <v>10</v>
+      </c>
+      <c r="M503">
+        <v>-1</v>
+      </c>
+      <c r="N503">
+        <v>0</v>
+      </c>
+      <c r="O503">
+        <v>0</v>
+      </c>
+      <c r="P503">
+        <v>0</v>
+      </c>
+      <c r="Q503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A504">
+        <v>5</v>
+      </c>
+      <c r="B504">
+        <v>60</v>
+      </c>
+      <c r="C504">
+        <v>-910</v>
+      </c>
+      <c r="D504">
+        <v>0</v>
+      </c>
+      <c r="E504">
+        <v>0</v>
+      </c>
+      <c r="F504">
+        <v>0</v>
+      </c>
+      <c r="G504">
+        <v>1</v>
+      </c>
+      <c r="H504">
+        <v>1</v>
+      </c>
+      <c r="I504">
+        <v>1</v>
+      </c>
+      <c r="J504">
+        <v>10</v>
+      </c>
+      <c r="K504">
+        <v>10</v>
+      </c>
+      <c r="L504">
+        <v>10</v>
+      </c>
+      <c r="M504">
+        <v>-1</v>
+      </c>
+      <c r="N504">
+        <v>0</v>
+      </c>
+      <c r="O504">
+        <v>0</v>
+      </c>
+      <c r="P504">
+        <v>0</v>
+      </c>
+      <c r="Q504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A505">
+        <v>5</v>
+      </c>
+      <c r="B505">
+        <v>60</v>
+      </c>
+      <c r="C505">
+        <v>-920</v>
+      </c>
+      <c r="D505">
+        <v>0</v>
+      </c>
+      <c r="E505">
+        <v>0</v>
+      </c>
+      <c r="F505">
+        <v>0</v>
+      </c>
+      <c r="G505">
+        <v>1</v>
+      </c>
+      <c r="H505">
+        <v>1</v>
+      </c>
+      <c r="I505">
+        <v>1</v>
+      </c>
+      <c r="J505">
+        <v>10</v>
+      </c>
+      <c r="K505">
+        <v>10</v>
+      </c>
+      <c r="L505">
+        <v>10</v>
+      </c>
+      <c r="M505">
+        <v>-1</v>
+      </c>
+      <c r="N505">
+        <v>0</v>
+      </c>
+      <c r="O505">
+        <v>0</v>
+      </c>
+      <c r="P505">
+        <v>0</v>
+      </c>
+      <c r="Q505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A506">
+        <v>5</v>
+      </c>
+      <c r="B506">
+        <v>60</v>
+      </c>
+      <c r="C506">
+        <v>-930</v>
+      </c>
+      <c r="D506">
+        <v>0</v>
+      </c>
+      <c r="E506">
+        <v>0</v>
+      </c>
+      <c r="F506">
+        <v>0</v>
+      </c>
+      <c r="G506">
+        <v>1</v>
+      </c>
+      <c r="H506">
+        <v>1</v>
+      </c>
+      <c r="I506">
+        <v>1</v>
+      </c>
+      <c r="J506">
+        <v>10</v>
+      </c>
+      <c r="K506">
+        <v>10</v>
+      </c>
+      <c r="L506">
+        <v>10</v>
+      </c>
+      <c r="M506">
+        <v>-1</v>
+      </c>
+      <c r="N506">
+        <v>0</v>
+      </c>
+      <c r="O506">
+        <v>0</v>
+      </c>
+      <c r="P506">
+        <v>0</v>
+      </c>
+      <c r="Q506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A507">
+        <v>5</v>
+      </c>
+      <c r="B507">
+        <v>60</v>
+      </c>
+      <c r="C507">
+        <v>-940</v>
+      </c>
+      <c r="D507">
+        <v>0</v>
+      </c>
+      <c r="E507">
+        <v>0</v>
+      </c>
+      <c r="F507">
+        <v>0</v>
+      </c>
+      <c r="G507">
+        <v>1</v>
+      </c>
+      <c r="H507">
+        <v>1</v>
+      </c>
+      <c r="I507">
+        <v>1</v>
+      </c>
+      <c r="J507">
+        <v>10</v>
+      </c>
+      <c r="K507">
+        <v>10</v>
+      </c>
+      <c r="L507">
+        <v>10</v>
+      </c>
+      <c r="M507">
+        <v>-1</v>
+      </c>
+      <c r="N507">
+        <v>0</v>
+      </c>
+      <c r="O507">
+        <v>0</v>
+      </c>
+      <c r="P507">
+        <v>0</v>
+      </c>
+      <c r="Q507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A508">
+        <v>5</v>
+      </c>
+      <c r="B508">
+        <v>60</v>
+      </c>
+      <c r="C508">
+        <v>-950</v>
+      </c>
+      <c r="D508">
+        <v>0</v>
+      </c>
+      <c r="E508">
+        <v>0</v>
+      </c>
+      <c r="F508">
+        <v>0</v>
+      </c>
+      <c r="G508">
+        <v>1</v>
+      </c>
+      <c r="H508">
+        <v>1</v>
+      </c>
+      <c r="I508">
+        <v>1</v>
+      </c>
+      <c r="J508">
+        <v>10</v>
+      </c>
+      <c r="K508">
+        <v>10</v>
+      </c>
+      <c r="L508">
+        <v>10</v>
+      </c>
+      <c r="M508">
+        <v>-1</v>
+      </c>
+      <c r="N508">
+        <v>0</v>
+      </c>
+      <c r="O508">
+        <v>0</v>
+      </c>
+      <c r="P508">
+        <v>0</v>
+      </c>
+      <c r="Q508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A509">
+        <v>5</v>
+      </c>
+      <c r="B509">
+        <v>60</v>
+      </c>
+      <c r="C509">
+        <v>-960</v>
+      </c>
+      <c r="D509">
+        <v>0</v>
+      </c>
+      <c r="E509">
+        <v>0</v>
+      </c>
+      <c r="F509">
+        <v>0</v>
+      </c>
+      <c r="G509">
+        <v>1</v>
+      </c>
+      <c r="H509">
+        <v>1</v>
+      </c>
+      <c r="I509">
+        <v>1</v>
+      </c>
+      <c r="J509">
+        <v>10</v>
+      </c>
+      <c r="K509">
+        <v>10</v>
+      </c>
+      <c r="L509">
+        <v>10</v>
+      </c>
+      <c r="M509">
+        <v>-1</v>
+      </c>
+      <c r="N509">
+        <v>0</v>
+      </c>
+      <c r="O509">
+        <v>0</v>
+      </c>
+      <c r="P509">
+        <v>0</v>
+      </c>
+      <c r="Q509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A510">
+        <v>5</v>
+      </c>
+      <c r="B510">
+        <v>60</v>
+      </c>
+      <c r="C510">
+        <v>-970</v>
+      </c>
+      <c r="D510">
+        <v>0</v>
+      </c>
+      <c r="E510">
+        <v>0</v>
+      </c>
+      <c r="F510">
+        <v>0</v>
+      </c>
+      <c r="G510">
+        <v>1</v>
+      </c>
+      <c r="H510">
+        <v>1</v>
+      </c>
+      <c r="I510">
+        <v>1</v>
+      </c>
+      <c r="J510">
+        <v>10</v>
+      </c>
+      <c r="K510">
+        <v>10</v>
+      </c>
+      <c r="L510">
+        <v>10</v>
+      </c>
+      <c r="M510">
+        <v>-1</v>
+      </c>
+      <c r="N510">
+        <v>0</v>
+      </c>
+      <c r="O510">
+        <v>0</v>
+      </c>
+      <c r="P510">
+        <v>0</v>
+      </c>
+      <c r="Q510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A511">
+        <v>5</v>
+      </c>
+      <c r="B511">
+        <v>60</v>
+      </c>
+      <c r="C511">
+        <v>-980</v>
+      </c>
+      <c r="D511">
+        <v>0</v>
+      </c>
+      <c r="E511">
+        <v>0</v>
+      </c>
+      <c r="F511">
+        <v>0</v>
+      </c>
+      <c r="G511">
+        <v>1</v>
+      </c>
+      <c r="H511">
+        <v>1</v>
+      </c>
+      <c r="I511">
+        <v>1</v>
+      </c>
+      <c r="J511">
+        <v>10</v>
+      </c>
+      <c r="K511">
+        <v>10</v>
+      </c>
+      <c r="L511">
+        <v>10</v>
+      </c>
+      <c r="M511">
+        <v>-1</v>
+      </c>
+      <c r="N511">
+        <v>0</v>
+      </c>
+      <c r="O511">
+        <v>0</v>
+      </c>
+      <c r="P511">
+        <v>0</v>
+      </c>
+      <c r="Q511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A512">
+        <v>5</v>
+      </c>
+      <c r="B512">
+        <v>60</v>
+      </c>
+      <c r="C512">
+        <v>-990</v>
+      </c>
+      <c r="D512">
+        <v>0</v>
+      </c>
+      <c r="E512">
+        <v>0</v>
+      </c>
+      <c r="F512">
+        <v>0</v>
+      </c>
+      <c r="G512">
+        <v>1</v>
+      </c>
+      <c r="H512">
+        <v>1</v>
+      </c>
+      <c r="I512">
+        <v>1</v>
+      </c>
+      <c r="J512">
+        <v>10</v>
+      </c>
+      <c r="K512">
+        <v>10</v>
+      </c>
+      <c r="L512">
+        <v>10</v>
+      </c>
+      <c r="M512">
+        <v>-1</v>
+      </c>
+      <c r="N512">
+        <v>0</v>
+      </c>
+      <c r="O512">
+        <v>0</v>
+      </c>
+      <c r="P512">
+        <v>0</v>
+      </c>
+      <c r="Q512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A513">
+        <v>-5</v>
+      </c>
+      <c r="B513">
+        <v>60</v>
+      </c>
+      <c r="C513">
+        <v>-900</v>
+      </c>
+      <c r="D513">
+        <v>0</v>
+      </c>
+      <c r="E513">
+        <v>0</v>
+      </c>
+      <c r="F513">
+        <v>0</v>
+      </c>
+      <c r="G513">
+        <v>1</v>
+      </c>
+      <c r="H513">
+        <v>1</v>
+      </c>
+      <c r="I513">
+        <v>1</v>
+      </c>
+      <c r="J513">
+        <v>10</v>
+      </c>
+      <c r="K513">
+        <v>10</v>
+      </c>
+      <c r="L513">
+        <v>10</v>
+      </c>
+      <c r="M513">
+        <v>-1</v>
+      </c>
+      <c r="N513">
+        <v>0</v>
+      </c>
+      <c r="O513">
+        <v>0</v>
+      </c>
+      <c r="P513">
+        <v>0</v>
+      </c>
+      <c r="Q513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A514">
+        <v>-5</v>
+      </c>
+      <c r="B514">
+        <v>60</v>
+      </c>
+      <c r="C514">
+        <v>-910</v>
+      </c>
+      <c r="D514">
+        <v>0</v>
+      </c>
+      <c r="E514">
+        <v>0</v>
+      </c>
+      <c r="F514">
+        <v>0</v>
+      </c>
+      <c r="G514">
+        <v>1</v>
+      </c>
+      <c r="H514">
+        <v>1</v>
+      </c>
+      <c r="I514">
+        <v>1</v>
+      </c>
+      <c r="J514">
+        <v>10</v>
+      </c>
+      <c r="K514">
+        <v>10</v>
+      </c>
+      <c r="L514">
+        <v>10</v>
+      </c>
+      <c r="M514">
+        <v>-1</v>
+      </c>
+      <c r="N514">
+        <v>0</v>
+      </c>
+      <c r="O514">
+        <v>0</v>
+      </c>
+      <c r="P514">
+        <v>0</v>
+      </c>
+      <c r="Q514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A515">
+        <v>-5</v>
+      </c>
+      <c r="B515">
+        <v>60</v>
+      </c>
+      <c r="C515">
+        <v>-920</v>
+      </c>
+      <c r="D515">
+        <v>0</v>
+      </c>
+      <c r="E515">
+        <v>0</v>
+      </c>
+      <c r="F515">
+        <v>0</v>
+      </c>
+      <c r="G515">
+        <v>1</v>
+      </c>
+      <c r="H515">
+        <v>1</v>
+      </c>
+      <c r="I515">
+        <v>1</v>
+      </c>
+      <c r="J515">
+        <v>10</v>
+      </c>
+      <c r="K515">
+        <v>10</v>
+      </c>
+      <c r="L515">
+        <v>10</v>
+      </c>
+      <c r="M515">
+        <v>-1</v>
+      </c>
+      <c r="N515">
+        <v>0</v>
+      </c>
+      <c r="O515">
+        <v>0</v>
+      </c>
+      <c r="P515">
+        <v>0</v>
+      </c>
+      <c r="Q515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A516">
+        <v>-5</v>
+      </c>
+      <c r="B516">
+        <v>60</v>
+      </c>
+      <c r="C516">
+        <v>-930</v>
+      </c>
+      <c r="D516">
+        <v>0</v>
+      </c>
+      <c r="E516">
+        <v>0</v>
+      </c>
+      <c r="F516">
+        <v>0</v>
+      </c>
+      <c r="G516">
+        <v>1</v>
+      </c>
+      <c r="H516">
+        <v>1</v>
+      </c>
+      <c r="I516">
+        <v>1</v>
+      </c>
+      <c r="J516">
+        <v>10</v>
+      </c>
+      <c r="K516">
+        <v>10</v>
+      </c>
+      <c r="L516">
+        <v>10</v>
+      </c>
+      <c r="M516">
+        <v>-1</v>
+      </c>
+      <c r="N516">
+        <v>0</v>
+      </c>
+      <c r="O516">
+        <v>0</v>
+      </c>
+      <c r="P516">
+        <v>0</v>
+      </c>
+      <c r="Q516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A517">
+        <v>-5</v>
+      </c>
+      <c r="B517">
+        <v>60</v>
+      </c>
+      <c r="C517">
+        <v>-940</v>
+      </c>
+      <c r="D517">
+        <v>0</v>
+      </c>
+      <c r="E517">
+        <v>0</v>
+      </c>
+      <c r="F517">
+        <v>0</v>
+      </c>
+      <c r="G517">
+        <v>1</v>
+      </c>
+      <c r="H517">
+        <v>1</v>
+      </c>
+      <c r="I517">
+        <v>1</v>
+      </c>
+      <c r="J517">
+        <v>10</v>
+      </c>
+      <c r="K517">
+        <v>10</v>
+      </c>
+      <c r="L517">
+        <v>10</v>
+      </c>
+      <c r="M517">
+        <v>-1</v>
+      </c>
+      <c r="N517">
+        <v>0</v>
+      </c>
+      <c r="O517">
+        <v>0</v>
+      </c>
+      <c r="P517">
+        <v>0</v>
+      </c>
+      <c r="Q517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A518">
+        <v>-5</v>
+      </c>
+      <c r="B518">
+        <v>60</v>
+      </c>
+      <c r="C518">
+        <v>-950</v>
+      </c>
+      <c r="D518">
+        <v>0</v>
+      </c>
+      <c r="E518">
+        <v>0</v>
+      </c>
+      <c r="F518">
+        <v>0</v>
+      </c>
+      <c r="G518">
+        <v>1</v>
+      </c>
+      <c r="H518">
+        <v>1</v>
+      </c>
+      <c r="I518">
+        <v>1</v>
+      </c>
+      <c r="J518">
+        <v>10</v>
+      </c>
+      <c r="K518">
+        <v>10</v>
+      </c>
+      <c r="L518">
+        <v>10</v>
+      </c>
+      <c r="M518">
+        <v>-1</v>
+      </c>
+      <c r="N518">
+        <v>0</v>
+      </c>
+      <c r="O518">
+        <v>0</v>
+      </c>
+      <c r="P518">
+        <v>0</v>
+      </c>
+      <c r="Q518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A519">
+        <v>-5</v>
+      </c>
+      <c r="B519">
+        <v>60</v>
+      </c>
+      <c r="C519">
+        <v>-960</v>
+      </c>
+      <c r="D519">
+        <v>0</v>
+      </c>
+      <c r="E519">
+        <v>0</v>
+      </c>
+      <c r="F519">
+        <v>0</v>
+      </c>
+      <c r="G519">
+        <v>1</v>
+      </c>
+      <c r="H519">
+        <v>1</v>
+      </c>
+      <c r="I519">
+        <v>1</v>
+      </c>
+      <c r="J519">
+        <v>10</v>
+      </c>
+      <c r="K519">
+        <v>10</v>
+      </c>
+      <c r="L519">
+        <v>10</v>
+      </c>
+      <c r="M519">
+        <v>-1</v>
+      </c>
+      <c r="N519">
+        <v>0</v>
+      </c>
+      <c r="O519">
+        <v>0</v>
+      </c>
+      <c r="P519">
+        <v>0</v>
+      </c>
+      <c r="Q519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A520">
+        <v>-5</v>
+      </c>
+      <c r="B520">
+        <v>60</v>
+      </c>
+      <c r="C520">
+        <v>-970</v>
+      </c>
+      <c r="D520">
+        <v>0</v>
+      </c>
+      <c r="E520">
+        <v>0</v>
+      </c>
+      <c r="F520">
+        <v>0</v>
+      </c>
+      <c r="G520">
+        <v>1</v>
+      </c>
+      <c r="H520">
+        <v>1</v>
+      </c>
+      <c r="I520">
+        <v>1</v>
+      </c>
+      <c r="J520">
+        <v>10</v>
+      </c>
+      <c r="K520">
+        <v>10</v>
+      </c>
+      <c r="L520">
+        <v>10</v>
+      </c>
+      <c r="M520">
+        <v>-1</v>
+      </c>
+      <c r="N520">
+        <v>0</v>
+      </c>
+      <c r="O520">
+        <v>0</v>
+      </c>
+      <c r="P520">
+        <v>0</v>
+      </c>
+      <c r="Q520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A521">
+        <v>-5</v>
+      </c>
+      <c r="B521">
+        <v>60</v>
+      </c>
+      <c r="C521">
+        <v>-980</v>
+      </c>
+      <c r="D521">
+        <v>0</v>
+      </c>
+      <c r="E521">
+        <v>0</v>
+      </c>
+      <c r="F521">
+        <v>0</v>
+      </c>
+      <c r="G521">
+        <v>1</v>
+      </c>
+      <c r="H521">
+        <v>1</v>
+      </c>
+      <c r="I521">
+        <v>1</v>
+      </c>
+      <c r="J521">
+        <v>10</v>
+      </c>
+      <c r="K521">
+        <v>10</v>
+      </c>
+      <c r="L521">
+        <v>10</v>
+      </c>
+      <c r="M521">
+        <v>-1</v>
+      </c>
+      <c r="N521">
+        <v>0</v>
+      </c>
+      <c r="O521">
+        <v>0</v>
+      </c>
+      <c r="P521">
+        <v>0</v>
+      </c>
+      <c r="Q521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A522">
+        <v>-5</v>
+      </c>
+      <c r="B522">
+        <v>60</v>
+      </c>
+      <c r="C522">
+        <v>-990</v>
+      </c>
+      <c r="D522">
+        <v>0</v>
+      </c>
+      <c r="E522">
+        <v>0</v>
+      </c>
+      <c r="F522">
+        <v>0</v>
+      </c>
+      <c r="G522">
+        <v>1</v>
+      </c>
+      <c r="H522">
+        <v>1</v>
+      </c>
+      <c r="I522">
+        <v>1</v>
+      </c>
+      <c r="J522">
+        <v>10</v>
+      </c>
+      <c r="K522">
+        <v>10</v>
+      </c>
+      <c r="L522">
+        <v>10</v>
+      </c>
+      <c r="M522">
+        <v>-1</v>
+      </c>
+      <c r="N522">
+        <v>0</v>
+      </c>
+      <c r="O522">
+        <v>0</v>
+      </c>
+      <c r="P522">
+        <v>0</v>
+      </c>
+      <c r="Q522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A523">
+        <v>0</v>
+      </c>
+      <c r="B523">
+        <v>80</v>
+      </c>
+      <c r="C523">
+        <v>-1280</v>
+      </c>
+      <c r="D523">
+        <v>0</v>
+      </c>
+      <c r="E523">
+        <v>0</v>
+      </c>
+      <c r="F523">
+        <v>0</v>
+      </c>
+      <c r="G523">
+        <v>1</v>
+      </c>
+      <c r="H523">
+        <v>1</v>
+      </c>
+      <c r="I523">
+        <v>1</v>
+      </c>
+      <c r="J523">
+        <v>10</v>
+      </c>
+      <c r="K523">
+        <v>10</v>
+      </c>
+      <c r="L523">
+        <v>10</v>
+      </c>
+      <c r="M523">
+        <v>-1</v>
+      </c>
+      <c r="N523">
+        <v>0</v>
+      </c>
+      <c r="O523">
+        <v>0</v>
+      </c>
+      <c r="P523">
+        <v>0</v>
+      </c>
+      <c r="Q523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A524">
+        <v>0</v>
+      </c>
+      <c r="B524">
+        <v>105</v>
+      </c>
+      <c r="C524">
+        <v>-1295</v>
+      </c>
+      <c r="D524">
+        <v>0</v>
+      </c>
+      <c r="E524">
+        <v>0</v>
+      </c>
+      <c r="F524">
+        <v>0</v>
+      </c>
+      <c r="G524">
+        <v>1</v>
+      </c>
+      <c r="H524">
+        <v>1</v>
+      </c>
+      <c r="I524">
+        <v>1</v>
+      </c>
+      <c r="J524">
+        <v>10</v>
+      </c>
+      <c r="K524">
+        <v>10</v>
+      </c>
+      <c r="L524">
+        <v>10</v>
+      </c>
+      <c r="M524">
+        <v>-1</v>
+      </c>
+      <c r="N524">
+        <v>0</v>
+      </c>
+      <c r="O524">
+        <v>0</v>
+      </c>
+      <c r="P524">
+        <v>0</v>
+      </c>
+      <c r="Q524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A525">
+        <v>0</v>
+      </c>
+      <c r="B525">
+        <v>120</v>
+      </c>
+      <c r="C525">
+        <v>-1310</v>
+      </c>
+      <c r="D525">
+        <v>0</v>
+      </c>
+      <c r="E525">
+        <v>0</v>
+      </c>
+      <c r="F525">
+        <v>0</v>
+      </c>
+      <c r="G525">
+        <v>1</v>
+      </c>
+      <c r="H525">
+        <v>1</v>
+      </c>
+      <c r="I525">
+        <v>1</v>
+      </c>
+      <c r="J525">
+        <v>10</v>
+      </c>
+      <c r="K525">
+        <v>10</v>
+      </c>
+      <c r="L525">
+        <v>10</v>
+      </c>
+      <c r="M525">
+        <v>-1</v>
+      </c>
+      <c r="N525">
+        <v>0</v>
+      </c>
+      <c r="O525">
+        <v>0</v>
+      </c>
+      <c r="P525">
+        <v>0</v>
+      </c>
+      <c r="Q525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A526">
+        <v>0</v>
+      </c>
+      <c r="B526">
+        <v>125</v>
+      </c>
+      <c r="C526">
+        <v>-1325</v>
+      </c>
+      <c r="D526">
+        <v>0</v>
+      </c>
+      <c r="E526">
+        <v>0</v>
+      </c>
+      <c r="F526">
+        <v>0</v>
+      </c>
+      <c r="G526">
+        <v>1</v>
+      </c>
+      <c r="H526">
+        <v>1</v>
+      </c>
+      <c r="I526">
+        <v>1</v>
+      </c>
+      <c r="J526">
+        <v>10</v>
+      </c>
+      <c r="K526">
+        <v>10</v>
+      </c>
+      <c r="L526">
+        <v>10</v>
+      </c>
+      <c r="M526">
+        <v>-1</v>
+      </c>
+      <c r="N526">
+        <v>0</v>
+      </c>
+      <c r="O526">
+        <v>0</v>
+      </c>
+      <c r="P526">
+        <v>0</v>
+      </c>
+      <c r="Q526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A527">
+        <v>0</v>
+      </c>
+      <c r="B527">
+        <v>120</v>
+      </c>
+      <c r="C527">
+        <v>-1340</v>
+      </c>
+      <c r="D527">
+        <v>0</v>
+      </c>
+      <c r="E527">
+        <v>0</v>
+      </c>
+      <c r="F527">
+        <v>0</v>
+      </c>
+      <c r="G527">
+        <v>1</v>
+      </c>
+      <c r="H527">
+        <v>1</v>
+      </c>
+      <c r="I527">
+        <v>1</v>
+      </c>
+      <c r="J527">
+        <v>10</v>
+      </c>
+      <c r="K527">
+        <v>10</v>
+      </c>
+      <c r="L527">
+        <v>10</v>
+      </c>
+      <c r="M527">
+        <v>-1</v>
+      </c>
+      <c r="N527">
+        <v>0</v>
+      </c>
+      <c r="O527">
+        <v>0</v>
+      </c>
+      <c r="P527">
+        <v>0</v>
+      </c>
+      <c r="Q527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A528">
+        <v>0</v>
+      </c>
+      <c r="B528">
+        <v>105</v>
+      </c>
+      <c r="C528">
+        <v>-1355</v>
+      </c>
+      <c r="D528">
+        <v>0</v>
+      </c>
+      <c r="E528">
+        <v>0</v>
+      </c>
+      <c r="F528">
+        <v>0</v>
+      </c>
+      <c r="G528">
+        <v>1</v>
+      </c>
+      <c r="H528">
+        <v>1</v>
+      </c>
+      <c r="I528">
+        <v>1</v>
+      </c>
+      <c r="J528">
+        <v>10</v>
+      </c>
+      <c r="K528">
+        <v>10</v>
+      </c>
+      <c r="L528">
+        <v>10</v>
+      </c>
+      <c r="M528">
+        <v>-1</v>
+      </c>
+      <c r="N528">
+        <v>0</v>
+      </c>
+      <c r="O528">
+        <v>0</v>
+      </c>
+      <c r="P528">
+        <v>0</v>
+      </c>
+      <c r="Q528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A529">
+        <v>0</v>
+      </c>
+      <c r="B529">
+        <v>80</v>
+      </c>
+      <c r="C529">
+        <v>-1370</v>
+      </c>
+      <c r="D529">
+        <v>0</v>
+      </c>
+      <c r="E529">
+        <v>0</v>
+      </c>
+      <c r="F529">
+        <v>0</v>
+      </c>
+      <c r="G529">
+        <v>1</v>
+      </c>
+      <c r="H529">
+        <v>1</v>
+      </c>
+      <c r="I529">
+        <v>1</v>
+      </c>
+      <c r="J529">
+        <v>10</v>
+      </c>
+      <c r="K529">
+        <v>10</v>
+      </c>
+      <c r="L529">
+        <v>10</v>
+      </c>
+      <c r="M529">
+        <v>-1</v>
+      </c>
+      <c r="N529">
+        <v>0</v>
+      </c>
+      <c r="O529">
+        <v>0</v>
+      </c>
+      <c r="P529">
+        <v>0</v>
+      </c>
+      <c r="Q529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A530">
+        <v>0</v>
+      </c>
+      <c r="B530">
+        <v>80</v>
+      </c>
+      <c r="C530">
+        <v>-1380</v>
+      </c>
+      <c r="D530">
+        <v>0</v>
+      </c>
+      <c r="E530">
+        <v>0</v>
+      </c>
+      <c r="F530">
+        <v>0</v>
+      </c>
+      <c r="G530">
+        <v>1</v>
+      </c>
+      <c r="H530">
+        <v>1</v>
+      </c>
+      <c r="I530">
+        <v>1</v>
+      </c>
+      <c r="J530">
+        <v>10</v>
+      </c>
+      <c r="K530">
+        <v>10</v>
+      </c>
+      <c r="L530">
+        <v>10</v>
+      </c>
+      <c r="M530">
+        <v>-1</v>
+      </c>
+      <c r="N530">
+        <v>0</v>
+      </c>
+      <c r="O530">
+        <v>0</v>
+      </c>
+      <c r="P530">
+        <v>0</v>
+      </c>
+      <c r="Q530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A531">
+        <v>0</v>
+      </c>
+      <c r="B531">
+        <v>99.4</v>
+      </c>
+      <c r="C531">
+        <v>-1391</v>
+      </c>
+      <c r="D531">
+        <v>0</v>
+      </c>
+      <c r="E531">
+        <v>0</v>
+      </c>
+      <c r="F531">
+        <v>0</v>
+      </c>
+      <c r="G531">
+        <v>1</v>
+      </c>
+      <c r="H531">
+        <v>1</v>
+      </c>
+      <c r="I531">
+        <v>1</v>
+      </c>
+      <c r="J531">
+        <v>10</v>
+      </c>
+      <c r="K531">
+        <v>10</v>
+      </c>
+      <c r="L531">
+        <v>10</v>
+      </c>
+      <c r="M531">
+        <v>-1</v>
+      </c>
+      <c r="N531">
+        <v>0</v>
+      </c>
+      <c r="O531">
+        <v>0</v>
+      </c>
+      <c r="P531">
+        <v>0</v>
+      </c>
+      <c r="Q531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A532">
+        <v>0</v>
+      </c>
+      <c r="B532">
+        <v>114</v>
+      </c>
+      <c r="C532">
+        <v>-1403</v>
+      </c>
+      <c r="D532">
+        <v>0</v>
+      </c>
+      <c r="E532">
+        <v>0</v>
+      </c>
+      <c r="F532">
+        <v>0</v>
+      </c>
+      <c r="G532">
+        <v>1</v>
+      </c>
+      <c r="H532">
+        <v>1</v>
+      </c>
+      <c r="I532">
+        <v>1</v>
+      </c>
+      <c r="J532">
+        <v>10</v>
+      </c>
+      <c r="K532">
+        <v>10</v>
+      </c>
+      <c r="L532">
+        <v>10</v>
+      </c>
+      <c r="M532">
+        <v>-1</v>
+      </c>
+      <c r="N532">
+        <v>0</v>
+      </c>
+      <c r="O532">
+        <v>0</v>
+      </c>
+      <c r="P532">
+        <v>0</v>
+      </c>
+      <c r="Q532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A533">
+        <v>0</v>
+      </c>
+      <c r="B533">
+        <v>122.8</v>
+      </c>
+      <c r="C533">
+        <v>-1414</v>
+      </c>
+      <c r="D533">
+        <v>0</v>
+      </c>
+      <c r="E533">
+        <v>0</v>
+      </c>
+      <c r="F533">
+        <v>0</v>
+      </c>
+      <c r="G533">
+        <v>1</v>
+      </c>
+      <c r="H533">
+        <v>1</v>
+      </c>
+      <c r="I533">
+        <v>1</v>
+      </c>
+      <c r="J533">
+        <v>10</v>
+      </c>
+      <c r="K533">
+        <v>10</v>
+      </c>
+      <c r="L533">
+        <v>10</v>
+      </c>
+      <c r="M533">
+        <v>-1</v>
+      </c>
+      <c r="N533">
+        <v>0</v>
+      </c>
+      <c r="O533">
+        <v>0</v>
+      </c>
+      <c r="P533">
+        <v>0</v>
+      </c>
+      <c r="Q533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A534">
+        <v>0</v>
+      </c>
+      <c r="B534">
+        <v>125</v>
+      </c>
+      <c r="C534">
+        <v>-1425</v>
+      </c>
+      <c r="D534">
+        <v>0</v>
+      </c>
+      <c r="E534">
+        <v>0</v>
+      </c>
+      <c r="F534">
+        <v>0</v>
+      </c>
+      <c r="G534">
+        <v>1</v>
+      </c>
+      <c r="H534">
+        <v>1</v>
+      </c>
+      <c r="I534">
+        <v>1</v>
+      </c>
+      <c r="J534">
+        <v>10</v>
+      </c>
+      <c r="K534">
+        <v>10</v>
+      </c>
+      <c r="L534">
+        <v>10</v>
+      </c>
+      <c r="M534">
+        <v>-1</v>
+      </c>
+      <c r="N534">
+        <v>0</v>
+      </c>
+      <c r="O534">
+        <v>0</v>
+      </c>
+      <c r="P534">
+        <v>0</v>
+      </c>
+      <c r="Q534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A535">
+        <v>0</v>
+      </c>
+      <c r="B535">
+        <v>122.8</v>
+      </c>
+      <c r="C535">
+        <v>-1436</v>
+      </c>
+      <c r="D535">
+        <v>0</v>
+      </c>
+      <c r="E535">
+        <v>0</v>
+      </c>
+      <c r="F535">
+        <v>0</v>
+      </c>
+      <c r="G535">
+        <v>1</v>
+      </c>
+      <c r="H535">
+        <v>1</v>
+      </c>
+      <c r="I535">
+        <v>1</v>
+      </c>
+      <c r="J535">
+        <v>10</v>
+      </c>
+      <c r="K535">
+        <v>10</v>
+      </c>
+      <c r="L535">
+        <v>10</v>
+      </c>
+      <c r="M535">
+        <v>-1</v>
+      </c>
+      <c r="N535">
+        <v>0</v>
+      </c>
+      <c r="O535">
+        <v>0</v>
+      </c>
+      <c r="P535">
+        <v>0</v>
+      </c>
+      <c r="Q535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A536">
+        <v>0</v>
+      </c>
+      <c r="B536">
+        <v>114</v>
+      </c>
+      <c r="C536">
+        <v>-1448</v>
+      </c>
+      <c r="D536">
+        <v>0</v>
+      </c>
+      <c r="E536">
+        <v>0</v>
+      </c>
+      <c r="F536">
+        <v>0</v>
+      </c>
+      <c r="G536">
+        <v>1</v>
+      </c>
+      <c r="H536">
+        <v>1</v>
+      </c>
+      <c r="I536">
+        <v>1</v>
+      </c>
+      <c r="J536">
+        <v>10</v>
+      </c>
+      <c r="K536">
+        <v>10</v>
+      </c>
+      <c r="L536">
+        <v>10</v>
+      </c>
+      <c r="M536">
+        <v>-1</v>
+      </c>
+      <c r="N536">
+        <v>0</v>
+      </c>
+      <c r="O536">
+        <v>0</v>
+      </c>
+      <c r="P536">
+        <v>0</v>
+      </c>
+      <c r="Q536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A537">
+        <v>0</v>
+      </c>
+      <c r="B537">
+        <v>99.4</v>
+      </c>
+      <c r="C537">
+        <v>-1459</v>
+      </c>
+      <c r="D537">
+        <v>0</v>
+      </c>
+      <c r="E537">
+        <v>0</v>
+      </c>
+      <c r="F537">
+        <v>0</v>
+      </c>
+      <c r="G537">
+        <v>1</v>
+      </c>
+      <c r="H537">
+        <v>1</v>
+      </c>
+      <c r="I537">
+        <v>1</v>
+      </c>
+      <c r="J537">
+        <v>10</v>
+      </c>
+      <c r="K537">
+        <v>10</v>
+      </c>
+      <c r="L537">
+        <v>10</v>
+      </c>
+      <c r="M537">
+        <v>-1</v>
+      </c>
+      <c r="N537">
+        <v>0</v>
+      </c>
+      <c r="O537">
+        <v>0</v>
+      </c>
+      <c r="P537">
+        <v>0</v>
+      </c>
+      <c r="Q537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A538">
+        <v>0</v>
+      </c>
+      <c r="B538">
+        <v>80</v>
+      </c>
+      <c r="C538">
+        <v>-1470</v>
+      </c>
+      <c r="D538">
+        <v>0</v>
+      </c>
+      <c r="E538">
+        <v>0</v>
+      </c>
+      <c r="F538">
+        <v>0</v>
+      </c>
+      <c r="G538">
+        <v>1</v>
+      </c>
+      <c r="H538">
+        <v>1</v>
+      </c>
+      <c r="I538">
+        <v>1</v>
+      </c>
+      <c r="J538">
+        <v>10</v>
+      </c>
+      <c r="K538">
+        <v>10</v>
+      </c>
+      <c r="L538">
+        <v>10</v>
+      </c>
+      <c r="M538">
+        <v>-1</v>
+      </c>
+      <c r="N538">
+        <v>0</v>
+      </c>
+      <c r="O538">
+        <v>0</v>
+      </c>
+      <c r="P538">
+        <v>0</v>
+      </c>
+      <c r="Q538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A539">
+        <v>0</v>
+      </c>
+      <c r="B539">
+        <v>80</v>
+      </c>
+      <c r="C539">
+        <v>-1500</v>
+      </c>
+      <c r="D539">
+        <v>0</v>
+      </c>
+      <c r="E539">
+        <v>0</v>
+      </c>
+      <c r="F539">
+        <v>0</v>
+      </c>
+      <c r="G539">
+        <v>1</v>
+      </c>
+      <c r="H539">
+        <v>1</v>
+      </c>
+      <c r="I539">
+        <v>1</v>
+      </c>
+      <c r="J539">
+        <v>10</v>
+      </c>
+      <c r="K539">
+        <v>10</v>
+      </c>
+      <c r="L539">
+        <v>10</v>
+      </c>
+      <c r="M539">
+        <v>-1</v>
+      </c>
+      <c r="N539">
+        <v>0</v>
+      </c>
+      <c r="O539">
+        <v>0</v>
+      </c>
+      <c r="P539">
+        <v>0</v>
+      </c>
+      <c r="Q539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A540">
+        <v>0</v>
+      </c>
+      <c r="B540">
+        <v>94.3</v>
+      </c>
+      <c r="C540">
+        <v>-1507</v>
+      </c>
+      <c r="D540">
+        <v>0</v>
+      </c>
+      <c r="E540">
+        <v>0</v>
+      </c>
+      <c r="F540">
+        <v>0</v>
+      </c>
+      <c r="G540">
+        <v>1</v>
+      </c>
+      <c r="H540">
+        <v>1</v>
+      </c>
+      <c r="I540">
+        <v>1</v>
+      </c>
+      <c r="J540">
+        <v>10</v>
+      </c>
+      <c r="K540">
+        <v>10</v>
+      </c>
+      <c r="L540">
+        <v>10</v>
+      </c>
+      <c r="M540">
+        <v>-1</v>
+      </c>
+      <c r="N540">
+        <v>0</v>
+      </c>
+      <c r="O540">
+        <v>0</v>
+      </c>
+      <c r="P540">
+        <v>0</v>
+      </c>
+      <c r="Q540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A541">
+        <v>0</v>
+      </c>
+      <c r="B541">
+        <v>105.9</v>
+      </c>
+      <c r="C541">
+        <v>-1514</v>
+      </c>
+      <c r="D541">
+        <v>0</v>
+      </c>
+      <c r="E541">
+        <v>0</v>
+      </c>
+      <c r="F541">
+        <v>0</v>
+      </c>
+      <c r="G541">
+        <v>1</v>
+      </c>
+      <c r="H541">
+        <v>1</v>
+      </c>
+      <c r="I541">
+        <v>1</v>
+      </c>
+      <c r="J541">
+        <v>10</v>
+      </c>
+      <c r="K541">
+        <v>10</v>
+      </c>
+      <c r="L541">
+        <v>10</v>
+      </c>
+      <c r="M541">
+        <v>-1</v>
+      </c>
+      <c r="N541">
+        <v>0</v>
+      </c>
+      <c r="O541">
+        <v>0</v>
+      </c>
+      <c r="P541">
+        <v>0</v>
+      </c>
+      <c r="Q541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A542">
+        <v>0</v>
+      </c>
+      <c r="B542">
+        <v>114.8</v>
+      </c>
+      <c r="C542">
+        <v>-1521</v>
+      </c>
+      <c r="D542">
+        <v>0</v>
+      </c>
+      <c r="E542">
+        <v>0</v>
+      </c>
+      <c r="F542">
+        <v>0</v>
+      </c>
+      <c r="G542">
+        <v>1</v>
+      </c>
+      <c r="H542">
+        <v>1</v>
+      </c>
+      <c r="I542">
+        <v>1</v>
+      </c>
+      <c r="J542">
+        <v>10</v>
+      </c>
+      <c r="K542">
+        <v>10</v>
+      </c>
+      <c r="L542">
+        <v>10</v>
+      </c>
+      <c r="M542">
+        <v>-1</v>
+      </c>
+      <c r="N542">
+        <v>0</v>
+      </c>
+      <c r="O542">
+        <v>0</v>
+      </c>
+      <c r="P542">
+        <v>0</v>
+      </c>
+      <c r="Q542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A543">
+        <v>0</v>
+      </c>
+      <c r="B543">
+        <v>120.9</v>
+      </c>
+      <c r="C543">
+        <v>-1528</v>
+      </c>
+      <c r="D543">
+        <v>0</v>
+      </c>
+      <c r="E543">
+        <v>0</v>
+      </c>
+      <c r="F543">
+        <v>0</v>
+      </c>
+      <c r="G543">
+        <v>1</v>
+      </c>
+      <c r="H543">
+        <v>1</v>
+      </c>
+      <c r="I543">
+        <v>1</v>
+      </c>
+      <c r="J543">
+        <v>10</v>
+      </c>
+      <c r="K543">
+        <v>10</v>
+      </c>
+      <c r="L543">
+        <v>10</v>
+      </c>
+      <c r="M543">
+        <v>-1</v>
+      </c>
+      <c r="N543">
+        <v>0</v>
+      </c>
+      <c r="O543">
+        <v>0</v>
+      </c>
+      <c r="P543">
+        <v>0</v>
+      </c>
+      <c r="Q543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A544">
+        <v>0</v>
+      </c>
+      <c r="B544">
+        <v>124.3</v>
+      </c>
+      <c r="C544">
+        <v>-1535</v>
+      </c>
+      <c r="D544">
+        <v>0</v>
+      </c>
+      <c r="E544">
+        <v>0</v>
+      </c>
+      <c r="F544">
+        <v>0</v>
+      </c>
+      <c r="G544">
+        <v>1</v>
+      </c>
+      <c r="H544">
+        <v>1</v>
+      </c>
+      <c r="I544">
+        <v>1</v>
+      </c>
+      <c r="J544">
+        <v>10</v>
+      </c>
+      <c r="K544">
+        <v>10</v>
+      </c>
+      <c r="L544">
+        <v>10</v>
+      </c>
+      <c r="M544">
+        <v>-1</v>
+      </c>
+      <c r="N544">
+        <v>0</v>
+      </c>
+      <c r="O544">
+        <v>0</v>
+      </c>
+      <c r="P544">
+        <v>0</v>
+      </c>
+      <c r="Q544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A545">
+        <v>0</v>
+      </c>
+      <c r="B545">
+        <v>124.9</v>
+      </c>
+      <c r="C545">
+        <v>-1542</v>
+      </c>
+      <c r="D545">
+        <v>0</v>
+      </c>
+      <c r="E545">
+        <v>0</v>
+      </c>
+      <c r="F545">
+        <v>0</v>
+      </c>
+      <c r="G545">
+        <v>1</v>
+      </c>
+      <c r="H545">
+        <v>1</v>
+      </c>
+      <c r="I545">
+        <v>1</v>
+      </c>
+      <c r="J545">
+        <v>10</v>
+      </c>
+      <c r="K545">
+        <v>10</v>
+      </c>
+      <c r="L545">
+        <v>10</v>
+      </c>
+      <c r="M545">
+        <v>-1</v>
+      </c>
+      <c r="N545">
+        <v>0</v>
+      </c>
+      <c r="O545">
+        <v>0</v>
+      </c>
+      <c r="P545">
+        <v>0</v>
+      </c>
+      <c r="Q545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A546">
+        <v>0</v>
+      </c>
+      <c r="B546">
+        <v>122.8</v>
+      </c>
+      <c r="C546">
+        <v>-1549</v>
+      </c>
+      <c r="D546">
+        <v>0</v>
+      </c>
+      <c r="E546">
+        <v>0</v>
+      </c>
+      <c r="F546">
+        <v>0</v>
+      </c>
+      <c r="G546">
+        <v>1</v>
+      </c>
+      <c r="H546">
+        <v>1</v>
+      </c>
+      <c r="I546">
+        <v>1</v>
+      </c>
+      <c r="J546">
+        <v>10</v>
+      </c>
+      <c r="K546">
+        <v>10</v>
+      </c>
+      <c r="L546">
+        <v>10</v>
+      </c>
+      <c r="M546">
+        <v>-1</v>
+      </c>
+      <c r="N546">
+        <v>0</v>
+      </c>
+      <c r="O546">
+        <v>0</v>
+      </c>
+      <c r="P546">
+        <v>0</v>
+      </c>
+      <c r="Q546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A547">
+        <v>0</v>
+      </c>
+      <c r="B547">
+        <v>117.9</v>
+      </c>
+      <c r="C547">
+        <v>-1556</v>
+      </c>
+      <c r="D547">
+        <v>0</v>
+      </c>
+      <c r="E547">
+        <v>0</v>
+      </c>
+      <c r="F547">
+        <v>0</v>
+      </c>
+      <c r="G547">
+        <v>1</v>
+      </c>
+      <c r="H547">
+        <v>1</v>
+      </c>
+      <c r="I547">
+        <v>1</v>
+      </c>
+      <c r="J547">
+        <v>10</v>
+      </c>
+      <c r="K547">
+        <v>10</v>
+      </c>
+      <c r="L547">
+        <v>10</v>
+      </c>
+      <c r="M547">
+        <v>-1</v>
+      </c>
+      <c r="N547">
+        <v>0</v>
+      </c>
+      <c r="O547">
+        <v>0</v>
+      </c>
+      <c r="P547">
+        <v>0</v>
+      </c>
+      <c r="Q547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A548">
+        <v>0</v>
+      </c>
+      <c r="B548">
+        <v>110.3</v>
+      </c>
+      <c r="C548">
+        <v>-1563</v>
+      </c>
+      <c r="D548">
+        <v>0</v>
+      </c>
+      <c r="E548">
+        <v>0</v>
+      </c>
+      <c r="F548">
+        <v>0</v>
+      </c>
+      <c r="G548">
+        <v>1</v>
+      </c>
+      <c r="H548">
+        <v>1</v>
+      </c>
+      <c r="I548">
+        <v>1</v>
+      </c>
+      <c r="J548">
+        <v>10</v>
+      </c>
+      <c r="K548">
+        <v>10</v>
+      </c>
+      <c r="L548">
+        <v>10</v>
+      </c>
+      <c r="M548">
+        <v>-1</v>
+      </c>
+      <c r="N548">
+        <v>0</v>
+      </c>
+      <c r="O548">
+        <v>0</v>
+      </c>
+      <c r="P548">
+        <v>0</v>
+      </c>
+      <c r="Q548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A549">
+        <v>0</v>
+      </c>
+      <c r="B549">
+        <v>100</v>
+      </c>
+      <c r="C549">
+        <v>-1570</v>
+      </c>
+      <c r="D549">
+        <v>0</v>
+      </c>
+      <c r="E549">
+        <v>0</v>
+      </c>
+      <c r="F549">
+        <v>0</v>
+      </c>
+      <c r="G549">
+        <v>1</v>
+      </c>
+      <c r="H549">
+        <v>1</v>
+      </c>
+      <c r="I549">
+        <v>1</v>
+      </c>
+      <c r="J549">
+        <v>10</v>
+      </c>
+      <c r="K549">
+        <v>10</v>
+      </c>
+      <c r="L549">
+        <v>10</v>
+      </c>
+      <c r="M549">
+        <v>-1</v>
+      </c>
+      <c r="N549">
+        <v>0</v>
+      </c>
+      <c r="O549">
+        <v>0</v>
+      </c>
+      <c r="P549">
+        <v>0</v>
+      </c>
+      <c r="Q549">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
+++ b/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Map1\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76A4AA1C-A57C-4EFA-94CF-19DE7A5CE4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89FBFF16-4DBA-4721-A255-39E4CF7DA201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +33,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,6 +190,14 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -618,9 +627,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -977,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q549"/>
+  <dimension ref="A1:Q651"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="17" width="5.625" customWidth="1"/>
@@ -27249,7 +27261,7 @@
         <v>20</v>
       </c>
       <c r="C473">
-        <f t="shared" ref="C473:C480" si="215">C472-20</f>
+        <f t="shared" ref="C473" si="215">C472-20</f>
         <v>-140</v>
       </c>
       <c r="D473">
@@ -31320,6 +31332,5444 @@
         <v>0</v>
       </c>
       <c r="Q549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A550">
+        <v>0</v>
+      </c>
+      <c r="B550">
+        <v>100</v>
+      </c>
+      <c r="C550">
+        <v>-1600</v>
+      </c>
+      <c r="D550">
+        <v>0</v>
+      </c>
+      <c r="E550">
+        <v>0</v>
+      </c>
+      <c r="F550">
+        <v>0</v>
+      </c>
+      <c r="G550">
+        <v>1</v>
+      </c>
+      <c r="H550">
+        <v>1</v>
+      </c>
+      <c r="I550">
+        <v>1</v>
+      </c>
+      <c r="J550">
+        <v>10</v>
+      </c>
+      <c r="K550">
+        <v>10</v>
+      </c>
+      <c r="L550">
+        <v>10</v>
+      </c>
+      <c r="M550">
+        <v>-1</v>
+      </c>
+      <c r="N550">
+        <v>0</v>
+      </c>
+      <c r="O550">
+        <v>0</v>
+      </c>
+      <c r="P550">
+        <v>0</v>
+      </c>
+      <c r="Q550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A551">
+        <v>0</v>
+      </c>
+      <c r="B551">
+        <v>118</v>
+      </c>
+      <c r="C551">
+        <v>-1610</v>
+      </c>
+      <c r="D551">
+        <v>0</v>
+      </c>
+      <c r="E551">
+        <v>0</v>
+      </c>
+      <c r="F551">
+        <v>0</v>
+      </c>
+      <c r="G551">
+        <v>1</v>
+      </c>
+      <c r="H551">
+        <v>1</v>
+      </c>
+      <c r="I551">
+        <v>1</v>
+      </c>
+      <c r="J551">
+        <v>10</v>
+      </c>
+      <c r="K551">
+        <v>10</v>
+      </c>
+      <c r="L551">
+        <v>10</v>
+      </c>
+      <c r="M551">
+        <v>-1</v>
+      </c>
+      <c r="N551">
+        <v>0</v>
+      </c>
+      <c r="O551">
+        <v>0</v>
+      </c>
+      <c r="P551">
+        <v>0</v>
+      </c>
+      <c r="Q551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A552">
+        <v>0</v>
+      </c>
+      <c r="B552">
+        <v>131.1</v>
+      </c>
+      <c r="C552">
+        <v>-1620</v>
+      </c>
+      <c r="D552">
+        <v>0</v>
+      </c>
+      <c r="E552">
+        <v>0</v>
+      </c>
+      <c r="F552">
+        <v>0</v>
+      </c>
+      <c r="G552">
+        <v>1</v>
+      </c>
+      <c r="H552">
+        <v>1</v>
+      </c>
+      <c r="I552">
+        <v>1</v>
+      </c>
+      <c r="J552">
+        <v>10</v>
+      </c>
+      <c r="K552">
+        <v>10</v>
+      </c>
+      <c r="L552">
+        <v>10</v>
+      </c>
+      <c r="M552">
+        <v>-1</v>
+      </c>
+      <c r="N552">
+        <v>0</v>
+      </c>
+      <c r="O552">
+        <v>0</v>
+      </c>
+      <c r="P552">
+        <v>0</v>
+      </c>
+      <c r="Q552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A553">
+        <v>0</v>
+      </c>
+      <c r="B553">
+        <v>139</v>
+      </c>
+      <c r="C553">
+        <v>-1630</v>
+      </c>
+      <c r="D553">
+        <v>0</v>
+      </c>
+      <c r="E553">
+        <v>0</v>
+      </c>
+      <c r="F553">
+        <v>0</v>
+      </c>
+      <c r="G553">
+        <v>1</v>
+      </c>
+      <c r="H553">
+        <v>1</v>
+      </c>
+      <c r="I553">
+        <v>1</v>
+      </c>
+      <c r="J553">
+        <v>10</v>
+      </c>
+      <c r="K553">
+        <v>10</v>
+      </c>
+      <c r="L553">
+        <v>10</v>
+      </c>
+      <c r="M553">
+        <v>-1</v>
+      </c>
+      <c r="N553">
+        <v>0</v>
+      </c>
+      <c r="O553">
+        <v>0</v>
+      </c>
+      <c r="P553">
+        <v>0</v>
+      </c>
+      <c r="Q553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A554">
+        <v>0</v>
+      </c>
+      <c r="B554">
+        <v>142.19999999999999</v>
+      </c>
+      <c r="C554">
+        <v>-1640</v>
+      </c>
+      <c r="D554">
+        <v>0</v>
+      </c>
+      <c r="E554">
+        <v>0</v>
+      </c>
+      <c r="F554">
+        <v>0</v>
+      </c>
+      <c r="G554">
+        <v>1</v>
+      </c>
+      <c r="H554">
+        <v>1</v>
+      </c>
+      <c r="I554">
+        <v>1</v>
+      </c>
+      <c r="J554">
+        <v>10</v>
+      </c>
+      <c r="K554">
+        <v>10</v>
+      </c>
+      <c r="L554">
+        <v>10</v>
+      </c>
+      <c r="M554">
+        <v>-1</v>
+      </c>
+      <c r="N554">
+        <v>0</v>
+      </c>
+      <c r="O554">
+        <v>0</v>
+      </c>
+      <c r="P554">
+        <v>0</v>
+      </c>
+      <c r="Q554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A555">
+        <v>0</v>
+      </c>
+      <c r="B555">
+        <v>145</v>
+      </c>
+      <c r="C555">
+        <v>-1640</v>
+      </c>
+      <c r="D555">
+        <v>0</v>
+      </c>
+      <c r="E555">
+        <v>0</v>
+      </c>
+      <c r="F555">
+        <v>0</v>
+      </c>
+      <c r="G555">
+        <v>1</v>
+      </c>
+      <c r="H555">
+        <v>1</v>
+      </c>
+      <c r="I555">
+        <v>1</v>
+      </c>
+      <c r="J555">
+        <v>10</v>
+      </c>
+      <c r="K555">
+        <v>10</v>
+      </c>
+      <c r="L555">
+        <v>10</v>
+      </c>
+      <c r="M555">
+        <v>-1</v>
+      </c>
+      <c r="N555">
+        <v>0</v>
+      </c>
+      <c r="O555">
+        <v>0</v>
+      </c>
+      <c r="P555">
+        <v>0</v>
+      </c>
+      <c r="Q555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A556">
+        <v>0</v>
+      </c>
+      <c r="B556">
+        <v>142.19999999999999</v>
+      </c>
+      <c r="C556">
+        <v>-1650</v>
+      </c>
+      <c r="D556">
+        <v>0</v>
+      </c>
+      <c r="E556">
+        <v>0</v>
+      </c>
+      <c r="F556">
+        <v>0</v>
+      </c>
+      <c r="G556">
+        <v>1</v>
+      </c>
+      <c r="H556">
+        <v>1</v>
+      </c>
+      <c r="I556">
+        <v>1</v>
+      </c>
+      <c r="J556">
+        <v>10</v>
+      </c>
+      <c r="K556">
+        <v>10</v>
+      </c>
+      <c r="L556">
+        <v>10</v>
+      </c>
+      <c r="M556">
+        <v>-1</v>
+      </c>
+      <c r="N556">
+        <v>0</v>
+      </c>
+      <c r="O556">
+        <v>0</v>
+      </c>
+      <c r="P556">
+        <v>0</v>
+      </c>
+      <c r="Q556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A557">
+        <v>0</v>
+      </c>
+      <c r="B557">
+        <v>139</v>
+      </c>
+      <c r="C557">
+        <v>-1660</v>
+      </c>
+      <c r="D557">
+        <v>0</v>
+      </c>
+      <c r="E557">
+        <v>0</v>
+      </c>
+      <c r="F557">
+        <v>0</v>
+      </c>
+      <c r="G557">
+        <v>1</v>
+      </c>
+      <c r="H557">
+        <v>1</v>
+      </c>
+      <c r="I557">
+        <v>1</v>
+      </c>
+      <c r="J557">
+        <v>10</v>
+      </c>
+      <c r="K557">
+        <v>10</v>
+      </c>
+      <c r="L557">
+        <v>10</v>
+      </c>
+      <c r="M557">
+        <v>-1</v>
+      </c>
+      <c r="N557">
+        <v>0</v>
+      </c>
+      <c r="O557">
+        <v>0</v>
+      </c>
+      <c r="P557">
+        <v>0</v>
+      </c>
+      <c r="Q557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A558">
+        <v>0</v>
+      </c>
+      <c r="B558">
+        <v>131.1</v>
+      </c>
+      <c r="C558">
+        <v>-1670</v>
+      </c>
+      <c r="D558">
+        <v>0</v>
+      </c>
+      <c r="E558">
+        <v>0</v>
+      </c>
+      <c r="F558">
+        <v>0</v>
+      </c>
+      <c r="G558">
+        <v>1</v>
+      </c>
+      <c r="H558">
+        <v>1</v>
+      </c>
+      <c r="I558">
+        <v>1</v>
+      </c>
+      <c r="J558">
+        <v>10</v>
+      </c>
+      <c r="K558">
+        <v>10</v>
+      </c>
+      <c r="L558">
+        <v>10</v>
+      </c>
+      <c r="M558">
+        <v>-1</v>
+      </c>
+      <c r="N558">
+        <v>0</v>
+      </c>
+      <c r="O558">
+        <v>0</v>
+      </c>
+      <c r="P558">
+        <v>0</v>
+      </c>
+      <c r="Q558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A559">
+        <v>0</v>
+      </c>
+      <c r="B559">
+        <v>118</v>
+      </c>
+      <c r="C559">
+        <v>-1675</v>
+      </c>
+      <c r="D559">
+        <v>0</v>
+      </c>
+      <c r="E559">
+        <v>0</v>
+      </c>
+      <c r="F559">
+        <v>0</v>
+      </c>
+      <c r="G559">
+        <v>1</v>
+      </c>
+      <c r="H559">
+        <v>1</v>
+      </c>
+      <c r="I559">
+        <v>1</v>
+      </c>
+      <c r="J559">
+        <v>10</v>
+      </c>
+      <c r="K559">
+        <v>10</v>
+      </c>
+      <c r="L559">
+        <v>10</v>
+      </c>
+      <c r="M559">
+        <v>-1</v>
+      </c>
+      <c r="N559">
+        <v>0</v>
+      </c>
+      <c r="O559">
+        <v>0</v>
+      </c>
+      <c r="P559">
+        <v>0</v>
+      </c>
+      <c r="Q559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A560">
+        <v>0</v>
+      </c>
+      <c r="B560">
+        <v>100</v>
+      </c>
+      <c r="C560">
+        <v>-1680</v>
+      </c>
+      <c r="D560">
+        <v>0</v>
+      </c>
+      <c r="E560">
+        <v>0</v>
+      </c>
+      <c r="F560">
+        <v>0</v>
+      </c>
+      <c r="G560">
+        <v>1</v>
+      </c>
+      <c r="H560">
+        <v>1</v>
+      </c>
+      <c r="I560">
+        <v>1</v>
+      </c>
+      <c r="J560">
+        <v>10</v>
+      </c>
+      <c r="K560">
+        <v>10</v>
+      </c>
+      <c r="L560">
+        <v>10</v>
+      </c>
+      <c r="M560">
+        <v>-1</v>
+      </c>
+      <c r="N560">
+        <v>0</v>
+      </c>
+      <c r="O560">
+        <v>0</v>
+      </c>
+      <c r="P560">
+        <v>0</v>
+      </c>
+      <c r="Q560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A561">
+        <v>0</v>
+      </c>
+      <c r="B561">
+        <v>100</v>
+      </c>
+      <c r="C561">
+        <v>-2000</v>
+      </c>
+      <c r="D561">
+        <v>0</v>
+      </c>
+      <c r="E561">
+        <v>0</v>
+      </c>
+      <c r="F561">
+        <v>0</v>
+      </c>
+      <c r="G561">
+        <v>1</v>
+      </c>
+      <c r="H561">
+        <v>1</v>
+      </c>
+      <c r="I561">
+        <v>1</v>
+      </c>
+      <c r="J561">
+        <v>10</v>
+      </c>
+      <c r="K561">
+        <v>10</v>
+      </c>
+      <c r="L561">
+        <v>10</v>
+      </c>
+      <c r="M561">
+        <v>-1</v>
+      </c>
+      <c r="N561">
+        <v>0</v>
+      </c>
+      <c r="O561">
+        <v>0</v>
+      </c>
+      <c r="P561">
+        <v>0</v>
+      </c>
+      <c r="Q561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A562">
+        <v>0</v>
+      </c>
+      <c r="B562">
+        <v>100</v>
+      </c>
+      <c r="C562">
+        <v>-2010</v>
+      </c>
+      <c r="D562">
+        <v>0</v>
+      </c>
+      <c r="E562">
+        <v>0</v>
+      </c>
+      <c r="F562">
+        <v>0</v>
+      </c>
+      <c r="G562">
+        <v>1</v>
+      </c>
+      <c r="H562">
+        <v>1</v>
+      </c>
+      <c r="I562">
+        <v>1</v>
+      </c>
+      <c r="J562">
+        <v>10</v>
+      </c>
+      <c r="K562">
+        <v>10</v>
+      </c>
+      <c r="L562">
+        <v>10</v>
+      </c>
+      <c r="M562">
+        <v>-1</v>
+      </c>
+      <c r="N562">
+        <v>0</v>
+      </c>
+      <c r="O562">
+        <v>0</v>
+      </c>
+      <c r="P562">
+        <v>0</v>
+      </c>
+      <c r="Q562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A563">
+        <v>0</v>
+      </c>
+      <c r="B563">
+        <v>100</v>
+      </c>
+      <c r="C563">
+        <v>-2020</v>
+      </c>
+      <c r="D563">
+        <v>0</v>
+      </c>
+      <c r="E563">
+        <v>0</v>
+      </c>
+      <c r="F563">
+        <v>0</v>
+      </c>
+      <c r="G563">
+        <v>1</v>
+      </c>
+      <c r="H563">
+        <v>1</v>
+      </c>
+      <c r="I563">
+        <v>1</v>
+      </c>
+      <c r="J563">
+        <v>10</v>
+      </c>
+      <c r="K563">
+        <v>10</v>
+      </c>
+      <c r="L563">
+        <v>10</v>
+      </c>
+      <c r="M563">
+        <v>-1</v>
+      </c>
+      <c r="N563">
+        <v>0</v>
+      </c>
+      <c r="O563">
+        <v>0</v>
+      </c>
+      <c r="P563">
+        <v>0</v>
+      </c>
+      <c r="Q563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A564">
+        <v>0</v>
+      </c>
+      <c r="B564">
+        <v>100</v>
+      </c>
+      <c r="C564">
+        <v>-2030</v>
+      </c>
+      <c r="D564">
+        <v>0</v>
+      </c>
+      <c r="E564">
+        <v>0</v>
+      </c>
+      <c r="F564">
+        <v>0</v>
+      </c>
+      <c r="G564">
+        <v>1</v>
+      </c>
+      <c r="H564">
+        <v>1</v>
+      </c>
+      <c r="I564">
+        <v>1</v>
+      </c>
+      <c r="J564">
+        <v>10</v>
+      </c>
+      <c r="K564">
+        <v>10</v>
+      </c>
+      <c r="L564">
+        <v>10</v>
+      </c>
+      <c r="M564">
+        <v>-1</v>
+      </c>
+      <c r="N564">
+        <v>0</v>
+      </c>
+      <c r="O564">
+        <v>0</v>
+      </c>
+      <c r="P564">
+        <v>0</v>
+      </c>
+      <c r="Q564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A565">
+        <v>0</v>
+      </c>
+      <c r="B565">
+        <v>100</v>
+      </c>
+      <c r="C565">
+        <v>-2040</v>
+      </c>
+      <c r="D565">
+        <v>0</v>
+      </c>
+      <c r="E565">
+        <v>0</v>
+      </c>
+      <c r="F565">
+        <v>0</v>
+      </c>
+      <c r="G565">
+        <v>1</v>
+      </c>
+      <c r="H565">
+        <v>1</v>
+      </c>
+      <c r="I565">
+        <v>1</v>
+      </c>
+      <c r="J565">
+        <v>10</v>
+      </c>
+      <c r="K565">
+        <v>10</v>
+      </c>
+      <c r="L565">
+        <v>10</v>
+      </c>
+      <c r="M565">
+        <v>-1</v>
+      </c>
+      <c r="N565">
+        <v>0</v>
+      </c>
+      <c r="O565">
+        <v>0</v>
+      </c>
+      <c r="P565">
+        <v>0</v>
+      </c>
+      <c r="Q565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A566">
+        <v>0</v>
+      </c>
+      <c r="B566">
+        <v>100</v>
+      </c>
+      <c r="C566">
+        <v>-2050</v>
+      </c>
+      <c r="D566">
+        <v>0</v>
+      </c>
+      <c r="E566">
+        <v>0</v>
+      </c>
+      <c r="F566">
+        <v>0</v>
+      </c>
+      <c r="G566">
+        <v>1</v>
+      </c>
+      <c r="H566">
+        <v>1</v>
+      </c>
+      <c r="I566">
+        <v>1</v>
+      </c>
+      <c r="J566">
+        <v>10</v>
+      </c>
+      <c r="K566">
+        <v>10</v>
+      </c>
+      <c r="L566">
+        <v>10</v>
+      </c>
+      <c r="M566">
+        <v>-1</v>
+      </c>
+      <c r="N566">
+        <v>0</v>
+      </c>
+      <c r="O566">
+        <v>0</v>
+      </c>
+      <c r="P566">
+        <v>0</v>
+      </c>
+      <c r="Q566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A567">
+        <v>0</v>
+      </c>
+      <c r="B567">
+        <v>120</v>
+      </c>
+      <c r="C567">
+        <v>-2064</v>
+      </c>
+      <c r="D567">
+        <v>0</v>
+      </c>
+      <c r="E567">
+        <v>0</v>
+      </c>
+      <c r="F567">
+        <v>0</v>
+      </c>
+      <c r="G567">
+        <v>1</v>
+      </c>
+      <c r="H567">
+        <v>1</v>
+      </c>
+      <c r="I567">
+        <v>1</v>
+      </c>
+      <c r="J567">
+        <v>10</v>
+      </c>
+      <c r="K567">
+        <v>10</v>
+      </c>
+      <c r="L567">
+        <v>10</v>
+      </c>
+      <c r="M567">
+        <v>-1</v>
+      </c>
+      <c r="N567">
+        <v>0</v>
+      </c>
+      <c r="O567">
+        <v>0</v>
+      </c>
+      <c r="P567">
+        <v>0</v>
+      </c>
+      <c r="Q567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A568">
+        <v>0</v>
+      </c>
+      <c r="B568">
+        <v>140</v>
+      </c>
+      <c r="C568">
+        <v>-2078</v>
+      </c>
+      <c r="D568">
+        <v>0</v>
+      </c>
+      <c r="E568">
+        <v>0</v>
+      </c>
+      <c r="F568">
+        <v>0</v>
+      </c>
+      <c r="G568">
+        <v>1</v>
+      </c>
+      <c r="H568">
+        <v>1</v>
+      </c>
+      <c r="I568">
+        <v>1</v>
+      </c>
+      <c r="J568">
+        <v>10</v>
+      </c>
+      <c r="K568">
+        <v>10</v>
+      </c>
+      <c r="L568">
+        <v>10</v>
+      </c>
+      <c r="M568">
+        <v>-1</v>
+      </c>
+      <c r="N568">
+        <v>0</v>
+      </c>
+      <c r="O568">
+        <v>0</v>
+      </c>
+      <c r="P568">
+        <v>0</v>
+      </c>
+      <c r="Q568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A569">
+        <v>0</v>
+      </c>
+      <c r="B569">
+        <v>145</v>
+      </c>
+      <c r="C569">
+        <v>-2095</v>
+      </c>
+      <c r="D569">
+        <v>0</v>
+      </c>
+      <c r="E569">
+        <v>0</v>
+      </c>
+      <c r="F569">
+        <v>0</v>
+      </c>
+      <c r="G569">
+        <v>1</v>
+      </c>
+      <c r="H569">
+        <v>1</v>
+      </c>
+      <c r="I569">
+        <v>1</v>
+      </c>
+      <c r="J569">
+        <v>10</v>
+      </c>
+      <c r="K569">
+        <v>10</v>
+      </c>
+      <c r="L569">
+        <v>10</v>
+      </c>
+      <c r="M569">
+        <v>-1</v>
+      </c>
+      <c r="N569">
+        <v>0</v>
+      </c>
+      <c r="O569">
+        <v>0</v>
+      </c>
+      <c r="P569">
+        <v>0</v>
+      </c>
+      <c r="Q569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A570">
+        <v>0</v>
+      </c>
+      <c r="B570">
+        <v>120</v>
+      </c>
+      <c r="C570">
+        <v>-2120</v>
+      </c>
+      <c r="D570">
+        <v>0</v>
+      </c>
+      <c r="E570">
+        <v>0</v>
+      </c>
+      <c r="F570">
+        <v>0</v>
+      </c>
+      <c r="G570">
+        <v>1</v>
+      </c>
+      <c r="H570">
+        <v>1</v>
+      </c>
+      <c r="I570">
+        <v>1</v>
+      </c>
+      <c r="J570">
+        <v>10</v>
+      </c>
+      <c r="K570">
+        <v>10</v>
+      </c>
+      <c r="L570">
+        <v>10</v>
+      </c>
+      <c r="M570">
+        <v>-1</v>
+      </c>
+      <c r="N570">
+        <v>0</v>
+      </c>
+      <c r="O570">
+        <v>0</v>
+      </c>
+      <c r="P570">
+        <v>0</v>
+      </c>
+      <c r="Q570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A571">
+        <v>0</v>
+      </c>
+      <c r="B571">
+        <v>100</v>
+      </c>
+      <c r="C571">
+        <v>-2660</v>
+      </c>
+      <c r="D571">
+        <v>0</v>
+      </c>
+      <c r="E571">
+        <v>0</v>
+      </c>
+      <c r="F571">
+        <v>0</v>
+      </c>
+      <c r="G571">
+        <v>1</v>
+      </c>
+      <c r="H571">
+        <v>1</v>
+      </c>
+      <c r="I571">
+        <v>1</v>
+      </c>
+      <c r="J571">
+        <v>10</v>
+      </c>
+      <c r="K571">
+        <v>10</v>
+      </c>
+      <c r="L571">
+        <v>10</v>
+      </c>
+      <c r="M571">
+        <v>-1</v>
+      </c>
+      <c r="N571">
+        <v>0</v>
+      </c>
+      <c r="O571">
+        <v>0</v>
+      </c>
+      <c r="P571">
+        <v>0</v>
+      </c>
+      <c r="Q571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A572">
+        <v>0</v>
+      </c>
+      <c r="B572">
+        <f>B571+10</f>
+        <v>110</v>
+      </c>
+      <c r="C572">
+        <v>-2660</v>
+      </c>
+      <c r="D572">
+        <v>0</v>
+      </c>
+      <c r="E572">
+        <v>0</v>
+      </c>
+      <c r="F572">
+        <v>0</v>
+      </c>
+      <c r="G572">
+        <v>1</v>
+      </c>
+      <c r="H572">
+        <v>1</v>
+      </c>
+      <c r="I572">
+        <v>1</v>
+      </c>
+      <c r="J572">
+        <v>10</v>
+      </c>
+      <c r="K572">
+        <v>10</v>
+      </c>
+      <c r="L572">
+        <v>10</v>
+      </c>
+      <c r="M572">
+        <v>-1</v>
+      </c>
+      <c r="N572">
+        <v>0</v>
+      </c>
+      <c r="O572">
+        <v>0</v>
+      </c>
+      <c r="P572">
+        <v>0</v>
+      </c>
+      <c r="Q572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A573">
+        <v>0</v>
+      </c>
+      <c r="B573">
+        <f t="shared" ref="B573:B583" si="216">B572+10</f>
+        <v>120</v>
+      </c>
+      <c r="C573">
+        <v>-2660</v>
+      </c>
+      <c r="D573">
+        <v>0</v>
+      </c>
+      <c r="E573">
+        <v>0</v>
+      </c>
+      <c r="F573">
+        <v>0</v>
+      </c>
+      <c r="G573">
+        <v>1</v>
+      </c>
+      <c r="H573">
+        <v>1</v>
+      </c>
+      <c r="I573">
+        <v>1</v>
+      </c>
+      <c r="J573">
+        <v>10</v>
+      </c>
+      <c r="K573">
+        <v>10</v>
+      </c>
+      <c r="L573">
+        <v>10</v>
+      </c>
+      <c r="M573">
+        <v>-1</v>
+      </c>
+      <c r="N573">
+        <v>0</v>
+      </c>
+      <c r="O573">
+        <v>0</v>
+      </c>
+      <c r="P573">
+        <v>0</v>
+      </c>
+      <c r="Q573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A574">
+        <v>0</v>
+      </c>
+      <c r="B574">
+        <f t="shared" si="216"/>
+        <v>130</v>
+      </c>
+      <c r="C574">
+        <v>-2660</v>
+      </c>
+      <c r="D574">
+        <v>0</v>
+      </c>
+      <c r="E574">
+        <v>0</v>
+      </c>
+      <c r="F574">
+        <v>0</v>
+      </c>
+      <c r="G574">
+        <v>1</v>
+      </c>
+      <c r="H574">
+        <v>1</v>
+      </c>
+      <c r="I574">
+        <v>1</v>
+      </c>
+      <c r="J574">
+        <v>10</v>
+      </c>
+      <c r="K574">
+        <v>10</v>
+      </c>
+      <c r="L574">
+        <v>10</v>
+      </c>
+      <c r="M574">
+        <v>-1</v>
+      </c>
+      <c r="N574">
+        <v>0</v>
+      </c>
+      <c r="O574">
+        <v>0</v>
+      </c>
+      <c r="P574">
+        <v>0</v>
+      </c>
+      <c r="Q574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A575">
+        <v>0</v>
+      </c>
+      <c r="B575">
+        <f t="shared" si="216"/>
+        <v>140</v>
+      </c>
+      <c r="C575">
+        <v>-2660</v>
+      </c>
+      <c r="D575">
+        <v>0</v>
+      </c>
+      <c r="E575">
+        <v>0</v>
+      </c>
+      <c r="F575">
+        <v>0</v>
+      </c>
+      <c r="G575">
+        <v>1</v>
+      </c>
+      <c r="H575">
+        <v>1</v>
+      </c>
+      <c r="I575">
+        <v>1</v>
+      </c>
+      <c r="J575">
+        <v>10</v>
+      </c>
+      <c r="K575">
+        <v>10</v>
+      </c>
+      <c r="L575">
+        <v>10</v>
+      </c>
+      <c r="M575">
+        <v>-1</v>
+      </c>
+      <c r="N575">
+        <v>0</v>
+      </c>
+      <c r="O575">
+        <v>0</v>
+      </c>
+      <c r="P575">
+        <v>0</v>
+      </c>
+      <c r="Q575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A576">
+        <v>0</v>
+      </c>
+      <c r="B576">
+        <f t="shared" si="216"/>
+        <v>150</v>
+      </c>
+      <c r="C576">
+        <v>-2660</v>
+      </c>
+      <c r="D576">
+        <v>0</v>
+      </c>
+      <c r="E576">
+        <v>0</v>
+      </c>
+      <c r="F576">
+        <v>0</v>
+      </c>
+      <c r="G576">
+        <v>1</v>
+      </c>
+      <c r="H576">
+        <v>1</v>
+      </c>
+      <c r="I576">
+        <v>1</v>
+      </c>
+      <c r="J576">
+        <v>10</v>
+      </c>
+      <c r="K576">
+        <v>10</v>
+      </c>
+      <c r="L576">
+        <v>10</v>
+      </c>
+      <c r="M576">
+        <v>-1</v>
+      </c>
+      <c r="N576">
+        <v>0</v>
+      </c>
+      <c r="O576">
+        <v>0</v>
+      </c>
+      <c r="P576">
+        <v>0</v>
+      </c>
+      <c r="Q576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A577">
+        <v>0</v>
+      </c>
+      <c r="B577">
+        <f t="shared" si="216"/>
+        <v>160</v>
+      </c>
+      <c r="C577">
+        <v>-2660</v>
+      </c>
+      <c r="D577">
+        <v>0</v>
+      </c>
+      <c r="E577">
+        <v>0</v>
+      </c>
+      <c r="F577">
+        <v>0</v>
+      </c>
+      <c r="G577">
+        <v>1</v>
+      </c>
+      <c r="H577">
+        <v>1</v>
+      </c>
+      <c r="I577">
+        <v>1</v>
+      </c>
+      <c r="J577">
+        <v>10</v>
+      </c>
+      <c r="K577">
+        <v>10</v>
+      </c>
+      <c r="L577">
+        <v>10</v>
+      </c>
+      <c r="M577">
+        <v>-1</v>
+      </c>
+      <c r="N577">
+        <v>0</v>
+      </c>
+      <c r="O577">
+        <v>0</v>
+      </c>
+      <c r="P577">
+        <v>0</v>
+      </c>
+      <c r="Q577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A578">
+        <v>0</v>
+      </c>
+      <c r="B578">
+        <f t="shared" si="216"/>
+        <v>170</v>
+      </c>
+      <c r="C578">
+        <v>-2660</v>
+      </c>
+      <c r="D578">
+        <v>0</v>
+      </c>
+      <c r="E578">
+        <v>0</v>
+      </c>
+      <c r="F578">
+        <v>0</v>
+      </c>
+      <c r="G578">
+        <v>1</v>
+      </c>
+      <c r="H578">
+        <v>1</v>
+      </c>
+      <c r="I578">
+        <v>1</v>
+      </c>
+      <c r="J578">
+        <v>10</v>
+      </c>
+      <c r="K578">
+        <v>10</v>
+      </c>
+      <c r="L578">
+        <v>10</v>
+      </c>
+      <c r="M578">
+        <v>-1</v>
+      </c>
+      <c r="N578">
+        <v>0</v>
+      </c>
+      <c r="O578">
+        <v>0</v>
+      </c>
+      <c r="P578">
+        <v>0</v>
+      </c>
+      <c r="Q578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A579">
+        <v>0</v>
+      </c>
+      <c r="B579">
+        <f t="shared" si="216"/>
+        <v>180</v>
+      </c>
+      <c r="C579">
+        <v>-2660</v>
+      </c>
+      <c r="D579">
+        <v>0</v>
+      </c>
+      <c r="E579">
+        <v>0</v>
+      </c>
+      <c r="F579">
+        <v>0</v>
+      </c>
+      <c r="G579">
+        <v>1</v>
+      </c>
+      <c r="H579">
+        <v>1</v>
+      </c>
+      <c r="I579">
+        <v>1</v>
+      </c>
+      <c r="J579">
+        <v>10</v>
+      </c>
+      <c r="K579">
+        <v>10</v>
+      </c>
+      <c r="L579">
+        <v>10</v>
+      </c>
+      <c r="M579">
+        <v>-1</v>
+      </c>
+      <c r="N579">
+        <v>0</v>
+      </c>
+      <c r="O579">
+        <v>0</v>
+      </c>
+      <c r="P579">
+        <v>0</v>
+      </c>
+      <c r="Q579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A580">
+        <v>0</v>
+      </c>
+      <c r="B580">
+        <f t="shared" si="216"/>
+        <v>190</v>
+      </c>
+      <c r="C580">
+        <v>-2660</v>
+      </c>
+      <c r="D580">
+        <v>0</v>
+      </c>
+      <c r="E580">
+        <v>0</v>
+      </c>
+      <c r="F580">
+        <v>0</v>
+      </c>
+      <c r="G580">
+        <v>1</v>
+      </c>
+      <c r="H580">
+        <v>1</v>
+      </c>
+      <c r="I580">
+        <v>1</v>
+      </c>
+      <c r="J580">
+        <v>10</v>
+      </c>
+      <c r="K580">
+        <v>10</v>
+      </c>
+      <c r="L580">
+        <v>10</v>
+      </c>
+      <c r="M580">
+        <v>-1</v>
+      </c>
+      <c r="N580">
+        <v>0</v>
+      </c>
+      <c r="O580">
+        <v>0</v>
+      </c>
+      <c r="P580">
+        <v>0</v>
+      </c>
+      <c r="Q580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A581">
+        <v>0</v>
+      </c>
+      <c r="B581">
+        <f t="shared" si="216"/>
+        <v>200</v>
+      </c>
+      <c r="C581">
+        <v>-2660</v>
+      </c>
+      <c r="D581">
+        <v>0</v>
+      </c>
+      <c r="E581">
+        <v>0</v>
+      </c>
+      <c r="F581">
+        <v>0</v>
+      </c>
+      <c r="G581">
+        <v>1</v>
+      </c>
+      <c r="H581">
+        <v>1</v>
+      </c>
+      <c r="I581">
+        <v>1</v>
+      </c>
+      <c r="J581">
+        <v>10</v>
+      </c>
+      <c r="K581">
+        <v>10</v>
+      </c>
+      <c r="L581">
+        <v>10</v>
+      </c>
+      <c r="M581">
+        <v>-1</v>
+      </c>
+      <c r="N581">
+        <v>0</v>
+      </c>
+      <c r="O581">
+        <v>0</v>
+      </c>
+      <c r="P581">
+        <v>0</v>
+      </c>
+      <c r="Q581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A582">
+        <v>0</v>
+      </c>
+      <c r="B582">
+        <f t="shared" si="216"/>
+        <v>210</v>
+      </c>
+      <c r="C582">
+        <v>-2660</v>
+      </c>
+      <c r="D582">
+        <v>0</v>
+      </c>
+      <c r="E582">
+        <v>0</v>
+      </c>
+      <c r="F582">
+        <v>0</v>
+      </c>
+      <c r="G582">
+        <v>1</v>
+      </c>
+      <c r="H582">
+        <v>1</v>
+      </c>
+      <c r="I582">
+        <v>1</v>
+      </c>
+      <c r="J582">
+        <v>10</v>
+      </c>
+      <c r="K582">
+        <v>10</v>
+      </c>
+      <c r="L582">
+        <v>10</v>
+      </c>
+      <c r="M582">
+        <v>-1</v>
+      </c>
+      <c r="N582">
+        <v>0</v>
+      </c>
+      <c r="O582">
+        <v>0</v>
+      </c>
+      <c r="P582">
+        <v>0</v>
+      </c>
+      <c r="Q582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A583">
+        <v>0</v>
+      </c>
+      <c r="B583">
+        <f t="shared" si="216"/>
+        <v>220</v>
+      </c>
+      <c r="C583">
+        <v>-2660</v>
+      </c>
+      <c r="D583">
+        <v>0</v>
+      </c>
+      <c r="E583">
+        <v>0</v>
+      </c>
+      <c r="F583">
+        <v>0</v>
+      </c>
+      <c r="G583">
+        <v>1</v>
+      </c>
+      <c r="H583">
+        <v>1</v>
+      </c>
+      <c r="I583">
+        <v>1</v>
+      </c>
+      <c r="J583">
+        <v>10</v>
+      </c>
+      <c r="K583">
+        <v>10</v>
+      </c>
+      <c r="L583">
+        <v>10</v>
+      </c>
+      <c r="M583">
+        <v>-1</v>
+      </c>
+      <c r="N583">
+        <v>0</v>
+      </c>
+      <c r="O583">
+        <v>0</v>
+      </c>
+      <c r="P583">
+        <v>0</v>
+      </c>
+      <c r="Q583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A584">
+        <v>0</v>
+      </c>
+      <c r="B584">
+        <f>B583+10</f>
+        <v>230</v>
+      </c>
+      <c r="C584">
+        <v>-2660</v>
+      </c>
+      <c r="D584">
+        <v>0</v>
+      </c>
+      <c r="E584">
+        <v>0</v>
+      </c>
+      <c r="F584">
+        <v>0</v>
+      </c>
+      <c r="G584">
+        <v>1</v>
+      </c>
+      <c r="H584">
+        <v>1</v>
+      </c>
+      <c r="I584">
+        <v>1</v>
+      </c>
+      <c r="J584">
+        <v>10</v>
+      </c>
+      <c r="K584">
+        <v>10</v>
+      </c>
+      <c r="L584">
+        <v>10</v>
+      </c>
+      <c r="M584">
+        <v>-1</v>
+      </c>
+      <c r="N584">
+        <v>0</v>
+      </c>
+      <c r="O584">
+        <v>0</v>
+      </c>
+      <c r="P584">
+        <v>0</v>
+      </c>
+      <c r="Q584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A585">
+        <v>0</v>
+      </c>
+      <c r="B585">
+        <f t="shared" ref="B585:B590" si="217">B584+10</f>
+        <v>240</v>
+      </c>
+      <c r="C585">
+        <v>-2660</v>
+      </c>
+      <c r="D585">
+        <v>0</v>
+      </c>
+      <c r="E585">
+        <v>0</v>
+      </c>
+      <c r="F585">
+        <v>0</v>
+      </c>
+      <c r="G585">
+        <v>1</v>
+      </c>
+      <c r="H585">
+        <v>1</v>
+      </c>
+      <c r="I585">
+        <v>1</v>
+      </c>
+      <c r="J585">
+        <v>10</v>
+      </c>
+      <c r="K585">
+        <v>10</v>
+      </c>
+      <c r="L585">
+        <v>10</v>
+      </c>
+      <c r="M585">
+        <v>-1</v>
+      </c>
+      <c r="N585">
+        <v>0</v>
+      </c>
+      <c r="O585">
+        <v>0</v>
+      </c>
+      <c r="P585">
+        <v>0</v>
+      </c>
+      <c r="Q585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A586">
+        <v>0</v>
+      </c>
+      <c r="B586">
+        <f t="shared" si="217"/>
+        <v>250</v>
+      </c>
+      <c r="C586">
+        <v>-2660</v>
+      </c>
+      <c r="D586">
+        <v>0</v>
+      </c>
+      <c r="E586">
+        <v>0</v>
+      </c>
+      <c r="F586">
+        <v>0</v>
+      </c>
+      <c r="G586">
+        <v>1</v>
+      </c>
+      <c r="H586">
+        <v>1</v>
+      </c>
+      <c r="I586">
+        <v>1</v>
+      </c>
+      <c r="J586">
+        <v>10</v>
+      </c>
+      <c r="K586">
+        <v>10</v>
+      </c>
+      <c r="L586">
+        <v>10</v>
+      </c>
+      <c r="M586">
+        <v>-1</v>
+      </c>
+      <c r="N586">
+        <v>0</v>
+      </c>
+      <c r="O586">
+        <v>0</v>
+      </c>
+      <c r="P586">
+        <v>0</v>
+      </c>
+      <c r="Q586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A587">
+        <v>0</v>
+      </c>
+      <c r="B587">
+        <f t="shared" si="217"/>
+        <v>260</v>
+      </c>
+      <c r="C587">
+        <v>-2660</v>
+      </c>
+      <c r="D587">
+        <v>0</v>
+      </c>
+      <c r="E587">
+        <v>0</v>
+      </c>
+      <c r="F587">
+        <v>0</v>
+      </c>
+      <c r="G587">
+        <v>1</v>
+      </c>
+      <c r="H587">
+        <v>1</v>
+      </c>
+      <c r="I587">
+        <v>1</v>
+      </c>
+      <c r="J587">
+        <v>10</v>
+      </c>
+      <c r="K587">
+        <v>10</v>
+      </c>
+      <c r="L587">
+        <v>10</v>
+      </c>
+      <c r="M587">
+        <v>-1</v>
+      </c>
+      <c r="N587">
+        <v>0</v>
+      </c>
+      <c r="O587">
+        <v>0</v>
+      </c>
+      <c r="P587">
+        <v>0</v>
+      </c>
+      <c r="Q587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A588">
+        <v>0</v>
+      </c>
+      <c r="B588">
+        <f t="shared" si="217"/>
+        <v>270</v>
+      </c>
+      <c r="C588">
+        <v>-2660</v>
+      </c>
+      <c r="D588">
+        <v>0</v>
+      </c>
+      <c r="E588">
+        <v>0</v>
+      </c>
+      <c r="F588">
+        <v>0</v>
+      </c>
+      <c r="G588">
+        <v>1</v>
+      </c>
+      <c r="H588">
+        <v>1</v>
+      </c>
+      <c r="I588">
+        <v>1</v>
+      </c>
+      <c r="J588">
+        <v>10</v>
+      </c>
+      <c r="K588">
+        <v>10</v>
+      </c>
+      <c r="L588">
+        <v>10</v>
+      </c>
+      <c r="M588">
+        <v>-1</v>
+      </c>
+      <c r="N588">
+        <v>0</v>
+      </c>
+      <c r="O588">
+        <v>0</v>
+      </c>
+      <c r="P588">
+        <v>0</v>
+      </c>
+      <c r="Q588">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A589">
+        <v>0</v>
+      </c>
+      <c r="B589">
+        <f t="shared" si="217"/>
+        <v>280</v>
+      </c>
+      <c r="C589">
+        <v>-2660</v>
+      </c>
+      <c r="D589">
+        <v>0</v>
+      </c>
+      <c r="E589">
+        <v>0</v>
+      </c>
+      <c r="F589">
+        <v>0</v>
+      </c>
+      <c r="G589">
+        <v>1</v>
+      </c>
+      <c r="H589">
+        <v>1</v>
+      </c>
+      <c r="I589">
+        <v>1</v>
+      </c>
+      <c r="J589">
+        <v>10</v>
+      </c>
+      <c r="K589">
+        <v>10</v>
+      </c>
+      <c r="L589">
+        <v>10</v>
+      </c>
+      <c r="M589">
+        <v>-1</v>
+      </c>
+      <c r="N589">
+        <v>0</v>
+      </c>
+      <c r="O589">
+        <v>0</v>
+      </c>
+      <c r="P589">
+        <v>0</v>
+      </c>
+      <c r="Q589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A590">
+        <v>0</v>
+      </c>
+      <c r="B590">
+        <f t="shared" si="217"/>
+        <v>290</v>
+      </c>
+      <c r="C590">
+        <v>-2660</v>
+      </c>
+      <c r="D590">
+        <v>0</v>
+      </c>
+      <c r="E590">
+        <v>0</v>
+      </c>
+      <c r="F590">
+        <v>0</v>
+      </c>
+      <c r="G590">
+        <v>1</v>
+      </c>
+      <c r="H590">
+        <v>1</v>
+      </c>
+      <c r="I590">
+        <v>1</v>
+      </c>
+      <c r="J590">
+        <v>10</v>
+      </c>
+      <c r="K590">
+        <v>10</v>
+      </c>
+      <c r="L590">
+        <v>10</v>
+      </c>
+      <c r="M590">
+        <v>-1</v>
+      </c>
+      <c r="N590">
+        <v>0</v>
+      </c>
+      <c r="O590">
+        <v>0</v>
+      </c>
+      <c r="P590">
+        <v>0</v>
+      </c>
+      <c r="Q590">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A591">
+        <v>0</v>
+      </c>
+      <c r="B591">
+        <f>B590+10</f>
+        <v>300</v>
+      </c>
+      <c r="C591">
+        <v>-2660</v>
+      </c>
+      <c r="D591">
+        <v>0</v>
+      </c>
+      <c r="E591">
+        <v>0</v>
+      </c>
+      <c r="F591">
+        <v>0</v>
+      </c>
+      <c r="G591">
+        <v>1</v>
+      </c>
+      <c r="H591">
+        <v>1</v>
+      </c>
+      <c r="I591">
+        <v>1</v>
+      </c>
+      <c r="J591">
+        <v>10</v>
+      </c>
+      <c r="K591">
+        <v>10</v>
+      </c>
+      <c r="L591">
+        <v>10</v>
+      </c>
+      <c r="M591">
+        <v>-1</v>
+      </c>
+      <c r="N591">
+        <v>0</v>
+      </c>
+      <c r="O591">
+        <v>0</v>
+      </c>
+      <c r="P591">
+        <v>0</v>
+      </c>
+      <c r="Q591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A592">
+        <v>0</v>
+      </c>
+      <c r="B592">
+        <f t="shared" ref="B592" si="218">B591+10</f>
+        <v>310</v>
+      </c>
+      <c r="C592">
+        <v>-2660</v>
+      </c>
+      <c r="D592">
+        <v>0</v>
+      </c>
+      <c r="E592">
+        <v>0</v>
+      </c>
+      <c r="F592">
+        <v>0</v>
+      </c>
+      <c r="G592">
+        <v>1</v>
+      </c>
+      <c r="H592">
+        <v>1</v>
+      </c>
+      <c r="I592">
+        <v>1</v>
+      </c>
+      <c r="J592">
+        <v>10</v>
+      </c>
+      <c r="K592">
+        <v>10</v>
+      </c>
+      <c r="L592">
+        <v>10</v>
+      </c>
+      <c r="M592">
+        <v>-1</v>
+      </c>
+      <c r="N592">
+        <v>0</v>
+      </c>
+      <c r="O592">
+        <v>0</v>
+      </c>
+      <c r="P592">
+        <v>0</v>
+      </c>
+      <c r="Q592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A593">
+        <v>0</v>
+      </c>
+      <c r="B593">
+        <f>B592+10</f>
+        <v>320</v>
+      </c>
+      <c r="C593">
+        <v>-2660</v>
+      </c>
+      <c r="D593">
+        <v>0</v>
+      </c>
+      <c r="E593">
+        <v>0</v>
+      </c>
+      <c r="F593">
+        <v>0</v>
+      </c>
+      <c r="G593">
+        <v>1</v>
+      </c>
+      <c r="H593">
+        <v>1</v>
+      </c>
+      <c r="I593">
+        <v>1</v>
+      </c>
+      <c r="J593">
+        <v>10</v>
+      </c>
+      <c r="K593">
+        <v>10</v>
+      </c>
+      <c r="L593">
+        <v>10</v>
+      </c>
+      <c r="M593">
+        <v>-1</v>
+      </c>
+      <c r="N593">
+        <v>0</v>
+      </c>
+      <c r="O593">
+        <v>0</v>
+      </c>
+      <c r="P593">
+        <v>0</v>
+      </c>
+      <c r="Q593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A594">
+        <v>0</v>
+      </c>
+      <c r="B594">
+        <f>B593+10</f>
+        <v>330</v>
+      </c>
+      <c r="C594">
+        <v>-2660</v>
+      </c>
+      <c r="D594">
+        <v>0</v>
+      </c>
+      <c r="E594">
+        <v>0</v>
+      </c>
+      <c r="F594">
+        <v>0</v>
+      </c>
+      <c r="G594">
+        <v>1</v>
+      </c>
+      <c r="H594">
+        <v>1</v>
+      </c>
+      <c r="I594">
+        <v>1</v>
+      </c>
+      <c r="J594">
+        <v>10</v>
+      </c>
+      <c r="K594">
+        <v>10</v>
+      </c>
+      <c r="L594">
+        <v>10</v>
+      </c>
+      <c r="M594">
+        <v>-1</v>
+      </c>
+      <c r="N594">
+        <v>0</v>
+      </c>
+      <c r="O594">
+        <v>0</v>
+      </c>
+      <c r="P594">
+        <v>0</v>
+      </c>
+      <c r="Q594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A595">
+        <v>0</v>
+      </c>
+      <c r="B595">
+        <f>B594+10</f>
+        <v>340</v>
+      </c>
+      <c r="C595">
+        <v>-2660</v>
+      </c>
+      <c r="D595">
+        <v>0</v>
+      </c>
+      <c r="E595">
+        <v>0</v>
+      </c>
+      <c r="F595">
+        <v>0</v>
+      </c>
+      <c r="G595">
+        <v>1</v>
+      </c>
+      <c r="H595">
+        <v>1</v>
+      </c>
+      <c r="I595">
+        <v>1</v>
+      </c>
+      <c r="J595">
+        <v>10</v>
+      </c>
+      <c r="K595">
+        <v>10</v>
+      </c>
+      <c r="L595">
+        <v>10</v>
+      </c>
+      <c r="M595">
+        <v>-1</v>
+      </c>
+      <c r="N595">
+        <v>0</v>
+      </c>
+      <c r="O595">
+        <v>0</v>
+      </c>
+      <c r="P595">
+        <v>0</v>
+      </c>
+      <c r="Q595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A596" s="1">
+        <v>0</v>
+      </c>
+      <c r="B596">
+        <v>320</v>
+      </c>
+      <c r="C596" s="1">
+        <v>-2980</v>
+      </c>
+      <c r="D596">
+        <v>0</v>
+      </c>
+      <c r="E596">
+        <v>0</v>
+      </c>
+      <c r="F596">
+        <v>0</v>
+      </c>
+      <c r="G596">
+        <v>1</v>
+      </c>
+      <c r="H596">
+        <v>1</v>
+      </c>
+      <c r="I596">
+        <v>1</v>
+      </c>
+      <c r="J596">
+        <v>10</v>
+      </c>
+      <c r="K596">
+        <v>10</v>
+      </c>
+      <c r="L596">
+        <v>10</v>
+      </c>
+      <c r="M596">
+        <v>-1</v>
+      </c>
+      <c r="N596">
+        <v>0</v>
+      </c>
+      <c r="O596">
+        <v>0</v>
+      </c>
+      <c r="P596">
+        <v>0</v>
+      </c>
+      <c r="Q596">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A597" s="1">
+        <v>25</v>
+      </c>
+      <c r="B597">
+        <v>320</v>
+      </c>
+      <c r="C597" s="1">
+        <v>-2986.7</v>
+      </c>
+      <c r="D597">
+        <v>0</v>
+      </c>
+      <c r="E597">
+        <v>0</v>
+      </c>
+      <c r="F597">
+        <v>0</v>
+      </c>
+      <c r="G597">
+        <v>1</v>
+      </c>
+      <c r="H597">
+        <v>1</v>
+      </c>
+      <c r="I597">
+        <v>1</v>
+      </c>
+      <c r="J597">
+        <v>10</v>
+      </c>
+      <c r="K597">
+        <v>10</v>
+      </c>
+      <c r="L597">
+        <v>10</v>
+      </c>
+      <c r="M597">
+        <v>-1</v>
+      </c>
+      <c r="N597">
+        <v>0</v>
+      </c>
+      <c r="O597">
+        <v>0</v>
+      </c>
+      <c r="P597">
+        <v>0</v>
+      </c>
+      <c r="Q597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A598" s="1">
+        <v>43.3</v>
+      </c>
+      <c r="B598">
+        <v>320</v>
+      </c>
+      <c r="C598" s="1">
+        <v>-3005</v>
+      </c>
+      <c r="D598">
+        <v>0</v>
+      </c>
+      <c r="E598">
+        <v>0</v>
+      </c>
+      <c r="F598">
+        <v>0</v>
+      </c>
+      <c r="G598">
+        <v>1</v>
+      </c>
+      <c r="H598">
+        <v>1</v>
+      </c>
+      <c r="I598">
+        <v>1</v>
+      </c>
+      <c r="J598">
+        <v>10</v>
+      </c>
+      <c r="K598">
+        <v>10</v>
+      </c>
+      <c r="L598">
+        <v>10</v>
+      </c>
+      <c r="M598">
+        <v>-1</v>
+      </c>
+      <c r="N598">
+        <v>0</v>
+      </c>
+      <c r="O598">
+        <v>0</v>
+      </c>
+      <c r="P598">
+        <v>0</v>
+      </c>
+      <c r="Q598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A599" s="1">
+        <v>50</v>
+      </c>
+      <c r="B599">
+        <v>320</v>
+      </c>
+      <c r="C599" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D599">
+        <v>0</v>
+      </c>
+      <c r="E599">
+        <v>0</v>
+      </c>
+      <c r="F599">
+        <v>0</v>
+      </c>
+      <c r="G599">
+        <v>1</v>
+      </c>
+      <c r="H599">
+        <v>1</v>
+      </c>
+      <c r="I599">
+        <v>1</v>
+      </c>
+      <c r="J599">
+        <v>10</v>
+      </c>
+      <c r="K599">
+        <v>10</v>
+      </c>
+      <c r="L599">
+        <v>10</v>
+      </c>
+      <c r="M599">
+        <v>-1</v>
+      </c>
+      <c r="N599">
+        <v>0</v>
+      </c>
+      <c r="O599">
+        <v>0</v>
+      </c>
+      <c r="P599">
+        <v>0</v>
+      </c>
+      <c r="Q599">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="600" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A600" s="1">
+        <v>43.3</v>
+      </c>
+      <c r="B600">
+        <v>320</v>
+      </c>
+      <c r="C600" s="1">
+        <v>-3055</v>
+      </c>
+      <c r="D600">
+        <v>0</v>
+      </c>
+      <c r="E600">
+        <v>0</v>
+      </c>
+      <c r="F600">
+        <v>0</v>
+      </c>
+      <c r="G600">
+        <v>1</v>
+      </c>
+      <c r="H600">
+        <v>1</v>
+      </c>
+      <c r="I600">
+        <v>1</v>
+      </c>
+      <c r="J600">
+        <v>10</v>
+      </c>
+      <c r="K600">
+        <v>10</v>
+      </c>
+      <c r="L600">
+        <v>10</v>
+      </c>
+      <c r="M600">
+        <v>-1</v>
+      </c>
+      <c r="N600">
+        <v>0</v>
+      </c>
+      <c r="O600">
+        <v>0</v>
+      </c>
+      <c r="P600">
+        <v>0</v>
+      </c>
+      <c r="Q600">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A601" s="1">
+        <v>25</v>
+      </c>
+      <c r="B601">
+        <v>320</v>
+      </c>
+      <c r="C601" s="1">
+        <v>-3073.3</v>
+      </c>
+      <c r="D601">
+        <v>0</v>
+      </c>
+      <c r="E601">
+        <v>0</v>
+      </c>
+      <c r="F601">
+        <v>0</v>
+      </c>
+      <c r="G601">
+        <v>1</v>
+      </c>
+      <c r="H601">
+        <v>1</v>
+      </c>
+      <c r="I601">
+        <v>1</v>
+      </c>
+      <c r="J601">
+        <v>10</v>
+      </c>
+      <c r="K601">
+        <v>10</v>
+      </c>
+      <c r="L601">
+        <v>10</v>
+      </c>
+      <c r="M601">
+        <v>-1</v>
+      </c>
+      <c r="N601">
+        <v>0</v>
+      </c>
+      <c r="O601">
+        <v>0</v>
+      </c>
+      <c r="P601">
+        <v>0</v>
+      </c>
+      <c r="Q601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A602" s="1">
+        <v>0</v>
+      </c>
+      <c r="B602">
+        <v>320</v>
+      </c>
+      <c r="C602" s="1">
+        <v>-3080</v>
+      </c>
+      <c r="D602">
+        <v>0</v>
+      </c>
+      <c r="E602">
+        <v>0</v>
+      </c>
+      <c r="F602">
+        <v>0</v>
+      </c>
+      <c r="G602">
+        <v>1</v>
+      </c>
+      <c r="H602">
+        <v>1</v>
+      </c>
+      <c r="I602">
+        <v>1</v>
+      </c>
+      <c r="J602">
+        <v>10</v>
+      </c>
+      <c r="K602">
+        <v>10</v>
+      </c>
+      <c r="L602">
+        <v>10</v>
+      </c>
+      <c r="M602">
+        <v>-1</v>
+      </c>
+      <c r="N602">
+        <v>0</v>
+      </c>
+      <c r="O602">
+        <v>0</v>
+      </c>
+      <c r="P602">
+        <v>0</v>
+      </c>
+      <c r="Q602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A603" s="1">
+        <v>-25</v>
+      </c>
+      <c r="B603">
+        <v>320</v>
+      </c>
+      <c r="C603" s="1">
+        <v>-3073.3</v>
+      </c>
+      <c r="D603">
+        <v>0</v>
+      </c>
+      <c r="E603">
+        <v>0</v>
+      </c>
+      <c r="F603">
+        <v>0</v>
+      </c>
+      <c r="G603">
+        <v>1</v>
+      </c>
+      <c r="H603">
+        <v>1</v>
+      </c>
+      <c r="I603">
+        <v>1</v>
+      </c>
+      <c r="J603">
+        <v>10</v>
+      </c>
+      <c r="K603">
+        <v>10</v>
+      </c>
+      <c r="L603">
+        <v>10</v>
+      </c>
+      <c r="M603">
+        <v>-1</v>
+      </c>
+      <c r="N603">
+        <v>0</v>
+      </c>
+      <c r="O603">
+        <v>0</v>
+      </c>
+      <c r="P603">
+        <v>0</v>
+      </c>
+      <c r="Q603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A604" s="1">
+        <v>-43.3</v>
+      </c>
+      <c r="B604">
+        <v>320</v>
+      </c>
+      <c r="C604" s="1">
+        <v>-3055</v>
+      </c>
+      <c r="D604">
+        <v>0</v>
+      </c>
+      <c r="E604">
+        <v>0</v>
+      </c>
+      <c r="F604">
+        <v>0</v>
+      </c>
+      <c r="G604">
+        <v>1</v>
+      </c>
+      <c r="H604">
+        <v>1</v>
+      </c>
+      <c r="I604">
+        <v>1</v>
+      </c>
+      <c r="J604">
+        <v>10</v>
+      </c>
+      <c r="K604">
+        <v>10</v>
+      </c>
+      <c r="L604">
+        <v>10</v>
+      </c>
+      <c r="M604">
+        <v>-1</v>
+      </c>
+      <c r="N604">
+        <v>0</v>
+      </c>
+      <c r="O604">
+        <v>0</v>
+      </c>
+      <c r="P604">
+        <v>0</v>
+      </c>
+      <c r="Q604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A605" s="1">
+        <v>-50</v>
+      </c>
+      <c r="B605">
+        <v>320</v>
+      </c>
+      <c r="C605" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D605">
+        <v>0</v>
+      </c>
+      <c r="E605">
+        <v>0</v>
+      </c>
+      <c r="F605">
+        <v>0</v>
+      </c>
+      <c r="G605">
+        <v>1</v>
+      </c>
+      <c r="H605">
+        <v>1</v>
+      </c>
+      <c r="I605">
+        <v>1</v>
+      </c>
+      <c r="J605">
+        <v>10</v>
+      </c>
+      <c r="K605">
+        <v>10</v>
+      </c>
+      <c r="L605">
+        <v>10</v>
+      </c>
+      <c r="M605">
+        <v>-1</v>
+      </c>
+      <c r="N605">
+        <v>0</v>
+      </c>
+      <c r="O605">
+        <v>0</v>
+      </c>
+      <c r="P605">
+        <v>0</v>
+      </c>
+      <c r="Q605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A606" s="1">
+        <v>-43.3</v>
+      </c>
+      <c r="B606">
+        <v>320</v>
+      </c>
+      <c r="C606" s="1">
+        <v>-3005</v>
+      </c>
+      <c r="D606">
+        <v>0</v>
+      </c>
+      <c r="E606">
+        <v>0</v>
+      </c>
+      <c r="F606">
+        <v>0</v>
+      </c>
+      <c r="G606">
+        <v>1</v>
+      </c>
+      <c r="H606">
+        <v>1</v>
+      </c>
+      <c r="I606">
+        <v>1</v>
+      </c>
+      <c r="J606">
+        <v>10</v>
+      </c>
+      <c r="K606">
+        <v>10</v>
+      </c>
+      <c r="L606">
+        <v>10</v>
+      </c>
+      <c r="M606">
+        <v>-1</v>
+      </c>
+      <c r="N606">
+        <v>0</v>
+      </c>
+      <c r="O606">
+        <v>0</v>
+      </c>
+      <c r="P606">
+        <v>0</v>
+      </c>
+      <c r="Q606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A607" s="1">
+        <v>-25</v>
+      </c>
+      <c r="B607">
+        <v>320</v>
+      </c>
+      <c r="C607" s="1">
+        <v>-2986.7</v>
+      </c>
+      <c r="D607">
+        <v>0</v>
+      </c>
+      <c r="E607">
+        <v>0</v>
+      </c>
+      <c r="F607">
+        <v>0</v>
+      </c>
+      <c r="G607">
+        <v>1</v>
+      </c>
+      <c r="H607">
+        <v>1</v>
+      </c>
+      <c r="I607">
+        <v>1</v>
+      </c>
+      <c r="J607">
+        <v>10</v>
+      </c>
+      <c r="K607">
+        <v>10</v>
+      </c>
+      <c r="L607">
+        <v>10</v>
+      </c>
+      <c r="M607">
+        <v>-1</v>
+      </c>
+      <c r="N607">
+        <v>0</v>
+      </c>
+      <c r="O607">
+        <v>0</v>
+      </c>
+      <c r="P607">
+        <v>0</v>
+      </c>
+      <c r="Q607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A608" s="1">
+        <v>460</v>
+      </c>
+      <c r="B608" s="1">
+        <v>320</v>
+      </c>
+      <c r="C608" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D608">
+        <v>0</v>
+      </c>
+      <c r="E608">
+        <v>0</v>
+      </c>
+      <c r="F608">
+        <v>0</v>
+      </c>
+      <c r="G608">
+        <v>1</v>
+      </c>
+      <c r="H608">
+        <v>1</v>
+      </c>
+      <c r="I608">
+        <v>1</v>
+      </c>
+      <c r="J608">
+        <v>10</v>
+      </c>
+      <c r="K608">
+        <v>10</v>
+      </c>
+      <c r="L608">
+        <v>10</v>
+      </c>
+      <c r="M608">
+        <v>-1</v>
+      </c>
+      <c r="N608">
+        <v>0</v>
+      </c>
+      <c r="O608">
+        <v>0</v>
+      </c>
+      <c r="P608">
+        <v>0</v>
+      </c>
+      <c r="Q608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A609" s="1">
+        <v>472</v>
+      </c>
+      <c r="B609" s="1">
+        <v>348.8</v>
+      </c>
+      <c r="C609" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D609">
+        <v>0</v>
+      </c>
+      <c r="E609">
+        <v>0</v>
+      </c>
+      <c r="F609">
+        <v>0</v>
+      </c>
+      <c r="G609">
+        <v>1</v>
+      </c>
+      <c r="H609">
+        <v>1</v>
+      </c>
+      <c r="I609">
+        <v>1</v>
+      </c>
+      <c r="J609">
+        <v>10</v>
+      </c>
+      <c r="K609">
+        <v>10</v>
+      </c>
+      <c r="L609">
+        <v>10</v>
+      </c>
+      <c r="M609">
+        <v>-1</v>
+      </c>
+      <c r="N609">
+        <v>0</v>
+      </c>
+      <c r="O609">
+        <v>0</v>
+      </c>
+      <c r="P609">
+        <v>0</v>
+      </c>
+      <c r="Q609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A610" s="1">
+        <v>484</v>
+      </c>
+      <c r="B610" s="1">
+        <v>362.1</v>
+      </c>
+      <c r="C610" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D610">
+        <v>0</v>
+      </c>
+      <c r="E610">
+        <v>0</v>
+      </c>
+      <c r="F610">
+        <v>0</v>
+      </c>
+      <c r="G610">
+        <v>1</v>
+      </c>
+      <c r="H610">
+        <v>1</v>
+      </c>
+      <c r="I610">
+        <v>1</v>
+      </c>
+      <c r="J610">
+        <v>10</v>
+      </c>
+      <c r="K610">
+        <v>10</v>
+      </c>
+      <c r="L610">
+        <v>10</v>
+      </c>
+      <c r="M610">
+        <v>-1</v>
+      </c>
+      <c r="N610">
+        <v>0</v>
+      </c>
+      <c r="O610">
+        <v>0</v>
+      </c>
+      <c r="P610">
+        <v>0</v>
+      </c>
+      <c r="Q610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A611" s="1">
+        <v>500</v>
+      </c>
+      <c r="B611" s="1">
+        <v>365</v>
+      </c>
+      <c r="C611" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D611">
+        <v>0</v>
+      </c>
+      <c r="E611">
+        <v>0</v>
+      </c>
+      <c r="F611">
+        <v>0</v>
+      </c>
+      <c r="G611">
+        <v>1</v>
+      </c>
+      <c r="H611">
+        <v>1</v>
+      </c>
+      <c r="I611">
+        <v>1</v>
+      </c>
+      <c r="J611">
+        <v>10</v>
+      </c>
+      <c r="K611">
+        <v>10</v>
+      </c>
+      <c r="L611">
+        <v>10</v>
+      </c>
+      <c r="M611">
+        <v>-1</v>
+      </c>
+      <c r="N611">
+        <v>0</v>
+      </c>
+      <c r="O611">
+        <v>0</v>
+      </c>
+      <c r="P611">
+        <v>0</v>
+      </c>
+      <c r="Q611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A612" s="1">
+        <v>512</v>
+      </c>
+      <c r="B612" s="1">
+        <v>360.3</v>
+      </c>
+      <c r="C612" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D612">
+        <v>0</v>
+      </c>
+      <c r="E612">
+        <v>0</v>
+      </c>
+      <c r="F612">
+        <v>0</v>
+      </c>
+      <c r="G612">
+        <v>1</v>
+      </c>
+      <c r="H612">
+        <v>1</v>
+      </c>
+      <c r="I612">
+        <v>1</v>
+      </c>
+      <c r="J612">
+        <v>10</v>
+      </c>
+      <c r="K612">
+        <v>10</v>
+      </c>
+      <c r="L612">
+        <v>10</v>
+      </c>
+      <c r="M612">
+        <v>-1</v>
+      </c>
+      <c r="N612">
+        <v>0</v>
+      </c>
+      <c r="O612">
+        <v>0</v>
+      </c>
+      <c r="P612">
+        <v>0</v>
+      </c>
+      <c r="Q612">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A613" s="1">
+        <v>521</v>
+      </c>
+      <c r="B613" s="1">
+        <v>351.2</v>
+      </c>
+      <c r="C613" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D613">
+        <v>0</v>
+      </c>
+      <c r="E613">
+        <v>0</v>
+      </c>
+      <c r="F613">
+        <v>0</v>
+      </c>
+      <c r="G613">
+        <v>1</v>
+      </c>
+      <c r="H613">
+        <v>1</v>
+      </c>
+      <c r="I613">
+        <v>1</v>
+      </c>
+      <c r="J613">
+        <v>10</v>
+      </c>
+      <c r="K613">
+        <v>10</v>
+      </c>
+      <c r="L613">
+        <v>10</v>
+      </c>
+      <c r="M613">
+        <v>-1</v>
+      </c>
+      <c r="N613">
+        <v>0</v>
+      </c>
+      <c r="O613">
+        <v>0</v>
+      </c>
+      <c r="P613">
+        <v>0</v>
+      </c>
+      <c r="Q613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A614" s="1">
+        <v>530</v>
+      </c>
+      <c r="B614" s="1">
+        <v>340</v>
+      </c>
+      <c r="C614" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D614">
+        <v>0</v>
+      </c>
+      <c r="E614">
+        <v>0</v>
+      </c>
+      <c r="F614">
+        <v>0</v>
+      </c>
+      <c r="G614">
+        <v>1</v>
+      </c>
+      <c r="H614">
+        <v>1</v>
+      </c>
+      <c r="I614">
+        <v>1</v>
+      </c>
+      <c r="J614">
+        <v>10</v>
+      </c>
+      <c r="K614">
+        <v>10</v>
+      </c>
+      <c r="L614">
+        <v>10</v>
+      </c>
+      <c r="M614">
+        <v>-1</v>
+      </c>
+      <c r="N614">
+        <v>0</v>
+      </c>
+      <c r="O614">
+        <v>0</v>
+      </c>
+      <c r="P614">
+        <v>0</v>
+      </c>
+      <c r="Q614">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A615" s="1">
+        <v>970</v>
+      </c>
+      <c r="B615" s="1">
+        <v>340</v>
+      </c>
+      <c r="C615" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D615">
+        <v>0</v>
+      </c>
+      <c r="E615">
+        <v>0</v>
+      </c>
+      <c r="F615">
+        <v>0</v>
+      </c>
+      <c r="G615">
+        <v>1</v>
+      </c>
+      <c r="H615">
+        <v>1</v>
+      </c>
+      <c r="I615">
+        <v>1</v>
+      </c>
+      <c r="J615">
+        <v>10</v>
+      </c>
+      <c r="K615">
+        <v>10</v>
+      </c>
+      <c r="L615">
+        <v>10</v>
+      </c>
+      <c r="M615">
+        <v>-1</v>
+      </c>
+      <c r="N615">
+        <v>0</v>
+      </c>
+      <c r="O615">
+        <v>0</v>
+      </c>
+      <c r="P615">
+        <v>0</v>
+      </c>
+      <c r="Q615">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A616" s="1">
+        <v>990</v>
+      </c>
+      <c r="B616" s="1">
+        <v>340</v>
+      </c>
+      <c r="C616" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D616">
+        <v>0</v>
+      </c>
+      <c r="E616">
+        <v>0</v>
+      </c>
+      <c r="F616">
+        <v>0</v>
+      </c>
+      <c r="G616">
+        <v>1</v>
+      </c>
+      <c r="H616">
+        <v>1</v>
+      </c>
+      <c r="I616">
+        <v>1</v>
+      </c>
+      <c r="J616">
+        <v>10</v>
+      </c>
+      <c r="K616">
+        <v>10</v>
+      </c>
+      <c r="L616">
+        <v>10</v>
+      </c>
+      <c r="M616">
+        <v>-1</v>
+      </c>
+      <c r="N616">
+        <v>0</v>
+      </c>
+      <c r="O616">
+        <v>0</v>
+      </c>
+      <c r="P616">
+        <v>0</v>
+      </c>
+      <c r="Q616">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A617" s="1">
+        <v>1010</v>
+      </c>
+      <c r="B617" s="1">
+        <v>340</v>
+      </c>
+      <c r="C617" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D617">
+        <v>0</v>
+      </c>
+      <c r="E617">
+        <v>0</v>
+      </c>
+      <c r="F617">
+        <v>0</v>
+      </c>
+      <c r="G617">
+        <v>1</v>
+      </c>
+      <c r="H617">
+        <v>1</v>
+      </c>
+      <c r="I617">
+        <v>1</v>
+      </c>
+      <c r="J617">
+        <v>10</v>
+      </c>
+      <c r="K617">
+        <v>10</v>
+      </c>
+      <c r="L617">
+        <v>10</v>
+      </c>
+      <c r="M617">
+        <v>-1</v>
+      </c>
+      <c r="N617">
+        <v>0</v>
+      </c>
+      <c r="O617">
+        <v>0</v>
+      </c>
+      <c r="P617">
+        <v>0</v>
+      </c>
+      <c r="Q617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A618">
+        <v>1030</v>
+      </c>
+      <c r="B618" s="1">
+        <v>340</v>
+      </c>
+      <c r="C618" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D618">
+        <v>0</v>
+      </c>
+      <c r="E618">
+        <v>0</v>
+      </c>
+      <c r="F618">
+        <v>0</v>
+      </c>
+      <c r="G618">
+        <v>1</v>
+      </c>
+      <c r="H618">
+        <v>1</v>
+      </c>
+      <c r="I618">
+        <v>1</v>
+      </c>
+      <c r="J618">
+        <v>10</v>
+      </c>
+      <c r="K618">
+        <v>10</v>
+      </c>
+      <c r="L618">
+        <v>10</v>
+      </c>
+      <c r="M618">
+        <v>-1</v>
+      </c>
+      <c r="N618">
+        <v>0</v>
+      </c>
+      <c r="O618">
+        <v>0</v>
+      </c>
+      <c r="P618">
+        <v>0</v>
+      </c>
+      <c r="Q618">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A619">
+        <v>1050</v>
+      </c>
+      <c r="B619" s="1">
+        <v>340</v>
+      </c>
+      <c r="C619" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D619">
+        <v>0</v>
+      </c>
+      <c r="E619">
+        <v>0</v>
+      </c>
+      <c r="F619">
+        <v>0</v>
+      </c>
+      <c r="G619">
+        <v>1</v>
+      </c>
+      <c r="H619">
+        <v>1</v>
+      </c>
+      <c r="I619">
+        <v>1</v>
+      </c>
+      <c r="J619">
+        <v>10</v>
+      </c>
+      <c r="K619">
+        <v>10</v>
+      </c>
+      <c r="L619">
+        <v>10</v>
+      </c>
+      <c r="M619">
+        <v>-1</v>
+      </c>
+      <c r="N619">
+        <v>0</v>
+      </c>
+      <c r="O619">
+        <v>0</v>
+      </c>
+      <c r="P619">
+        <v>0</v>
+      </c>
+      <c r="Q619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A620">
+        <f>A619+20</f>
+        <v>1070</v>
+      </c>
+      <c r="B620" s="1">
+        <v>340</v>
+      </c>
+      <c r="C620" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D620">
+        <v>0</v>
+      </c>
+      <c r="E620">
+        <v>0</v>
+      </c>
+      <c r="F620">
+        <v>0</v>
+      </c>
+      <c r="G620">
+        <v>1</v>
+      </c>
+      <c r="H620">
+        <v>1</v>
+      </c>
+      <c r="I620">
+        <v>1</v>
+      </c>
+      <c r="J620">
+        <v>10</v>
+      </c>
+      <c r="K620">
+        <v>10</v>
+      </c>
+      <c r="L620">
+        <v>10</v>
+      </c>
+      <c r="M620">
+        <v>-1</v>
+      </c>
+      <c r="N620">
+        <v>0</v>
+      </c>
+      <c r="O620">
+        <v>0</v>
+      </c>
+      <c r="P620">
+        <v>0</v>
+      </c>
+      <c r="Q620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A621">
+        <f t="shared" ref="A621:A627" si="219">A620+20</f>
+        <v>1090</v>
+      </c>
+      <c r="B621" s="1">
+        <v>340</v>
+      </c>
+      <c r="C621" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D621">
+        <v>0</v>
+      </c>
+      <c r="E621">
+        <v>0</v>
+      </c>
+      <c r="F621">
+        <v>0</v>
+      </c>
+      <c r="G621">
+        <v>1</v>
+      </c>
+      <c r="H621">
+        <v>1</v>
+      </c>
+      <c r="I621">
+        <v>1</v>
+      </c>
+      <c r="J621">
+        <v>10</v>
+      </c>
+      <c r="K621">
+        <v>10</v>
+      </c>
+      <c r="L621">
+        <v>10</v>
+      </c>
+      <c r="M621">
+        <v>-1</v>
+      </c>
+      <c r="N621">
+        <v>0</v>
+      </c>
+      <c r="O621">
+        <v>0</v>
+      </c>
+      <c r="P621">
+        <v>0</v>
+      </c>
+      <c r="Q621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A622">
+        <f t="shared" si="219"/>
+        <v>1110</v>
+      </c>
+      <c r="B622" s="1">
+        <v>340</v>
+      </c>
+      <c r="C622" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D622">
+        <v>0</v>
+      </c>
+      <c r="E622">
+        <v>0</v>
+      </c>
+      <c r="F622">
+        <v>0</v>
+      </c>
+      <c r="G622">
+        <v>1</v>
+      </c>
+      <c r="H622">
+        <v>1</v>
+      </c>
+      <c r="I622">
+        <v>1</v>
+      </c>
+      <c r="J622">
+        <v>10</v>
+      </c>
+      <c r="K622">
+        <v>10</v>
+      </c>
+      <c r="L622">
+        <v>10</v>
+      </c>
+      <c r="M622">
+        <v>-1</v>
+      </c>
+      <c r="N622">
+        <v>0</v>
+      </c>
+      <c r="O622">
+        <v>0</v>
+      </c>
+      <c r="P622">
+        <v>0</v>
+      </c>
+      <c r="Q622">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A623">
+        <f t="shared" si="219"/>
+        <v>1130</v>
+      </c>
+      <c r="B623" s="1">
+        <v>340</v>
+      </c>
+      <c r="C623" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D623">
+        <v>0</v>
+      </c>
+      <c r="E623">
+        <v>0</v>
+      </c>
+      <c r="F623">
+        <v>0</v>
+      </c>
+      <c r="G623">
+        <v>1</v>
+      </c>
+      <c r="H623">
+        <v>1</v>
+      </c>
+      <c r="I623">
+        <v>1</v>
+      </c>
+      <c r="J623">
+        <v>10</v>
+      </c>
+      <c r="K623">
+        <v>10</v>
+      </c>
+      <c r="L623">
+        <v>10</v>
+      </c>
+      <c r="M623">
+        <v>-1</v>
+      </c>
+      <c r="N623">
+        <v>0</v>
+      </c>
+      <c r="O623">
+        <v>0</v>
+      </c>
+      <c r="P623">
+        <v>0</v>
+      </c>
+      <c r="Q623">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A624">
+        <f t="shared" si="219"/>
+        <v>1150</v>
+      </c>
+      <c r="B624" s="1">
+        <v>340</v>
+      </c>
+      <c r="C624" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D624">
+        <v>0</v>
+      </c>
+      <c r="E624">
+        <v>0</v>
+      </c>
+      <c r="F624">
+        <v>0</v>
+      </c>
+      <c r="G624">
+        <v>1</v>
+      </c>
+      <c r="H624">
+        <v>1</v>
+      </c>
+      <c r="I624">
+        <v>1</v>
+      </c>
+      <c r="J624">
+        <v>10</v>
+      </c>
+      <c r="K624">
+        <v>10</v>
+      </c>
+      <c r="L624">
+        <v>10</v>
+      </c>
+      <c r="M624">
+        <v>-1</v>
+      </c>
+      <c r="N624">
+        <v>0</v>
+      </c>
+      <c r="O624">
+        <v>0</v>
+      </c>
+      <c r="P624">
+        <v>0</v>
+      </c>
+      <c r="Q624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A625">
+        <f t="shared" si="219"/>
+        <v>1170</v>
+      </c>
+      <c r="B625" s="1">
+        <v>340</v>
+      </c>
+      <c r="C625" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D625">
+        <v>0</v>
+      </c>
+      <c r="E625">
+        <v>0</v>
+      </c>
+      <c r="F625">
+        <v>0</v>
+      </c>
+      <c r="G625">
+        <v>1</v>
+      </c>
+      <c r="H625">
+        <v>1</v>
+      </c>
+      <c r="I625">
+        <v>1</v>
+      </c>
+      <c r="J625">
+        <v>10</v>
+      </c>
+      <c r="K625">
+        <v>10</v>
+      </c>
+      <c r="L625">
+        <v>10</v>
+      </c>
+      <c r="M625">
+        <v>-1</v>
+      </c>
+      <c r="N625">
+        <v>0</v>
+      </c>
+      <c r="O625">
+        <v>0</v>
+      </c>
+      <c r="P625">
+        <v>0</v>
+      </c>
+      <c r="Q625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A626">
+        <f t="shared" si="219"/>
+        <v>1190</v>
+      </c>
+      <c r="B626" s="1">
+        <v>340</v>
+      </c>
+      <c r="C626" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D626">
+        <v>0</v>
+      </c>
+      <c r="E626">
+        <v>0</v>
+      </c>
+      <c r="F626">
+        <v>0</v>
+      </c>
+      <c r="G626">
+        <v>1</v>
+      </c>
+      <c r="H626">
+        <v>1</v>
+      </c>
+      <c r="I626">
+        <v>1</v>
+      </c>
+      <c r="J626">
+        <v>10</v>
+      </c>
+      <c r="K626">
+        <v>10</v>
+      </c>
+      <c r="L626">
+        <v>10</v>
+      </c>
+      <c r="M626">
+        <v>-1</v>
+      </c>
+      <c r="N626">
+        <v>0</v>
+      </c>
+      <c r="O626">
+        <v>0</v>
+      </c>
+      <c r="P626">
+        <v>0</v>
+      </c>
+      <c r="Q626">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A627">
+        <f t="shared" si="219"/>
+        <v>1210</v>
+      </c>
+      <c r="B627" s="1">
+        <v>340</v>
+      </c>
+      <c r="C627" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D627">
+        <v>0</v>
+      </c>
+      <c r="E627">
+        <v>0</v>
+      </c>
+      <c r="F627">
+        <v>0</v>
+      </c>
+      <c r="G627">
+        <v>1</v>
+      </c>
+      <c r="H627">
+        <v>1</v>
+      </c>
+      <c r="I627">
+        <v>1</v>
+      </c>
+      <c r="J627">
+        <v>10</v>
+      </c>
+      <c r="K627">
+        <v>10</v>
+      </c>
+      <c r="L627">
+        <v>10</v>
+      </c>
+      <c r="M627">
+        <v>-1</v>
+      </c>
+      <c r="N627">
+        <v>0</v>
+      </c>
+      <c r="O627">
+        <v>0</v>
+      </c>
+      <c r="P627">
+        <v>0</v>
+      </c>
+      <c r="Q627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A628" s="1">
+        <v>1630</v>
+      </c>
+      <c r="B628" s="1">
+        <v>340</v>
+      </c>
+      <c r="C628" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D628">
+        <v>0</v>
+      </c>
+      <c r="E628">
+        <v>0</v>
+      </c>
+      <c r="F628">
+        <v>0</v>
+      </c>
+      <c r="G628">
+        <v>1</v>
+      </c>
+      <c r="H628">
+        <v>1</v>
+      </c>
+      <c r="I628">
+        <v>1</v>
+      </c>
+      <c r="J628">
+        <v>10</v>
+      </c>
+      <c r="K628">
+        <v>10</v>
+      </c>
+      <c r="L628">
+        <v>10</v>
+      </c>
+      <c r="M628">
+        <v>-1</v>
+      </c>
+      <c r="N628">
+        <v>0</v>
+      </c>
+      <c r="O628">
+        <v>0</v>
+      </c>
+      <c r="P628">
+        <v>0</v>
+      </c>
+      <c r="Q628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A629" s="1">
+        <v>1624.6</v>
+      </c>
+      <c r="B629" s="1">
+        <v>340</v>
+      </c>
+      <c r="C629" s="1">
+        <v>-3010</v>
+      </c>
+      <c r="D629">
+        <v>0</v>
+      </c>
+      <c r="E629">
+        <v>0</v>
+      </c>
+      <c r="F629">
+        <v>0</v>
+      </c>
+      <c r="G629">
+        <v>1</v>
+      </c>
+      <c r="H629">
+        <v>1</v>
+      </c>
+      <c r="I629">
+        <v>1</v>
+      </c>
+      <c r="J629">
+        <v>10</v>
+      </c>
+      <c r="K629">
+        <v>10</v>
+      </c>
+      <c r="L629">
+        <v>10</v>
+      </c>
+      <c r="M629">
+        <v>-1</v>
+      </c>
+      <c r="N629">
+        <v>0</v>
+      </c>
+      <c r="O629">
+        <v>0</v>
+      </c>
+      <c r="P629">
+        <v>0</v>
+      </c>
+      <c r="Q629">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A630" s="1">
+        <v>1610</v>
+      </c>
+      <c r="B630" s="1">
+        <v>340</v>
+      </c>
+      <c r="C630" s="1">
+        <v>-2995.4</v>
+      </c>
+      <c r="D630">
+        <v>0</v>
+      </c>
+      <c r="E630">
+        <v>0</v>
+      </c>
+      <c r="F630">
+        <v>0</v>
+      </c>
+      <c r="G630">
+        <v>1</v>
+      </c>
+      <c r="H630">
+        <v>1</v>
+      </c>
+      <c r="I630">
+        <v>1</v>
+      </c>
+      <c r="J630">
+        <v>10</v>
+      </c>
+      <c r="K630">
+        <v>10</v>
+      </c>
+      <c r="L630">
+        <v>10</v>
+      </c>
+      <c r="M630">
+        <v>-1</v>
+      </c>
+      <c r="N630">
+        <v>0</v>
+      </c>
+      <c r="O630">
+        <v>0</v>
+      </c>
+      <c r="P630">
+        <v>0</v>
+      </c>
+      <c r="Q630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A631" s="1">
+        <v>1590</v>
+      </c>
+      <c r="B631" s="1">
+        <v>340</v>
+      </c>
+      <c r="C631" s="1">
+        <v>-2990</v>
+      </c>
+      <c r="D631">
+        <v>0</v>
+      </c>
+      <c r="E631">
+        <v>0</v>
+      </c>
+      <c r="F631">
+        <v>0</v>
+      </c>
+      <c r="G631">
+        <v>1</v>
+      </c>
+      <c r="H631">
+        <v>1</v>
+      </c>
+      <c r="I631">
+        <v>1</v>
+      </c>
+      <c r="J631">
+        <v>10</v>
+      </c>
+      <c r="K631">
+        <v>10</v>
+      </c>
+      <c r="L631">
+        <v>10</v>
+      </c>
+      <c r="M631">
+        <v>-1</v>
+      </c>
+      <c r="N631">
+        <v>0</v>
+      </c>
+      <c r="O631">
+        <v>0</v>
+      </c>
+      <c r="P631">
+        <v>0</v>
+      </c>
+      <c r="Q631">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A632" s="1">
+        <v>1570</v>
+      </c>
+      <c r="B632" s="1">
+        <v>340</v>
+      </c>
+      <c r="C632" s="1">
+        <v>-2995.4</v>
+      </c>
+      <c r="D632">
+        <v>0</v>
+      </c>
+      <c r="E632">
+        <v>0</v>
+      </c>
+      <c r="F632">
+        <v>0</v>
+      </c>
+      <c r="G632">
+        <v>1</v>
+      </c>
+      <c r="H632">
+        <v>1</v>
+      </c>
+      <c r="I632">
+        <v>1</v>
+      </c>
+      <c r="J632">
+        <v>10</v>
+      </c>
+      <c r="K632">
+        <v>10</v>
+      </c>
+      <c r="L632">
+        <v>10</v>
+      </c>
+      <c r="M632">
+        <v>-1</v>
+      </c>
+      <c r="N632">
+        <v>0</v>
+      </c>
+      <c r="O632">
+        <v>0</v>
+      </c>
+      <c r="P632">
+        <v>0</v>
+      </c>
+      <c r="Q632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A633" s="1">
+        <v>1555.4</v>
+      </c>
+      <c r="B633" s="1">
+        <v>340</v>
+      </c>
+      <c r="C633" s="1">
+        <v>-3010</v>
+      </c>
+      <c r="D633">
+        <v>0</v>
+      </c>
+      <c r="E633">
+        <v>0</v>
+      </c>
+      <c r="F633">
+        <v>0</v>
+      </c>
+      <c r="G633">
+        <v>1</v>
+      </c>
+      <c r="H633">
+        <v>1</v>
+      </c>
+      <c r="I633">
+        <v>1</v>
+      </c>
+      <c r="J633">
+        <v>10</v>
+      </c>
+      <c r="K633">
+        <v>10</v>
+      </c>
+      <c r="L633">
+        <v>10</v>
+      </c>
+      <c r="M633">
+        <v>-1</v>
+      </c>
+      <c r="N633">
+        <v>0</v>
+      </c>
+      <c r="O633">
+        <v>0</v>
+      </c>
+      <c r="P633">
+        <v>0</v>
+      </c>
+      <c r="Q633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A634" s="1">
+        <v>1550</v>
+      </c>
+      <c r="B634" s="1">
+        <v>340</v>
+      </c>
+      <c r="C634" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D634">
+        <v>0</v>
+      </c>
+      <c r="E634">
+        <v>0</v>
+      </c>
+      <c r="F634">
+        <v>0</v>
+      </c>
+      <c r="G634">
+        <v>1</v>
+      </c>
+      <c r="H634">
+        <v>1</v>
+      </c>
+      <c r="I634">
+        <v>1</v>
+      </c>
+      <c r="J634">
+        <v>10</v>
+      </c>
+      <c r="K634">
+        <v>10</v>
+      </c>
+      <c r="L634">
+        <v>10</v>
+      </c>
+      <c r="M634">
+        <v>-1</v>
+      </c>
+      <c r="N634">
+        <v>0</v>
+      </c>
+      <c r="O634">
+        <v>0</v>
+      </c>
+      <c r="P634">
+        <v>0</v>
+      </c>
+      <c r="Q634">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A635" s="1">
+        <v>1555.4</v>
+      </c>
+      <c r="B635" s="1">
+        <v>340</v>
+      </c>
+      <c r="C635" s="1">
+        <v>-3050</v>
+      </c>
+      <c r="D635">
+        <v>0</v>
+      </c>
+      <c r="E635">
+        <v>0</v>
+      </c>
+      <c r="F635">
+        <v>0</v>
+      </c>
+      <c r="G635">
+        <v>1</v>
+      </c>
+      <c r="H635">
+        <v>1</v>
+      </c>
+      <c r="I635">
+        <v>1</v>
+      </c>
+      <c r="J635">
+        <v>10</v>
+      </c>
+      <c r="K635">
+        <v>10</v>
+      </c>
+      <c r="L635">
+        <v>10</v>
+      </c>
+      <c r="M635">
+        <v>-1</v>
+      </c>
+      <c r="N635">
+        <v>0</v>
+      </c>
+      <c r="O635">
+        <v>0</v>
+      </c>
+      <c r="P635">
+        <v>0</v>
+      </c>
+      <c r="Q635">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A636" s="1">
+        <v>1570</v>
+      </c>
+      <c r="B636" s="1">
+        <v>340</v>
+      </c>
+      <c r="C636" s="1">
+        <v>-3064.6</v>
+      </c>
+      <c r="D636">
+        <v>0</v>
+      </c>
+      <c r="E636">
+        <v>0</v>
+      </c>
+      <c r="F636">
+        <v>0</v>
+      </c>
+      <c r="G636">
+        <v>1</v>
+      </c>
+      <c r="H636">
+        <v>1</v>
+      </c>
+      <c r="I636">
+        <v>1</v>
+      </c>
+      <c r="J636">
+        <v>10</v>
+      </c>
+      <c r="K636">
+        <v>10</v>
+      </c>
+      <c r="L636">
+        <v>10</v>
+      </c>
+      <c r="M636">
+        <v>-1</v>
+      </c>
+      <c r="N636">
+        <v>0</v>
+      </c>
+      <c r="O636">
+        <v>0</v>
+      </c>
+      <c r="P636">
+        <v>0</v>
+      </c>
+      <c r="Q636">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A637" s="1">
+        <v>1590</v>
+      </c>
+      <c r="B637" s="1">
+        <v>340</v>
+      </c>
+      <c r="C637" s="1">
+        <v>-3070</v>
+      </c>
+      <c r="D637">
+        <v>0</v>
+      </c>
+      <c r="E637">
+        <v>0</v>
+      </c>
+      <c r="F637">
+        <v>0</v>
+      </c>
+      <c r="G637">
+        <v>1</v>
+      </c>
+      <c r="H637">
+        <v>1</v>
+      </c>
+      <c r="I637">
+        <v>1</v>
+      </c>
+      <c r="J637">
+        <v>10</v>
+      </c>
+      <c r="K637">
+        <v>10</v>
+      </c>
+      <c r="L637">
+        <v>10</v>
+      </c>
+      <c r="M637">
+        <v>-1</v>
+      </c>
+      <c r="N637">
+        <v>0</v>
+      </c>
+      <c r="O637">
+        <v>0</v>
+      </c>
+      <c r="P637">
+        <v>0</v>
+      </c>
+      <c r="Q637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A638" s="1">
+        <v>1610</v>
+      </c>
+      <c r="B638" s="1">
+        <v>340</v>
+      </c>
+      <c r="C638" s="1">
+        <v>-3064.6</v>
+      </c>
+      <c r="D638">
+        <v>0</v>
+      </c>
+      <c r="E638">
+        <v>0</v>
+      </c>
+      <c r="F638">
+        <v>0</v>
+      </c>
+      <c r="G638">
+        <v>1</v>
+      </c>
+      <c r="H638">
+        <v>1</v>
+      </c>
+      <c r="I638">
+        <v>1</v>
+      </c>
+      <c r="J638">
+        <v>10</v>
+      </c>
+      <c r="K638">
+        <v>10</v>
+      </c>
+      <c r="L638">
+        <v>10</v>
+      </c>
+      <c r="M638">
+        <v>-1</v>
+      </c>
+      <c r="N638">
+        <v>0</v>
+      </c>
+      <c r="O638">
+        <v>0</v>
+      </c>
+      <c r="P638">
+        <v>0</v>
+      </c>
+      <c r="Q638">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A639" s="1">
+        <v>1624.6</v>
+      </c>
+      <c r="B639" s="1">
+        <v>340</v>
+      </c>
+      <c r="C639" s="1">
+        <v>-3050</v>
+      </c>
+      <c r="D639">
+        <v>0</v>
+      </c>
+      <c r="E639">
+        <v>0</v>
+      </c>
+      <c r="F639">
+        <v>0</v>
+      </c>
+      <c r="G639">
+        <v>1</v>
+      </c>
+      <c r="H639">
+        <v>1</v>
+      </c>
+      <c r="I639">
+        <v>1</v>
+      </c>
+      <c r="J639">
+        <v>10</v>
+      </c>
+      <c r="K639">
+        <v>10</v>
+      </c>
+      <c r="L639">
+        <v>10</v>
+      </c>
+      <c r="M639">
+        <v>-1</v>
+      </c>
+      <c r="N639">
+        <v>0</v>
+      </c>
+      <c r="O639">
+        <v>0</v>
+      </c>
+      <c r="P639">
+        <v>0</v>
+      </c>
+      <c r="Q639">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A640" s="1">
+        <v>2670</v>
+      </c>
+      <c r="B640" s="1">
+        <v>340</v>
+      </c>
+      <c r="C640" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D640">
+        <v>0</v>
+      </c>
+      <c r="E640">
+        <v>0</v>
+      </c>
+      <c r="F640">
+        <v>0</v>
+      </c>
+      <c r="G640">
+        <v>1</v>
+      </c>
+      <c r="H640">
+        <v>1</v>
+      </c>
+      <c r="I640">
+        <v>1</v>
+      </c>
+      <c r="J640">
+        <v>10</v>
+      </c>
+      <c r="K640">
+        <v>10</v>
+      </c>
+      <c r="L640">
+        <v>10</v>
+      </c>
+      <c r="M640">
+        <v>-1</v>
+      </c>
+      <c r="N640">
+        <v>0</v>
+      </c>
+      <c r="O640">
+        <v>0</v>
+      </c>
+      <c r="P640">
+        <v>0</v>
+      </c>
+      <c r="Q640">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A641" s="1">
+        <v>2664.6</v>
+      </c>
+      <c r="B641" s="1">
+        <v>340</v>
+      </c>
+      <c r="C641" s="1">
+        <v>-3010</v>
+      </c>
+      <c r="D641">
+        <v>0</v>
+      </c>
+      <c r="E641">
+        <v>0</v>
+      </c>
+      <c r="F641">
+        <v>0</v>
+      </c>
+      <c r="G641">
+        <v>1</v>
+      </c>
+      <c r="H641">
+        <v>1</v>
+      </c>
+      <c r="I641">
+        <v>1</v>
+      </c>
+      <c r="J641">
+        <v>10</v>
+      </c>
+      <c r="K641">
+        <v>10</v>
+      </c>
+      <c r="L641">
+        <v>10</v>
+      </c>
+      <c r="M641">
+        <v>-1</v>
+      </c>
+      <c r="N641">
+        <v>0</v>
+      </c>
+      <c r="O641">
+        <v>0</v>
+      </c>
+      <c r="P641">
+        <v>0</v>
+      </c>
+      <c r="Q641">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A642" s="1">
+        <v>2650</v>
+      </c>
+      <c r="B642" s="1">
+        <v>340</v>
+      </c>
+      <c r="C642" s="1">
+        <v>-2995.4</v>
+      </c>
+      <c r="D642">
+        <v>0</v>
+      </c>
+      <c r="E642">
+        <v>0</v>
+      </c>
+      <c r="F642">
+        <v>0</v>
+      </c>
+      <c r="G642">
+        <v>1</v>
+      </c>
+      <c r="H642">
+        <v>1</v>
+      </c>
+      <c r="I642">
+        <v>1</v>
+      </c>
+      <c r="J642">
+        <v>10</v>
+      </c>
+      <c r="K642">
+        <v>10</v>
+      </c>
+      <c r="L642">
+        <v>10</v>
+      </c>
+      <c r="M642">
+        <v>-1</v>
+      </c>
+      <c r="N642">
+        <v>0</v>
+      </c>
+      <c r="O642">
+        <v>0</v>
+      </c>
+      <c r="P642">
+        <v>0</v>
+      </c>
+      <c r="Q642">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A643" s="1">
+        <v>2630</v>
+      </c>
+      <c r="B643" s="1">
+        <v>340</v>
+      </c>
+      <c r="C643" s="1">
+        <v>-2990</v>
+      </c>
+      <c r="D643">
+        <v>0</v>
+      </c>
+      <c r="E643">
+        <v>0</v>
+      </c>
+      <c r="F643">
+        <v>0</v>
+      </c>
+      <c r="G643">
+        <v>1</v>
+      </c>
+      <c r="H643">
+        <v>1</v>
+      </c>
+      <c r="I643">
+        <v>1</v>
+      </c>
+      <c r="J643">
+        <v>10</v>
+      </c>
+      <c r="K643">
+        <v>10</v>
+      </c>
+      <c r="L643">
+        <v>10</v>
+      </c>
+      <c r="M643">
+        <v>-1</v>
+      </c>
+      <c r="N643">
+        <v>0</v>
+      </c>
+      <c r="O643">
+        <v>0</v>
+      </c>
+      <c r="P643">
+        <v>0</v>
+      </c>
+      <c r="Q643">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A644" s="1">
+        <v>2610</v>
+      </c>
+      <c r="B644" s="1">
+        <v>340</v>
+      </c>
+      <c r="C644" s="1">
+        <v>-2995.4</v>
+      </c>
+      <c r="D644">
+        <v>0</v>
+      </c>
+      <c r="E644">
+        <v>0</v>
+      </c>
+      <c r="F644">
+        <v>0</v>
+      </c>
+      <c r="G644">
+        <v>1</v>
+      </c>
+      <c r="H644">
+        <v>1</v>
+      </c>
+      <c r="I644">
+        <v>1</v>
+      </c>
+      <c r="J644">
+        <v>10</v>
+      </c>
+      <c r="K644">
+        <v>10</v>
+      </c>
+      <c r="L644">
+        <v>10</v>
+      </c>
+      <c r="M644">
+        <v>-1</v>
+      </c>
+      <c r="N644">
+        <v>0</v>
+      </c>
+      <c r="O644">
+        <v>0</v>
+      </c>
+      <c r="P644">
+        <v>0</v>
+      </c>
+      <c r="Q644">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A645" s="1">
+        <v>2595.4</v>
+      </c>
+      <c r="B645" s="1">
+        <v>340</v>
+      </c>
+      <c r="C645" s="1">
+        <v>-3010</v>
+      </c>
+      <c r="D645">
+        <v>0</v>
+      </c>
+      <c r="E645">
+        <v>0</v>
+      </c>
+      <c r="F645">
+        <v>0</v>
+      </c>
+      <c r="G645">
+        <v>1</v>
+      </c>
+      <c r="H645">
+        <v>1</v>
+      </c>
+      <c r="I645">
+        <v>1</v>
+      </c>
+      <c r="J645">
+        <v>10</v>
+      </c>
+      <c r="K645">
+        <v>10</v>
+      </c>
+      <c r="L645">
+        <v>10</v>
+      </c>
+      <c r="M645">
+        <v>-1</v>
+      </c>
+      <c r="N645">
+        <v>0</v>
+      </c>
+      <c r="O645">
+        <v>0</v>
+      </c>
+      <c r="P645">
+        <v>0</v>
+      </c>
+      <c r="Q645">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A646" s="1">
+        <v>2590</v>
+      </c>
+      <c r="B646" s="1">
+        <v>340</v>
+      </c>
+      <c r="C646" s="1">
+        <v>-3030</v>
+      </c>
+      <c r="D646">
+        <v>0</v>
+      </c>
+      <c r="E646">
+        <v>0</v>
+      </c>
+      <c r="F646">
+        <v>0</v>
+      </c>
+      <c r="G646">
+        <v>1</v>
+      </c>
+      <c r="H646">
+        <v>1</v>
+      </c>
+      <c r="I646">
+        <v>1</v>
+      </c>
+      <c r="J646">
+        <v>10</v>
+      </c>
+      <c r="K646">
+        <v>10</v>
+      </c>
+      <c r="L646">
+        <v>10</v>
+      </c>
+      <c r="M646">
+        <v>-1</v>
+      </c>
+      <c r="N646">
+        <v>0</v>
+      </c>
+      <c r="O646">
+        <v>0</v>
+      </c>
+      <c r="P646">
+        <v>0</v>
+      </c>
+      <c r="Q646">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A647" s="1">
+        <v>2595.4</v>
+      </c>
+      <c r="B647" s="1">
+        <v>340</v>
+      </c>
+      <c r="C647" s="1">
+        <v>-3050</v>
+      </c>
+      <c r="D647">
+        <v>0</v>
+      </c>
+      <c r="E647">
+        <v>0</v>
+      </c>
+      <c r="F647">
+        <v>0</v>
+      </c>
+      <c r="G647">
+        <v>1</v>
+      </c>
+      <c r="H647">
+        <v>1</v>
+      </c>
+      <c r="I647">
+        <v>1</v>
+      </c>
+      <c r="J647">
+        <v>10</v>
+      </c>
+      <c r="K647">
+        <v>10</v>
+      </c>
+      <c r="L647">
+        <v>10</v>
+      </c>
+      <c r="M647">
+        <v>-1</v>
+      </c>
+      <c r="N647">
+        <v>0</v>
+      </c>
+      <c r="O647">
+        <v>0</v>
+      </c>
+      <c r="P647">
+        <v>0</v>
+      </c>
+      <c r="Q647">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A648" s="1">
+        <v>2610</v>
+      </c>
+      <c r="B648" s="1">
+        <v>340</v>
+      </c>
+      <c r="C648" s="1">
+        <v>-3064.6</v>
+      </c>
+      <c r="D648">
+        <v>0</v>
+      </c>
+      <c r="E648">
+        <v>0</v>
+      </c>
+      <c r="F648">
+        <v>0</v>
+      </c>
+      <c r="G648">
+        <v>1</v>
+      </c>
+      <c r="H648">
+        <v>1</v>
+      </c>
+      <c r="I648">
+        <v>1</v>
+      </c>
+      <c r="J648">
+        <v>10</v>
+      </c>
+      <c r="K648">
+        <v>10</v>
+      </c>
+      <c r="L648">
+        <v>10</v>
+      </c>
+      <c r="M648">
+        <v>-1</v>
+      </c>
+      <c r="N648">
+        <v>0</v>
+      </c>
+      <c r="O648">
+        <v>0</v>
+      </c>
+      <c r="P648">
+        <v>0</v>
+      </c>
+      <c r="Q648">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A649" s="1">
+        <v>2630</v>
+      </c>
+      <c r="B649" s="1">
+        <v>340</v>
+      </c>
+      <c r="C649" s="1">
+        <v>-3070</v>
+      </c>
+      <c r="D649">
+        <v>0</v>
+      </c>
+      <c r="E649">
+        <v>0</v>
+      </c>
+      <c r="F649">
+        <v>0</v>
+      </c>
+      <c r="G649">
+        <v>1</v>
+      </c>
+      <c r="H649">
+        <v>1</v>
+      </c>
+      <c r="I649">
+        <v>1</v>
+      </c>
+      <c r="J649">
+        <v>10</v>
+      </c>
+      <c r="K649">
+        <v>10</v>
+      </c>
+      <c r="L649">
+        <v>10</v>
+      </c>
+      <c r="M649">
+        <v>-1</v>
+      </c>
+      <c r="N649">
+        <v>0</v>
+      </c>
+      <c r="O649">
+        <v>0</v>
+      </c>
+      <c r="P649">
+        <v>0</v>
+      </c>
+      <c r="Q649">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A650" s="1">
+        <v>2650</v>
+      </c>
+      <c r="B650" s="1">
+        <v>340</v>
+      </c>
+      <c r="C650" s="1">
+        <v>-3064.6</v>
+      </c>
+      <c r="D650">
+        <v>0</v>
+      </c>
+      <c r="E650">
+        <v>0</v>
+      </c>
+      <c r="F650">
+        <v>0</v>
+      </c>
+      <c r="G650">
+        <v>1</v>
+      </c>
+      <c r="H650">
+        <v>1</v>
+      </c>
+      <c r="I650">
+        <v>1</v>
+      </c>
+      <c r="J650">
+        <v>10</v>
+      </c>
+      <c r="K650">
+        <v>10</v>
+      </c>
+      <c r="L650">
+        <v>10</v>
+      </c>
+      <c r="M650">
+        <v>-1</v>
+      </c>
+      <c r="N650">
+        <v>0</v>
+      </c>
+      <c r="O650">
+        <v>0</v>
+      </c>
+      <c r="P650">
+        <v>0</v>
+      </c>
+      <c r="Q650">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A651" s="1">
+        <v>2664.6</v>
+      </c>
+      <c r="B651" s="1">
+        <v>340</v>
+      </c>
+      <c r="C651" s="1">
+        <v>-3050</v>
+      </c>
+      <c r="D651">
+        <v>0</v>
+      </c>
+      <c r="E651">
+        <v>0</v>
+      </c>
+      <c r="F651">
+        <v>0</v>
+      </c>
+      <c r="G651">
+        <v>1</v>
+      </c>
+      <c r="H651">
+        <v>1</v>
+      </c>
+      <c r="I651">
+        <v>1</v>
+      </c>
+      <c r="J651">
+        <v>10</v>
+      </c>
+      <c r="K651">
+        <v>10</v>
+      </c>
+      <c r="L651">
+        <v>10</v>
+      </c>
+      <c r="M651">
+        <v>-1</v>
+      </c>
+      <c r="N651">
+        <v>0</v>
+      </c>
+      <c r="O651">
+        <v>0</v>
+      </c>
+      <c r="P651">
+        <v>0</v>
+      </c>
+      <c r="Q651">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
+++ b/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\Map1\Platform\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Map1\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89FBFF16-4DBA-4721-A255-39E4CF7DA201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46598551-33D0-4CB4-A081-9722F8177001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="2955" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -627,11 +626,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -693,9 +695,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -733,7 +735,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -839,7 +841,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -981,7 +983,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -989,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q651"/>
+  <dimension ref="A1:Q619"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="17" width="5.625" customWidth="1"/>
@@ -3363,7 +3365,7 @@
         <v>300</v>
       </c>
       <c r="C43">
-        <v>-2920</v>
+        <v>-3030</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -3391,7 +3393,7 @@
         <v>20</v>
       </c>
       <c r="L43">
-        <v>420</v>
+        <v>200</v>
       </c>
       <c r="M43">
         <v>-1</v>
@@ -27150,11 +27152,11 @@
       <c r="A471">
         <v>0</v>
       </c>
-      <c r="B471">
-        <v>20</v>
-      </c>
-      <c r="C471">
-        <v>-100</v>
+      <c r="B471" s="2">
+        <v>40</v>
+      </c>
+      <c r="C471" s="2">
+        <v>-420</v>
       </c>
       <c r="D471">
         <v>0</v>
@@ -27175,13 +27177,16 @@
         <v>1</v>
       </c>
       <c r="J471">
-        <v>10</v>
+        <f t="shared" ref="J471:J501" si="215">G471*20</f>
+        <v>20</v>
       </c>
       <c r="K471">
-        <v>10</v>
+        <f t="shared" ref="K471:K501" si="216">H471*20</f>
+        <v>20</v>
       </c>
       <c r="L471">
-        <v>10</v>
+        <f t="shared" ref="L471:L501" si="217">I471*20</f>
+        <v>20</v>
       </c>
       <c r="M471">
         <v>-1</v>
@@ -27200,15 +27205,14 @@
       </c>
     </row>
     <row r="472" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A472">
-        <v>0</v>
-      </c>
-      <c r="B472">
-        <v>20</v>
-      </c>
-      <c r="C472">
-        <f>C471-20</f>
-        <v>-120</v>
+      <c r="A472" s="2">
+        <v>0</v>
+      </c>
+      <c r="B472" s="1">
+        <v>40</v>
+      </c>
+      <c r="C472" s="1">
+        <v>-770</v>
       </c>
       <c r="D472">
         <v>0</v>
@@ -27229,13 +27233,16 @@
         <v>1</v>
       </c>
       <c r="J472">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K472">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L472">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M472">
         <v>-1</v>
@@ -27254,15 +27261,14 @@
       </c>
     </row>
     <row r="473" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A473">
-        <v>0</v>
-      </c>
-      <c r="B473">
-        <v>20</v>
-      </c>
-      <c r="C473">
-        <f t="shared" ref="C473" si="215">C472-20</f>
-        <v>-140</v>
+      <c r="A473" s="2">
+        <v>0</v>
+      </c>
+      <c r="B473" s="1">
+        <v>60</v>
+      </c>
+      <c r="C473" s="1">
+        <v>-840</v>
       </c>
       <c r="D473">
         <v>0</v>
@@ -27283,13 +27289,16 @@
         <v>1</v>
       </c>
       <c r="J473">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K473">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L473">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M473">
         <v>-1</v>
@@ -27309,13 +27318,13 @@
     </row>
     <row r="474" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A474">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B474">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C474">
-        <v>-350</v>
+        <v>-880</v>
       </c>
       <c r="D474">
         <v>0</v>
@@ -27336,13 +27345,16 @@
         <v>1</v>
       </c>
       <c r="J474">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K474">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L474">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M474">
         <v>-1</v>
@@ -27362,13 +27374,13 @@
     </row>
     <row r="475" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A475">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B475">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C475">
-        <v>-360</v>
+        <v>-900</v>
       </c>
       <c r="D475">
         <v>0</v>
@@ -27389,13 +27401,16 @@
         <v>1</v>
       </c>
       <c r="J475">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K475">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L475">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M475">
         <v>-1</v>
@@ -27415,13 +27430,13 @@
     </row>
     <row r="476" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A476">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B476">
-        <v>54.3</v>
+        <v>60</v>
       </c>
       <c r="C476">
-        <v>-370</v>
+        <v>-920</v>
       </c>
       <c r="D476">
         <v>0</v>
@@ -27442,13 +27457,16 @@
         <v>1</v>
       </c>
       <c r="J476">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K476">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L476">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M476">
         <v>-1</v>
@@ -27468,13 +27486,13 @@
     </row>
     <row r="477" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A477">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B477">
-        <v>62.9</v>
+        <v>60</v>
       </c>
       <c r="C477">
-        <v>-380</v>
+        <v>-960</v>
       </c>
       <c r="D477">
         <v>0</v>
@@ -27495,13 +27513,16 @@
         <v>1</v>
       </c>
       <c r="J477">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K477">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L477">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M477">
         <v>-1</v>
@@ -27521,13 +27542,13 @@
     </row>
     <row r="478" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A478">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B478">
-        <v>65.7</v>
+        <v>60</v>
       </c>
       <c r="C478">
-        <v>-390</v>
+        <v>-980</v>
       </c>
       <c r="D478">
         <v>0</v>
@@ -27548,13 +27569,16 @@
         <v>1</v>
       </c>
       <c r="J478">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K478">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L478">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M478">
         <v>-1</v>
@@ -27574,13 +27598,13 @@
     </row>
     <row r="479" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A479">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B479">
-        <v>62.9</v>
+        <v>60</v>
       </c>
       <c r="C479">
-        <v>-400</v>
+        <v>-1000</v>
       </c>
       <c r="D479">
         <v>0</v>
@@ -27601,13 +27625,16 @@
         <v>1</v>
       </c>
       <c r="J479">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K479">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L479">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M479">
         <v>-1</v>
@@ -27627,13 +27654,13 @@
     </row>
     <row r="480" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A480">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="B480">
-        <v>54.3</v>
+        <v>60</v>
       </c>
       <c r="C480">
-        <v>-410</v>
+        <v>-880</v>
       </c>
       <c r="D480">
         <v>0</v>
@@ -27654,13 +27681,16 @@
         <v>1</v>
       </c>
       <c r="J480">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K480">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L480">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M480">
         <v>-1</v>
@@ -27680,13 +27710,13 @@
     </row>
     <row r="481" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A481">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="B481">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C481">
-        <v>-420</v>
+        <v>-900</v>
       </c>
       <c r="D481">
         <v>0</v>
@@ -27707,13 +27737,16 @@
         <v>1</v>
       </c>
       <c r="J481">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K481">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L481">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M481">
         <v>-1</v>
@@ -27733,13 +27766,13 @@
     </row>
     <row r="482" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A482">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="B482">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C482">
-        <v>-500</v>
+        <v>-920</v>
       </c>
       <c r="D482">
         <v>0</v>
@@ -27760,13 +27793,16 @@
         <v>1</v>
       </c>
       <c r="J482">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K482">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L482">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M482">
         <v>-1</v>
@@ -27786,13 +27822,13 @@
     </row>
     <row r="483" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A483">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="B483">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C483">
-        <v>-510</v>
+        <v>-960</v>
       </c>
       <c r="D483">
         <v>0</v>
@@ -27813,13 +27849,16 @@
         <v>1</v>
       </c>
       <c r="J483">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K483">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L483">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M483">
         <v>-1</v>
@@ -27839,13 +27878,13 @@
     </row>
     <row r="484" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A484">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="B484">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C484">
-        <v>-520</v>
+        <v>-980</v>
       </c>
       <c r="D484">
         <v>0</v>
@@ -27866,13 +27905,16 @@
         <v>1</v>
       </c>
       <c r="J484">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K484">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L484">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M484">
         <v>-1</v>
@@ -27892,13 +27934,13 @@
     </row>
     <row r="485" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A485">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="B485">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C485">
-        <v>-530</v>
+        <v>-1000</v>
       </c>
       <c r="D485">
         <v>0</v>
@@ -27919,13 +27961,16 @@
         <v>1</v>
       </c>
       <c r="J485">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K485">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L485">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M485">
         <v>-1</v>
@@ -27945,13 +27990,13 @@
     </row>
     <row r="486" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A486">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B486">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C486">
-        <v>-540</v>
+        <v>-1270</v>
       </c>
       <c r="D486">
         <v>0</v>
@@ -27972,13 +28017,16 @@
         <v>1</v>
       </c>
       <c r="J486">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K486">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L486">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M486">
         <v>-1</v>
@@ -27998,13 +28046,13 @@
     </row>
     <row r="487" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A487">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="B487">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C487">
-        <v>-500</v>
+        <v>-1270</v>
       </c>
       <c r="D487">
         <v>0</v>
@@ -28025,13 +28073,16 @@
         <v>1</v>
       </c>
       <c r="J487">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K487">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L487">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M487">
         <v>-1</v>
@@ -28051,13 +28102,13 @@
     </row>
     <row r="488" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A488">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="B488">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C488">
-        <v>-510</v>
+        <v>-1290</v>
       </c>
       <c r="D488">
         <v>0</v>
@@ -28078,13 +28129,16 @@
         <v>1</v>
       </c>
       <c r="J488">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K488">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L488">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M488">
         <v>-1</v>
@@ -28104,13 +28158,13 @@
     </row>
     <row r="489" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A489">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="B489">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C489">
-        <v>-520</v>
+        <v>-1290</v>
       </c>
       <c r="D489">
         <v>0</v>
@@ -28131,13 +28185,16 @@
         <v>1</v>
       </c>
       <c r="J489">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K489">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L489">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M489">
         <v>-1</v>
@@ -28157,13 +28214,13 @@
     </row>
     <row r="490" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A490">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="B490">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C490">
-        <v>-530</v>
+        <v>-1360</v>
       </c>
       <c r="D490">
         <v>0</v>
@@ -28184,13 +28241,16 @@
         <v>1</v>
       </c>
       <c r="J490">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K490">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L490">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M490">
         <v>-1</v>
@@ -28210,13 +28270,13 @@
     </row>
     <row r="491" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A491">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="B491">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C491">
-        <v>-540</v>
+        <v>-1360</v>
       </c>
       <c r="D491">
         <v>0</v>
@@ -28237,13 +28297,16 @@
         <v>1</v>
       </c>
       <c r="J491">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K491">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L491">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M491">
         <v>-1</v>
@@ -28263,13 +28326,13 @@
     </row>
     <row r="492" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A492">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B492">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C492">
-        <v>-770</v>
+        <v>-1380</v>
       </c>
       <c r="D492">
         <v>0</v>
@@ -28290,13 +28353,16 @@
         <v>1</v>
       </c>
       <c r="J492">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K492">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L492">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M492">
         <v>-1</v>
@@ -28316,13 +28382,13 @@
     </row>
     <row r="493" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A493">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="B493">
-        <v>54.3</v>
+        <v>80</v>
       </c>
       <c r="C493">
-        <v>-777</v>
+        <v>-1380</v>
       </c>
       <c r="D493">
         <v>0</v>
@@ -28343,13 +28409,16 @@
         <v>1</v>
       </c>
       <c r="J493">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K493">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L493">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M493">
         <v>-1</v>
@@ -28369,13 +28438,13 @@
     </row>
     <row r="494" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A494">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B494">
-        <v>65.900000000000006</v>
+        <v>80</v>
       </c>
       <c r="C494">
-        <v>-784</v>
+        <v>-1460</v>
       </c>
       <c r="D494">
         <v>0</v>
@@ -28396,13 +28465,16 @@
         <v>1</v>
       </c>
       <c r="J494">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K494">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L494">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M494">
         <v>-1</v>
@@ -28422,13 +28494,13 @@
     </row>
     <row r="495" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A495">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="B495">
-        <v>74.8</v>
+        <v>80</v>
       </c>
       <c r="C495">
-        <v>-791</v>
+        <v>-1460</v>
       </c>
       <c r="D495">
         <v>0</v>
@@ -28449,13 +28521,16 @@
         <v>1</v>
       </c>
       <c r="J495">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K495">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L495">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M495">
         <v>-1</v>
@@ -28475,13 +28550,13 @@
     </row>
     <row r="496" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A496">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B496">
-        <v>80.900000000000006</v>
+        <v>80</v>
       </c>
       <c r="C496">
-        <v>-798</v>
+        <v>-1480</v>
       </c>
       <c r="D496">
         <v>0</v>
@@ -28502,13 +28577,16 @@
         <v>1</v>
       </c>
       <c r="J496">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K496">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L496">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M496">
         <v>-1</v>
@@ -28528,13 +28606,13 @@
     </row>
     <row r="497" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A497">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="B497">
-        <v>84.3</v>
+        <v>80</v>
       </c>
       <c r="C497">
-        <v>-805</v>
+        <v>-1480</v>
       </c>
       <c r="D497">
         <v>0</v>
@@ -28555,13 +28633,16 @@
         <v>1</v>
       </c>
       <c r="J497">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K497">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L497">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M497">
         <v>-1</v>
@@ -28581,13 +28662,13 @@
     </row>
     <row r="498" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A498">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B498">
-        <v>84.9</v>
+        <v>100</v>
       </c>
       <c r="C498">
-        <v>-812</v>
+        <v>-1580</v>
       </c>
       <c r="D498">
         <v>0</v>
@@ -28608,13 +28689,16 @@
         <v>1</v>
       </c>
       <c r="J498">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K498">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L498">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M498">
         <v>-1</v>
@@ -28634,13 +28718,13 @@
     </row>
     <row r="499" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A499">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="B499">
-        <v>82.8</v>
+        <v>100</v>
       </c>
       <c r="C499">
-        <v>-819</v>
+        <v>-1580</v>
       </c>
       <c r="D499">
         <v>0</v>
@@ -28661,13 +28745,16 @@
         <v>1</v>
       </c>
       <c r="J499">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K499">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L499">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M499">
         <v>-1</v>
@@ -28687,13 +28774,13 @@
     </row>
     <row r="500" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A500">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B500">
-        <v>77.900000000000006</v>
+        <v>100</v>
       </c>
       <c r="C500">
-        <v>-826</v>
+        <v>-1600</v>
       </c>
       <c r="D500">
         <v>0</v>
@@ -28714,13 +28801,16 @@
         <v>1</v>
       </c>
       <c r="J500">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K500">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L500">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M500">
         <v>-1</v>
@@ -28740,13 +28830,13 @@
     </row>
     <row r="501" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A501">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="B501">
-        <v>70.3</v>
+        <v>100</v>
       </c>
       <c r="C501">
-        <v>-833</v>
+        <v>-1600</v>
       </c>
       <c r="D501">
         <v>0</v>
@@ -28767,13 +28857,16 @@
         <v>1</v>
       </c>
       <c r="J501">
-        <v>10</v>
+        <f t="shared" si="215"/>
+        <v>20</v>
       </c>
       <c r="K501">
-        <v>10</v>
+        <f t="shared" si="216"/>
+        <v>20</v>
       </c>
       <c r="L501">
-        <v>10</v>
+        <f t="shared" si="217"/>
+        <v>20</v>
       </c>
       <c r="M501">
         <v>-1</v>
@@ -28796,10 +28889,10 @@
         <v>0</v>
       </c>
       <c r="B502">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="C502">
-        <v>-840</v>
+        <v>-2660</v>
       </c>
       <c r="D502">
         <v>0</v>
@@ -28820,13 +28913,16 @@
         <v>1</v>
       </c>
       <c r="J502">
-        <v>10</v>
+        <f t="shared" ref="J502:J545" si="218">G502*20</f>
+        <v>20</v>
       </c>
       <c r="K502">
-        <v>10</v>
+        <f t="shared" ref="K502:K545" si="219">H502*20</f>
+        <v>20</v>
       </c>
       <c r="L502">
-        <v>10</v>
+        <f t="shared" ref="L502:L545" si="220">I502*20</f>
+        <v>20</v>
       </c>
       <c r="M502">
         <v>-1</v>
@@ -28846,13 +28942,14 @@
     </row>
     <row r="503" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A503">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B503">
-        <v>60</v>
+        <f>B502+20</f>
+        <v>140</v>
       </c>
       <c r="C503">
-        <v>-900</v>
+        <v>-2660</v>
       </c>
       <c r="D503">
         <v>0</v>
@@ -28873,13 +28970,16 @@
         <v>1</v>
       </c>
       <c r="J503">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K503">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L503">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M503">
         <v>-1</v>
@@ -28899,13 +28999,14 @@
     </row>
     <row r="504" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A504">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B504">
-        <v>60</v>
+        <f t="shared" ref="B504:B513" si="221">B503+20</f>
+        <v>160</v>
       </c>
       <c r="C504">
-        <v>-910</v>
+        <v>-2660</v>
       </c>
       <c r="D504">
         <v>0</v>
@@ -28926,13 +29027,16 @@
         <v>1</v>
       </c>
       <c r="J504">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K504">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L504">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M504">
         <v>-1</v>
@@ -28952,13 +29056,14 @@
     </row>
     <row r="505" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A505">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B505">
-        <v>60</v>
+        <f t="shared" si="221"/>
+        <v>180</v>
       </c>
       <c r="C505">
-        <v>-920</v>
+        <v>-2660</v>
       </c>
       <c r="D505">
         <v>0</v>
@@ -28979,13 +29084,16 @@
         <v>1</v>
       </c>
       <c r="J505">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K505">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L505">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M505">
         <v>-1</v>
@@ -29005,13 +29113,14 @@
     </row>
     <row r="506" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A506">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B506">
-        <v>60</v>
+        <f t="shared" si="221"/>
+        <v>200</v>
       </c>
       <c r="C506">
-        <v>-930</v>
+        <v>-2660</v>
       </c>
       <c r="D506">
         <v>0</v>
@@ -29032,13 +29141,16 @@
         <v>1</v>
       </c>
       <c r="J506">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K506">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L506">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M506">
         <v>-1</v>
@@ -29058,13 +29170,14 @@
     </row>
     <row r="507" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A507">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B507">
-        <v>60</v>
+        <f t="shared" si="221"/>
+        <v>220</v>
       </c>
       <c r="C507">
-        <v>-940</v>
+        <v>-2660</v>
       </c>
       <c r="D507">
         <v>0</v>
@@ -29085,13 +29198,16 @@
         <v>1</v>
       </c>
       <c r="J507">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K507">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L507">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M507">
         <v>-1</v>
@@ -29111,13 +29227,14 @@
     </row>
     <row r="508" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A508">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B508">
-        <v>60</v>
+        <f t="shared" si="221"/>
+        <v>240</v>
       </c>
       <c r="C508">
-        <v>-950</v>
+        <v>-2660</v>
       </c>
       <c r="D508">
         <v>0</v>
@@ -29138,13 +29255,16 @@
         <v>1</v>
       </c>
       <c r="J508">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K508">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L508">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M508">
         <v>-1</v>
@@ -29164,13 +29284,14 @@
     </row>
     <row r="509" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A509">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B509">
-        <v>60</v>
+        <f t="shared" si="221"/>
+        <v>260</v>
       </c>
       <c r="C509">
-        <v>-960</v>
+        <v>-2660</v>
       </c>
       <c r="D509">
         <v>0</v>
@@ -29191,13 +29312,16 @@
         <v>1</v>
       </c>
       <c r="J509">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K509">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L509">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M509">
         <v>-1</v>
@@ -29217,13 +29341,14 @@
     </row>
     <row r="510" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A510">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B510">
-        <v>60</v>
+        <f t="shared" si="221"/>
+        <v>280</v>
       </c>
       <c r="C510">
-        <v>-970</v>
+        <v>-2660</v>
       </c>
       <c r="D510">
         <v>0</v>
@@ -29244,13 +29369,16 @@
         <v>1</v>
       </c>
       <c r="J510">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K510">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L510">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M510">
         <v>-1</v>
@@ -29270,13 +29398,14 @@
     </row>
     <row r="511" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A511">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B511">
-        <v>60</v>
+        <f t="shared" si="221"/>
+        <v>300</v>
       </c>
       <c r="C511">
-        <v>-980</v>
+        <v>-2660</v>
       </c>
       <c r="D511">
         <v>0</v>
@@ -29297,13 +29426,16 @@
         <v>1</v>
       </c>
       <c r="J511">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K511">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L511">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M511">
         <v>-1</v>
@@ -29323,13 +29455,14 @@
     </row>
     <row r="512" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A512">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B512">
-        <v>60</v>
+        <f t="shared" si="221"/>
+        <v>320</v>
       </c>
       <c r="C512">
-        <v>-990</v>
+        <v>-2660</v>
       </c>
       <c r="D512">
         <v>0</v>
@@ -29350,13 +29483,16 @@
         <v>1</v>
       </c>
       <c r="J512">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K512">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L512">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M512">
         <v>-1</v>
@@ -29376,13 +29512,14 @@
     </row>
     <row r="513" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A513">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="B513">
-        <v>60</v>
+        <f t="shared" si="221"/>
+        <v>340</v>
       </c>
       <c r="C513">
-        <v>-900</v>
+        <v>-2660</v>
       </c>
       <c r="D513">
         <v>0</v>
@@ -29403,13 +29540,16 @@
         <v>1</v>
       </c>
       <c r="J513">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K513">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L513">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M513">
         <v>-1</v>
@@ -29428,14 +29568,14 @@
       </c>
     </row>
     <row r="514" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A514">
-        <v>-5</v>
+      <c r="A514" s="1">
+        <v>0</v>
       </c>
       <c r="B514">
-        <v>60</v>
-      </c>
-      <c r="C514">
-        <v>-910</v>
+        <v>320</v>
+      </c>
+      <c r="C514" s="1">
+        <v>-2980</v>
       </c>
       <c r="D514">
         <v>0</v>
@@ -29456,13 +29596,16 @@
         <v>1</v>
       </c>
       <c r="J514">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K514">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L514">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M514">
         <v>-1</v>
@@ -29481,14 +29624,14 @@
       </c>
     </row>
     <row r="515" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A515">
-        <v>-5</v>
+      <c r="A515" s="1">
+        <v>25</v>
       </c>
       <c r="B515">
-        <v>60</v>
-      </c>
-      <c r="C515">
-        <v>-920</v>
+        <v>320</v>
+      </c>
+      <c r="C515" s="1">
+        <v>-2986.7</v>
       </c>
       <c r="D515">
         <v>0</v>
@@ -29509,13 +29652,16 @@
         <v>1</v>
       </c>
       <c r="J515">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K515">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L515">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M515">
         <v>-1</v>
@@ -29534,14 +29680,14 @@
       </c>
     </row>
     <row r="516" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A516">
-        <v>-5</v>
+      <c r="A516" s="1">
+        <v>43.3</v>
       </c>
       <c r="B516">
-        <v>60</v>
-      </c>
-      <c r="C516">
-        <v>-930</v>
+        <v>320</v>
+      </c>
+      <c r="C516" s="1">
+        <v>-3005</v>
       </c>
       <c r="D516">
         <v>0</v>
@@ -29562,13 +29708,16 @@
         <v>1</v>
       </c>
       <c r="J516">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K516">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L516">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M516">
         <v>-1</v>
@@ -29587,14 +29736,14 @@
       </c>
     </row>
     <row r="517" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A517">
-        <v>-5</v>
+      <c r="A517" s="1">
+        <v>50</v>
       </c>
       <c r="B517">
-        <v>60</v>
-      </c>
-      <c r="C517">
-        <v>-940</v>
+        <v>320</v>
+      </c>
+      <c r="C517" s="1">
+        <v>-3030</v>
       </c>
       <c r="D517">
         <v>0</v>
@@ -29615,13 +29764,16 @@
         <v>1</v>
       </c>
       <c r="J517">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K517">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L517">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M517">
         <v>-1</v>
@@ -29640,14 +29792,14 @@
       </c>
     </row>
     <row r="518" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A518">
-        <v>-5</v>
+      <c r="A518" s="1">
+        <v>43.3</v>
       </c>
       <c r="B518">
-        <v>60</v>
-      </c>
-      <c r="C518">
-        <v>-950</v>
+        <v>320</v>
+      </c>
+      <c r="C518" s="1">
+        <v>-3055</v>
       </c>
       <c r="D518">
         <v>0</v>
@@ -29668,13 +29820,16 @@
         <v>1</v>
       </c>
       <c r="J518">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K518">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L518">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M518">
         <v>-1</v>
@@ -29693,14 +29848,14 @@
       </c>
     </row>
     <row r="519" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A519">
-        <v>-5</v>
+      <c r="A519" s="1">
+        <v>25</v>
       </c>
       <c r="B519">
-        <v>60</v>
-      </c>
-      <c r="C519">
-        <v>-960</v>
+        <v>320</v>
+      </c>
+      <c r="C519" s="1">
+        <v>-3073.3</v>
       </c>
       <c r="D519">
         <v>0</v>
@@ -29721,13 +29876,16 @@
         <v>1</v>
       </c>
       <c r="J519">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K519">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L519">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M519">
         <v>-1</v>
@@ -29746,14 +29904,14 @@
       </c>
     </row>
     <row r="520" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A520">
-        <v>-5</v>
+      <c r="A520" s="1">
+        <v>0</v>
       </c>
       <c r="B520">
-        <v>60</v>
-      </c>
-      <c r="C520">
-        <v>-970</v>
+        <v>320</v>
+      </c>
+      <c r="C520" s="1">
+        <v>-3080</v>
       </c>
       <c r="D520">
         <v>0</v>
@@ -29774,13 +29932,16 @@
         <v>1</v>
       </c>
       <c r="J520">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K520">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L520">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M520">
         <v>-1</v>
@@ -29799,14 +29960,14 @@
       </c>
     </row>
     <row r="521" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A521">
-        <v>-5</v>
+      <c r="A521" s="1">
+        <v>-25</v>
       </c>
       <c r="B521">
-        <v>60</v>
-      </c>
-      <c r="C521">
-        <v>-980</v>
+        <v>320</v>
+      </c>
+      <c r="C521" s="1">
+        <v>-3073.3</v>
       </c>
       <c r="D521">
         <v>0</v>
@@ -29827,13 +29988,16 @@
         <v>1</v>
       </c>
       <c r="J521">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K521">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L521">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M521">
         <v>-1</v>
@@ -29852,14 +30016,14 @@
       </c>
     </row>
     <row r="522" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A522">
-        <v>-5</v>
+      <c r="A522" s="1">
+        <v>-43.3</v>
       </c>
       <c r="B522">
-        <v>60</v>
-      </c>
-      <c r="C522">
-        <v>-990</v>
+        <v>320</v>
+      </c>
+      <c r="C522" s="1">
+        <v>-3055</v>
       </c>
       <c r="D522">
         <v>0</v>
@@ -29880,13 +30044,16 @@
         <v>1</v>
       </c>
       <c r="J522">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K522">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L522">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M522">
         <v>-1</v>
@@ -29905,14 +30072,14 @@
       </c>
     </row>
     <row r="523" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A523">
-        <v>0</v>
+      <c r="A523" s="1">
+        <v>-50</v>
       </c>
       <c r="B523">
-        <v>80</v>
-      </c>
-      <c r="C523">
-        <v>-1280</v>
+        <v>320</v>
+      </c>
+      <c r="C523" s="1">
+        <v>-3030</v>
       </c>
       <c r="D523">
         <v>0</v>
@@ -29933,13 +30100,16 @@
         <v>1</v>
       </c>
       <c r="J523">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K523">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L523">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M523">
         <v>-1</v>
@@ -29958,14 +30128,14 @@
       </c>
     </row>
     <row r="524" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A524">
-        <v>0</v>
+      <c r="A524" s="1">
+        <v>-43.3</v>
       </c>
       <c r="B524">
-        <v>105</v>
-      </c>
-      <c r="C524">
-        <v>-1295</v>
+        <v>320</v>
+      </c>
+      <c r="C524" s="1">
+        <v>-3005</v>
       </c>
       <c r="D524">
         <v>0</v>
@@ -29986,13 +30156,16 @@
         <v>1</v>
       </c>
       <c r="J524">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K524">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L524">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M524">
         <v>-1</v>
@@ -30011,14 +30184,14 @@
       </c>
     </row>
     <row r="525" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A525">
-        <v>0</v>
+      <c r="A525" s="1">
+        <v>-25</v>
       </c>
       <c r="B525">
-        <v>120</v>
-      </c>
-      <c r="C525">
-        <v>-1310</v>
+        <v>320</v>
+      </c>
+      <c r="C525" s="1">
+        <v>-2986.7</v>
       </c>
       <c r="D525">
         <v>0</v>
@@ -30039,13 +30212,16 @@
         <v>1</v>
       </c>
       <c r="J525">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K525">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L525">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M525">
         <v>-1</v>
@@ -30064,14 +30240,14 @@
       </c>
     </row>
     <row r="526" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A526">
-        <v>0</v>
-      </c>
-      <c r="B526">
-        <v>125</v>
-      </c>
-      <c r="C526">
-        <v>-1325</v>
+      <c r="A526" s="1">
+        <v>460</v>
+      </c>
+      <c r="B526" s="1">
+        <v>320</v>
+      </c>
+      <c r="C526" s="1">
+        <v>-3030</v>
       </c>
       <c r="D526">
         <v>0</v>
@@ -30092,13 +30268,16 @@
         <v>1</v>
       </c>
       <c r="J526">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K526">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L526">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M526">
         <v>-1</v>
@@ -30117,14 +30296,14 @@
       </c>
     </row>
     <row r="527" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A527">
-        <v>0</v>
-      </c>
-      <c r="B527">
-        <v>120</v>
-      </c>
-      <c r="C527">
-        <v>-1340</v>
+      <c r="A527" s="1">
+        <v>500</v>
+      </c>
+      <c r="B527" s="1">
+        <v>365</v>
+      </c>
+      <c r="C527" s="1">
+        <v>-3030</v>
       </c>
       <c r="D527">
         <v>0</v>
@@ -30145,13 +30324,16 @@
         <v>1</v>
       </c>
       <c r="J527">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K527">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L527">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M527">
         <v>-1</v>
@@ -30170,14 +30352,14 @@
       </c>
     </row>
     <row r="528" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A528">
-        <v>0</v>
-      </c>
-      <c r="B528">
-        <v>105</v>
-      </c>
-      <c r="C528">
-        <v>-1355</v>
+      <c r="A528" s="1">
+        <v>530</v>
+      </c>
+      <c r="B528" s="1">
+        <v>340</v>
+      </c>
+      <c r="C528" s="1">
+        <v>-3030</v>
       </c>
       <c r="D528">
         <v>0</v>
@@ -30198,13 +30380,16 @@
         <v>1</v>
       </c>
       <c r="J528">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K528">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L528">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M528">
         <v>-1</v>
@@ -30223,14 +30408,14 @@
       </c>
     </row>
     <row r="529" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A529">
-        <v>0</v>
-      </c>
-      <c r="B529">
-        <v>80</v>
-      </c>
-      <c r="C529">
-        <v>-1370</v>
+      <c r="A529" s="1">
+        <v>970</v>
+      </c>
+      <c r="B529" s="1">
+        <v>340</v>
+      </c>
+      <c r="C529" s="1">
+        <v>-3030</v>
       </c>
       <c r="D529">
         <v>0</v>
@@ -30251,13 +30436,16 @@
         <v>1</v>
       </c>
       <c r="J529">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K529">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L529">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M529">
         <v>-1</v>
@@ -30276,14 +30464,14 @@
       </c>
     </row>
     <row r="530" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A530">
-        <v>0</v>
-      </c>
-      <c r="B530">
-        <v>80</v>
-      </c>
-      <c r="C530">
-        <v>-1380</v>
+      <c r="A530" s="1">
+        <v>990</v>
+      </c>
+      <c r="B530" s="1">
+        <v>340</v>
+      </c>
+      <c r="C530" s="1">
+        <v>-3030</v>
       </c>
       <c r="D530">
         <v>0</v>
@@ -30304,13 +30492,16 @@
         <v>1</v>
       </c>
       <c r="J530">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K530">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L530">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M530">
         <v>-1</v>
@@ -30329,14 +30520,14 @@
       </c>
     </row>
     <row r="531" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A531">
-        <v>0</v>
-      </c>
-      <c r="B531">
-        <v>99.4</v>
-      </c>
-      <c r="C531">
-        <v>-1391</v>
+      <c r="A531" s="1">
+        <v>1010</v>
+      </c>
+      <c r="B531" s="1">
+        <v>340</v>
+      </c>
+      <c r="C531" s="1">
+        <v>-3030</v>
       </c>
       <c r="D531">
         <v>0</v>
@@ -30357,13 +30548,16 @@
         <v>1</v>
       </c>
       <c r="J531">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K531">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L531">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M531">
         <v>-1</v>
@@ -30383,13 +30577,13 @@
     </row>
     <row r="532" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A532">
-        <v>0</v>
-      </c>
-      <c r="B532">
-        <v>114</v>
-      </c>
-      <c r="C532">
-        <v>-1403</v>
+        <v>1030</v>
+      </c>
+      <c r="B532" s="1">
+        <v>340</v>
+      </c>
+      <c r="C532" s="1">
+        <v>-3030</v>
       </c>
       <c r="D532">
         <v>0</v>
@@ -30410,13 +30604,16 @@
         <v>1</v>
       </c>
       <c r="J532">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K532">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L532">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M532">
         <v>-1</v>
@@ -30436,13 +30633,13 @@
     </row>
     <row r="533" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A533">
-        <v>0</v>
-      </c>
-      <c r="B533">
-        <v>122.8</v>
-      </c>
-      <c r="C533">
-        <v>-1414</v>
+        <v>1050</v>
+      </c>
+      <c r="B533" s="1">
+        <v>340</v>
+      </c>
+      <c r="C533" s="1">
+        <v>-3030</v>
       </c>
       <c r="D533">
         <v>0</v>
@@ -30463,13 +30660,16 @@
         <v>1</v>
       </c>
       <c r="J533">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K533">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L533">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M533">
         <v>-1</v>
@@ -30489,13 +30689,14 @@
     </row>
     <row r="534" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A534">
-        <v>0</v>
-      </c>
-      <c r="B534">
-        <v>125</v>
-      </c>
-      <c r="C534">
-        <v>-1425</v>
+        <f>A533+20</f>
+        <v>1070</v>
+      </c>
+      <c r="B534" s="1">
+        <v>340</v>
+      </c>
+      <c r="C534" s="1">
+        <v>-3030</v>
       </c>
       <c r="D534">
         <v>0</v>
@@ -30516,13 +30717,16 @@
         <v>1</v>
       </c>
       <c r="J534">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K534">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L534">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M534">
         <v>-1</v>
@@ -30542,13 +30746,14 @@
     </row>
     <row r="535" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A535">
-        <v>0</v>
-      </c>
-      <c r="B535">
-        <v>122.8</v>
-      </c>
-      <c r="C535">
-        <v>-1436</v>
+        <f t="shared" ref="A535:A541" si="222">A534+20</f>
+        <v>1090</v>
+      </c>
+      <c r="B535" s="1">
+        <v>340</v>
+      </c>
+      <c r="C535" s="1">
+        <v>-3030</v>
       </c>
       <c r="D535">
         <v>0</v>
@@ -30569,13 +30774,16 @@
         <v>1</v>
       </c>
       <c r="J535">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K535">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L535">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M535">
         <v>-1</v>
@@ -30595,13 +30803,14 @@
     </row>
     <row r="536" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A536">
-        <v>0</v>
-      </c>
-      <c r="B536">
-        <v>114</v>
-      </c>
-      <c r="C536">
-        <v>-1448</v>
+        <f t="shared" si="222"/>
+        <v>1110</v>
+      </c>
+      <c r="B536" s="1">
+        <v>340</v>
+      </c>
+      <c r="C536" s="1">
+        <v>-3030</v>
       </c>
       <c r="D536">
         <v>0</v>
@@ -30622,13 +30831,16 @@
         <v>1</v>
       </c>
       <c r="J536">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K536">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L536">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M536">
         <v>-1</v>
@@ -30648,13 +30860,14 @@
     </row>
     <row r="537" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A537">
-        <v>0</v>
-      </c>
-      <c r="B537">
-        <v>99.4</v>
-      </c>
-      <c r="C537">
-        <v>-1459</v>
+        <f t="shared" si="222"/>
+        <v>1130</v>
+      </c>
+      <c r="B537" s="1">
+        <v>340</v>
+      </c>
+      <c r="C537" s="1">
+        <v>-3030</v>
       </c>
       <c r="D537">
         <v>0</v>
@@ -30675,13 +30888,16 @@
         <v>1</v>
       </c>
       <c r="J537">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K537">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L537">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M537">
         <v>-1</v>
@@ -30701,13 +30917,14 @@
     </row>
     <row r="538" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A538">
-        <v>0</v>
-      </c>
-      <c r="B538">
-        <v>80</v>
-      </c>
-      <c r="C538">
-        <v>-1470</v>
+        <f t="shared" si="222"/>
+        <v>1150</v>
+      </c>
+      <c r="B538" s="1">
+        <v>340</v>
+      </c>
+      <c r="C538" s="1">
+        <v>-3030</v>
       </c>
       <c r="D538">
         <v>0</v>
@@ -30728,13 +30945,16 @@
         <v>1</v>
       </c>
       <c r="J538">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K538">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L538">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M538">
         <v>-1</v>
@@ -30754,13 +30974,14 @@
     </row>
     <row r="539" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A539">
-        <v>0</v>
-      </c>
-      <c r="B539">
-        <v>80</v>
-      </c>
-      <c r="C539">
-        <v>-1500</v>
+        <f t="shared" si="222"/>
+        <v>1170</v>
+      </c>
+      <c r="B539" s="1">
+        <v>340</v>
+      </c>
+      <c r="C539" s="1">
+        <v>-3030</v>
       </c>
       <c r="D539">
         <v>0</v>
@@ -30781,13 +31002,16 @@
         <v>1</v>
       </c>
       <c r="J539">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K539">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L539">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M539">
         <v>-1</v>
@@ -30807,13 +31031,14 @@
     </row>
     <row r="540" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A540">
-        <v>0</v>
-      </c>
-      <c r="B540">
-        <v>94.3</v>
-      </c>
-      <c r="C540">
-        <v>-1507</v>
+        <f t="shared" si="222"/>
+        <v>1190</v>
+      </c>
+      <c r="B540" s="1">
+        <v>340</v>
+      </c>
+      <c r="C540" s="1">
+        <v>-3030</v>
       </c>
       <c r="D540">
         <v>0</v>
@@ -30834,13 +31059,16 @@
         <v>1</v>
       </c>
       <c r="J540">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K540">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L540">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M540">
         <v>-1</v>
@@ -30860,13 +31088,14 @@
     </row>
     <row r="541" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A541">
-        <v>0</v>
-      </c>
-      <c r="B541">
-        <v>105.9</v>
-      </c>
-      <c r="C541">
-        <v>-1514</v>
+        <f t="shared" si="222"/>
+        <v>1210</v>
+      </c>
+      <c r="B541" s="1">
+        <v>340</v>
+      </c>
+      <c r="C541" s="1">
+        <v>-3030</v>
       </c>
       <c r="D541">
         <v>0</v>
@@ -30887,13 +31116,16 @@
         <v>1</v>
       </c>
       <c r="J541">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K541">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L541">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M541">
         <v>-1</v>
@@ -30912,14 +31144,14 @@
       </c>
     </row>
     <row r="542" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A542">
-        <v>0</v>
-      </c>
-      <c r="B542">
-        <v>114.8</v>
-      </c>
-      <c r="C542">
-        <v>-1521</v>
+      <c r="A542" s="1">
+        <v>1630</v>
+      </c>
+      <c r="B542" s="1">
+        <v>340</v>
+      </c>
+      <c r="C542" s="1">
+        <v>-3030</v>
       </c>
       <c r="D542">
         <v>0</v>
@@ -30940,13 +31172,16 @@
         <v>1</v>
       </c>
       <c r="J542">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K542">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L542">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M542">
         <v>-1</v>
@@ -30965,14 +31200,14 @@
       </c>
     </row>
     <row r="543" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A543">
-        <v>0</v>
-      </c>
-      <c r="B543">
-        <v>120.9</v>
-      </c>
-      <c r="C543">
-        <v>-1528</v>
+      <c r="A543" s="1">
+        <v>1624.6</v>
+      </c>
+      <c r="B543" s="1">
+        <v>340</v>
+      </c>
+      <c r="C543" s="1">
+        <v>-3010</v>
       </c>
       <c r="D543">
         <v>0</v>
@@ -30993,13 +31228,16 @@
         <v>1</v>
       </c>
       <c r="J543">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K543">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L543">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M543">
         <v>-1</v>
@@ -31018,14 +31256,14 @@
       </c>
     </row>
     <row r="544" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A544">
-        <v>0</v>
-      </c>
-      <c r="B544">
-        <v>124.3</v>
-      </c>
-      <c r="C544">
-        <v>-1535</v>
+      <c r="A544" s="1">
+        <v>1610</v>
+      </c>
+      <c r="B544" s="1">
+        <v>340</v>
+      </c>
+      <c r="C544" s="1">
+        <v>-2995.4</v>
       </c>
       <c r="D544">
         <v>0</v>
@@ -31046,13 +31284,16 @@
         <v>1</v>
       </c>
       <c r="J544">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K544">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L544">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M544">
         <v>-1</v>
@@ -31071,14 +31312,14 @@
       </c>
     </row>
     <row r="545" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A545">
-        <v>0</v>
-      </c>
-      <c r="B545">
-        <v>124.9</v>
-      </c>
-      <c r="C545">
-        <v>-1542</v>
+      <c r="A545" s="1">
+        <v>1590</v>
+      </c>
+      <c r="B545" s="1">
+        <v>340</v>
+      </c>
+      <c r="C545" s="1">
+        <v>-2990</v>
       </c>
       <c r="D545">
         <v>0</v>
@@ -31099,13 +31340,16 @@
         <v>1</v>
       </c>
       <c r="J545">
-        <v>10</v>
+        <f t="shared" si="218"/>
+        <v>20</v>
       </c>
       <c r="K545">
-        <v>10</v>
+        <f t="shared" si="219"/>
+        <v>20</v>
       </c>
       <c r="L545">
-        <v>10</v>
+        <f t="shared" si="220"/>
+        <v>20</v>
       </c>
       <c r="M545">
         <v>-1</v>
@@ -31124,14 +31368,14 @@
       </c>
     </row>
     <row r="546" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A546">
-        <v>0</v>
-      </c>
-      <c r="B546">
-        <v>122.8</v>
-      </c>
-      <c r="C546">
-        <v>-1549</v>
+      <c r="A546" s="1">
+        <v>1570</v>
+      </c>
+      <c r="B546" s="1">
+        <v>340</v>
+      </c>
+      <c r="C546" s="1">
+        <v>-2995.4</v>
       </c>
       <c r="D546">
         <v>0</v>
@@ -31152,13 +31396,16 @@
         <v>1</v>
       </c>
       <c r="J546">
-        <v>10</v>
+        <f t="shared" ref="J546:J565" si="223">G546*20</f>
+        <v>20</v>
       </c>
       <c r="K546">
-        <v>10</v>
+        <f t="shared" ref="K546:K565" si="224">H546*20</f>
+        <v>20</v>
       </c>
       <c r="L546">
-        <v>10</v>
+        <f t="shared" ref="L546:L565" si="225">I546*20</f>
+        <v>20</v>
       </c>
       <c r="M546">
         <v>-1</v>
@@ -31177,14 +31424,14 @@
       </c>
     </row>
     <row r="547" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A547">
-        <v>0</v>
-      </c>
-      <c r="B547">
-        <v>117.9</v>
-      </c>
-      <c r="C547">
-        <v>-1556</v>
+      <c r="A547" s="1">
+        <v>1555.4</v>
+      </c>
+      <c r="B547" s="1">
+        <v>340</v>
+      </c>
+      <c r="C547" s="1">
+        <v>-3010</v>
       </c>
       <c r="D547">
         <v>0</v>
@@ -31205,13 +31452,16 @@
         <v>1</v>
       </c>
       <c r="J547">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K547">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L547">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M547">
         <v>-1</v>
@@ -31230,14 +31480,14 @@
       </c>
     </row>
     <row r="548" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A548">
-        <v>0</v>
-      </c>
-      <c r="B548">
-        <v>110.3</v>
-      </c>
-      <c r="C548">
-        <v>-1563</v>
+      <c r="A548" s="1">
+        <v>1550</v>
+      </c>
+      <c r="B548" s="1">
+        <v>340</v>
+      </c>
+      <c r="C548" s="1">
+        <v>-3030</v>
       </c>
       <c r="D548">
         <v>0</v>
@@ -31258,13 +31508,16 @@
         <v>1</v>
       </c>
       <c r="J548">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K548">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L548">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M548">
         <v>-1</v>
@@ -31283,14 +31536,14 @@
       </c>
     </row>
     <row r="549" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A549">
-        <v>0</v>
-      </c>
-      <c r="B549">
-        <v>100</v>
-      </c>
-      <c r="C549">
-        <v>-1570</v>
+      <c r="A549" s="1">
+        <v>1555.4</v>
+      </c>
+      <c r="B549" s="1">
+        <v>340</v>
+      </c>
+      <c r="C549" s="1">
+        <v>-3050</v>
       </c>
       <c r="D549">
         <v>0</v>
@@ -31311,13 +31564,16 @@
         <v>1</v>
       </c>
       <c r="J549">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K549">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L549">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M549">
         <v>-1</v>
@@ -31336,14 +31592,14 @@
       </c>
     </row>
     <row r="550" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A550">
-        <v>0</v>
-      </c>
-      <c r="B550">
-        <v>100</v>
-      </c>
-      <c r="C550">
-        <v>-1600</v>
+      <c r="A550" s="1">
+        <v>1570</v>
+      </c>
+      <c r="B550" s="1">
+        <v>340</v>
+      </c>
+      <c r="C550" s="1">
+        <v>-3064.6</v>
       </c>
       <c r="D550">
         <v>0</v>
@@ -31364,13 +31620,16 @@
         <v>1</v>
       </c>
       <c r="J550">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K550">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L550">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M550">
         <v>-1</v>
@@ -31389,14 +31648,14 @@
       </c>
     </row>
     <row r="551" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A551">
-        <v>0</v>
-      </c>
-      <c r="B551">
-        <v>118</v>
-      </c>
-      <c r="C551">
-        <v>-1610</v>
+      <c r="A551" s="1">
+        <v>1590</v>
+      </c>
+      <c r="B551" s="1">
+        <v>340</v>
+      </c>
+      <c r="C551" s="1">
+        <v>-3070</v>
       </c>
       <c r="D551">
         <v>0</v>
@@ -31417,13 +31676,16 @@
         <v>1</v>
       </c>
       <c r="J551">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K551">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L551">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M551">
         <v>-1</v>
@@ -31442,14 +31704,14 @@
       </c>
     </row>
     <row r="552" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A552">
-        <v>0</v>
-      </c>
-      <c r="B552">
-        <v>131.1</v>
-      </c>
-      <c r="C552">
-        <v>-1620</v>
+      <c r="A552" s="1">
+        <v>1610</v>
+      </c>
+      <c r="B552" s="1">
+        <v>340</v>
+      </c>
+      <c r="C552" s="1">
+        <v>-3064.6</v>
       </c>
       <c r="D552">
         <v>0</v>
@@ -31470,13 +31732,16 @@
         <v>1</v>
       </c>
       <c r="J552">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K552">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L552">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M552">
         <v>-1</v>
@@ -31495,14 +31760,14 @@
       </c>
     </row>
     <row r="553" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A553">
-        <v>0</v>
-      </c>
-      <c r="B553">
-        <v>139</v>
-      </c>
-      <c r="C553">
-        <v>-1630</v>
+      <c r="A553" s="1">
+        <v>1624.6</v>
+      </c>
+      <c r="B553" s="1">
+        <v>340</v>
+      </c>
+      <c r="C553" s="1">
+        <v>-3050</v>
       </c>
       <c r="D553">
         <v>0</v>
@@ -31523,13 +31788,16 @@
         <v>1</v>
       </c>
       <c r="J553">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K553">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L553">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M553">
         <v>-1</v>
@@ -31548,14 +31816,14 @@
       </c>
     </row>
     <row r="554" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A554">
-        <v>0</v>
-      </c>
-      <c r="B554">
-        <v>142.19999999999999</v>
-      </c>
-      <c r="C554">
-        <v>-1640</v>
+      <c r="A554" s="1">
+        <v>2670</v>
+      </c>
+      <c r="B554" s="1">
+        <v>340</v>
+      </c>
+      <c r="C554" s="1">
+        <v>-3030</v>
       </c>
       <c r="D554">
         <v>0</v>
@@ -31576,13 +31844,16 @@
         <v>1</v>
       </c>
       <c r="J554">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K554">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L554">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M554">
         <v>-1</v>
@@ -31601,14 +31872,14 @@
       </c>
     </row>
     <row r="555" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A555">
-        <v>0</v>
-      </c>
-      <c r="B555">
-        <v>145</v>
-      </c>
-      <c r="C555">
-        <v>-1640</v>
+      <c r="A555" s="1">
+        <v>2664.6</v>
+      </c>
+      <c r="B555" s="1">
+        <v>340</v>
+      </c>
+      <c r="C555" s="1">
+        <v>-3010</v>
       </c>
       <c r="D555">
         <v>0</v>
@@ -31629,13 +31900,16 @@
         <v>1</v>
       </c>
       <c r="J555">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K555">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L555">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M555">
         <v>-1</v>
@@ -31654,14 +31928,14 @@
       </c>
     </row>
     <row r="556" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A556">
-        <v>0</v>
-      </c>
-      <c r="B556">
-        <v>142.19999999999999</v>
-      </c>
-      <c r="C556">
-        <v>-1650</v>
+      <c r="A556" s="1">
+        <v>2650</v>
+      </c>
+      <c r="B556" s="1">
+        <v>340</v>
+      </c>
+      <c r="C556" s="1">
+        <v>-2995.4</v>
       </c>
       <c r="D556">
         <v>0</v>
@@ -31682,13 +31956,16 @@
         <v>1</v>
       </c>
       <c r="J556">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K556">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L556">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M556">
         <v>-1</v>
@@ -31707,14 +31984,14 @@
       </c>
     </row>
     <row r="557" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A557">
-        <v>0</v>
-      </c>
-      <c r="B557">
-        <v>139</v>
-      </c>
-      <c r="C557">
-        <v>-1660</v>
+      <c r="A557" s="1">
+        <v>2630</v>
+      </c>
+      <c r="B557" s="1">
+        <v>340</v>
+      </c>
+      <c r="C557" s="1">
+        <v>-2990</v>
       </c>
       <c r="D557">
         <v>0</v>
@@ -31735,13 +32012,16 @@
         <v>1</v>
       </c>
       <c r="J557">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K557">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L557">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M557">
         <v>-1</v>
@@ -31760,14 +32040,14 @@
       </c>
     </row>
     <row r="558" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A558">
-        <v>0</v>
-      </c>
-      <c r="B558">
-        <v>131.1</v>
-      </c>
-      <c r="C558">
-        <v>-1670</v>
+      <c r="A558" s="1">
+        <v>2610</v>
+      </c>
+      <c r="B558" s="1">
+        <v>340</v>
+      </c>
+      <c r="C558" s="1">
+        <v>-2995.4</v>
       </c>
       <c r="D558">
         <v>0</v>
@@ -31788,13 +32068,16 @@
         <v>1</v>
       </c>
       <c r="J558">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K558">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L558">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M558">
         <v>-1</v>
@@ -31813,14 +32096,14 @@
       </c>
     </row>
     <row r="559" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A559">
-        <v>0</v>
-      </c>
-      <c r="B559">
-        <v>118</v>
-      </c>
-      <c r="C559">
-        <v>-1675</v>
+      <c r="A559" s="1">
+        <v>2595.4</v>
+      </c>
+      <c r="B559" s="1">
+        <v>340</v>
+      </c>
+      <c r="C559" s="1">
+        <v>-3010</v>
       </c>
       <c r="D559">
         <v>0</v>
@@ -31841,13 +32124,16 @@
         <v>1</v>
       </c>
       <c r="J559">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K559">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L559">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M559">
         <v>-1</v>
@@ -31866,14 +32152,14 @@
       </c>
     </row>
     <row r="560" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A560">
-        <v>0</v>
-      </c>
-      <c r="B560">
-        <v>100</v>
-      </c>
-      <c r="C560">
-        <v>-1680</v>
+      <c r="A560" s="1">
+        <v>2590</v>
+      </c>
+      <c r="B560" s="1">
+        <v>340</v>
+      </c>
+      <c r="C560" s="1">
+        <v>-3030</v>
       </c>
       <c r="D560">
         <v>0</v>
@@ -31894,13 +32180,16 @@
         <v>1</v>
       </c>
       <c r="J560">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K560">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L560">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M560">
         <v>-1</v>
@@ -31919,14 +32208,14 @@
       </c>
     </row>
     <row r="561" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A561">
-        <v>0</v>
-      </c>
-      <c r="B561">
-        <v>100</v>
-      </c>
-      <c r="C561">
-        <v>-2000</v>
+      <c r="A561" s="1">
+        <v>2595.4</v>
+      </c>
+      <c r="B561" s="1">
+        <v>340</v>
+      </c>
+      <c r="C561" s="1">
+        <v>-3050</v>
       </c>
       <c r="D561">
         <v>0</v>
@@ -31947,13 +32236,16 @@
         <v>1</v>
       </c>
       <c r="J561">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K561">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L561">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M561">
         <v>-1</v>
@@ -31972,14 +32264,14 @@
       </c>
     </row>
     <row r="562" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A562">
-        <v>0</v>
-      </c>
-      <c r="B562">
-        <v>100</v>
-      </c>
-      <c r="C562">
-        <v>-2010</v>
+      <c r="A562" s="1">
+        <v>2610</v>
+      </c>
+      <c r="B562" s="1">
+        <v>340</v>
+      </c>
+      <c r="C562" s="1">
+        <v>-3064.6</v>
       </c>
       <c r="D562">
         <v>0</v>
@@ -32000,13 +32292,16 @@
         <v>1</v>
       </c>
       <c r="J562">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K562">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L562">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M562">
         <v>-1</v>
@@ -32025,14 +32320,14 @@
       </c>
     </row>
     <row r="563" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A563">
-        <v>0</v>
-      </c>
-      <c r="B563">
-        <v>100</v>
-      </c>
-      <c r="C563">
-        <v>-2020</v>
+      <c r="A563" s="1">
+        <v>2630</v>
+      </c>
+      <c r="B563" s="1">
+        <v>340</v>
+      </c>
+      <c r="C563" s="1">
+        <v>-3070</v>
       </c>
       <c r="D563">
         <v>0</v>
@@ -32053,13 +32348,16 @@
         <v>1</v>
       </c>
       <c r="J563">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K563">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L563">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M563">
         <v>-1</v>
@@ -32078,14 +32376,14 @@
       </c>
     </row>
     <row r="564" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A564">
-        <v>0</v>
-      </c>
-      <c r="B564">
-        <v>100</v>
-      </c>
-      <c r="C564">
-        <v>-2030</v>
+      <c r="A564" s="1">
+        <v>2650</v>
+      </c>
+      <c r="B564" s="1">
+        <v>340</v>
+      </c>
+      <c r="C564" s="1">
+        <v>-3064.6</v>
       </c>
       <c r="D564">
         <v>0</v>
@@ -32106,13 +32404,16 @@
         <v>1</v>
       </c>
       <c r="J564">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K564">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L564">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M564">
         <v>-1</v>
@@ -32131,14 +32432,14 @@
       </c>
     </row>
     <row r="565" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A565">
-        <v>0</v>
-      </c>
-      <c r="B565">
-        <v>100</v>
-      </c>
-      <c r="C565">
-        <v>-2040</v>
+      <c r="A565" s="1">
+        <v>2664.6</v>
+      </c>
+      <c r="B565" s="1">
+        <v>340</v>
+      </c>
+      <c r="C565" s="1">
+        <v>-3050</v>
       </c>
       <c r="D565">
         <v>0</v>
@@ -32159,13 +32460,16 @@
         <v>1</v>
       </c>
       <c r="J565">
-        <v>10</v>
+        <f t="shared" si="223"/>
+        <v>20</v>
       </c>
       <c r="K565">
-        <v>10</v>
+        <f t="shared" si="224"/>
+        <v>20</v>
       </c>
       <c r="L565">
-        <v>10</v>
+        <f t="shared" si="225"/>
+        <v>20</v>
       </c>
       <c r="M565">
         <v>-1</v>
@@ -32184,14 +32488,14 @@
       </c>
     </row>
     <row r="566" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A566">
-        <v>0</v>
-      </c>
-      <c r="B566">
-        <v>100</v>
+      <c r="A566" s="1">
+        <v>1700</v>
+      </c>
+      <c r="B566" s="1">
+        <v>340</v>
       </c>
       <c r="C566">
-        <v>-2050</v>
+        <v>-3160</v>
       </c>
       <c r="D566">
         <v>0</v>
@@ -32212,13 +32516,16 @@
         <v>1</v>
       </c>
       <c r="J566">
-        <v>10</v>
+        <f t="shared" ref="J566:J577" si="226">G566*20</f>
+        <v>20</v>
       </c>
       <c r="K566">
-        <v>10</v>
+        <f t="shared" ref="K566:K577" si="227">H566*20</f>
+        <v>20</v>
       </c>
       <c r="L566">
-        <v>10</v>
+        <f t="shared" ref="L566:L577" si="228">I566*20</f>
+        <v>20</v>
       </c>
       <c r="M566">
         <v>-1</v>
@@ -32237,14 +32544,14 @@
       </c>
     </row>
     <row r="567" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A567">
-        <v>0</v>
-      </c>
-      <c r="B567">
-        <v>120</v>
+      <c r="A567" s="1">
+        <v>1720</v>
+      </c>
+      <c r="B567" s="1">
+        <v>340</v>
       </c>
       <c r="C567">
-        <v>-2064</v>
+        <v>-3160</v>
       </c>
       <c r="D567">
         <v>0</v>
@@ -32265,13 +32572,16 @@
         <v>1</v>
       </c>
       <c r="J567">
-        <v>10</v>
+        <f t="shared" si="226"/>
+        <v>20</v>
       </c>
       <c r="K567">
-        <v>10</v>
+        <f t="shared" si="227"/>
+        <v>20</v>
       </c>
       <c r="L567">
-        <v>10</v>
+        <f t="shared" si="228"/>
+        <v>20</v>
       </c>
       <c r="M567">
         <v>-1</v>
@@ -32290,14 +32600,14 @@
       </c>
     </row>
     <row r="568" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A568">
-        <v>0</v>
-      </c>
-      <c r="B568">
-        <v>140</v>
+      <c r="A568" s="1">
+        <v>1740</v>
+      </c>
+      <c r="B568" s="1">
+        <v>340</v>
       </c>
       <c r="C568">
-        <v>-2078</v>
+        <v>-3160</v>
       </c>
       <c r="D568">
         <v>0</v>
@@ -32318,13 +32628,16 @@
         <v>1</v>
       </c>
       <c r="J568">
-        <v>10</v>
+        <f t="shared" si="226"/>
+        <v>20</v>
       </c>
       <c r="K568">
-        <v>10</v>
+        <f t="shared" si="227"/>
+        <v>20</v>
       </c>
       <c r="L568">
-        <v>10</v>
+        <f t="shared" si="228"/>
+        <v>20</v>
       </c>
       <c r="M568">
         <v>-1</v>
@@ -32343,14 +32656,14 @@
       </c>
     </row>
     <row r="569" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A569">
-        <v>0</v>
-      </c>
-      <c r="B569">
-        <v>145</v>
+      <c r="A569" s="1">
+        <v>1800</v>
+      </c>
+      <c r="B569" s="1">
+        <v>340</v>
       </c>
       <c r="C569">
-        <v>-2095</v>
+        <v>-3200</v>
       </c>
       <c r="D569">
         <v>0</v>
@@ -32371,13 +32684,16 @@
         <v>1</v>
       </c>
       <c r="J569">
-        <v>10</v>
+        <f t="shared" si="226"/>
+        <v>20</v>
       </c>
       <c r="K569">
-        <v>10</v>
+        <f t="shared" si="227"/>
+        <v>20</v>
       </c>
       <c r="L569">
-        <v>10</v>
+        <f t="shared" si="228"/>
+        <v>20</v>
       </c>
       <c r="M569">
         <v>-1</v>
@@ -32396,14 +32712,14 @@
       </c>
     </row>
     <row r="570" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A570">
-        <v>0</v>
-      </c>
-      <c r="B570">
-        <v>120</v>
+      <c r="A570" s="1">
+        <v>1820</v>
+      </c>
+      <c r="B570" s="1">
+        <v>340</v>
       </c>
       <c r="C570">
-        <v>-2120</v>
+        <v>-3200</v>
       </c>
       <c r="D570">
         <v>0</v>
@@ -32424,13 +32740,16 @@
         <v>1</v>
       </c>
       <c r="J570">
-        <v>10</v>
+        <f t="shared" si="226"/>
+        <v>20</v>
       </c>
       <c r="K570">
-        <v>10</v>
+        <f t="shared" si="227"/>
+        <v>20</v>
       </c>
       <c r="L570">
-        <v>10</v>
+        <f t="shared" si="228"/>
+        <v>20</v>
       </c>
       <c r="M570">
         <v>-1</v>
@@ -32449,14 +32768,14 @@
       </c>
     </row>
     <row r="571" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A571">
-        <v>0</v>
-      </c>
-      <c r="B571">
-        <v>100</v>
+      <c r="A571" s="1">
+        <v>1840</v>
+      </c>
+      <c r="B571" s="1">
+        <v>340</v>
       </c>
       <c r="C571">
-        <v>-2660</v>
+        <v>-3200</v>
       </c>
       <c r="D571">
         <v>0</v>
@@ -32477,13 +32796,16 @@
         <v>1</v>
       </c>
       <c r="J571">
-        <v>10</v>
+        <f t="shared" si="226"/>
+        <v>20</v>
       </c>
       <c r="K571">
-        <v>10</v>
+        <f t="shared" si="227"/>
+        <v>20</v>
       </c>
       <c r="L571">
-        <v>10</v>
+        <f t="shared" si="228"/>
+        <v>20</v>
       </c>
       <c r="M571">
         <v>-1</v>
@@ -32502,15 +32824,14 @@
       </c>
     </row>
     <row r="572" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A572">
-        <v>0</v>
-      </c>
-      <c r="B572">
-        <f>B571+10</f>
-        <v>110</v>
+      <c r="A572" s="1">
+        <v>1900</v>
+      </c>
+      <c r="B572" s="1">
+        <v>340</v>
       </c>
       <c r="C572">
-        <v>-2660</v>
+        <v>-3160</v>
       </c>
       <c r="D572">
         <v>0</v>
@@ -32531,13 +32852,16 @@
         <v>1</v>
       </c>
       <c r="J572">
-        <v>10</v>
+        <f t="shared" si="226"/>
+        <v>20</v>
       </c>
       <c r="K572">
-        <v>10</v>
+        <f t="shared" si="227"/>
+        <v>20</v>
       </c>
       <c r="L572">
-        <v>10</v>
+        <f t="shared" si="228"/>
+        <v>20</v>
       </c>
       <c r="M572">
         <v>-1</v>
@@ -32556,15 +32880,14 @@
       </c>
     </row>
     <row r="573" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A573">
-        <v>0</v>
-      </c>
-      <c r="B573">
-        <f t="shared" ref="B573:B583" si="216">B572+10</f>
-        <v>120</v>
+      <c r="A573" s="1">
+        <v>1920</v>
+      </c>
+      <c r="B573" s="1">
+        <v>340</v>
       </c>
       <c r="C573">
-        <v>-2660</v>
+        <v>-3160</v>
       </c>
       <c r="D573">
         <v>0</v>
@@ -32585,13 +32908,16 @@
         <v>1</v>
       </c>
       <c r="J573">
-        <v>10</v>
+        <f t="shared" si="226"/>
+        <v>20</v>
       </c>
       <c r="K573">
-        <v>10</v>
+        <f t="shared" si="227"/>
+        <v>20</v>
       </c>
       <c r="L573">
-        <v>10</v>
+        <f t="shared" si="228"/>
+        <v>20</v>
       </c>
       <c r="M573">
         <v>-1</v>
@@ -32610,15 +32936,14 @@
       </c>
     </row>
     <row r="574" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A574">
-        <v>0</v>
-      </c>
-      <c r="B574">
-        <f t="shared" si="216"/>
-        <v>130</v>
+      <c r="A574" s="1">
+        <v>1940</v>
+      </c>
+      <c r="B574" s="1">
+        <v>340</v>
       </c>
       <c r="C574">
-        <v>-2660</v>
+        <v>-3160</v>
       </c>
       <c r="D574">
         <v>0</v>
@@ -32639,13 +32964,16 @@
         <v>1</v>
       </c>
       <c r="J574">
-        <v>10</v>
+        <f t="shared" si="226"/>
+        <v>20</v>
       </c>
       <c r="K574">
-        <v>10</v>
+        <f t="shared" si="227"/>
+        <v>20</v>
       </c>
       <c r="L574">
-        <v>10</v>
+        <f t="shared" si="228"/>
+        <v>20</v>
       </c>
       <c r="M574">
         <v>-1</v>
@@ -32664,15 +32992,14 @@
       </c>
     </row>
     <row r="575" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A575">
-        <v>0</v>
-      </c>
-      <c r="B575">
-        <f t="shared" si="216"/>
-        <v>140</v>
+      <c r="A575" s="1">
+        <v>2000</v>
+      </c>
+      <c r="B575" s="1">
+        <v>340</v>
       </c>
       <c r="C575">
-        <v>-2660</v>
+        <v>-3200</v>
       </c>
       <c r="D575">
         <v>0</v>
@@ -32693,13 +33020,16 @@
         <v>1</v>
       </c>
       <c r="J575">
-        <v>10</v>
+        <f t="shared" si="226"/>
+        <v>20</v>
       </c>
       <c r="K575">
-        <v>10</v>
+        <f t="shared" si="227"/>
+        <v>20</v>
       </c>
       <c r="L575">
-        <v>10</v>
+        <f t="shared" si="228"/>
+        <v>20</v>
       </c>
       <c r="M575">
         <v>-1</v>
@@ -32718,15 +33048,14 @@
       </c>
     </row>
     <row r="576" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A576">
-        <v>0</v>
-      </c>
-      <c r="B576">
-        <f t="shared" si="216"/>
-        <v>150</v>
+      <c r="A576" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B576" s="1">
+        <v>340</v>
       </c>
       <c r="C576">
-        <v>-2660</v>
+        <v>-3200</v>
       </c>
       <c r="D576">
         <v>0</v>
@@ -32747,13 +33076,16 @@
         <v>1</v>
       </c>
       <c r="J576">
-        <v>10</v>
+        <f t="shared" si="226"/>
+        <v>20</v>
       </c>
       <c r="K576">
-        <v>10</v>
+        <f t="shared" si="227"/>
+        <v>20</v>
       </c>
       <c r="L576">
-        <v>10</v>
+        <f t="shared" si="228"/>
+        <v>20</v>
       </c>
       <c r="M576">
         <v>-1</v>
@@ -32772,15 +33104,14 @@
       </c>
     </row>
     <row r="577" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A577">
-        <v>0</v>
-      </c>
-      <c r="B577">
-        <f t="shared" si="216"/>
-        <v>160</v>
+      <c r="A577" s="1">
+        <v>2040</v>
+      </c>
+      <c r="B577" s="1">
+        <v>340</v>
       </c>
       <c r="C577">
-        <v>-2660</v>
+        <v>-3200</v>
       </c>
       <c r="D577">
         <v>0</v>
@@ -32801,13 +33132,16 @@
         <v>1</v>
       </c>
       <c r="J577">
-        <v>10</v>
+        <f t="shared" si="226"/>
+        <v>20</v>
       </c>
       <c r="K577">
-        <v>10</v>
+        <f t="shared" si="227"/>
+        <v>20</v>
       </c>
       <c r="L577">
-        <v>10</v>
+        <f t="shared" si="228"/>
+        <v>20</v>
       </c>
       <c r="M577">
         <v>-1</v>
@@ -32826,15 +33160,14 @@
       </c>
     </row>
     <row r="578" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A578">
-        <v>0</v>
-      </c>
-      <c r="B578">
-        <f t="shared" si="216"/>
-        <v>170</v>
+      <c r="A578" s="1">
+        <v>2100</v>
+      </c>
+      <c r="B578" s="1">
+        <v>340</v>
       </c>
       <c r="C578">
-        <v>-2660</v>
+        <v>-3160</v>
       </c>
       <c r="D578">
         <v>0</v>
@@ -32855,13 +33188,16 @@
         <v>1</v>
       </c>
       <c r="J578">
-        <v>10</v>
+        <f t="shared" ref="J578:J604" si="229">G578*20</f>
+        <v>20</v>
       </c>
       <c r="K578">
-        <v>10</v>
+        <f t="shared" ref="K578:K604" si="230">H578*20</f>
+        <v>20</v>
       </c>
       <c r="L578">
-        <v>10</v>
+        <f t="shared" ref="L578:L604" si="231">I578*20</f>
+        <v>20</v>
       </c>
       <c r="M578">
         <v>-1</v>
@@ -32880,15 +33216,14 @@
       </c>
     </row>
     <row r="579" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A579">
-        <v>0</v>
-      </c>
-      <c r="B579">
-        <f t="shared" si="216"/>
-        <v>180</v>
+      <c r="A579" s="1">
+        <v>2120</v>
+      </c>
+      <c r="B579" s="1">
+        <v>340</v>
       </c>
       <c r="C579">
-        <v>-2660</v>
+        <v>-3160</v>
       </c>
       <c r="D579">
         <v>0</v>
@@ -32909,13 +33244,16 @@
         <v>1</v>
       </c>
       <c r="J579">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K579">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L579">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M579">
         <v>-1</v>
@@ -32934,15 +33272,14 @@
       </c>
     </row>
     <row r="580" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A580">
-        <v>0</v>
-      </c>
-      <c r="B580">
-        <f t="shared" si="216"/>
-        <v>190</v>
+      <c r="A580" s="1">
+        <v>2140</v>
+      </c>
+      <c r="B580" s="1">
+        <v>340</v>
       </c>
       <c r="C580">
-        <v>-2660</v>
+        <v>-3160</v>
       </c>
       <c r="D580">
         <v>0</v>
@@ -32963,13 +33300,16 @@
         <v>1</v>
       </c>
       <c r="J580">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K580">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L580">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M580">
         <v>-1</v>
@@ -32988,15 +33328,14 @@
       </c>
     </row>
     <row r="581" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A581">
-        <v>0</v>
-      </c>
-      <c r="B581">
-        <f t="shared" si="216"/>
-        <v>200</v>
+      <c r="A581" s="1">
+        <v>2200</v>
+      </c>
+      <c r="B581" s="1">
+        <v>340</v>
       </c>
       <c r="C581">
-        <v>-2660</v>
+        <v>-3200</v>
       </c>
       <c r="D581">
         <v>0</v>
@@ -33017,13 +33356,16 @@
         <v>1</v>
       </c>
       <c r="J581">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K581">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L581">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M581">
         <v>-1</v>
@@ -33042,15 +33384,14 @@
       </c>
     </row>
     <row r="582" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A582">
-        <v>0</v>
-      </c>
-      <c r="B582">
-        <f t="shared" si="216"/>
-        <v>210</v>
+      <c r="A582" s="1">
+        <v>2220</v>
+      </c>
+      <c r="B582" s="1">
+        <v>340</v>
       </c>
       <c r="C582">
-        <v>-2660</v>
+        <v>-3200</v>
       </c>
       <c r="D582">
         <v>0</v>
@@ -33071,13 +33412,16 @@
         <v>1</v>
       </c>
       <c r="J582">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K582">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L582">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M582">
         <v>-1</v>
@@ -33096,15 +33440,14 @@
       </c>
     </row>
     <row r="583" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A583">
-        <v>0</v>
-      </c>
-      <c r="B583">
-        <f t="shared" si="216"/>
-        <v>220</v>
+      <c r="A583" s="1">
+        <v>2240</v>
+      </c>
+      <c r="B583" s="1">
+        <v>340</v>
       </c>
       <c r="C583">
-        <v>-2660</v>
+        <v>-3200</v>
       </c>
       <c r="D583">
         <v>0</v>
@@ -33125,13 +33468,16 @@
         <v>1</v>
       </c>
       <c r="J583">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K583">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L583">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M583">
         <v>-1</v>
@@ -33150,15 +33496,14 @@
       </c>
     </row>
     <row r="584" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A584">
-        <v>0</v>
-      </c>
-      <c r="B584">
-        <f>B583+10</f>
-        <v>230</v>
+      <c r="A584" s="1">
+        <v>2300</v>
+      </c>
+      <c r="B584" s="1">
+        <v>340</v>
       </c>
       <c r="C584">
-        <v>-2660</v>
+        <v>-3160</v>
       </c>
       <c r="D584">
         <v>0</v>
@@ -33179,13 +33524,16 @@
         <v>1</v>
       </c>
       <c r="J584">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K584">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L584">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M584">
         <v>-1</v>
@@ -33204,15 +33552,14 @@
       </c>
     </row>
     <row r="585" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A585">
-        <v>0</v>
-      </c>
-      <c r="B585">
-        <f t="shared" ref="B585:B590" si="217">B584+10</f>
-        <v>240</v>
+      <c r="A585" s="1">
+        <v>2320</v>
+      </c>
+      <c r="B585" s="1">
+        <v>340</v>
       </c>
       <c r="C585">
-        <v>-2660</v>
+        <v>-3160</v>
       </c>
       <c r="D585">
         <v>0</v>
@@ -33233,13 +33580,16 @@
         <v>1</v>
       </c>
       <c r="J585">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K585">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L585">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M585">
         <v>-1</v>
@@ -33258,15 +33608,14 @@
       </c>
     </row>
     <row r="586" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A586">
-        <v>0</v>
-      </c>
-      <c r="B586">
-        <f t="shared" si="217"/>
-        <v>250</v>
+      <c r="A586" s="1">
+        <v>2340</v>
+      </c>
+      <c r="B586" s="1">
+        <v>340</v>
       </c>
       <c r="C586">
-        <v>-2660</v>
+        <v>-3160</v>
       </c>
       <c r="D586">
         <v>0</v>
@@ -33287,13 +33636,16 @@
         <v>1</v>
       </c>
       <c r="J586">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K586">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L586">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M586">
         <v>-1</v>
@@ -33312,15 +33664,14 @@
       </c>
     </row>
     <row r="587" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A587">
-        <v>0</v>
-      </c>
-      <c r="B587">
-        <f t="shared" si="217"/>
-        <v>260</v>
+      <c r="A587" s="1">
+        <v>2400</v>
+      </c>
+      <c r="B587" s="1">
+        <v>340</v>
       </c>
       <c r="C587">
-        <v>-2660</v>
+        <v>-3200</v>
       </c>
       <c r="D587">
         <v>0</v>
@@ -33341,13 +33692,16 @@
         <v>1</v>
       </c>
       <c r="J587">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K587">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L587">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M587">
         <v>-1</v>
@@ -33366,15 +33720,14 @@
       </c>
     </row>
     <row r="588" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A588">
-        <v>0</v>
-      </c>
-      <c r="B588">
-        <f t="shared" si="217"/>
-        <v>270</v>
+      <c r="A588" s="1">
+        <v>2420</v>
+      </c>
+      <c r="B588" s="1">
+        <v>340</v>
       </c>
       <c r="C588">
-        <v>-2660</v>
+        <v>-3200</v>
       </c>
       <c r="D588">
         <v>0</v>
@@ -33395,13 +33748,16 @@
         <v>1</v>
       </c>
       <c r="J588">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K588">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L588">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M588">
         <v>-1</v>
@@ -33420,15 +33776,14 @@
       </c>
     </row>
     <row r="589" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A589">
-        <v>0</v>
-      </c>
-      <c r="B589">
-        <f t="shared" si="217"/>
-        <v>280</v>
+      <c r="A589" s="1">
+        <v>2440</v>
+      </c>
+      <c r="B589" s="1">
+        <v>340</v>
       </c>
       <c r="C589">
-        <v>-2660</v>
+        <v>-3200</v>
       </c>
       <c r="D589">
         <v>0</v>
@@ -33449,13 +33804,16 @@
         <v>1</v>
       </c>
       <c r="J589">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K589">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L589">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M589">
         <v>-1</v>
@@ -33474,15 +33832,14 @@
       </c>
     </row>
     <row r="590" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A590">
-        <v>0</v>
-      </c>
-      <c r="B590">
-        <f t="shared" si="217"/>
-        <v>290</v>
+      <c r="A590" s="1">
+        <v>2500</v>
+      </c>
+      <c r="B590" s="1">
+        <v>340</v>
       </c>
       <c r="C590">
-        <v>-2660</v>
+        <v>-3160</v>
       </c>
       <c r="D590">
         <v>0</v>
@@ -33503,13 +33860,16 @@
         <v>1</v>
       </c>
       <c r="J590">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K590">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L590">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M590">
         <v>-1</v>
@@ -33528,15 +33888,14 @@
       </c>
     </row>
     <row r="591" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A591">
-        <v>0</v>
-      </c>
-      <c r="B591">
-        <f>B590+10</f>
-        <v>300</v>
+      <c r="A591" s="1">
+        <v>2520</v>
+      </c>
+      <c r="B591" s="1">
+        <v>340</v>
       </c>
       <c r="C591">
-        <v>-2660</v>
+        <v>-3160</v>
       </c>
       <c r="D591">
         <v>0</v>
@@ -33557,13 +33916,16 @@
         <v>1</v>
       </c>
       <c r="J591">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K591">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L591">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M591">
         <v>-1</v>
@@ -33582,15 +33944,14 @@
       </c>
     </row>
     <row r="592" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A592">
-        <v>0</v>
-      </c>
-      <c r="B592">
-        <f t="shared" ref="B592" si="218">B591+10</f>
-        <v>310</v>
+      <c r="A592" s="1">
+        <v>2540</v>
+      </c>
+      <c r="B592" s="1">
+        <v>340</v>
       </c>
       <c r="C592">
-        <v>-2660</v>
+        <v>-3160</v>
       </c>
       <c r="D592">
         <v>0</v>
@@ -33611,13 +33972,16 @@
         <v>1</v>
       </c>
       <c r="J592">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K592">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L592">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M592">
         <v>-1</v>
@@ -33636,15 +34000,14 @@
       </c>
     </row>
     <row r="593" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A593">
-        <v>0</v>
-      </c>
-      <c r="B593">
-        <f>B592+10</f>
-        <v>320</v>
+      <c r="A593" s="1">
+        <v>1700</v>
+      </c>
+      <c r="B593" s="1">
+        <v>340</v>
       </c>
       <c r="C593">
-        <v>-2660</v>
+        <v>-2900</v>
       </c>
       <c r="D593">
         <v>0</v>
@@ -33665,13 +34028,16 @@
         <v>1</v>
       </c>
       <c r="J593">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K593">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L593">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M593">
         <v>-1</v>
@@ -33690,15 +34056,14 @@
       </c>
     </row>
     <row r="594" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A594">
-        <v>0</v>
-      </c>
-      <c r="B594">
-        <f>B593+10</f>
-        <v>330</v>
+      <c r="A594" s="1">
+        <v>1720</v>
+      </c>
+      <c r="B594" s="1">
+        <v>340</v>
       </c>
       <c r="C594">
-        <v>-2660</v>
+        <v>-2900</v>
       </c>
       <c r="D594">
         <v>0</v>
@@ -33719,13 +34084,16 @@
         <v>1</v>
       </c>
       <c r="J594">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K594">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L594">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M594">
         <v>-1</v>
@@ -33744,15 +34112,14 @@
       </c>
     </row>
     <row r="595" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A595">
-        <v>0</v>
-      </c>
-      <c r="B595">
-        <f>B594+10</f>
+      <c r="A595" s="1">
+        <v>1740</v>
+      </c>
+      <c r="B595" s="1">
         <v>340</v>
       </c>
       <c r="C595">
-        <v>-2660</v>
+        <v>-2900</v>
       </c>
       <c r="D595">
         <v>0</v>
@@ -33773,13 +34140,16 @@
         <v>1</v>
       </c>
       <c r="J595">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K595">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L595">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M595">
         <v>-1</v>
@@ -33799,13 +34169,13 @@
     </row>
     <row r="596" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A596" s="1">
-        <v>0</v>
-      </c>
-      <c r="B596">
-        <v>320</v>
-      </c>
-      <c r="C596" s="1">
-        <v>-2980</v>
+        <v>1800</v>
+      </c>
+      <c r="B596" s="1">
+        <v>340</v>
+      </c>
+      <c r="C596">
+        <v>-2860</v>
       </c>
       <c r="D596">
         <v>0</v>
@@ -33826,13 +34196,16 @@
         <v>1</v>
       </c>
       <c r="J596">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K596">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L596">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M596">
         <v>-1</v>
@@ -33852,13 +34225,13 @@
     </row>
     <row r="597" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A597" s="1">
-        <v>25</v>
-      </c>
-      <c r="B597">
-        <v>320</v>
-      </c>
-      <c r="C597" s="1">
-        <v>-2986.7</v>
+        <v>1820</v>
+      </c>
+      <c r="B597" s="1">
+        <v>340</v>
+      </c>
+      <c r="C597">
+        <v>-2860</v>
       </c>
       <c r="D597">
         <v>0</v>
@@ -33879,13 +34252,16 @@
         <v>1</v>
       </c>
       <c r="J597">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K597">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L597">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M597">
         <v>-1</v>
@@ -33905,13 +34281,13 @@
     </row>
     <row r="598" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A598" s="1">
-        <v>43.3</v>
-      </c>
-      <c r="B598">
-        <v>320</v>
-      </c>
-      <c r="C598" s="1">
-        <v>-3005</v>
+        <v>1840</v>
+      </c>
+      <c r="B598" s="1">
+        <v>340</v>
+      </c>
+      <c r="C598">
+        <v>-2860</v>
       </c>
       <c r="D598">
         <v>0</v>
@@ -33932,13 +34308,16 @@
         <v>1</v>
       </c>
       <c r="J598">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K598">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L598">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M598">
         <v>-1</v>
@@ -33958,13 +34337,13 @@
     </row>
     <row r="599" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A599" s="1">
-        <v>50</v>
-      </c>
-      <c r="B599">
-        <v>320</v>
-      </c>
-      <c r="C599" s="1">
-        <v>-3030</v>
+        <v>1900</v>
+      </c>
+      <c r="B599" s="1">
+        <v>340</v>
+      </c>
+      <c r="C599">
+        <v>-2900</v>
       </c>
       <c r="D599">
         <v>0</v>
@@ -33985,13 +34364,16 @@
         <v>1</v>
       </c>
       <c r="J599">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K599">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L599">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M599">
         <v>-1</v>
@@ -34011,13 +34393,13 @@
     </row>
     <row r="600" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A600" s="1">
-        <v>43.3</v>
-      </c>
-      <c r="B600">
-        <v>320</v>
-      </c>
-      <c r="C600" s="1">
-        <v>-3055</v>
+        <v>1920</v>
+      </c>
+      <c r="B600" s="1">
+        <v>340</v>
+      </c>
+      <c r="C600">
+        <v>-2900</v>
       </c>
       <c r="D600">
         <v>0</v>
@@ -34038,13 +34420,16 @@
         <v>1</v>
       </c>
       <c r="J600">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K600">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L600">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M600">
         <v>-1</v>
@@ -34064,13 +34449,13 @@
     </row>
     <row r="601" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A601" s="1">
-        <v>25</v>
-      </c>
-      <c r="B601">
-        <v>320</v>
-      </c>
-      <c r="C601" s="1">
-        <v>-3073.3</v>
+        <v>1940</v>
+      </c>
+      <c r="B601" s="1">
+        <v>340</v>
+      </c>
+      <c r="C601">
+        <v>-2900</v>
       </c>
       <c r="D601">
         <v>0</v>
@@ -34091,13 +34476,16 @@
         <v>1</v>
       </c>
       <c r="J601">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K601">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L601">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M601">
         <v>-1</v>
@@ -34117,13 +34505,13 @@
     </row>
     <row r="602" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A602" s="1">
-        <v>0</v>
-      </c>
-      <c r="B602">
-        <v>320</v>
-      </c>
-      <c r="C602" s="1">
-        <v>-3080</v>
+        <v>2000</v>
+      </c>
+      <c r="B602" s="1">
+        <v>340</v>
+      </c>
+      <c r="C602">
+        <v>-2860</v>
       </c>
       <c r="D602">
         <v>0</v>
@@ -34144,13 +34532,16 @@
         <v>1</v>
       </c>
       <c r="J602">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K602">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L602">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M602">
         <v>-1</v>
@@ -34170,13 +34561,13 @@
     </row>
     <row r="603" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A603" s="1">
-        <v>-25</v>
-      </c>
-      <c r="B603">
-        <v>320</v>
-      </c>
-      <c r="C603" s="1">
-        <v>-3073.3</v>
+        <v>2020</v>
+      </c>
+      <c r="B603" s="1">
+        <v>340</v>
+      </c>
+      <c r="C603">
+        <v>-2860</v>
       </c>
       <c r="D603">
         <v>0</v>
@@ -34197,13 +34588,16 @@
         <v>1</v>
       </c>
       <c r="J603">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K603">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L603">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M603">
         <v>-1</v>
@@ -34223,13 +34617,13 @@
     </row>
     <row r="604" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A604" s="1">
-        <v>-43.3</v>
-      </c>
-      <c r="B604">
-        <v>320</v>
-      </c>
-      <c r="C604" s="1">
-        <v>-3055</v>
+        <v>2040</v>
+      </c>
+      <c r="B604" s="1">
+        <v>340</v>
+      </c>
+      <c r="C604">
+        <v>-2860</v>
       </c>
       <c r="D604">
         <v>0</v>
@@ -34250,13 +34644,16 @@
         <v>1</v>
       </c>
       <c r="J604">
-        <v>10</v>
+        <f t="shared" si="229"/>
+        <v>20</v>
       </c>
       <c r="K604">
-        <v>10</v>
+        <f t="shared" si="230"/>
+        <v>20</v>
       </c>
       <c r="L604">
-        <v>10</v>
+        <f t="shared" si="231"/>
+        <v>20</v>
       </c>
       <c r="M604">
         <v>-1</v>
@@ -34276,13 +34673,13 @@
     </row>
     <row r="605" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A605" s="1">
-        <v>-50</v>
-      </c>
-      <c r="B605">
-        <v>320</v>
-      </c>
-      <c r="C605" s="1">
-        <v>-3030</v>
+        <v>2100</v>
+      </c>
+      <c r="B605" s="1">
+        <v>340</v>
+      </c>
+      <c r="C605">
+        <v>-2900</v>
       </c>
       <c r="D605">
         <v>0</v>
@@ -34303,13 +34700,16 @@
         <v>1</v>
       </c>
       <c r="J605">
-        <v>10</v>
+        <f t="shared" ref="J605:J619" si="232">G605*20</f>
+        <v>20</v>
       </c>
       <c r="K605">
-        <v>10</v>
+        <f t="shared" ref="K605:K619" si="233">H605*20</f>
+        <v>20</v>
       </c>
       <c r="L605">
-        <v>10</v>
+        <f t="shared" ref="L605:L619" si="234">I605*20</f>
+        <v>20</v>
       </c>
       <c r="M605">
         <v>-1</v>
@@ -34329,13 +34729,13 @@
     </row>
     <row r="606" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A606" s="1">
-        <v>-43.3</v>
-      </c>
-      <c r="B606">
-        <v>320</v>
-      </c>
-      <c r="C606" s="1">
-        <v>-3005</v>
+        <v>2120</v>
+      </c>
+      <c r="B606" s="1">
+        <v>340</v>
+      </c>
+      <c r="C606">
+        <v>-2900</v>
       </c>
       <c r="D606">
         <v>0</v>
@@ -34356,13 +34756,16 @@
         <v>1</v>
       </c>
       <c r="J606">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K606">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L606">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M606">
         <v>-1</v>
@@ -34382,13 +34785,13 @@
     </row>
     <row r="607" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A607" s="1">
-        <v>-25</v>
-      </c>
-      <c r="B607">
-        <v>320</v>
-      </c>
-      <c r="C607" s="1">
-        <v>-2986.7</v>
+        <v>2140</v>
+      </c>
+      <c r="B607" s="1">
+        <v>340</v>
+      </c>
+      <c r="C607">
+        <v>-2900</v>
       </c>
       <c r="D607">
         <v>0</v>
@@ -34409,13 +34812,16 @@
         <v>1</v>
       </c>
       <c r="J607">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K607">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L607">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M607">
         <v>-1</v>
@@ -34435,13 +34841,13 @@
     </row>
     <row r="608" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A608" s="1">
-        <v>460</v>
+        <v>2200</v>
       </c>
       <c r="B608" s="1">
-        <v>320</v>
-      </c>
-      <c r="C608" s="1">
-        <v>-3030</v>
+        <v>340</v>
+      </c>
+      <c r="C608">
+        <v>-2860</v>
       </c>
       <c r="D608">
         <v>0</v>
@@ -34462,13 +34868,16 @@
         <v>1</v>
       </c>
       <c r="J608">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K608">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L608">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M608">
         <v>-1</v>
@@ -34488,13 +34897,13 @@
     </row>
     <row r="609" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A609" s="1">
-        <v>472</v>
+        <v>2220</v>
       </c>
       <c r="B609" s="1">
-        <v>348.8</v>
-      </c>
-      <c r="C609" s="1">
-        <v>-3030</v>
+        <v>340</v>
+      </c>
+      <c r="C609">
+        <v>-2860</v>
       </c>
       <c r="D609">
         <v>0</v>
@@ -34515,13 +34924,16 @@
         <v>1</v>
       </c>
       <c r="J609">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K609">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L609">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M609">
         <v>-1</v>
@@ -34541,13 +34953,13 @@
     </row>
     <row r="610" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A610" s="1">
-        <v>484</v>
+        <v>2240</v>
       </c>
       <c r="B610" s="1">
-        <v>362.1</v>
-      </c>
-      <c r="C610" s="1">
-        <v>-3030</v>
+        <v>340</v>
+      </c>
+      <c r="C610">
+        <v>-2860</v>
       </c>
       <c r="D610">
         <v>0</v>
@@ -34568,13 +34980,16 @@
         <v>1</v>
       </c>
       <c r="J610">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K610">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L610">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M610">
         <v>-1</v>
@@ -34594,13 +35009,13 @@
     </row>
     <row r="611" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A611" s="1">
-        <v>500</v>
+        <v>2300</v>
       </c>
       <c r="B611" s="1">
-        <v>365</v>
-      </c>
-      <c r="C611" s="1">
-        <v>-3030</v>
+        <v>340</v>
+      </c>
+      <c r="C611">
+        <v>-2900</v>
       </c>
       <c r="D611">
         <v>0</v>
@@ -34621,13 +35036,16 @@
         <v>1</v>
       </c>
       <c r="J611">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K611">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L611">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M611">
         <v>-1</v>
@@ -34647,13 +35065,13 @@
     </row>
     <row r="612" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A612" s="1">
-        <v>512</v>
+        <v>2320</v>
       </c>
       <c r="B612" s="1">
-        <v>360.3</v>
-      </c>
-      <c r="C612" s="1">
-        <v>-3030</v>
+        <v>340</v>
+      </c>
+      <c r="C612">
+        <v>-2900</v>
       </c>
       <c r="D612">
         <v>0</v>
@@ -34674,13 +35092,16 @@
         <v>1</v>
       </c>
       <c r="J612">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K612">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L612">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M612">
         <v>-1</v>
@@ -34700,13 +35121,13 @@
     </row>
     <row r="613" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A613" s="1">
-        <v>521</v>
+        <v>2340</v>
       </c>
       <c r="B613" s="1">
-        <v>351.2</v>
-      </c>
-      <c r="C613" s="1">
-        <v>-3030</v>
+        <v>340</v>
+      </c>
+      <c r="C613">
+        <v>-2900</v>
       </c>
       <c r="D613">
         <v>0</v>
@@ -34727,13 +35148,16 @@
         <v>1</v>
       </c>
       <c r="J613">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K613">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L613">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M613">
         <v>-1</v>
@@ -34753,13 +35177,13 @@
     </row>
     <row r="614" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A614" s="1">
-        <v>530</v>
+        <v>2400</v>
       </c>
       <c r="B614" s="1">
         <v>340</v>
       </c>
-      <c r="C614" s="1">
-        <v>-3030</v>
+      <c r="C614">
+        <v>-2860</v>
       </c>
       <c r="D614">
         <v>0</v>
@@ -34780,13 +35204,16 @@
         <v>1</v>
       </c>
       <c r="J614">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K614">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L614">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M614">
         <v>-1</v>
@@ -34806,13 +35233,13 @@
     </row>
     <row r="615" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A615" s="1">
-        <v>970</v>
+        <v>2420</v>
       </c>
       <c r="B615" s="1">
         <v>340</v>
       </c>
-      <c r="C615" s="1">
-        <v>-3030</v>
+      <c r="C615">
+        <v>-2860</v>
       </c>
       <c r="D615">
         <v>0</v>
@@ -34833,13 +35260,16 @@
         <v>1</v>
       </c>
       <c r="J615">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K615">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L615">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M615">
         <v>-1</v>
@@ -34859,13 +35289,13 @@
     </row>
     <row r="616" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A616" s="1">
-        <v>990</v>
+        <v>2440</v>
       </c>
       <c r="B616" s="1">
         <v>340</v>
       </c>
-      <c r="C616" s="1">
-        <v>-3030</v>
+      <c r="C616">
+        <v>-2860</v>
       </c>
       <c r="D616">
         <v>0</v>
@@ -34886,13 +35316,16 @@
         <v>1</v>
       </c>
       <c r="J616">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K616">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L616">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M616">
         <v>-1</v>
@@ -34912,13 +35345,13 @@
     </row>
     <row r="617" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A617" s="1">
-        <v>1010</v>
+        <v>2500</v>
       </c>
       <c r="B617" s="1">
         <v>340</v>
       </c>
-      <c r="C617" s="1">
-        <v>-3030</v>
+      <c r="C617">
+        <v>-2900</v>
       </c>
       <c r="D617">
         <v>0</v>
@@ -34939,13 +35372,16 @@
         <v>1</v>
       </c>
       <c r="J617">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K617">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L617">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M617">
         <v>-1</v>
@@ -34964,14 +35400,14 @@
       </c>
     </row>
     <row r="618" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A618">
-        <v>1030</v>
+      <c r="A618" s="1">
+        <v>2520</v>
       </c>
       <c r="B618" s="1">
         <v>340</v>
       </c>
-      <c r="C618" s="1">
-        <v>-3030</v>
+      <c r="C618">
+        <v>-2900</v>
       </c>
       <c r="D618">
         <v>0</v>
@@ -34992,13 +35428,16 @@
         <v>1</v>
       </c>
       <c r="J618">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K618">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L618">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M618">
         <v>-1</v>
@@ -35017,14 +35456,14 @@
       </c>
     </row>
     <row r="619" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A619">
-        <v>1050</v>
+      <c r="A619" s="1">
+        <v>2540</v>
       </c>
       <c r="B619" s="1">
         <v>340</v>
       </c>
-      <c r="C619" s="1">
-        <v>-3030</v>
+      <c r="C619">
+        <v>-2900</v>
       </c>
       <c r="D619">
         <v>0</v>
@@ -35045,13 +35484,16 @@
         <v>1</v>
       </c>
       <c r="J619">
-        <v>10</v>
+        <f t="shared" si="232"/>
+        <v>20</v>
       </c>
       <c r="K619">
-        <v>10</v>
+        <f t="shared" si="233"/>
+        <v>20</v>
       </c>
       <c r="L619">
-        <v>10</v>
+        <f t="shared" si="234"/>
+        <v>20</v>
       </c>
       <c r="M619">
         <v>-1</v>
@@ -35066,1710 +35508,6 @@
         <v>0</v>
       </c>
       <c r="Q619">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="620" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A620">
-        <f>A619+20</f>
-        <v>1070</v>
-      </c>
-      <c r="B620" s="1">
-        <v>340</v>
-      </c>
-      <c r="C620" s="1">
-        <v>-3030</v>
-      </c>
-      <c r="D620">
-        <v>0</v>
-      </c>
-      <c r="E620">
-        <v>0</v>
-      </c>
-      <c r="F620">
-        <v>0</v>
-      </c>
-      <c r="G620">
-        <v>1</v>
-      </c>
-      <c r="H620">
-        <v>1</v>
-      </c>
-      <c r="I620">
-        <v>1</v>
-      </c>
-      <c r="J620">
-        <v>10</v>
-      </c>
-      <c r="K620">
-        <v>10</v>
-      </c>
-      <c r="L620">
-        <v>10</v>
-      </c>
-      <c r="M620">
-        <v>-1</v>
-      </c>
-      <c r="N620">
-        <v>0</v>
-      </c>
-      <c r="O620">
-        <v>0</v>
-      </c>
-      <c r="P620">
-        <v>0</v>
-      </c>
-      <c r="Q620">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="621" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A621">
-        <f t="shared" ref="A621:A627" si="219">A620+20</f>
-        <v>1090</v>
-      </c>
-      <c r="B621" s="1">
-        <v>340</v>
-      </c>
-      <c r="C621" s="1">
-        <v>-3030</v>
-      </c>
-      <c r="D621">
-        <v>0</v>
-      </c>
-      <c r="E621">
-        <v>0</v>
-      </c>
-      <c r="F621">
-        <v>0</v>
-      </c>
-      <c r="G621">
-        <v>1</v>
-      </c>
-      <c r="H621">
-        <v>1</v>
-      </c>
-      <c r="I621">
-        <v>1</v>
-      </c>
-      <c r="J621">
-        <v>10</v>
-      </c>
-      <c r="K621">
-        <v>10</v>
-      </c>
-      <c r="L621">
-        <v>10</v>
-      </c>
-      <c r="M621">
-        <v>-1</v>
-      </c>
-      <c r="N621">
-        <v>0</v>
-      </c>
-      <c r="O621">
-        <v>0</v>
-      </c>
-      <c r="P621">
-        <v>0</v>
-      </c>
-      <c r="Q621">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="622" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A622">
-        <f t="shared" si="219"/>
-        <v>1110</v>
-      </c>
-      <c r="B622" s="1">
-        <v>340</v>
-      </c>
-      <c r="C622" s="1">
-        <v>-3030</v>
-      </c>
-      <c r="D622">
-        <v>0</v>
-      </c>
-      <c r="E622">
-        <v>0</v>
-      </c>
-      <c r="F622">
-        <v>0</v>
-      </c>
-      <c r="G622">
-        <v>1</v>
-      </c>
-      <c r="H622">
-        <v>1</v>
-      </c>
-      <c r="I622">
-        <v>1</v>
-      </c>
-      <c r="J622">
-        <v>10</v>
-      </c>
-      <c r="K622">
-        <v>10</v>
-      </c>
-      <c r="L622">
-        <v>10</v>
-      </c>
-      <c r="M622">
-        <v>-1</v>
-      </c>
-      <c r="N622">
-        <v>0</v>
-      </c>
-      <c r="O622">
-        <v>0</v>
-      </c>
-      <c r="P622">
-        <v>0</v>
-      </c>
-      <c r="Q622">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="623" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A623">
-        <f t="shared" si="219"/>
-        <v>1130</v>
-      </c>
-      <c r="B623" s="1">
-        <v>340</v>
-      </c>
-      <c r="C623" s="1">
-        <v>-3030</v>
-      </c>
-      <c r="D623">
-        <v>0</v>
-      </c>
-      <c r="E623">
-        <v>0</v>
-      </c>
-      <c r="F623">
-        <v>0</v>
-      </c>
-      <c r="G623">
-        <v>1</v>
-      </c>
-      <c r="H623">
-        <v>1</v>
-      </c>
-      <c r="I623">
-        <v>1</v>
-      </c>
-      <c r="J623">
-        <v>10</v>
-      </c>
-      <c r="K623">
-        <v>10</v>
-      </c>
-      <c r="L623">
-        <v>10</v>
-      </c>
-      <c r="M623">
-        <v>-1</v>
-      </c>
-      <c r="N623">
-        <v>0</v>
-      </c>
-      <c r="O623">
-        <v>0</v>
-      </c>
-      <c r="P623">
-        <v>0</v>
-      </c>
-      <c r="Q623">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="624" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A624">
-        <f t="shared" si="219"/>
-        <v>1150</v>
-      </c>
-      <c r="B624" s="1">
-        <v>340</v>
-      </c>
-      <c r="C624" s="1">
-        <v>-3030</v>
-      </c>
-      <c r="D624">
-        <v>0</v>
-      </c>
-      <c r="E624">
-        <v>0</v>
-      </c>
-      <c r="F624">
-        <v>0</v>
-      </c>
-      <c r="G624">
-        <v>1</v>
-      </c>
-      <c r="H624">
-        <v>1</v>
-      </c>
-      <c r="I624">
-        <v>1</v>
-      </c>
-      <c r="J624">
-        <v>10</v>
-      </c>
-      <c r="K624">
-        <v>10</v>
-      </c>
-      <c r="L624">
-        <v>10</v>
-      </c>
-      <c r="M624">
-        <v>-1</v>
-      </c>
-      <c r="N624">
-        <v>0</v>
-      </c>
-      <c r="O624">
-        <v>0</v>
-      </c>
-      <c r="P624">
-        <v>0</v>
-      </c>
-      <c r="Q624">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="625" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A625">
-        <f t="shared" si="219"/>
-        <v>1170</v>
-      </c>
-      <c r="B625" s="1">
-        <v>340</v>
-      </c>
-      <c r="C625" s="1">
-        <v>-3030</v>
-      </c>
-      <c r="D625">
-        <v>0</v>
-      </c>
-      <c r="E625">
-        <v>0</v>
-      </c>
-      <c r="F625">
-        <v>0</v>
-      </c>
-      <c r="G625">
-        <v>1</v>
-      </c>
-      <c r="H625">
-        <v>1</v>
-      </c>
-      <c r="I625">
-        <v>1</v>
-      </c>
-      <c r="J625">
-        <v>10</v>
-      </c>
-      <c r="K625">
-        <v>10</v>
-      </c>
-      <c r="L625">
-        <v>10</v>
-      </c>
-      <c r="M625">
-        <v>-1</v>
-      </c>
-      <c r="N625">
-        <v>0</v>
-      </c>
-      <c r="O625">
-        <v>0</v>
-      </c>
-      <c r="P625">
-        <v>0</v>
-      </c>
-      <c r="Q625">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="626" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A626">
-        <f t="shared" si="219"/>
-        <v>1190</v>
-      </c>
-      <c r="B626" s="1">
-        <v>340</v>
-      </c>
-      <c r="C626" s="1">
-        <v>-3030</v>
-      </c>
-      <c r="D626">
-        <v>0</v>
-      </c>
-      <c r="E626">
-        <v>0</v>
-      </c>
-      <c r="F626">
-        <v>0</v>
-      </c>
-      <c r="G626">
-        <v>1</v>
-      </c>
-      <c r="H626">
-        <v>1</v>
-      </c>
-      <c r="I626">
-        <v>1</v>
-      </c>
-      <c r="J626">
-        <v>10</v>
-      </c>
-      <c r="K626">
-        <v>10</v>
-      </c>
-      <c r="L626">
-        <v>10</v>
-      </c>
-      <c r="M626">
-        <v>-1</v>
-      </c>
-      <c r="N626">
-        <v>0</v>
-      </c>
-      <c r="O626">
-        <v>0</v>
-      </c>
-      <c r="P626">
-        <v>0</v>
-      </c>
-      <c r="Q626">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="627" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A627">
-        <f t="shared" si="219"/>
-        <v>1210</v>
-      </c>
-      <c r="B627" s="1">
-        <v>340</v>
-      </c>
-      <c r="C627" s="1">
-        <v>-3030</v>
-      </c>
-      <c r="D627">
-        <v>0</v>
-      </c>
-      <c r="E627">
-        <v>0</v>
-      </c>
-      <c r="F627">
-        <v>0</v>
-      </c>
-      <c r="G627">
-        <v>1</v>
-      </c>
-      <c r="H627">
-        <v>1</v>
-      </c>
-      <c r="I627">
-        <v>1</v>
-      </c>
-      <c r="J627">
-        <v>10</v>
-      </c>
-      <c r="K627">
-        <v>10</v>
-      </c>
-      <c r="L627">
-        <v>10</v>
-      </c>
-      <c r="M627">
-        <v>-1</v>
-      </c>
-      <c r="N627">
-        <v>0</v>
-      </c>
-      <c r="O627">
-        <v>0</v>
-      </c>
-      <c r="P627">
-        <v>0</v>
-      </c>
-      <c r="Q627">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="628" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A628" s="1">
-        <v>1630</v>
-      </c>
-      <c r="B628" s="1">
-        <v>340</v>
-      </c>
-      <c r="C628" s="1">
-        <v>-3030</v>
-      </c>
-      <c r="D628">
-        <v>0</v>
-      </c>
-      <c r="E628">
-        <v>0</v>
-      </c>
-      <c r="F628">
-        <v>0</v>
-      </c>
-      <c r="G628">
-        <v>1</v>
-      </c>
-      <c r="H628">
-        <v>1</v>
-      </c>
-      <c r="I628">
-        <v>1</v>
-      </c>
-      <c r="J628">
-        <v>10</v>
-      </c>
-      <c r="K628">
-        <v>10</v>
-      </c>
-      <c r="L628">
-        <v>10</v>
-      </c>
-      <c r="M628">
-        <v>-1</v>
-      </c>
-      <c r="N628">
-        <v>0</v>
-      </c>
-      <c r="O628">
-        <v>0</v>
-      </c>
-      <c r="P628">
-        <v>0</v>
-      </c>
-      <c r="Q628">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="629" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A629" s="1">
-        <v>1624.6</v>
-      </c>
-      <c r="B629" s="1">
-        <v>340</v>
-      </c>
-      <c r="C629" s="1">
-        <v>-3010</v>
-      </c>
-      <c r="D629">
-        <v>0</v>
-      </c>
-      <c r="E629">
-        <v>0</v>
-      </c>
-      <c r="F629">
-        <v>0</v>
-      </c>
-      <c r="G629">
-        <v>1</v>
-      </c>
-      <c r="H629">
-        <v>1</v>
-      </c>
-      <c r="I629">
-        <v>1</v>
-      </c>
-      <c r="J629">
-        <v>10</v>
-      </c>
-      <c r="K629">
-        <v>10</v>
-      </c>
-      <c r="L629">
-        <v>10</v>
-      </c>
-      <c r="M629">
-        <v>-1</v>
-      </c>
-      <c r="N629">
-        <v>0</v>
-      </c>
-      <c r="O629">
-        <v>0</v>
-      </c>
-      <c r="P629">
-        <v>0</v>
-      </c>
-      <c r="Q629">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="630" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A630" s="1">
-        <v>1610</v>
-      </c>
-      <c r="B630" s="1">
-        <v>340</v>
-      </c>
-      <c r="C630" s="1">
-        <v>-2995.4</v>
-      </c>
-      <c r="D630">
-        <v>0</v>
-      </c>
-      <c r="E630">
-        <v>0</v>
-      </c>
-      <c r="F630">
-        <v>0</v>
-      </c>
-      <c r="G630">
-        <v>1</v>
-      </c>
-      <c r="H630">
-        <v>1</v>
-      </c>
-      <c r="I630">
-        <v>1</v>
-      </c>
-      <c r="J630">
-        <v>10</v>
-      </c>
-      <c r="K630">
-        <v>10</v>
-      </c>
-      <c r="L630">
-        <v>10</v>
-      </c>
-      <c r="M630">
-        <v>-1</v>
-      </c>
-      <c r="N630">
-        <v>0</v>
-      </c>
-      <c r="O630">
-        <v>0</v>
-      </c>
-      <c r="P630">
-        <v>0</v>
-      </c>
-      <c r="Q630">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="631" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A631" s="1">
-        <v>1590</v>
-      </c>
-      <c r="B631" s="1">
-        <v>340</v>
-      </c>
-      <c r="C631" s="1">
-        <v>-2990</v>
-      </c>
-      <c r="D631">
-        <v>0</v>
-      </c>
-      <c r="E631">
-        <v>0</v>
-      </c>
-      <c r="F631">
-        <v>0</v>
-      </c>
-      <c r="G631">
-        <v>1</v>
-      </c>
-      <c r="H631">
-        <v>1</v>
-      </c>
-      <c r="I631">
-        <v>1</v>
-      </c>
-      <c r="J631">
-        <v>10</v>
-      </c>
-      <c r="K631">
-        <v>10</v>
-      </c>
-      <c r="L631">
-        <v>10</v>
-      </c>
-      <c r="M631">
-        <v>-1</v>
-      </c>
-      <c r="N631">
-        <v>0</v>
-      </c>
-      <c r="O631">
-        <v>0</v>
-      </c>
-      <c r="P631">
-        <v>0</v>
-      </c>
-      <c r="Q631">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="632" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A632" s="1">
-        <v>1570</v>
-      </c>
-      <c r="B632" s="1">
-        <v>340</v>
-      </c>
-      <c r="C632" s="1">
-        <v>-2995.4</v>
-      </c>
-      <c r="D632">
-        <v>0</v>
-      </c>
-      <c r="E632">
-        <v>0</v>
-      </c>
-      <c r="F632">
-        <v>0</v>
-      </c>
-      <c r="G632">
-        <v>1</v>
-      </c>
-      <c r="H632">
-        <v>1</v>
-      </c>
-      <c r="I632">
-        <v>1</v>
-      </c>
-      <c r="J632">
-        <v>10</v>
-      </c>
-      <c r="K632">
-        <v>10</v>
-      </c>
-      <c r="L632">
-        <v>10</v>
-      </c>
-      <c r="M632">
-        <v>-1</v>
-      </c>
-      <c r="N632">
-        <v>0</v>
-      </c>
-      <c r="O632">
-        <v>0</v>
-      </c>
-      <c r="P632">
-        <v>0</v>
-      </c>
-      <c r="Q632">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="633" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A633" s="1">
-        <v>1555.4</v>
-      </c>
-      <c r="B633" s="1">
-        <v>340</v>
-      </c>
-      <c r="C633" s="1">
-        <v>-3010</v>
-      </c>
-      <c r="D633">
-        <v>0</v>
-      </c>
-      <c r="E633">
-        <v>0</v>
-      </c>
-      <c r="F633">
-        <v>0</v>
-      </c>
-      <c r="G633">
-        <v>1</v>
-      </c>
-      <c r="H633">
-        <v>1</v>
-      </c>
-      <c r="I633">
-        <v>1</v>
-      </c>
-      <c r="J633">
-        <v>10</v>
-      </c>
-      <c r="K633">
-        <v>10</v>
-      </c>
-      <c r="L633">
-        <v>10</v>
-      </c>
-      <c r="M633">
-        <v>-1</v>
-      </c>
-      <c r="N633">
-        <v>0</v>
-      </c>
-      <c r="O633">
-        <v>0</v>
-      </c>
-      <c r="P633">
-        <v>0</v>
-      </c>
-      <c r="Q633">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="634" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A634" s="1">
-        <v>1550</v>
-      </c>
-      <c r="B634" s="1">
-        <v>340</v>
-      </c>
-      <c r="C634" s="1">
-        <v>-3030</v>
-      </c>
-      <c r="D634">
-        <v>0</v>
-      </c>
-      <c r="E634">
-        <v>0</v>
-      </c>
-      <c r="F634">
-        <v>0</v>
-      </c>
-      <c r="G634">
-        <v>1</v>
-      </c>
-      <c r="H634">
-        <v>1</v>
-      </c>
-      <c r="I634">
-        <v>1</v>
-      </c>
-      <c r="J634">
-        <v>10</v>
-      </c>
-      <c r="K634">
-        <v>10</v>
-      </c>
-      <c r="L634">
-        <v>10</v>
-      </c>
-      <c r="M634">
-        <v>-1</v>
-      </c>
-      <c r="N634">
-        <v>0</v>
-      </c>
-      <c r="O634">
-        <v>0</v>
-      </c>
-      <c r="P634">
-        <v>0</v>
-      </c>
-      <c r="Q634">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="635" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A635" s="1">
-        <v>1555.4</v>
-      </c>
-      <c r="B635" s="1">
-        <v>340</v>
-      </c>
-      <c r="C635" s="1">
-        <v>-3050</v>
-      </c>
-      <c r="D635">
-        <v>0</v>
-      </c>
-      <c r="E635">
-        <v>0</v>
-      </c>
-      <c r="F635">
-        <v>0</v>
-      </c>
-      <c r="G635">
-        <v>1</v>
-      </c>
-      <c r="H635">
-        <v>1</v>
-      </c>
-      <c r="I635">
-        <v>1</v>
-      </c>
-      <c r="J635">
-        <v>10</v>
-      </c>
-      <c r="K635">
-        <v>10</v>
-      </c>
-      <c r="L635">
-        <v>10</v>
-      </c>
-      <c r="M635">
-        <v>-1</v>
-      </c>
-      <c r="N635">
-        <v>0</v>
-      </c>
-      <c r="O635">
-        <v>0</v>
-      </c>
-      <c r="P635">
-        <v>0</v>
-      </c>
-      <c r="Q635">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="636" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A636" s="1">
-        <v>1570</v>
-      </c>
-      <c r="B636" s="1">
-        <v>340</v>
-      </c>
-      <c r="C636" s="1">
-        <v>-3064.6</v>
-      </c>
-      <c r="D636">
-        <v>0</v>
-      </c>
-      <c r="E636">
-        <v>0</v>
-      </c>
-      <c r="F636">
-        <v>0</v>
-      </c>
-      <c r="G636">
-        <v>1</v>
-      </c>
-      <c r="H636">
-        <v>1</v>
-      </c>
-      <c r="I636">
-        <v>1</v>
-      </c>
-      <c r="J636">
-        <v>10</v>
-      </c>
-      <c r="K636">
-        <v>10</v>
-      </c>
-      <c r="L636">
-        <v>10</v>
-      </c>
-      <c r="M636">
-        <v>-1</v>
-      </c>
-      <c r="N636">
-        <v>0</v>
-      </c>
-      <c r="O636">
-        <v>0</v>
-      </c>
-      <c r="P636">
-        <v>0</v>
-      </c>
-      <c r="Q636">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="637" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A637" s="1">
-        <v>1590</v>
-      </c>
-      <c r="B637" s="1">
-        <v>340</v>
-      </c>
-      <c r="C637" s="1">
-        <v>-3070</v>
-      </c>
-      <c r="D637">
-        <v>0</v>
-      </c>
-      <c r="E637">
-        <v>0</v>
-      </c>
-      <c r="F637">
-        <v>0</v>
-      </c>
-      <c r="G637">
-        <v>1</v>
-      </c>
-      <c r="H637">
-        <v>1</v>
-      </c>
-      <c r="I637">
-        <v>1</v>
-      </c>
-      <c r="J637">
-        <v>10</v>
-      </c>
-      <c r="K637">
-        <v>10</v>
-      </c>
-      <c r="L637">
-        <v>10</v>
-      </c>
-      <c r="M637">
-        <v>-1</v>
-      </c>
-      <c r="N637">
-        <v>0</v>
-      </c>
-      <c r="O637">
-        <v>0</v>
-      </c>
-      <c r="P637">
-        <v>0</v>
-      </c>
-      <c r="Q637">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="638" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A638" s="1">
-        <v>1610</v>
-      </c>
-      <c r="B638" s="1">
-        <v>340</v>
-      </c>
-      <c r="C638" s="1">
-        <v>-3064.6</v>
-      </c>
-      <c r="D638">
-        <v>0</v>
-      </c>
-      <c r="E638">
-        <v>0</v>
-      </c>
-      <c r="F638">
-        <v>0</v>
-      </c>
-      <c r="G638">
-        <v>1</v>
-      </c>
-      <c r="H638">
-        <v>1</v>
-      </c>
-      <c r="I638">
-        <v>1</v>
-      </c>
-      <c r="J638">
-        <v>10</v>
-      </c>
-      <c r="K638">
-        <v>10</v>
-      </c>
-      <c r="L638">
-        <v>10</v>
-      </c>
-      <c r="M638">
-        <v>-1</v>
-      </c>
-      <c r="N638">
-        <v>0</v>
-      </c>
-      <c r="O638">
-        <v>0</v>
-      </c>
-      <c r="P638">
-        <v>0</v>
-      </c>
-      <c r="Q638">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="639" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A639" s="1">
-        <v>1624.6</v>
-      </c>
-      <c r="B639" s="1">
-        <v>340</v>
-      </c>
-      <c r="C639" s="1">
-        <v>-3050</v>
-      </c>
-      <c r="D639">
-        <v>0</v>
-      </c>
-      <c r="E639">
-        <v>0</v>
-      </c>
-      <c r="F639">
-        <v>0</v>
-      </c>
-      <c r="G639">
-        <v>1</v>
-      </c>
-      <c r="H639">
-        <v>1</v>
-      </c>
-      <c r="I639">
-        <v>1</v>
-      </c>
-      <c r="J639">
-        <v>10</v>
-      </c>
-      <c r="K639">
-        <v>10</v>
-      </c>
-      <c r="L639">
-        <v>10</v>
-      </c>
-      <c r="M639">
-        <v>-1</v>
-      </c>
-      <c r="N639">
-        <v>0</v>
-      </c>
-      <c r="O639">
-        <v>0</v>
-      </c>
-      <c r="P639">
-        <v>0</v>
-      </c>
-      <c r="Q639">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="640" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A640" s="1">
-        <v>2670</v>
-      </c>
-      <c r="B640" s="1">
-        <v>340</v>
-      </c>
-      <c r="C640" s="1">
-        <v>-3030</v>
-      </c>
-      <c r="D640">
-        <v>0</v>
-      </c>
-      <c r="E640">
-        <v>0</v>
-      </c>
-      <c r="F640">
-        <v>0</v>
-      </c>
-      <c r="G640">
-        <v>1</v>
-      </c>
-      <c r="H640">
-        <v>1</v>
-      </c>
-      <c r="I640">
-        <v>1</v>
-      </c>
-      <c r="J640">
-        <v>10</v>
-      </c>
-      <c r="K640">
-        <v>10</v>
-      </c>
-      <c r="L640">
-        <v>10</v>
-      </c>
-      <c r="M640">
-        <v>-1</v>
-      </c>
-      <c r="N640">
-        <v>0</v>
-      </c>
-      <c r="O640">
-        <v>0</v>
-      </c>
-      <c r="P640">
-        <v>0</v>
-      </c>
-      <c r="Q640">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="641" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A641" s="1">
-        <v>2664.6</v>
-      </c>
-      <c r="B641" s="1">
-        <v>340</v>
-      </c>
-      <c r="C641" s="1">
-        <v>-3010</v>
-      </c>
-      <c r="D641">
-        <v>0</v>
-      </c>
-      <c r="E641">
-        <v>0</v>
-      </c>
-      <c r="F641">
-        <v>0</v>
-      </c>
-      <c r="G641">
-        <v>1</v>
-      </c>
-      <c r="H641">
-        <v>1</v>
-      </c>
-      <c r="I641">
-        <v>1</v>
-      </c>
-      <c r="J641">
-        <v>10</v>
-      </c>
-      <c r="K641">
-        <v>10</v>
-      </c>
-      <c r="L641">
-        <v>10</v>
-      </c>
-      <c r="M641">
-        <v>-1</v>
-      </c>
-      <c r="N641">
-        <v>0</v>
-      </c>
-      <c r="O641">
-        <v>0</v>
-      </c>
-      <c r="P641">
-        <v>0</v>
-      </c>
-      <c r="Q641">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="642" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A642" s="1">
-        <v>2650</v>
-      </c>
-      <c r="B642" s="1">
-        <v>340</v>
-      </c>
-      <c r="C642" s="1">
-        <v>-2995.4</v>
-      </c>
-      <c r="D642">
-        <v>0</v>
-      </c>
-      <c r="E642">
-        <v>0</v>
-      </c>
-      <c r="F642">
-        <v>0</v>
-      </c>
-      <c r="G642">
-        <v>1</v>
-      </c>
-      <c r="H642">
-        <v>1</v>
-      </c>
-      <c r="I642">
-        <v>1</v>
-      </c>
-      <c r="J642">
-        <v>10</v>
-      </c>
-      <c r="K642">
-        <v>10</v>
-      </c>
-      <c r="L642">
-        <v>10</v>
-      </c>
-      <c r="M642">
-        <v>-1</v>
-      </c>
-      <c r="N642">
-        <v>0</v>
-      </c>
-      <c r="O642">
-        <v>0</v>
-      </c>
-      <c r="P642">
-        <v>0</v>
-      </c>
-      <c r="Q642">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="643" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A643" s="1">
-        <v>2630</v>
-      </c>
-      <c r="B643" s="1">
-        <v>340</v>
-      </c>
-      <c r="C643" s="1">
-        <v>-2990</v>
-      </c>
-      <c r="D643">
-        <v>0</v>
-      </c>
-      <c r="E643">
-        <v>0</v>
-      </c>
-      <c r="F643">
-        <v>0</v>
-      </c>
-      <c r="G643">
-        <v>1</v>
-      </c>
-      <c r="H643">
-        <v>1</v>
-      </c>
-      <c r="I643">
-        <v>1</v>
-      </c>
-      <c r="J643">
-        <v>10</v>
-      </c>
-      <c r="K643">
-        <v>10</v>
-      </c>
-      <c r="L643">
-        <v>10</v>
-      </c>
-      <c r="M643">
-        <v>-1</v>
-      </c>
-      <c r="N643">
-        <v>0</v>
-      </c>
-      <c r="O643">
-        <v>0</v>
-      </c>
-      <c r="P643">
-        <v>0</v>
-      </c>
-      <c r="Q643">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="644" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A644" s="1">
-        <v>2610</v>
-      </c>
-      <c r="B644" s="1">
-        <v>340</v>
-      </c>
-      <c r="C644" s="1">
-        <v>-2995.4</v>
-      </c>
-      <c r="D644">
-        <v>0</v>
-      </c>
-      <c r="E644">
-        <v>0</v>
-      </c>
-      <c r="F644">
-        <v>0</v>
-      </c>
-      <c r="G644">
-        <v>1</v>
-      </c>
-      <c r="H644">
-        <v>1</v>
-      </c>
-      <c r="I644">
-        <v>1</v>
-      </c>
-      <c r="J644">
-        <v>10</v>
-      </c>
-      <c r="K644">
-        <v>10</v>
-      </c>
-      <c r="L644">
-        <v>10</v>
-      </c>
-      <c r="M644">
-        <v>-1</v>
-      </c>
-      <c r="N644">
-        <v>0</v>
-      </c>
-      <c r="O644">
-        <v>0</v>
-      </c>
-      <c r="P644">
-        <v>0</v>
-      </c>
-      <c r="Q644">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="645" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A645" s="1">
-        <v>2595.4</v>
-      </c>
-      <c r="B645" s="1">
-        <v>340</v>
-      </c>
-      <c r="C645" s="1">
-        <v>-3010</v>
-      </c>
-      <c r="D645">
-        <v>0</v>
-      </c>
-      <c r="E645">
-        <v>0</v>
-      </c>
-      <c r="F645">
-        <v>0</v>
-      </c>
-      <c r="G645">
-        <v>1</v>
-      </c>
-      <c r="H645">
-        <v>1</v>
-      </c>
-      <c r="I645">
-        <v>1</v>
-      </c>
-      <c r="J645">
-        <v>10</v>
-      </c>
-      <c r="K645">
-        <v>10</v>
-      </c>
-      <c r="L645">
-        <v>10</v>
-      </c>
-      <c r="M645">
-        <v>-1</v>
-      </c>
-      <c r="N645">
-        <v>0</v>
-      </c>
-      <c r="O645">
-        <v>0</v>
-      </c>
-      <c r="P645">
-        <v>0</v>
-      </c>
-      <c r="Q645">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="646" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A646" s="1">
-        <v>2590</v>
-      </c>
-      <c r="B646" s="1">
-        <v>340</v>
-      </c>
-      <c r="C646" s="1">
-        <v>-3030</v>
-      </c>
-      <c r="D646">
-        <v>0</v>
-      </c>
-      <c r="E646">
-        <v>0</v>
-      </c>
-      <c r="F646">
-        <v>0</v>
-      </c>
-      <c r="G646">
-        <v>1</v>
-      </c>
-      <c r="H646">
-        <v>1</v>
-      </c>
-      <c r="I646">
-        <v>1</v>
-      </c>
-      <c r="J646">
-        <v>10</v>
-      </c>
-      <c r="K646">
-        <v>10</v>
-      </c>
-      <c r="L646">
-        <v>10</v>
-      </c>
-      <c r="M646">
-        <v>-1</v>
-      </c>
-      <c r="N646">
-        <v>0</v>
-      </c>
-      <c r="O646">
-        <v>0</v>
-      </c>
-      <c r="P646">
-        <v>0</v>
-      </c>
-      <c r="Q646">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="647" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A647" s="1">
-        <v>2595.4</v>
-      </c>
-      <c r="B647" s="1">
-        <v>340</v>
-      </c>
-      <c r="C647" s="1">
-        <v>-3050</v>
-      </c>
-      <c r="D647">
-        <v>0</v>
-      </c>
-      <c r="E647">
-        <v>0</v>
-      </c>
-      <c r="F647">
-        <v>0</v>
-      </c>
-      <c r="G647">
-        <v>1</v>
-      </c>
-      <c r="H647">
-        <v>1</v>
-      </c>
-      <c r="I647">
-        <v>1</v>
-      </c>
-      <c r="J647">
-        <v>10</v>
-      </c>
-      <c r="K647">
-        <v>10</v>
-      </c>
-      <c r="L647">
-        <v>10</v>
-      </c>
-      <c r="M647">
-        <v>-1</v>
-      </c>
-      <c r="N647">
-        <v>0</v>
-      </c>
-      <c r="O647">
-        <v>0</v>
-      </c>
-      <c r="P647">
-        <v>0</v>
-      </c>
-      <c r="Q647">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="648" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A648" s="1">
-        <v>2610</v>
-      </c>
-      <c r="B648" s="1">
-        <v>340</v>
-      </c>
-      <c r="C648" s="1">
-        <v>-3064.6</v>
-      </c>
-      <c r="D648">
-        <v>0</v>
-      </c>
-      <c r="E648">
-        <v>0</v>
-      </c>
-      <c r="F648">
-        <v>0</v>
-      </c>
-      <c r="G648">
-        <v>1</v>
-      </c>
-      <c r="H648">
-        <v>1</v>
-      </c>
-      <c r="I648">
-        <v>1</v>
-      </c>
-      <c r="J648">
-        <v>10</v>
-      </c>
-      <c r="K648">
-        <v>10</v>
-      </c>
-      <c r="L648">
-        <v>10</v>
-      </c>
-      <c r="M648">
-        <v>-1</v>
-      </c>
-      <c r="N648">
-        <v>0</v>
-      </c>
-      <c r="O648">
-        <v>0</v>
-      </c>
-      <c r="P648">
-        <v>0</v>
-      </c>
-      <c r="Q648">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="649" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A649" s="1">
-        <v>2630</v>
-      </c>
-      <c r="B649" s="1">
-        <v>340</v>
-      </c>
-      <c r="C649" s="1">
-        <v>-3070</v>
-      </c>
-      <c r="D649">
-        <v>0</v>
-      </c>
-      <c r="E649">
-        <v>0</v>
-      </c>
-      <c r="F649">
-        <v>0</v>
-      </c>
-      <c r="G649">
-        <v>1</v>
-      </c>
-      <c r="H649">
-        <v>1</v>
-      </c>
-      <c r="I649">
-        <v>1</v>
-      </c>
-      <c r="J649">
-        <v>10</v>
-      </c>
-      <c r="K649">
-        <v>10</v>
-      </c>
-      <c r="L649">
-        <v>10</v>
-      </c>
-      <c r="M649">
-        <v>-1</v>
-      </c>
-      <c r="N649">
-        <v>0</v>
-      </c>
-      <c r="O649">
-        <v>0</v>
-      </c>
-      <c r="P649">
-        <v>0</v>
-      </c>
-      <c r="Q649">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="650" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A650" s="1">
-        <v>2650</v>
-      </c>
-      <c r="B650" s="1">
-        <v>340</v>
-      </c>
-      <c r="C650" s="1">
-        <v>-3064.6</v>
-      </c>
-      <c r="D650">
-        <v>0</v>
-      </c>
-      <c r="E650">
-        <v>0</v>
-      </c>
-      <c r="F650">
-        <v>0</v>
-      </c>
-      <c r="G650">
-        <v>1</v>
-      </c>
-      <c r="H650">
-        <v>1</v>
-      </c>
-      <c r="I650">
-        <v>1</v>
-      </c>
-      <c r="J650">
-        <v>10</v>
-      </c>
-      <c r="K650">
-        <v>10</v>
-      </c>
-      <c r="L650">
-        <v>10</v>
-      </c>
-      <c r="M650">
-        <v>-1</v>
-      </c>
-      <c r="N650">
-        <v>0</v>
-      </c>
-      <c r="O650">
-        <v>0</v>
-      </c>
-      <c r="P650">
-        <v>0</v>
-      </c>
-      <c r="Q650">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="651" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A651" s="1">
-        <v>2664.6</v>
-      </c>
-      <c r="B651" s="1">
-        <v>340</v>
-      </c>
-      <c r="C651" s="1">
-        <v>-3050</v>
-      </c>
-      <c r="D651">
-        <v>0</v>
-      </c>
-      <c r="E651">
-        <v>0</v>
-      </c>
-      <c r="F651">
-        <v>0</v>
-      </c>
-      <c r="G651">
-        <v>1</v>
-      </c>
-      <c r="H651">
-        <v>1</v>
-      </c>
-      <c r="I651">
-        <v>1</v>
-      </c>
-      <c r="J651">
-        <v>10</v>
-      </c>
-      <c r="K651">
-        <v>10</v>
-      </c>
-      <c r="L651">
-        <v>10</v>
-      </c>
-      <c r="M651">
-        <v>-1</v>
-      </c>
-      <c r="N651">
-        <v>0</v>
-      </c>
-      <c r="O651">
-        <v>0</v>
-      </c>
-      <c r="P651">
-        <v>0</v>
-      </c>
-      <c r="Q651">
         <v>0</v>
       </c>
     </row>

--- a/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
+++ b/Action/Data/CSV/Map1/Platform/PlatformData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Map1\Platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46598551-33D0-4CB4-A081-9722F8177001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{00683C4F-6F95-405A-991F-FDA4C24B904C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="2955" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformData" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -991,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q619"/>
+  <dimension ref="A1:Q621"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="17" width="5.625" customWidth="1"/>
@@ -35511,6 +35514,115 @@
         <v>0</v>
       </c>
     </row>
+    <row r="620" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A620" s="1">
+        <v>-40</v>
+      </c>
+      <c r="B620" s="1">
+        <v>20</v>
+      </c>
+      <c r="C620">
+        <v>-100</v>
+      </c>
+      <c r="D620">
+        <v>0</v>
+      </c>
+      <c r="E620">
+        <v>0</v>
+      </c>
+      <c r="F620">
+        <v>0</v>
+      </c>
+      <c r="G620">
+        <v>1</v>
+      </c>
+      <c r="H620">
+        <v>1</v>
+      </c>
+      <c r="I620">
+        <v>1</v>
+      </c>
+      <c r="J620">
+        <f t="shared" ref="J620:J621" si="235">G620*20</f>
+        <v>20</v>
+      </c>
+      <c r="K620">
+        <f t="shared" ref="K620:K621" si="236">H620*20</f>
+        <v>20</v>
+      </c>
+      <c r="L620">
+        <f t="shared" ref="L620:L621" si="237">I620*20</f>
+        <v>20</v>
+      </c>
+      <c r="M620">
+        <v>-1</v>
+      </c>
+      <c r="N620">
+        <v>0</v>
+      </c>
+      <c r="O620">
+        <v>0</v>
+      </c>
+      <c r="P620">
+        <v>0</v>
+      </c>
+      <c r="Q620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A621" s="1">
+        <v>40</v>
+      </c>
+      <c r="B621" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="C621">
+        <v>-100</v>
+      </c>
+      <c r="D621">
+        <v>0</v>
+      </c>
+      <c r="E621">
+        <v>0</v>
+      </c>
+      <c r="F621">
+        <v>0</v>
+      </c>
+      <c r="G621">
+        <v>1</v>
+      </c>
+      <c r="H621">
+        <v>1</v>
+      </c>
+      <c r="I621">
+        <v>1</v>
+      </c>
+      <c r="J621" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="K621" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="L621" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="M621">
+        <v>-1</v>
+      </c>
+      <c r="N621">
+        <v>0</v>
+      </c>
+      <c r="O621">
+        <v>0</v>
+      </c>
+      <c r="P621">
+        <v>0</v>
+      </c>
+      <c r="Q621">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
